--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,12 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
     <sheet name="枚举示例" sheetId="3" r:id="rId2"/>
     <sheet name="DogSkin" sheetId="2" r:id="rId3"/>
+    <sheet name="BlindBox" sheetId="4" r:id="rId4"/>
+    <sheet name="GameDevelopConfig" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="380">
   <si>
     <t>##var</t>
   </si>
@@ -49,6 +51,15 @@
     <t>SortOrder</t>
   </si>
   <si>
+    <t>BlindBoxWeight</t>
+  </si>
+  <si>
+    <t>isUnique</t>
+  </si>
+  <si>
+    <t>BlindBoxId</t>
+  </si>
+  <si>
     <t>*AssetPathList</t>
   </si>
   <si>
@@ -73,6 +84,9 @@
     <t>ERarity</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>list,string</t>
   </si>
   <si>
@@ -83,6 +97,12 @@
   </si>
   <si>
     <t>排序权重，数字越大约靠前</t>
+  </si>
+  <si>
+    <t>非唯一的物品可以重复获得</t>
+  </si>
+  <si>
+    <t>所属盲盒的id，相同id的物品在同一个组里进行随机</t>
   </si>
   <si>
     <t>由于部件拆的比较碎，因此需要文件夹路径如 `Assets\Eyewear\EyePatch.png`
@@ -113,6 +133,15 @@
     <t>排序权重</t>
   </si>
   <si>
+    <t>盲盒权重</t>
+  </si>
+  <si>
+    <t>是否唯一</t>
+  </si>
+  <si>
+    <t>随机组id</t>
+  </si>
+  <si>
     <t>对应素图片路径材列表</t>
   </si>
   <si>
@@ -143,12 +172,39 @@
     <t>Black</t>
   </si>
   <si>
+    <t>黑柴</t>
+  </si>
+  <si>
     <t>lucky-dog-rise\\Assets\Shiba\Black\</t>
   </si>
   <si>
     <t>lucky-dog-rise\\Assets\UI\ItemIcon\Shiba_Black.png</t>
   </si>
   <si>
+    <t>Cream</t>
+  </si>
+  <si>
+    <t>白柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Cream\</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_Cream.png</t>
+  </si>
+  <si>
+    <t>Sesame</t>
+  </si>
+  <si>
+    <t>胡麻柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Sesame\</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_Sesame.png</t>
+  </si>
+  <si>
     <t>Thin Red</t>
   </si>
   <si>
@@ -170,6 +226,63 @@
     <t>lucky-dog-rise\\Assets\UI\ItemIcon\Shiba_UnshavenRed.png</t>
   </si>
   <si>
+    <t>Thin Black</t>
+  </si>
+  <si>
+    <t>瘦黑柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Black\</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_ThinBlack.png</t>
+  </si>
+  <si>
+    <t>Unshaven Black</t>
+  </si>
+  <si>
+    <t>胡渣黑柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_UnshavenBlack.png</t>
+  </si>
+  <si>
+    <t>Thin Cream</t>
+  </si>
+  <si>
+    <t>瘦白柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_ThinCream.png</t>
+  </si>
+  <si>
+    <t>Unshaven Cream</t>
+  </si>
+  <si>
+    <t>胡渣白柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_UnshavenCream.png</t>
+  </si>
+  <si>
+    <t>Thin Sesame</t>
+  </si>
+  <si>
+    <t>瘦芝麻柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_ThinSesame.png</t>
+  </si>
+  <si>
+    <t>Unshaven Sesame</t>
+  </si>
+  <si>
+    <t>胡渣芝麻柴</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_UnshavenSesame.png</t>
+  </si>
+  <si>
     <t>Green Beret</t>
   </si>
   <si>
@@ -182,7 +295,88 @@
     <t>lucky-dog-rise\Assets\Headwear\Beret_Green.png</t>
   </si>
   <si>
-    <t>lucky-dog-rise\\Assets\UI\ItemIcon\Headwear_Beret_Green.png</t>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_Beret_Green.png</t>
+  </si>
+  <si>
+    <t>Red Beret</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Headwear\Beret_Red.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_Beret_Red.png</t>
+  </si>
+  <si>
+    <t>Gray Fedora Hat</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Headwear\FedoraHat_Gray.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_FedoraHat_Gray.png</t>
+  </si>
+  <si>
+    <t>Maroon Fedora Hat</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Headwear\FedoraHat_Maroon.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_FedoraHat_Maroon.png</t>
+  </si>
+  <si>
+    <t>Hole</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Headwear\Hole.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_Hole.png</t>
+  </si>
+  <si>
+    <t>Lucky</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Headwear\Lucky.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_Lucky.png</t>
+  </si>
+  <si>
+    <t>Black Magic Hat</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Headwear\MagicHat_Black.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_MagicHat_Black.png</t>
+  </si>
+  <si>
+    <t>White Magic Hat</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Headwear\MagicHat_White.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_MagicHat_White.png</t>
+  </si>
+  <si>
+    <t>Beige Sun Hat</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Headwear\SunHat_Beige.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_SunHat_Beige.png</t>
+  </si>
+  <si>
+    <t>Blue Sun Hat</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Headwear\SunHat_Blue.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_SunHat_Blue.png</t>
   </si>
   <si>
     <t>3D Glasses</t>
@@ -194,7 +388,526 @@
     <t>lucky-dog-rise\Assets\Eyewear\3DGlasses.png</t>
   </si>
   <si>
-    <t>lucky-dog-rise\\Assets\UI\ItemIcon\Eyewear_3DGlasses.png</t>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_3DGlasses.png</t>
+  </si>
+  <si>
+    <t>Eye Patch</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Eyewear\EyePatch.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_EyePatch.png</t>
+  </si>
+  <si>
+    <t>Black Monocle</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Eyewear\Monocle_black.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_Monocle_black.png</t>
+  </si>
+  <si>
+    <t>Golden Monocle</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Eyewear\Monocle_golden.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_Monocle_golden.png</t>
+  </si>
+  <si>
+    <t>Blade Sunglasses</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Eyewear\Sunglasses_Blade.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_Sunglasses_Blade.png</t>
+  </si>
+  <si>
+    <t>Male A</t>
+  </si>
+  <si>
+    <t>Hand</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Hand\MaleA.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Hand_MaleA.png</t>
+  </si>
+  <si>
+    <t>Male B</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Hand\MaleB.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Hand_MaleB.png</t>
+  </si>
+  <si>
+    <t>Male C</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Hand\MaleC.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Hand_MaleC.png</t>
+  </si>
+  <si>
+    <t>Male D</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Hand\MaleD.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Hand_MaleD.png</t>
+  </si>
+  <si>
+    <t>Baseball Jacket Black</t>
+  </si>
+  <si>
+    <t>Clothes</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Clothes\BaseballJacket_Black.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BaseballJacket_Black.png</t>
+  </si>
+  <si>
+    <t>Baseball Jacket Purple</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Clothes\BaseballJacket_Purple.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BaseballJacket_Purple.png</t>
+  </si>
+  <si>
+    <t>Black Business Suit</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Clothes\BlackBusinessSuit_Black.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BlackBusinessSuit_Black.png</t>
+  </si>
+  <si>
+    <t>Blue Shirt</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Clothes\BlueShirt_Cyan.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BlueShirt_Cyan.png</t>
+  </si>
+  <si>
+    <t>Blue Striped Shirt</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Clothes\BlueStripedShirt_RegattaStripe.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BlueStripedShirt_RegattaStripe.png</t>
+  </si>
+  <si>
+    <t>Cream Shirt</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Clothes\CreamShirt_Beige.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_CreamShirt_Beige.png</t>
+  </si>
+  <si>
+    <t>White Business Suit</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Clothes\WhiteBusinessSuit_LightGray.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_WhiteBusinessSuit_LightGray.png</t>
+  </si>
+  <si>
+    <t>White Shirt</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Clothes\WhiteShirt_White.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_WhiteShirt_White.png</t>
+  </si>
+  <si>
+    <t>Felt Emerald</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Table\FeltEmerald.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_FeltEmerald.png</t>
+  </si>
+  <si>
+    <t>Full Tilt Like</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Table\FullTiltLike.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_FullTiltLike.png</t>
+  </si>
+  <si>
+    <t>Hustler Like</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Table\HustlerLike.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_HustlerLike.png</t>
+  </si>
+  <si>
+    <t>Les Ambassadeurs Like</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Table\LesAmbassadeursLike.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_LesAmbassadeursLike.png</t>
+  </si>
+  <si>
+    <t>Maestral Like</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Table\MaestralLike.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_MaestralLike.png</t>
+  </si>
+  <si>
+    <t>Mezcal Like</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Table\MezcalLike.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_MezcalLike.png</t>
+  </si>
+  <si>
+    <t>Poker Go Like</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Table\PokerGoLike.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_PokerGoLike.png</t>
+  </si>
+  <si>
+    <t>Pure Indigo</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Table\PureIndigo.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_PureIndigo.png</t>
+  </si>
+  <si>
+    <t>Pure Purple</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Table\PurePurple.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_PurePurple.png</t>
+  </si>
+  <si>
+    <t>Pure Teal</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Table\PureTeal.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_PureTeal.png</t>
+  </si>
+  <si>
+    <t>The King of Hill Like</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Table\TheKingOfHillLike.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_TheKingOfHillLike.png</t>
+  </si>
+  <si>
+    <t>Blue A</t>
+  </si>
+  <si>
+    <t>Background</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\BlueA.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_BlueA.png</t>
+  </si>
+  <si>
+    <t>Brown A</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\BrownA.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_BrownA.png</t>
+  </si>
+  <si>
+    <t>Brown B</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\BrownB.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_BrownB.png</t>
+  </si>
+  <si>
+    <t>Gray A</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\GrayA.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_GrayA.png</t>
+  </si>
+  <si>
+    <t>Gray B</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\GrayB.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_GrayB.png</t>
+  </si>
+  <si>
+    <t>Green A</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\GreenA.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_GreenA.png</t>
+  </si>
+  <si>
+    <t>Green B</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\GreenB.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_GreenB.png</t>
+  </si>
+  <si>
+    <t>Highstakes Poker Like</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\HighstakesPokerLike.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_HighstakesPokerLike.png</t>
+  </si>
+  <si>
+    <t>Orange A</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\OrangeA.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_OrangeA.png</t>
+  </si>
+  <si>
+    <t>Part Poker Like</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\PartPokerLike.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_PartPokerLike.png</t>
+  </si>
+  <si>
+    <t>Pink A</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\PinkA.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_PinkA.png</t>
+  </si>
+  <si>
+    <t>Poker King Like</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\PokerKingLike.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_PokerKingLike.png</t>
+  </si>
+  <si>
+    <t>Purple A</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\PurpleA.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_PurpleA.png</t>
+  </si>
+  <si>
+    <t>Red A</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\RedA.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_RedA.png</t>
+  </si>
+  <si>
+    <t>Red B</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\RedB.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_RedB.png</t>
+  </si>
+  <si>
+    <t>Twitter Blue</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\TwitterBlue.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_TwitterBlue.png</t>
+  </si>
+  <si>
+    <t>World Poker Tour Like</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\WorldPokerTourtLike.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_WorldPokerTourtLike.png</t>
+  </si>
+  <si>
+    <t>Yellow A</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Background\YellowA.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_YellowA.png</t>
+  </si>
+  <si>
+    <t>A158UUA</t>
+  </si>
+  <si>
+    <t>Accessory</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Accessory\A158UUA.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_A158UUA.png</t>
+  </si>
+  <si>
+    <t>Anchor Tattoo</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Accessory\AnchorTattoo.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_AnchorTattoo.png</t>
+  </si>
+  <si>
+    <t>F91UU</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Accessory\F91UU.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_F91UU.png</t>
+  </si>
+  <si>
+    <t>Feng Shui Bracelet</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Accessory\FengShuiBracelet.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_FengShuiBracelet.png</t>
+  </si>
+  <si>
+    <t>Good Luck Bracelet</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Accessory\GoodLuckBracelet.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_GoodLuckBracelet.png</t>
+  </si>
+  <si>
+    <t>Hair</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Accessory\Hair.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_Hair.png</t>
+  </si>
+  <si>
+    <t>Relax Driver Black</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Accessory\RelaxDriver_Black.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_RelaxDriver_Black.png</t>
+  </si>
+  <si>
+    <t>Relax Driver Green</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Accessory\RelaxDriver_Green.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_RelaxDriver_Green.png</t>
+  </si>
+  <si>
+    <t>Text Wristband Green</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Accessory\TextWristband_Green.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_TextWristband_Green.png</t>
+  </si>
+  <si>
+    <t>Text Wristband Red</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Accessory\TextWristband_Red.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_TextWristband_Red.png</t>
+  </si>
+  <si>
+    <t>WSOP Gold Bracelet</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Accessory\WSOPGoldBracelet.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_WSOPGoldBracelet.png</t>
   </si>
   <si>
     <t>小狗本体</t>
@@ -215,9 +928,6 @@
     <t>Rare</t>
   </si>
   <si>
-    <t>Hand</t>
-  </si>
-  <si>
     <t>手臂层的装饰</t>
   </si>
   <si>
@@ -227,9 +937,6 @@
     <t>普通</t>
   </si>
   <si>
-    <t>Clothes</t>
-  </si>
-  <si>
     <t>玩家手臂衣服</t>
   </si>
   <si>
@@ -239,9 +946,6 @@
     <t>特殊1</t>
   </si>
   <si>
-    <t>Table</t>
-  </si>
-  <si>
     <t>桌布</t>
   </si>
   <si>
@@ -251,15 +955,9 @@
     <t>特殊2</t>
   </si>
   <si>
-    <t>Background</t>
-  </si>
-  <si>
     <t>背景</t>
   </si>
   <si>
-    <t>Accessory</t>
-  </si>
-  <si>
     <t>玩家手部装饰</t>
   </si>
   <si>
@@ -308,9 +1006,18 @@
     <t>图标名称</t>
   </si>
   <si>
+    <t>资源所在文件夹</t>
+  </si>
+  <si>
     <t>狗头</t>
   </si>
   <si>
+    <t>狗左爪</t>
+  </si>
+  <si>
+    <t>狗右爪</t>
+  </si>
+  <si>
     <t>高兴耳朵</t>
   </si>
   <si>
@@ -356,16 +1063,118 @@
     <t>Ears_Happy.png</t>
   </si>
   <si>
+    <t>Ears_Plane.png</t>
+  </si>
+  <si>
+    <t>Eyes_Bored.png</t>
+  </si>
+  <si>
+    <t>Eyes_Cute.png</t>
+  </si>
+  <si>
+    <t>Eyes_Happy.png</t>
+  </si>
+  <si>
+    <t>Eyes_Lucky.png</t>
+  </si>
+  <si>
+    <t>Eyes_Neutral.png</t>
+  </si>
+  <si>
     <t>Eyes_Wink.png</t>
   </si>
   <si>
-    <t>黑柴</t>
+    <t>Shiba_Black.png</t>
   </si>
   <si>
     <t>lucky-dog-rise\Assets\Shiba\Black</t>
   </si>
   <si>
+    <t>Shiba_Cream.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Cream</t>
+  </si>
+  <si>
+    <t>Shiba_Sesame.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Sesame</t>
+  </si>
+  <si>
+    <t>Shiba_ThinRed.png</t>
+  </si>
+  <si>
     <t>Head_Thin.png</t>
+  </si>
+  <si>
+    <t>Head_Unshaven.png</t>
+  </si>
+  <si>
+    <t>Shiba_ThinBlack.png</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenBlack.png</t>
+  </si>
+  <si>
+    <t>Shiba_ThinCream.png</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenCream.png</t>
+  </si>
+  <si>
+    <t>Shiba_ThinSesame.png</t>
+  </si>
+  <si>
+    <t>Shiba_UnshavenSesame.png</t>
+  </si>
+  <si>
+    <t>*PriceLadder</t>
+  </si>
+  <si>
+    <t>Cooldown</t>
+  </si>
+  <si>
+    <t>list,int</t>
+  </si>
+  <si>
+    <t>阶梯价格</t>
+  </si>
+  <si>
+    <t>多少秒之后重置阶梯价格</t>
+  </si>
+  <si>
+    <t>##column#var</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>GoldInheritanceRatio</t>
+  </si>
+  <si>
+    <t>金币继承比例</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>旅程失败时保留的金币比例</t>
+  </si>
+  <si>
+    <t>DrawCountPerTurn</t>
+  </si>
+  <si>
+    <t>每回合抽牌数</t>
+  </si>
+  <si>
+    <t>抽牌阶段从牌库抽取的张数</t>
   </si>
 </sst>
 </file>
@@ -378,10 +1187,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1C1E21"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -850,16 +1665,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -868,120 +1680,129 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -989,9 +1810,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1521,27 +2339,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="12.9166666666667" customWidth="1"/>
     <col min="4" max="4" width="13.25" customWidth="1"/>
-    <col min="8" max="8" width="44" customWidth="1"/>
-    <col min="9" max="9" width="55.9166666666667" customWidth="1"/>
-    <col min="10" max="10" width="15.4166666666667" customWidth="1"/>
+    <col min="8" max="8" width="11.0833333333333" customWidth="1"/>
+    <col min="10" max="10" width="9.91666666666667" customWidth="1"/>
+    <col min="11" max="11" width="44" customWidth="1"/>
+    <col min="12" max="12" width="55.9166666666667" customWidth="1"/>
+    <col min="13" max="13" width="15.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="3"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -1560,245 +2380,2724 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3"/>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
       <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" s="4" customFormat="1" ht="104.4" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" s="5" customFormat="1" ht="104.4" spans="1:13">
+      <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="G3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="I3" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="J3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G5">
         <v>200</v>
       </c>
-      <c r="H5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" t="s">
-        <v>34</v>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
       </c>
       <c r="J5">
         <v>1001</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <v>200</v>
       </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" t="s">
-        <v>37</v>
+      <c r="H6">
+        <v>200</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
       </c>
       <c r="J6">
+        <v>1001</v>
+      </c>
+      <c r="K6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6">
         <v>1002</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="7" spans="1:13">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>200</v>
+      </c>
+      <c r="H7">
+        <v>200</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1001</v>
+      </c>
+      <c r="K7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8">
+        <v>200</v>
+      </c>
+      <c r="H8">
+        <v>200</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1001</v>
+      </c>
+      <c r="K8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>100</v>
       </c>
-      <c r="H9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
       </c>
       <c r="J9">
+        <v>1001</v>
+      </c>
+      <c r="K9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9">
         <v>1005</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:13">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>100</v>
       </c>
-      <c r="H10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" t="s">
-        <v>44</v>
+      <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
       </c>
       <c r="J10">
+        <v>1001</v>
+      </c>
+      <c r="K10" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10">
         <v>1006</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="11" spans="1:13">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11">
+        <v>100</v>
+      </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1001</v>
+      </c>
+      <c r="K11" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12">
+        <v>100</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1001</v>
+      </c>
+      <c r="K12" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" t="s">
+        <v>69</v>
+      </c>
+      <c r="M12">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13">
+        <v>100</v>
+      </c>
+      <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1001</v>
+      </c>
+      <c r="K13" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13" t="s">
+        <v>72</v>
+      </c>
+      <c r="M13">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="B14">
+        <v>1010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14">
+        <v>100</v>
+      </c>
+      <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1001</v>
+      </c>
+      <c r="K14" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" t="s">
+        <v>75</v>
+      </c>
+      <c r="M14">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="B15">
+        <v>1011</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15">
+        <v>100</v>
+      </c>
+      <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1001</v>
+      </c>
+      <c r="K15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" t="s">
+        <v>78</v>
+      </c>
+      <c r="M15">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="B16">
-        <v>2001</v>
+        <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>46</v>
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G16">
         <v>100</v>
       </c>
-      <c r="H16" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9">
+      <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1001</v>
+      </c>
+      <c r="K16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" t="s">
+        <v>81</v>
+      </c>
+      <c r="M16">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="B18">
+        <v>2001</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18">
+        <v>300</v>
+      </c>
+      <c r="H18">
+        <v>300</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1001</v>
+      </c>
+      <c r="K18" t="s">
+        <v>85</v>
+      </c>
+      <c r="L18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="B19">
+        <v>2002</v>
+      </c>
+      <c r="C19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19">
+        <v>300</v>
+      </c>
+      <c r="H19">
+        <v>300</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1001</v>
+      </c>
+      <c r="K19" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="B20">
+        <v>2003</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20">
+        <v>300</v>
+      </c>
+      <c r="H20">
+        <v>300</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1001</v>
+      </c>
+      <c r="K20" t="s">
+        <v>91</v>
+      </c>
+      <c r="L20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="B21">
+        <v>2004</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21">
+        <v>300</v>
+      </c>
+      <c r="H21">
+        <v>300</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1001</v>
+      </c>
+      <c r="K21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="B22">
+        <v>2005</v>
+      </c>
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22">
+        <v>300</v>
+      </c>
+      <c r="H22">
+        <v>300</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1001</v>
+      </c>
+      <c r="K22" t="s">
+        <v>97</v>
+      </c>
+      <c r="L22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="B23">
+        <v>2006</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G23">
+        <v>300</v>
+      </c>
+      <c r="H23">
+        <v>300</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1001</v>
+      </c>
+      <c r="K23" t="s">
+        <v>100</v>
+      </c>
+      <c r="L23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="B24">
+        <v>2007</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24">
+        <v>300</v>
+      </c>
+      <c r="H24">
+        <v>300</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1001</v>
+      </c>
+      <c r="K24" t="s">
+        <v>103</v>
+      </c>
+      <c r="L24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="B25">
+        <v>2008</v>
+      </c>
+      <c r="C25" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25">
+        <v>300</v>
+      </c>
+      <c r="H25">
+        <v>300</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1001</v>
+      </c>
+      <c r="K25" t="s">
+        <v>106</v>
+      </c>
+      <c r="L25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="B26">
+        <v>2009</v>
+      </c>
+      <c r="C26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G26">
+        <v>300</v>
+      </c>
+      <c r="H26">
+        <v>300</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1001</v>
+      </c>
+      <c r="K26" t="s">
+        <v>109</v>
+      </c>
+      <c r="L26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="B27">
+        <v>2010</v>
+      </c>
+      <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27">
+        <v>300</v>
+      </c>
+      <c r="H27">
+        <v>300</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1001</v>
+      </c>
+      <c r="K27" t="s">
+        <v>112</v>
+      </c>
+      <c r="L27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="B28">
         <v>3001</v>
       </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19">
-        <v>100</v>
-      </c>
-      <c r="H19" t="s">
-        <v>52</v>
-      </c>
-      <c r="I19" t="s">
-        <v>53</v>
+      <c r="C28" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" t="s">
+        <v>84</v>
+      </c>
+      <c r="G28">
+        <v>300</v>
+      </c>
+      <c r="H28">
+        <v>300</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1001</v>
+      </c>
+      <c r="K28" t="s">
+        <v>116</v>
+      </c>
+      <c r="L28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="B29">
+        <v>3002</v>
+      </c>
+      <c r="C29" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29">
+        <v>300</v>
+      </c>
+      <c r="H29">
+        <v>300</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1001</v>
+      </c>
+      <c r="K29" t="s">
+        <v>119</v>
+      </c>
+      <c r="L29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="B30">
+        <v>3003</v>
+      </c>
+      <c r="C30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30">
+        <v>300</v>
+      </c>
+      <c r="H30">
+        <v>300</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1001</v>
+      </c>
+      <c r="K30" t="s">
+        <v>122</v>
+      </c>
+      <c r="L30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="B31">
+        <v>3004</v>
+      </c>
+      <c r="C31" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" t="s">
+        <v>84</v>
+      </c>
+      <c r="G31">
+        <v>300</v>
+      </c>
+      <c r="H31">
+        <v>300</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1001</v>
+      </c>
+      <c r="K31" t="s">
+        <v>125</v>
+      </c>
+      <c r="L31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="B32">
+        <v>3005</v>
+      </c>
+      <c r="C32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" t="s">
+        <v>84</v>
+      </c>
+      <c r="G32">
+        <v>300</v>
+      </c>
+      <c r="H32">
+        <v>300</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1001</v>
+      </c>
+      <c r="K32" t="s">
+        <v>128</v>
+      </c>
+      <c r="L32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12">
+      <c r="B33">
+        <v>4001</v>
+      </c>
+      <c r="C33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F33" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33">
+        <v>300</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>1001</v>
+      </c>
+      <c r="K33" t="s">
+        <v>132</v>
+      </c>
+      <c r="L33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34">
+        <v>4002</v>
+      </c>
+      <c r="C34" t="s">
+        <v>134</v>
+      </c>
+      <c r="E34" t="s">
+        <v>131</v>
+      </c>
+      <c r="F34" t="s">
+        <v>84</v>
+      </c>
+      <c r="G34">
+        <v>300</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>1001</v>
+      </c>
+      <c r="K34" t="s">
+        <v>135</v>
+      </c>
+      <c r="L34" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35">
+        <v>4003</v>
+      </c>
+      <c r="C35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F35" t="s">
+        <v>84</v>
+      </c>
+      <c r="G35">
+        <v>300</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>1001</v>
+      </c>
+      <c r="K35" t="s">
+        <v>138</v>
+      </c>
+      <c r="L35" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36">
+        <v>4004</v>
+      </c>
+      <c r="C36" t="s">
+        <v>140</v>
+      </c>
+      <c r="E36" t="s">
+        <v>131</v>
+      </c>
+      <c r="F36" t="s">
+        <v>84</v>
+      </c>
+      <c r="G36">
+        <v>300</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>1001</v>
+      </c>
+      <c r="K36" t="s">
+        <v>141</v>
+      </c>
+      <c r="L36" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="B37">
+        <v>5001</v>
+      </c>
+      <c r="C37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" t="s">
+        <v>144</v>
+      </c>
+      <c r="F37" t="s">
+        <v>84</v>
+      </c>
+      <c r="G37">
+        <v>300</v>
+      </c>
+      <c r="H37">
+        <v>300</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1001</v>
+      </c>
+      <c r="K37" t="s">
+        <v>145</v>
+      </c>
+      <c r="L37" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12">
+      <c r="B38">
+        <v>5002</v>
+      </c>
+      <c r="C38" t="s">
+        <v>147</v>
+      </c>
+      <c r="E38" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" t="s">
+        <v>84</v>
+      </c>
+      <c r="G38">
+        <v>300</v>
+      </c>
+      <c r="H38">
+        <v>300</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1001</v>
+      </c>
+      <c r="K38" t="s">
+        <v>148</v>
+      </c>
+      <c r="L38" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12">
+      <c r="B39">
+        <v>5003</v>
+      </c>
+      <c r="C39" t="s">
+        <v>150</v>
+      </c>
+      <c r="E39" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" t="s">
+        <v>84</v>
+      </c>
+      <c r="G39">
+        <v>300</v>
+      </c>
+      <c r="H39">
+        <v>300</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1001</v>
+      </c>
+      <c r="K39" t="s">
+        <v>151</v>
+      </c>
+      <c r="L39" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12">
+      <c r="B40">
+        <v>5004</v>
+      </c>
+      <c r="C40" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40" t="s">
+        <v>144</v>
+      </c>
+      <c r="F40" t="s">
+        <v>84</v>
+      </c>
+      <c r="G40">
+        <v>300</v>
+      </c>
+      <c r="H40">
+        <v>300</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1001</v>
+      </c>
+      <c r="K40" t="s">
+        <v>154</v>
+      </c>
+      <c r="L40" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12">
+      <c r="B41">
+        <v>5005</v>
+      </c>
+      <c r="C41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E41" t="s">
+        <v>144</v>
+      </c>
+      <c r="F41" t="s">
+        <v>84</v>
+      </c>
+      <c r="G41">
+        <v>300</v>
+      </c>
+      <c r="H41">
+        <v>300</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1001</v>
+      </c>
+      <c r="K41" t="s">
+        <v>157</v>
+      </c>
+      <c r="L41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12">
+      <c r="B42">
+        <v>5006</v>
+      </c>
+      <c r="C42" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42" t="s">
+        <v>144</v>
+      </c>
+      <c r="F42" t="s">
+        <v>84</v>
+      </c>
+      <c r="G42">
+        <v>300</v>
+      </c>
+      <c r="H42">
+        <v>300</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1001</v>
+      </c>
+      <c r="K42" t="s">
+        <v>160</v>
+      </c>
+      <c r="L42" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12">
+      <c r="B43">
+        <v>5007</v>
+      </c>
+      <c r="C43" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" t="s">
+        <v>144</v>
+      </c>
+      <c r="F43" t="s">
+        <v>84</v>
+      </c>
+      <c r="G43">
+        <v>300</v>
+      </c>
+      <c r="H43">
+        <v>300</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1001</v>
+      </c>
+      <c r="K43" t="s">
+        <v>163</v>
+      </c>
+      <c r="L43" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12">
+      <c r="B44">
+        <v>5008</v>
+      </c>
+      <c r="C44" t="s">
+        <v>165</v>
+      </c>
+      <c r="E44" t="s">
+        <v>144</v>
+      </c>
+      <c r="F44" t="s">
+        <v>84</v>
+      </c>
+      <c r="G44">
+        <v>300</v>
+      </c>
+      <c r="H44">
+        <v>300</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1001</v>
+      </c>
+      <c r="K44" t="s">
+        <v>166</v>
+      </c>
+      <c r="L44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12">
+      <c r="B45">
+        <v>6001</v>
+      </c>
+      <c r="C45" t="s">
+        <v>168</v>
+      </c>
+      <c r="E45" t="s">
+        <v>169</v>
+      </c>
+      <c r="F45" t="s">
+        <v>84</v>
+      </c>
+      <c r="G45">
+        <v>300</v>
+      </c>
+      <c r="H45">
+        <v>300</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1001</v>
+      </c>
+      <c r="K45" t="s">
+        <v>170</v>
+      </c>
+      <c r="L45" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12">
+      <c r="B46">
+        <v>6002</v>
+      </c>
+      <c r="C46" t="s">
+        <v>172</v>
+      </c>
+      <c r="E46" t="s">
+        <v>169</v>
+      </c>
+      <c r="F46" t="s">
+        <v>84</v>
+      </c>
+      <c r="G46">
+        <v>300</v>
+      </c>
+      <c r="H46">
+        <v>300</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1001</v>
+      </c>
+      <c r="K46" t="s">
+        <v>173</v>
+      </c>
+      <c r="L46" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12">
+      <c r="B47">
+        <v>6003</v>
+      </c>
+      <c r="C47" t="s">
+        <v>175</v>
+      </c>
+      <c r="E47" t="s">
+        <v>169</v>
+      </c>
+      <c r="F47" t="s">
+        <v>84</v>
+      </c>
+      <c r="G47">
+        <v>300</v>
+      </c>
+      <c r="H47">
+        <v>300</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1001</v>
+      </c>
+      <c r="K47" t="s">
+        <v>176</v>
+      </c>
+      <c r="L47" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12">
+      <c r="B48">
+        <v>6004</v>
+      </c>
+      <c r="C48" t="s">
+        <v>178</v>
+      </c>
+      <c r="E48" t="s">
+        <v>169</v>
+      </c>
+      <c r="F48" t="s">
+        <v>84</v>
+      </c>
+      <c r="G48">
+        <v>300</v>
+      </c>
+      <c r="H48">
+        <v>300</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1001</v>
+      </c>
+      <c r="K48" t="s">
+        <v>179</v>
+      </c>
+      <c r="L48" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12">
+      <c r="B49">
+        <v>6005</v>
+      </c>
+      <c r="C49" t="s">
+        <v>181</v>
+      </c>
+      <c r="E49" t="s">
+        <v>169</v>
+      </c>
+      <c r="F49" t="s">
+        <v>84</v>
+      </c>
+      <c r="G49">
+        <v>300</v>
+      </c>
+      <c r="H49">
+        <v>300</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1001</v>
+      </c>
+      <c r="K49" t="s">
+        <v>182</v>
+      </c>
+      <c r="L49" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12">
+      <c r="B50">
+        <v>6006</v>
+      </c>
+      <c r="C50" t="s">
+        <v>184</v>
+      </c>
+      <c r="E50" t="s">
+        <v>169</v>
+      </c>
+      <c r="F50" t="s">
+        <v>84</v>
+      </c>
+      <c r="G50">
+        <v>300</v>
+      </c>
+      <c r="H50">
+        <v>300</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1001</v>
+      </c>
+      <c r="K50" t="s">
+        <v>185</v>
+      </c>
+      <c r="L50" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12">
+      <c r="B51">
+        <v>6007</v>
+      </c>
+      <c r="C51" t="s">
+        <v>187</v>
+      </c>
+      <c r="E51" t="s">
+        <v>169</v>
+      </c>
+      <c r="F51" t="s">
+        <v>84</v>
+      </c>
+      <c r="G51">
+        <v>300</v>
+      </c>
+      <c r="H51">
+        <v>300</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1001</v>
+      </c>
+      <c r="K51" t="s">
+        <v>188</v>
+      </c>
+      <c r="L51" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12">
+      <c r="B52">
+        <v>6008</v>
+      </c>
+      <c r="C52" t="s">
+        <v>190</v>
+      </c>
+      <c r="E52" t="s">
+        <v>169</v>
+      </c>
+      <c r="F52" t="s">
+        <v>84</v>
+      </c>
+      <c r="G52">
+        <v>300</v>
+      </c>
+      <c r="H52">
+        <v>300</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1001</v>
+      </c>
+      <c r="K52" t="s">
+        <v>191</v>
+      </c>
+      <c r="L52" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12">
+      <c r="B53">
+        <v>6009</v>
+      </c>
+      <c r="C53" t="s">
+        <v>193</v>
+      </c>
+      <c r="E53" t="s">
+        <v>169</v>
+      </c>
+      <c r="F53" t="s">
+        <v>84</v>
+      </c>
+      <c r="G53">
+        <v>300</v>
+      </c>
+      <c r="H53">
+        <v>300</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1001</v>
+      </c>
+      <c r="K53" t="s">
+        <v>194</v>
+      </c>
+      <c r="L53" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12">
+      <c r="B54">
+        <v>6010</v>
+      </c>
+      <c r="C54" t="s">
+        <v>196</v>
+      </c>
+      <c r="E54" t="s">
+        <v>169</v>
+      </c>
+      <c r="F54" t="s">
+        <v>84</v>
+      </c>
+      <c r="G54">
+        <v>300</v>
+      </c>
+      <c r="H54">
+        <v>300</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1001</v>
+      </c>
+      <c r="K54" t="s">
+        <v>197</v>
+      </c>
+      <c r="L54" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12">
+      <c r="B55">
+        <v>6011</v>
+      </c>
+      <c r="C55" t="s">
+        <v>199</v>
+      </c>
+      <c r="E55" t="s">
+        <v>169</v>
+      </c>
+      <c r="F55" t="s">
+        <v>84</v>
+      </c>
+      <c r="G55">
+        <v>300</v>
+      </c>
+      <c r="H55">
+        <v>300</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1001</v>
+      </c>
+      <c r="K55" t="s">
+        <v>200</v>
+      </c>
+      <c r="L55" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12">
+      <c r="B56">
+        <v>7001</v>
+      </c>
+      <c r="C56" t="s">
+        <v>202</v>
+      </c>
+      <c r="E56" t="s">
+        <v>203</v>
+      </c>
+      <c r="F56" t="s">
+        <v>84</v>
+      </c>
+      <c r="G56">
+        <v>300</v>
+      </c>
+      <c r="H56">
+        <v>300</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1001</v>
+      </c>
+      <c r="K56" t="s">
+        <v>204</v>
+      </c>
+      <c r="L56" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12">
+      <c r="B57">
+        <v>7002</v>
+      </c>
+      <c r="C57" t="s">
+        <v>206</v>
+      </c>
+      <c r="E57" t="s">
+        <v>203</v>
+      </c>
+      <c r="F57" t="s">
+        <v>84</v>
+      </c>
+      <c r="G57">
+        <v>300</v>
+      </c>
+      <c r="H57">
+        <v>300</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1001</v>
+      </c>
+      <c r="K57" t="s">
+        <v>207</v>
+      </c>
+      <c r="L57" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12">
+      <c r="B58">
+        <v>7003</v>
+      </c>
+      <c r="C58" t="s">
+        <v>209</v>
+      </c>
+      <c r="E58" t="s">
+        <v>203</v>
+      </c>
+      <c r="F58" t="s">
+        <v>84</v>
+      </c>
+      <c r="G58">
+        <v>300</v>
+      </c>
+      <c r="H58">
+        <v>300</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1001</v>
+      </c>
+      <c r="K58" t="s">
+        <v>210</v>
+      </c>
+      <c r="L58" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12">
+      <c r="B59">
+        <v>7004</v>
+      </c>
+      <c r="C59" t="s">
+        <v>212</v>
+      </c>
+      <c r="E59" t="s">
+        <v>203</v>
+      </c>
+      <c r="F59" t="s">
+        <v>84</v>
+      </c>
+      <c r="G59">
+        <v>300</v>
+      </c>
+      <c r="H59">
+        <v>300</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1001</v>
+      </c>
+      <c r="K59" t="s">
+        <v>213</v>
+      </c>
+      <c r="L59" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12">
+      <c r="B60">
+        <v>7005</v>
+      </c>
+      <c r="C60" t="s">
+        <v>215</v>
+      </c>
+      <c r="E60" t="s">
+        <v>203</v>
+      </c>
+      <c r="F60" t="s">
+        <v>84</v>
+      </c>
+      <c r="G60">
+        <v>300</v>
+      </c>
+      <c r="H60">
+        <v>300</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1001</v>
+      </c>
+      <c r="K60" t="s">
+        <v>216</v>
+      </c>
+      <c r="L60" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12">
+      <c r="B61">
+        <v>7006</v>
+      </c>
+      <c r="C61" t="s">
+        <v>218</v>
+      </c>
+      <c r="E61" t="s">
+        <v>203</v>
+      </c>
+      <c r="F61" t="s">
+        <v>84</v>
+      </c>
+      <c r="G61">
+        <v>300</v>
+      </c>
+      <c r="H61">
+        <v>300</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1001</v>
+      </c>
+      <c r="K61" t="s">
+        <v>219</v>
+      </c>
+      <c r="L61" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12">
+      <c r="B62">
+        <v>7007</v>
+      </c>
+      <c r="C62" t="s">
+        <v>221</v>
+      </c>
+      <c r="E62" t="s">
+        <v>203</v>
+      </c>
+      <c r="F62" t="s">
+        <v>84</v>
+      </c>
+      <c r="G62">
+        <v>300</v>
+      </c>
+      <c r="H62">
+        <v>300</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1001</v>
+      </c>
+      <c r="K62" t="s">
+        <v>222</v>
+      </c>
+      <c r="L62" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12">
+      <c r="B63">
+        <v>7008</v>
+      </c>
+      <c r="C63" t="s">
+        <v>224</v>
+      </c>
+      <c r="E63" t="s">
+        <v>203</v>
+      </c>
+      <c r="F63" t="s">
+        <v>84</v>
+      </c>
+      <c r="G63">
+        <v>300</v>
+      </c>
+      <c r="H63">
+        <v>300</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1001</v>
+      </c>
+      <c r="K63" t="s">
+        <v>225</v>
+      </c>
+      <c r="L63" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="64" spans="2:12">
+      <c r="B64">
+        <v>7009</v>
+      </c>
+      <c r="C64" t="s">
+        <v>227</v>
+      </c>
+      <c r="E64" t="s">
+        <v>203</v>
+      </c>
+      <c r="F64" t="s">
+        <v>84</v>
+      </c>
+      <c r="G64">
+        <v>300</v>
+      </c>
+      <c r="H64">
+        <v>300</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1001</v>
+      </c>
+      <c r="K64" t="s">
+        <v>228</v>
+      </c>
+      <c r="L64" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12">
+      <c r="B65">
+        <v>7010</v>
+      </c>
+      <c r="C65" t="s">
+        <v>230</v>
+      </c>
+      <c r="E65" t="s">
+        <v>203</v>
+      </c>
+      <c r="F65" t="s">
+        <v>84</v>
+      </c>
+      <c r="G65">
+        <v>300</v>
+      </c>
+      <c r="H65">
+        <v>300</v>
+      </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1001</v>
+      </c>
+      <c r="K65" t="s">
+        <v>231</v>
+      </c>
+      <c r="L65" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12">
+      <c r="B66">
+        <v>7011</v>
+      </c>
+      <c r="C66" t="s">
+        <v>233</v>
+      </c>
+      <c r="E66" t="s">
+        <v>203</v>
+      </c>
+      <c r="F66" t="s">
+        <v>84</v>
+      </c>
+      <c r="G66">
+        <v>300</v>
+      </c>
+      <c r="H66">
+        <v>300</v>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1001</v>
+      </c>
+      <c r="K66" t="s">
+        <v>234</v>
+      </c>
+      <c r="L66" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12">
+      <c r="B67">
+        <v>7012</v>
+      </c>
+      <c r="C67" t="s">
+        <v>236</v>
+      </c>
+      <c r="E67" t="s">
+        <v>203</v>
+      </c>
+      <c r="F67" t="s">
+        <v>84</v>
+      </c>
+      <c r="G67">
+        <v>300</v>
+      </c>
+      <c r="H67">
+        <v>300</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1001</v>
+      </c>
+      <c r="K67" t="s">
+        <v>237</v>
+      </c>
+      <c r="L67" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12">
+      <c r="B68">
+        <v>7013</v>
+      </c>
+      <c r="C68" t="s">
+        <v>239</v>
+      </c>
+      <c r="E68" t="s">
+        <v>203</v>
+      </c>
+      <c r="F68" t="s">
+        <v>84</v>
+      </c>
+      <c r="G68">
+        <v>300</v>
+      </c>
+      <c r="H68">
+        <v>300</v>
+      </c>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1001</v>
+      </c>
+      <c r="K68" t="s">
+        <v>240</v>
+      </c>
+      <c r="L68" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12">
+      <c r="B69">
+        <v>7014</v>
+      </c>
+      <c r="C69" t="s">
+        <v>242</v>
+      </c>
+      <c r="E69" t="s">
+        <v>203</v>
+      </c>
+      <c r="F69" t="s">
+        <v>84</v>
+      </c>
+      <c r="G69">
+        <v>300</v>
+      </c>
+      <c r="H69">
+        <v>300</v>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1001</v>
+      </c>
+      <c r="K69" t="s">
+        <v>243</v>
+      </c>
+      <c r="L69" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12">
+      <c r="B70">
+        <v>7015</v>
+      </c>
+      <c r="C70" t="s">
+        <v>245</v>
+      </c>
+      <c r="E70" t="s">
+        <v>203</v>
+      </c>
+      <c r="F70" t="s">
+        <v>84</v>
+      </c>
+      <c r="G70">
+        <v>300</v>
+      </c>
+      <c r="H70">
+        <v>300</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1001</v>
+      </c>
+      <c r="K70" t="s">
+        <v>246</v>
+      </c>
+      <c r="L70" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12">
+      <c r="B71">
+        <v>7016</v>
+      </c>
+      <c r="C71" t="s">
+        <v>248</v>
+      </c>
+      <c r="E71" t="s">
+        <v>203</v>
+      </c>
+      <c r="F71" t="s">
+        <v>84</v>
+      </c>
+      <c r="G71">
+        <v>300</v>
+      </c>
+      <c r="H71">
+        <v>300</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1001</v>
+      </c>
+      <c r="K71" t="s">
+        <v>249</v>
+      </c>
+      <c r="L71" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12">
+      <c r="B72">
+        <v>7017</v>
+      </c>
+      <c r="C72" t="s">
+        <v>251</v>
+      </c>
+      <c r="E72" t="s">
+        <v>203</v>
+      </c>
+      <c r="F72" t="s">
+        <v>84</v>
+      </c>
+      <c r="G72">
+        <v>300</v>
+      </c>
+      <c r="H72">
+        <v>300</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1001</v>
+      </c>
+      <c r="K72" t="s">
+        <v>252</v>
+      </c>
+      <c r="L72" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12">
+      <c r="B73">
+        <v>7018</v>
+      </c>
+      <c r="C73" t="s">
+        <v>254</v>
+      </c>
+      <c r="E73" t="s">
+        <v>203</v>
+      </c>
+      <c r="F73" t="s">
+        <v>84</v>
+      </c>
+      <c r="G73">
+        <v>300</v>
+      </c>
+      <c r="H73">
+        <v>300</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1001</v>
+      </c>
+      <c r="K73" t="s">
+        <v>255</v>
+      </c>
+      <c r="L73" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12">
+      <c r="B74">
+        <v>8001</v>
+      </c>
+      <c r="C74" t="s">
+        <v>257</v>
+      </c>
+      <c r="E74" t="s">
+        <v>258</v>
+      </c>
+      <c r="F74" t="s">
+        <v>84</v>
+      </c>
+      <c r="G74">
+        <v>300</v>
+      </c>
+      <c r="H74">
+        <v>300</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1001</v>
+      </c>
+      <c r="K74" t="s">
+        <v>259</v>
+      </c>
+      <c r="L74" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12">
+      <c r="B75">
+        <v>8002</v>
+      </c>
+      <c r="C75" t="s">
+        <v>261</v>
+      </c>
+      <c r="E75" t="s">
+        <v>258</v>
+      </c>
+      <c r="F75" t="s">
+        <v>84</v>
+      </c>
+      <c r="G75">
+        <v>300</v>
+      </c>
+      <c r="H75">
+        <v>300</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1001</v>
+      </c>
+      <c r="K75" t="s">
+        <v>262</v>
+      </c>
+      <c r="L75" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12">
+      <c r="B76">
+        <v>8003</v>
+      </c>
+      <c r="C76" t="s">
+        <v>264</v>
+      </c>
+      <c r="E76" t="s">
+        <v>258</v>
+      </c>
+      <c r="F76" t="s">
+        <v>84</v>
+      </c>
+      <c r="G76">
+        <v>300</v>
+      </c>
+      <c r="H76">
+        <v>300</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1001</v>
+      </c>
+      <c r="K76" t="s">
+        <v>265</v>
+      </c>
+      <c r="L76" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12">
+      <c r="B77">
+        <v>8004</v>
+      </c>
+      <c r="C77" t="s">
+        <v>267</v>
+      </c>
+      <c r="E77" t="s">
+        <v>258</v>
+      </c>
+      <c r="F77" t="s">
+        <v>84</v>
+      </c>
+      <c r="G77">
+        <v>300</v>
+      </c>
+      <c r="H77">
+        <v>300</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1001</v>
+      </c>
+      <c r="K77" t="s">
+        <v>268</v>
+      </c>
+      <c r="L77" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12">
+      <c r="B78">
+        <v>8005</v>
+      </c>
+      <c r="C78" t="s">
+        <v>270</v>
+      </c>
+      <c r="E78" t="s">
+        <v>258</v>
+      </c>
+      <c r="F78" t="s">
+        <v>84</v>
+      </c>
+      <c r="G78">
+        <v>300</v>
+      </c>
+      <c r="H78">
+        <v>300</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1001</v>
+      </c>
+      <c r="K78" t="s">
+        <v>271</v>
+      </c>
+      <c r="L78" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12">
+      <c r="B79">
+        <v>8006</v>
+      </c>
+      <c r="C79" t="s">
+        <v>273</v>
+      </c>
+      <c r="E79" t="s">
+        <v>258</v>
+      </c>
+      <c r="F79" t="s">
+        <v>84</v>
+      </c>
+      <c r="G79">
+        <v>300</v>
+      </c>
+      <c r="H79">
+        <v>300</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1001</v>
+      </c>
+      <c r="K79" t="s">
+        <v>274</v>
+      </c>
+      <c r="L79" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="80" spans="2:12">
+      <c r="B80">
+        <v>8007</v>
+      </c>
+      <c r="C80" t="s">
+        <v>276</v>
+      </c>
+      <c r="E80" t="s">
+        <v>258</v>
+      </c>
+      <c r="F80" t="s">
+        <v>84</v>
+      </c>
+      <c r="G80">
+        <v>300</v>
+      </c>
+      <c r="H80">
+        <v>300</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1001</v>
+      </c>
+      <c r="K80" t="s">
+        <v>277</v>
+      </c>
+      <c r="L80" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12">
+      <c r="B81">
+        <v>8008</v>
+      </c>
+      <c r="C81" t="s">
+        <v>279</v>
+      </c>
+      <c r="E81" t="s">
+        <v>258</v>
+      </c>
+      <c r="F81" t="s">
+        <v>84</v>
+      </c>
+      <c r="G81">
+        <v>300</v>
+      </c>
+      <c r="H81">
+        <v>300</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1001</v>
+      </c>
+      <c r="K81" t="s">
+        <v>280</v>
+      </c>
+      <c r="L81" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12">
+      <c r="B82">
+        <v>8009</v>
+      </c>
+      <c r="C82" t="s">
+        <v>282</v>
+      </c>
+      <c r="E82" t="s">
+        <v>258</v>
+      </c>
+      <c r="F82" t="s">
+        <v>84</v>
+      </c>
+      <c r="G82">
+        <v>300</v>
+      </c>
+      <c r="H82">
+        <v>300</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1001</v>
+      </c>
+      <c r="K82" t="s">
+        <v>283</v>
+      </c>
+      <c r="L82" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12">
+      <c r="B83">
+        <v>8010</v>
+      </c>
+      <c r="C83" t="s">
+        <v>285</v>
+      </c>
+      <c r="E83" t="s">
+        <v>258</v>
+      </c>
+      <c r="F83" t="s">
+        <v>84</v>
+      </c>
+      <c r="G83">
+        <v>300</v>
+      </c>
+      <c r="H83">
+        <v>300</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1001</v>
+      </c>
+      <c r="K83" t="s">
+        <v>286</v>
+      </c>
+      <c r="L83" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="84" spans="2:12">
+      <c r="B84">
+        <v>8011</v>
+      </c>
+      <c r="C84" t="s">
+        <v>288</v>
+      </c>
+      <c r="E84" t="s">
+        <v>258</v>
+      </c>
+      <c r="F84" t="s">
+        <v>84</v>
+      </c>
+      <c r="G84">
+        <v>300</v>
+      </c>
+      <c r="H84">
+        <v>300</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1001</v>
+      </c>
+      <c r="K84" t="s">
+        <v>289</v>
+      </c>
+      <c r="L84" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -1817,118 +5116,118 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
-      <c r="B2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="G2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="3"/>
+      <c r="C2" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="G3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="3"/>
+      <c r="B3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="2"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="G4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="3"/>
+      <c r="B4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="2"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="G5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" s="3"/>
+      <c r="B5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="G6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I6" s="3"/>
+      <c r="B6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="G6" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I6" s="2"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="G7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I7" s="3"/>
+      <c r="B7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="3"/>
+      <c r="B8" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="3"/>
+      <c r="B9" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1939,171 +5238,181 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
-    <col min="2" max="2" width="10.8333333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.1666666666667" customWidth="1"/>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.25" customWidth="1"/>
+    <col min="3" max="3" width="7.91666666666667" customWidth="1"/>
     <col min="4" max="4" width="21.9166666666667" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="5" max="5" width="30.1666666666667" customWidth="1"/>
     <col min="6" max="6" width="16.5833333333333" customWidth="1"/>
-    <col min="7" max="7" width="20.4166666666667" customWidth="1"/>
+    <col min="7" max="7" width="18.5" customWidth="1"/>
     <col min="8" max="8" width="20.8333333333333" customWidth="1"/>
-    <col min="9" max="9" width="17.4166666666667" customWidth="1"/>
-    <col min="10" max="10" width="13.75" customWidth="1"/>
-    <col min="11" max="11" width="10.4166666666667" customWidth="1"/>
-    <col min="12" max="12" width="9.08333333333333" customWidth="1"/>
-    <col min="13" max="13" width="10.9166666666667" customWidth="1"/>
-    <col min="14" max="14" width="10.0833333333333" customWidth="1"/>
-    <col min="15" max="15" width="11.5" customWidth="1"/>
-    <col min="16" max="16" width="42.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="14.5" customWidth="1"/>
+    <col min="10" max="10" width="13.4166666666667" customWidth="1"/>
+    <col min="11" max="11" width="14.3333333333333" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="14.8333333333333" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="15.4166666666667" customWidth="1"/>
+    <col min="16" max="16" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>78</v>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>310</v>
       </c>
       <c r="G1" t="s">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="H1" t="s">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="I1" t="s">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="J1" t="s">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="K1" t="s">
-        <v>83</v>
+        <v>315</v>
       </c>
       <c r="L1" t="s">
-        <v>84</v>
+        <v>316</v>
       </c>
       <c r="M1" t="s">
-        <v>85</v>
+        <v>317</v>
       </c>
       <c r="N1" t="s">
-        <v>86</v>
+        <v>318</v>
       </c>
       <c r="O1" t="s">
-        <v>87</v>
+        <v>319</v>
       </c>
       <c r="P1" t="s">
-        <v>88</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>11</v>
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
+      <c r="A4" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>321</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>322</v>
+      </c>
+      <c r="E4" t="s">
+        <v>323</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>324</v>
+      </c>
+      <c r="G4" t="s">
+        <v>325</v>
+      </c>
+      <c r="H4" t="s">
+        <v>326</v>
       </c>
       <c r="I4" t="s">
-        <v>92</v>
+        <v>327</v>
       </c>
       <c r="J4" t="s">
-        <v>93</v>
+        <v>328</v>
       </c>
       <c r="K4" t="s">
-        <v>94</v>
+        <v>329</v>
       </c>
       <c r="L4" t="s">
-        <v>95</v>
+        <v>330</v>
       </c>
       <c r="M4" t="s">
-        <v>96</v>
+        <v>331</v>
       </c>
       <c r="N4" t="s">
-        <v>97</v>
+        <v>332</v>
       </c>
       <c r="O4" t="s">
-        <v>98</v>
+        <v>333</v>
       </c>
       <c r="P4" t="s">
-        <v>99</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2111,28 +5420,46 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>335</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>336</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>337</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>338</v>
       </c>
       <c r="G5" t="s">
-        <v>104</v>
+        <v>339</v>
       </c>
       <c r="H5" t="s">
-        <v>105</v>
+        <v>340</v>
       </c>
       <c r="I5" t="s">
-        <v>106</v>
+        <v>341</v>
+      </c>
+      <c r="J5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K5" t="s">
+        <v>343</v>
+      </c>
+      <c r="L5" t="s">
+        <v>344</v>
+      </c>
+      <c r="M5" t="s">
+        <v>345</v>
+      </c>
+      <c r="N5" t="s">
+        <v>346</v>
+      </c>
+      <c r="O5" t="s">
+        <v>347</v>
       </c>
       <c r="P5" t="s">
-        <v>107</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2140,13 +5467,140 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>349</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>350</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>338</v>
+      </c>
+      <c r="G6" t="s">
+        <v>339</v>
+      </c>
+      <c r="H6" t="s">
+        <v>340</v>
+      </c>
+      <c r="I6" t="s">
+        <v>341</v>
+      </c>
+      <c r="J6" t="s">
+        <v>342</v>
+      </c>
+      <c r="K6" t="s">
+        <v>343</v>
+      </c>
+      <c r="L6" t="s">
+        <v>344</v>
+      </c>
+      <c r="M6" t="s">
+        <v>345</v>
+      </c>
+      <c r="N6" t="s">
+        <v>346</v>
+      </c>
+      <c r="O6" t="s">
+        <v>347</v>
+      </c>
+      <c r="P6" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>351</v>
+      </c>
+      <c r="E7" t="s">
+        <v>352</v>
+      </c>
+      <c r="F7" t="s">
+        <v>338</v>
+      </c>
+      <c r="G7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H7" t="s">
+        <v>340</v>
+      </c>
+      <c r="I7" t="s">
+        <v>341</v>
+      </c>
+      <c r="J7" t="s">
+        <v>342</v>
+      </c>
+      <c r="K7" t="s">
+        <v>343</v>
+      </c>
+      <c r="L7" t="s">
+        <v>344</v>
+      </c>
+      <c r="M7" t="s">
+        <v>345</v>
+      </c>
+      <c r="N7" t="s">
+        <v>346</v>
+      </c>
+      <c r="O7" t="s">
+        <v>347</v>
+      </c>
+      <c r="P7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" t="s">
+        <v>353</v>
+      </c>
+      <c r="E8" t="s">
+        <v>354</v>
+      </c>
+      <c r="F8" t="s">
+        <v>338</v>
+      </c>
+      <c r="G8" t="s">
+        <v>339</v>
+      </c>
+      <c r="H8" t="s">
+        <v>340</v>
+      </c>
+      <c r="I8" t="s">
+        <v>341</v>
+      </c>
+      <c r="J8" t="s">
+        <v>342</v>
+      </c>
+      <c r="K8" t="s">
+        <v>343</v>
+      </c>
+      <c r="L8" t="s">
+        <v>344</v>
+      </c>
+      <c r="M8" t="s">
+        <v>345</v>
+      </c>
+      <c r="N8" t="s">
+        <v>346</v>
+      </c>
+      <c r="O8" t="s">
+        <v>347</v>
+      </c>
+      <c r="P8" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2154,14 +5608,650 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>355</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>337</v>
       </c>
       <c r="F9" t="s">
-        <v>110</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="G9" t="s">
+        <v>339</v>
+      </c>
+      <c r="H9" t="s">
+        <v>340</v>
+      </c>
+      <c r="I9" t="s">
+        <v>341</v>
+      </c>
+      <c r="J9" t="s">
+        <v>342</v>
+      </c>
+      <c r="K9" t="s">
+        <v>343</v>
+      </c>
+      <c r="L9" t="s">
+        <v>344</v>
+      </c>
+      <c r="M9" t="s">
+        <v>345</v>
+      </c>
+      <c r="N9" t="s">
+        <v>346</v>
+      </c>
+      <c r="O9" t="s">
+        <v>347</v>
+      </c>
+      <c r="P9" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>336</v>
+      </c>
+      <c r="E10" t="s">
+        <v>337</v>
+      </c>
+      <c r="F10" t="s">
+        <v>357</v>
+      </c>
+      <c r="G10" t="s">
+        <v>339</v>
+      </c>
+      <c r="H10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I10" t="s">
+        <v>341</v>
+      </c>
+      <c r="J10" t="s">
+        <v>342</v>
+      </c>
+      <c r="K10" t="s">
+        <v>343</v>
+      </c>
+      <c r="L10" t="s">
+        <v>344</v>
+      </c>
+      <c r="M10" t="s">
+        <v>345</v>
+      </c>
+      <c r="N10" t="s">
+        <v>346</v>
+      </c>
+      <c r="O10" t="s">
+        <v>347</v>
+      </c>
+      <c r="P10" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>358</v>
+      </c>
+      <c r="E11" t="s">
+        <v>350</v>
+      </c>
+      <c r="F11" t="s">
+        <v>356</v>
+      </c>
+      <c r="G11" t="s">
+        <v>339</v>
+      </c>
+      <c r="H11" t="s">
+        <v>340</v>
+      </c>
+      <c r="I11" t="s">
+        <v>341</v>
+      </c>
+      <c r="J11" t="s">
+        <v>342</v>
+      </c>
+      <c r="K11" t="s">
+        <v>343</v>
+      </c>
+      <c r="L11" t="s">
+        <v>344</v>
+      </c>
+      <c r="M11" t="s">
+        <v>345</v>
+      </c>
+      <c r="N11" t="s">
+        <v>346</v>
+      </c>
+      <c r="O11" t="s">
+        <v>347</v>
+      </c>
+      <c r="P11" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>359</v>
+      </c>
+      <c r="E12" t="s">
+        <v>350</v>
+      </c>
+      <c r="F12" t="s">
+        <v>357</v>
+      </c>
+      <c r="G12" t="s">
+        <v>339</v>
+      </c>
+      <c r="H12" t="s">
+        <v>340</v>
+      </c>
+      <c r="I12" t="s">
+        <v>341</v>
+      </c>
+      <c r="J12" t="s">
+        <v>342</v>
+      </c>
+      <c r="K12" t="s">
+        <v>343</v>
+      </c>
+      <c r="L12" t="s">
+        <v>344</v>
+      </c>
+      <c r="M12" t="s">
+        <v>345</v>
+      </c>
+      <c r="N12" t="s">
+        <v>346</v>
+      </c>
+      <c r="O12" t="s">
+        <v>347</v>
+      </c>
+      <c r="P12" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E13" t="s">
+        <v>352</v>
+      </c>
+      <c r="F13" t="s">
+        <v>356</v>
+      </c>
+      <c r="G13" t="s">
+        <v>339</v>
+      </c>
+      <c r="H13" t="s">
+        <v>340</v>
+      </c>
+      <c r="I13" t="s">
+        <v>341</v>
+      </c>
+      <c r="J13" t="s">
+        <v>342</v>
+      </c>
+      <c r="K13" t="s">
+        <v>343</v>
+      </c>
+      <c r="L13" t="s">
+        <v>344</v>
+      </c>
+      <c r="M13" t="s">
+        <v>345</v>
+      </c>
+      <c r="N13" t="s">
+        <v>346</v>
+      </c>
+      <c r="O13" t="s">
+        <v>347</v>
+      </c>
+      <c r="P13" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="B14">
+        <v>1010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>361</v>
+      </c>
+      <c r="E14" t="s">
+        <v>352</v>
+      </c>
+      <c r="F14" t="s">
+        <v>357</v>
+      </c>
+      <c r="G14" t="s">
+        <v>339</v>
+      </c>
+      <c r="H14" t="s">
+        <v>340</v>
+      </c>
+      <c r="I14" t="s">
+        <v>341</v>
+      </c>
+      <c r="J14" t="s">
+        <v>342</v>
+      </c>
+      <c r="K14" t="s">
+        <v>343</v>
+      </c>
+      <c r="L14" t="s">
+        <v>344</v>
+      </c>
+      <c r="M14" t="s">
+        <v>345</v>
+      </c>
+      <c r="N14" t="s">
+        <v>346</v>
+      </c>
+      <c r="O14" t="s">
+        <v>347</v>
+      </c>
+      <c r="P14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="B15">
+        <v>1011</v>
+      </c>
+      <c r="C15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" t="s">
+        <v>362</v>
+      </c>
+      <c r="E15" t="s">
+        <v>354</v>
+      </c>
+      <c r="F15" t="s">
+        <v>356</v>
+      </c>
+      <c r="G15" t="s">
+        <v>339</v>
+      </c>
+      <c r="H15" t="s">
+        <v>340</v>
+      </c>
+      <c r="I15" t="s">
+        <v>341</v>
+      </c>
+      <c r="J15" t="s">
+        <v>342</v>
+      </c>
+      <c r="K15" t="s">
+        <v>343</v>
+      </c>
+      <c r="L15" t="s">
+        <v>344</v>
+      </c>
+      <c r="M15" t="s">
+        <v>345</v>
+      </c>
+      <c r="N15" t="s">
+        <v>346</v>
+      </c>
+      <c r="O15" t="s">
+        <v>347</v>
+      </c>
+      <c r="P15" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="B16">
+        <v>1012</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>363</v>
+      </c>
+      <c r="E16" t="s">
+        <v>354</v>
+      </c>
+      <c r="F16" t="s">
+        <v>357</v>
+      </c>
+      <c r="G16" t="s">
+        <v>339</v>
+      </c>
+      <c r="H16" t="s">
+        <v>340</v>
+      </c>
+      <c r="I16" t="s">
+        <v>341</v>
+      </c>
+      <c r="J16" t="s">
+        <v>342</v>
+      </c>
+      <c r="K16" t="s">
+        <v>343</v>
+      </c>
+      <c r="L16" t="s">
+        <v>344</v>
+      </c>
+      <c r="M16" t="s">
+        <v>345</v>
+      </c>
+      <c r="N16" t="s">
+        <v>346</v>
+      </c>
+      <c r="O16" t="s">
+        <v>347</v>
+      </c>
+      <c r="P16" t="s">
+        <v>348</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="20.5833333333333" customWidth="1"/>
+    <col min="5" max="5" width="40.3333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D3" t="s">
+        <v>368</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4">
+        <v>1001</v>
+      </c>
+      <c r="C4">
+        <v>8000</v>
+      </c>
+      <c r="D4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="C5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="C6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="C8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="C9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="C10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="C11">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="C12">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="C13">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="C14">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="C15">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="C16">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17">
+        <v>200000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="381">
   <si>
     <t>##var</t>
   </si>
@@ -1045,67 +1045,70 @@
     <t>赤柴原色</t>
   </si>
   <si>
+    <t>Shiba_Red.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Red</t>
+  </si>
+  <si>
+    <t>Head_Chubby.png</t>
+  </si>
+  <si>
+    <t>Claw_Lucky_Left.tres</t>
+  </si>
+  <si>
+    <t>Claw_Lucky_Right.tres</t>
+  </si>
+  <si>
+    <t>Ears_Happy.png</t>
+  </si>
+  <si>
+    <t>Ears_Plane.png</t>
+  </si>
+  <si>
+    <t>Eyes_Bored.png</t>
+  </si>
+  <si>
+    <t>Eyes_Cute.png</t>
+  </si>
+  <si>
+    <t>Eyes_Happy.png</t>
+  </si>
+  <si>
+    <t>Eyes_Lucky.png</t>
+  </si>
+  <si>
+    <t>Eyes_Neutral.png</t>
+  </si>
+  <si>
+    <t>Eyes_Wink.png</t>
+  </si>
+  <si>
+    <t>Shiba_Black.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Black</t>
+  </si>
+  <si>
+    <t>Shiba_Cream.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Cream</t>
+  </si>
+  <si>
+    <t>Shiba_Sesame.png</t>
+  </si>
+  <si>
+    <t>lucky-dog-rise\Assets\Shiba\Sesame</t>
+  </si>
+  <si>
+    <t>Shiba_ThinRed.png</t>
+  </si>
+  <si>
+    <t>Head_Thin.png</t>
+  </si>
+  <si>
     <t>Shiba_UnshavenRed.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\Shiba\Red</t>
-  </si>
-  <si>
-    <t>Head_Chubby.png</t>
-  </si>
-  <si>
-    <t>Claw_Lucky_Left.tres</t>
-  </si>
-  <si>
-    <t>Claw_Lucky_Right.tres</t>
-  </si>
-  <si>
-    <t>Ears_Happy.png</t>
-  </si>
-  <si>
-    <t>Ears_Plane.png</t>
-  </si>
-  <si>
-    <t>Eyes_Bored.png</t>
-  </si>
-  <si>
-    <t>Eyes_Cute.png</t>
-  </si>
-  <si>
-    <t>Eyes_Happy.png</t>
-  </si>
-  <si>
-    <t>Eyes_Lucky.png</t>
-  </si>
-  <si>
-    <t>Eyes_Neutral.png</t>
-  </si>
-  <si>
-    <t>Eyes_Wink.png</t>
-  </si>
-  <si>
-    <t>Shiba_Black.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\Shiba\Black</t>
-  </si>
-  <si>
-    <t>Shiba_Cream.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\Shiba\Cream</t>
-  </si>
-  <si>
-    <t>Shiba_Sesame.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\Shiba\Sesame</t>
-  </si>
-  <si>
-    <t>Shiba_ThinRed.png</t>
-  </si>
-  <si>
-    <t>Head_Thin.png</t>
   </si>
   <si>
     <t>Head_Unshaven.png</t>
@@ -5658,13 +5661,13 @@
         <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="E10" t="s">
         <v>337</v>
       </c>
       <c r="F10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G10" t="s">
         <v>339</v>
@@ -5705,7 +5708,7 @@
         <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E11" t="s">
         <v>350</v>
@@ -5752,13 +5755,13 @@
         <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E12" t="s">
         <v>350</v>
       </c>
       <c r="F12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G12" t="s">
         <v>339</v>
@@ -5799,7 +5802,7 @@
         <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E13" t="s">
         <v>352</v>
@@ -5846,13 +5849,13 @@
         <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E14" t="s">
         <v>352</v>
       </c>
       <c r="F14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G14" t="s">
         <v>339</v>
@@ -5893,7 +5896,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E15" t="s">
         <v>354</v>
@@ -5940,13 +5943,13 @@
         <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E16" t="s">
         <v>354</v>
       </c>
       <c r="F16" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G16" t="s">
         <v>339</v>
@@ -6004,10 +6007,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
@@ -6021,7 +6024,7 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -6038,10 +6041,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>36</v>
@@ -6137,7 +6140,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>19</v>
@@ -6153,39 +6156,39 @@
     <row r="2" spans="1:5">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D3" s="3">
         <v>0.5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
@@ -6194,7 +6197,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6207,7 +6210,6 @@
     <row r="6" spans="1:5">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
-      <c r="C6"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
@@ -6221,7 +6223,6 @@
     <row r="8" spans="1:5">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
-      <c r="C8"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
@@ -6234,8 +6235,6 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3"/>
-      <c r="B10"/>
-      <c r="C10"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="387">
   <si>
     <t>##var</t>
   </si>
@@ -964,6 +964,12 @@
     <t>IconName</t>
   </si>
   <si>
+    <t>DefaultEars</t>
+  </si>
+  <si>
+    <t>DefaultEyes</t>
+  </si>
+  <si>
     <t>FolderPath</t>
   </si>
   <si>
@@ -1000,12 +1006,21 @@
     <t>Eyes_Wink</t>
   </si>
   <si>
+    <t>只影响图标和伪装模式，不影响打牌模式</t>
+  </si>
+  <si>
     <t>备注名</t>
   </si>
   <si>
     <t>图标名称</t>
   </si>
   <si>
+    <t>默认耳朵</t>
+  </si>
+  <si>
+    <t>默认眼神</t>
+  </si>
+  <si>
     <t>资源所在文件夹</t>
   </si>
   <si>
@@ -1048,6 +1063,12 @@
     <t>Shiba_Red.png</t>
   </si>
   <si>
+    <t>Ears_Happy.png</t>
+  </si>
+  <si>
+    <t>Eyes_Cute.png</t>
+  </si>
+  <si>
     <t>lucky-dog-rise\Assets\Shiba\Red</t>
   </si>
   <si>
@@ -1060,18 +1081,12 @@
     <t>Claw_Lucky_Right.tres</t>
   </si>
   <si>
-    <t>Ears_Happy.png</t>
-  </si>
-  <si>
     <t>Ears_Plane.png</t>
   </si>
   <si>
     <t>Eyes_Bored.png</t>
   </si>
   <si>
-    <t>Eyes_Cute.png</t>
-  </si>
-  <si>
     <t>Eyes_Happy.png</t>
   </si>
   <si>
@@ -1127,6 +1142,9 @@
   </si>
   <si>
     <t>Shiba_ThinSesame.png</t>
+  </si>
+  <si>
+    <t>胡渣胡麻柴</t>
   </si>
   <si>
     <t>Shiba_UnshavenSesame.png</t>
@@ -5241,28 +5259,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
-    <col min="3" max="3" width="7.91666666666667" customWidth="1"/>
-    <col min="4" max="4" width="21.9166666666667" customWidth="1"/>
-    <col min="5" max="5" width="30.1666666666667" customWidth="1"/>
-    <col min="6" max="6" width="16.5833333333333" customWidth="1"/>
-    <col min="7" max="7" width="18.5" customWidth="1"/>
-    <col min="8" max="8" width="20.8333333333333" customWidth="1"/>
-    <col min="9" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="10" width="13.4166666666667" customWidth="1"/>
-    <col min="11" max="11" width="14.3333333333333" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="14.8333333333333" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="15.4166666666667" customWidth="1"/>
-    <col min="16" max="16" width="13.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
+    <col min="4" max="6" width="21.9166666666667" customWidth="1"/>
+    <col min="7" max="7" width="30.1666666666667" customWidth="1"/>
+    <col min="8" max="8" width="16.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="18.5" customWidth="1"/>
+    <col min="10" max="10" width="20.8333333333333" customWidth="1"/>
+    <col min="11" max="11" width="14.5" customWidth="1"/>
+    <col min="12" max="12" width="13.4166666666667" customWidth="1"/>
+    <col min="13" max="13" width="14.3333333333333" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="14.8333333333333" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="15.4166666666667" customWidth="1"/>
+    <col min="18" max="18" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5279,10 +5297,10 @@
       <c r="F1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>312</v>
       </c>
       <c r="I1" t="s">
@@ -5309,8 +5327,14 @@
       <c r="P1" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" t="s">
+        <v>321</v>
+      </c>
+      <c r="R1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -5357,18 +5381,30 @@
       <c r="P2" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="34.8" spans="1:18">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="E3" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="4" t="s">
         <v>19</v>
       </c>
@@ -5376,96 +5412,108 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G4" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="H4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="J4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K4" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="N4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="O4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="P4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>337</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>338</v>
+      </c>
+      <c r="R4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D5" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E5" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F5" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="G5" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="H5" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="I5" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J5" t="s">
+        <v>347</v>
+      </c>
+      <c r="K5" t="s">
         <v>342</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>348</v>
+      </c>
+      <c r="M5" t="s">
+        <v>349</v>
+      </c>
+      <c r="N5" t="s">
         <v>343</v>
       </c>
-      <c r="L5" t="s">
-        <v>344</v>
-      </c>
-      <c r="M5" t="s">
-        <v>345</v>
-      </c>
-      <c r="N5" t="s">
-        <v>346</v>
-      </c>
       <c r="O5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P5" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>351</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>352</v>
+      </c>
+      <c r="R5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -5473,46 +5521,52 @@
         <v>45</v>
       </c>
       <c r="D6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E6" t="s">
+        <v>342</v>
+      </c>
+      <c r="F6" t="s">
+        <v>350</v>
+      </c>
+      <c r="G6" t="s">
+        <v>355</v>
+      </c>
+      <c r="H6" t="s">
+        <v>345</v>
+      </c>
+      <c r="I6" t="s">
+        <v>346</v>
+      </c>
+      <c r="J6" t="s">
+        <v>347</v>
+      </c>
+      <c r="K6" t="s">
+        <v>342</v>
+      </c>
+      <c r="L6" t="s">
+        <v>348</v>
+      </c>
+      <c r="M6" t="s">
         <v>349</v>
       </c>
-      <c r="E6" t="s">
+      <c r="N6" t="s">
+        <v>343</v>
+      </c>
+      <c r="O6" t="s">
         <v>350</v>
       </c>
-      <c r="F6" t="s">
-        <v>338</v>
-      </c>
-      <c r="G6" t="s">
-        <v>339</v>
-      </c>
-      <c r="H6" t="s">
-        <v>340</v>
-      </c>
-      <c r="I6" t="s">
-        <v>341</v>
-      </c>
-      <c r="J6" t="s">
-        <v>342</v>
-      </c>
-      <c r="K6" t="s">
-        <v>343</v>
-      </c>
-      <c r="L6" t="s">
-        <v>344</v>
-      </c>
-      <c r="M6" t="s">
-        <v>345</v>
-      </c>
-      <c r="N6" t="s">
-        <v>346</v>
-      </c>
-      <c r="O6" t="s">
-        <v>347</v>
-      </c>
       <c r="P6" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>351</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>352</v>
+      </c>
+      <c r="R6" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -5520,46 +5574,52 @@
         <v>49</v>
       </c>
       <c r="D7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E7" t="s">
+        <v>342</v>
+      </c>
+      <c r="F7" t="s">
         <v>351</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
+        <v>357</v>
+      </c>
+      <c r="H7" t="s">
+        <v>345</v>
+      </c>
+      <c r="I7" t="s">
+        <v>346</v>
+      </c>
+      <c r="J7" t="s">
+        <v>347</v>
+      </c>
+      <c r="K7" t="s">
+        <v>342</v>
+      </c>
+      <c r="L7" t="s">
+        <v>348</v>
+      </c>
+      <c r="M7" t="s">
+        <v>349</v>
+      </c>
+      <c r="N7" t="s">
+        <v>343</v>
+      </c>
+      <c r="O7" t="s">
+        <v>350</v>
+      </c>
+      <c r="P7" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q7" t="s">
         <v>352</v>
       </c>
-      <c r="F7" t="s">
-        <v>338</v>
-      </c>
-      <c r="G7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H7" t="s">
-        <v>340</v>
-      </c>
-      <c r="I7" t="s">
-        <v>341</v>
-      </c>
-      <c r="J7" t="s">
-        <v>342</v>
-      </c>
-      <c r="K7" t="s">
-        <v>343</v>
-      </c>
-      <c r="L7" t="s">
-        <v>344</v>
-      </c>
-      <c r="M7" t="s">
-        <v>345</v>
-      </c>
-      <c r="N7" t="s">
-        <v>346</v>
-      </c>
-      <c r="O7" t="s">
-        <v>347</v>
-      </c>
-      <c r="P7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="R7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -5567,46 +5627,52 @@
         <v>53</v>
       </c>
       <c r="D8" t="s">
+        <v>358</v>
+      </c>
+      <c r="E8" t="s">
+        <v>348</v>
+      </c>
+      <c r="F8" t="s">
+        <v>349</v>
+      </c>
+      <c r="G8" t="s">
+        <v>359</v>
+      </c>
+      <c r="H8" t="s">
+        <v>345</v>
+      </c>
+      <c r="I8" t="s">
+        <v>346</v>
+      </c>
+      <c r="J8" t="s">
+        <v>347</v>
+      </c>
+      <c r="K8" t="s">
+        <v>342</v>
+      </c>
+      <c r="L8" t="s">
+        <v>348</v>
+      </c>
+      <c r="M8" t="s">
+        <v>349</v>
+      </c>
+      <c r="N8" t="s">
+        <v>343</v>
+      </c>
+      <c r="O8" t="s">
+        <v>350</v>
+      </c>
+      <c r="P8" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>352</v>
+      </c>
+      <c r="R8" t="s">
         <v>353</v>
       </c>
-      <c r="E8" t="s">
-        <v>354</v>
-      </c>
-      <c r="F8" t="s">
-        <v>338</v>
-      </c>
-      <c r="G8" t="s">
-        <v>339</v>
-      </c>
-      <c r="H8" t="s">
-        <v>340</v>
-      </c>
-      <c r="I8" t="s">
-        <v>341</v>
-      </c>
-      <c r="J8" t="s">
-        <v>342</v>
-      </c>
-      <c r="K8" t="s">
-        <v>343</v>
-      </c>
-      <c r="L8" t="s">
-        <v>344</v>
-      </c>
-      <c r="M8" t="s">
-        <v>345</v>
-      </c>
-      <c r="N8" t="s">
-        <v>346</v>
-      </c>
-      <c r="O8" t="s">
-        <v>347</v>
-      </c>
-      <c r="P8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+    </row>
+    <row r="9" spans="1:18">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -5614,46 +5680,52 @@
         <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E9" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F9" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G9" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="H9" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="I9" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J9" t="s">
+        <v>347</v>
+      </c>
+      <c r="K9" t="s">
         <v>342</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
+        <v>348</v>
+      </c>
+      <c r="M9" t="s">
+        <v>349</v>
+      </c>
+      <c r="N9" t="s">
         <v>343</v>
       </c>
-      <c r="L9" t="s">
-        <v>344</v>
-      </c>
-      <c r="M9" t="s">
-        <v>345</v>
-      </c>
-      <c r="N9" t="s">
-        <v>346</v>
-      </c>
       <c r="O9" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>351</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>352</v>
+      </c>
+      <c r="R9" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -5661,46 +5733,52 @@
         <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E10" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="F10" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="G10" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="H10" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="I10" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J10" t="s">
+        <v>347</v>
+      </c>
+      <c r="K10" t="s">
         <v>342</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
+        <v>348</v>
+      </c>
+      <c r="M10" t="s">
+        <v>349</v>
+      </c>
+      <c r="N10" t="s">
         <v>343</v>
       </c>
-      <c r="L10" t="s">
-        <v>344</v>
-      </c>
-      <c r="M10" t="s">
-        <v>345</v>
-      </c>
-      <c r="N10" t="s">
-        <v>346</v>
-      </c>
       <c r="O10" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P10" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>351</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>352</v>
+      </c>
+      <c r="R10" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="B11">
         <v>1007</v>
       </c>
@@ -5708,46 +5786,52 @@
         <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="E11" t="s">
+        <v>342</v>
+      </c>
+      <c r="F11" t="s">
+        <v>353</v>
+      </c>
+      <c r="G11" t="s">
+        <v>355</v>
+      </c>
+      <c r="H11" t="s">
+        <v>361</v>
+      </c>
+      <c r="I11" t="s">
+        <v>346</v>
+      </c>
+      <c r="J11" t="s">
+        <v>347</v>
+      </c>
+      <c r="K11" t="s">
+        <v>342</v>
+      </c>
+      <c r="L11" t="s">
+        <v>348</v>
+      </c>
+      <c r="M11" t="s">
+        <v>349</v>
+      </c>
+      <c r="N11" t="s">
+        <v>343</v>
+      </c>
+      <c r="O11" t="s">
         <v>350</v>
       </c>
-      <c r="F11" t="s">
-        <v>356</v>
-      </c>
-      <c r="G11" t="s">
-        <v>339</v>
-      </c>
-      <c r="H11" t="s">
-        <v>340</v>
-      </c>
-      <c r="I11" t="s">
-        <v>341</v>
-      </c>
-      <c r="J11" t="s">
-        <v>342</v>
-      </c>
-      <c r="K11" t="s">
-        <v>343</v>
-      </c>
-      <c r="L11" t="s">
-        <v>344</v>
-      </c>
-      <c r="M11" t="s">
-        <v>345</v>
-      </c>
-      <c r="N11" t="s">
-        <v>346</v>
-      </c>
-      <c r="O11" t="s">
-        <v>347</v>
-      </c>
       <c r="P11" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>351</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>352</v>
+      </c>
+      <c r="R11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="B12">
         <v>1008</v>
       </c>
@@ -5755,46 +5839,52 @@
         <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E12" t="s">
+        <v>342</v>
+      </c>
+      <c r="F12" t="s">
+        <v>343</v>
+      </c>
+      <c r="G12" t="s">
+        <v>355</v>
+      </c>
+      <c r="H12" t="s">
+        <v>363</v>
+      </c>
+      <c r="I12" t="s">
+        <v>346</v>
+      </c>
+      <c r="J12" t="s">
+        <v>347</v>
+      </c>
+      <c r="K12" t="s">
+        <v>342</v>
+      </c>
+      <c r="L12" t="s">
+        <v>348</v>
+      </c>
+      <c r="M12" t="s">
+        <v>349</v>
+      </c>
+      <c r="N12" t="s">
+        <v>343</v>
+      </c>
+      <c r="O12" t="s">
         <v>350</v>
       </c>
-      <c r="F12" t="s">
-        <v>358</v>
-      </c>
-      <c r="G12" t="s">
-        <v>339</v>
-      </c>
-      <c r="H12" t="s">
-        <v>340</v>
-      </c>
-      <c r="I12" t="s">
-        <v>341</v>
-      </c>
-      <c r="J12" t="s">
-        <v>342</v>
-      </c>
-      <c r="K12" t="s">
-        <v>343</v>
-      </c>
-      <c r="L12" t="s">
-        <v>344</v>
-      </c>
-      <c r="M12" t="s">
-        <v>345</v>
-      </c>
-      <c r="N12" t="s">
-        <v>346</v>
-      </c>
-      <c r="O12" t="s">
-        <v>347</v>
-      </c>
       <c r="P12" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>351</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>352</v>
+      </c>
+      <c r="R12" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="B13">
         <v>1009</v>
       </c>
@@ -5802,46 +5892,52 @@
         <v>71</v>
       </c>
       <c r="D13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E13" t="s">
+        <v>342</v>
+      </c>
+      <c r="F13" t="s">
+        <v>353</v>
+      </c>
+      <c r="G13" t="s">
+        <v>357</v>
+      </c>
+      <c r="H13" t="s">
         <v>361</v>
       </c>
-      <c r="E13" t="s">
+      <c r="I13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J13" t="s">
+        <v>347</v>
+      </c>
+      <c r="K13" t="s">
+        <v>342</v>
+      </c>
+      <c r="L13" t="s">
+        <v>348</v>
+      </c>
+      <c r="M13" t="s">
+        <v>349</v>
+      </c>
+      <c r="N13" t="s">
+        <v>343</v>
+      </c>
+      <c r="O13" t="s">
+        <v>350</v>
+      </c>
+      <c r="P13" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q13" t="s">
         <v>352</v>
       </c>
-      <c r="F13" t="s">
-        <v>356</v>
-      </c>
-      <c r="G13" t="s">
-        <v>339</v>
-      </c>
-      <c r="H13" t="s">
-        <v>340</v>
-      </c>
-      <c r="I13" t="s">
-        <v>341</v>
-      </c>
-      <c r="J13" t="s">
-        <v>342</v>
-      </c>
-      <c r="K13" t="s">
-        <v>343</v>
-      </c>
-      <c r="L13" t="s">
-        <v>344</v>
-      </c>
-      <c r="M13" t="s">
-        <v>345</v>
-      </c>
-      <c r="N13" t="s">
-        <v>346</v>
-      </c>
-      <c r="O13" t="s">
-        <v>347</v>
-      </c>
-      <c r="P13" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="R13" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="B14">
         <v>1010</v>
       </c>
@@ -5849,46 +5945,52 @@
         <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E14" t="s">
+        <v>342</v>
+      </c>
+      <c r="F14" t="s">
+        <v>343</v>
+      </c>
+      <c r="G14" t="s">
+        <v>357</v>
+      </c>
+      <c r="H14" t="s">
+        <v>363</v>
+      </c>
+      <c r="I14" t="s">
+        <v>346</v>
+      </c>
+      <c r="J14" t="s">
+        <v>347</v>
+      </c>
+      <c r="K14" t="s">
+        <v>342</v>
+      </c>
+      <c r="L14" t="s">
+        <v>348</v>
+      </c>
+      <c r="M14" t="s">
+        <v>349</v>
+      </c>
+      <c r="N14" t="s">
+        <v>343</v>
+      </c>
+      <c r="O14" t="s">
+        <v>350</v>
+      </c>
+      <c r="P14" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q14" t="s">
         <v>352</v>
       </c>
-      <c r="F14" t="s">
-        <v>358</v>
-      </c>
-      <c r="G14" t="s">
-        <v>339</v>
-      </c>
-      <c r="H14" t="s">
-        <v>340</v>
-      </c>
-      <c r="I14" t="s">
-        <v>341</v>
-      </c>
-      <c r="J14" t="s">
-        <v>342</v>
-      </c>
-      <c r="K14" t="s">
-        <v>343</v>
-      </c>
-      <c r="L14" t="s">
-        <v>344</v>
-      </c>
-      <c r="M14" t="s">
-        <v>345</v>
-      </c>
-      <c r="N14" t="s">
-        <v>346</v>
-      </c>
-      <c r="O14" t="s">
-        <v>347</v>
-      </c>
-      <c r="P14" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="R14" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="B15">
         <v>1011</v>
       </c>
@@ -5896,90 +5998,102 @@
         <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E15" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="F15" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="G15" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="H15" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="I15" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J15" t="s">
+        <v>347</v>
+      </c>
+      <c r="K15" t="s">
         <v>342</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
+        <v>348</v>
+      </c>
+      <c r="M15" t="s">
+        <v>349</v>
+      </c>
+      <c r="N15" t="s">
         <v>343</v>
       </c>
-      <c r="L15" t="s">
-        <v>344</v>
-      </c>
-      <c r="M15" t="s">
-        <v>345</v>
-      </c>
-      <c r="N15" t="s">
-        <v>346</v>
-      </c>
       <c r="O15" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P15" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+        <v>351</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>352</v>
+      </c>
+      <c r="R15" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>369</v>
       </c>
       <c r="D16" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E16" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="F16" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="G16" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="H16" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="I16" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J16" t="s">
+        <v>347</v>
+      </c>
+      <c r="K16" t="s">
         <v>342</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
+        <v>348</v>
+      </c>
+      <c r="M16" t="s">
+        <v>349</v>
+      </c>
+      <c r="N16" t="s">
         <v>343</v>
       </c>
-      <c r="L16" t="s">
-        <v>344</v>
-      </c>
-      <c r="M16" t="s">
-        <v>345</v>
-      </c>
-      <c r="N16" t="s">
-        <v>346</v>
-      </c>
       <c r="O16" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P16" t="s">
-        <v>348</v>
+        <v>351</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>352</v>
+      </c>
+      <c r="R16" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -6007,10 +6121,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
@@ -6024,7 +6138,7 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -6041,10 +6155,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="D3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>36</v>
@@ -6140,7 +6254,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>19</v>
@@ -6156,39 +6270,39 @@
     <row r="2" spans="1:5">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D3" s="3">
         <v>0.5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
@@ -6197,7 +6311,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:5">

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="242">
   <si>
     <t>##var</t>
   </si>
@@ -163,10 +163,10 @@
     <t>史诗</t>
   </si>
   <si>
-    <t>lucky-dog-rise\\Assets\Shiba\Red\</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\\Assets\UI\ItemIcon\Shiba_Red.png</t>
+    <t>v1\Assets\Shiba\Red\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Red.png</t>
   </si>
   <si>
     <t>Black</t>
@@ -175,36 +175,18 @@
     <t>黑柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\\Assets\Shiba\Black\</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\\Assets\UI\ItemIcon\Shiba_Black.png</t>
-  </si>
-  <si>
     <t>Cream</t>
   </si>
   <si>
     <t>白柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Cream\</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_Cream.png</t>
-  </si>
-  <si>
     <t>Sesame</t>
   </si>
   <si>
     <t>胡麻柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Sesame\</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_Sesame.png</t>
-  </si>
-  <si>
     <t>Thin Red</t>
   </si>
   <si>
@@ -214,75 +196,48 @@
     <t>传说</t>
   </si>
   <si>
-    <t>lucky-dog-rise\\Assets\UI\ItemIcon\Shiba_ThinRed.png</t>
-  </si>
-  <si>
     <t>Unshaven Red</t>
   </si>
   <si>
     <t>胡渣赤柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\\Assets\UI\ItemIcon\Shiba_UnshavenRed.png</t>
-  </si>
-  <si>
     <t>Thin Black</t>
   </si>
   <si>
     <t>瘦黑柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Black\</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_ThinBlack.png</t>
-  </si>
-  <si>
     <t>Unshaven Black</t>
   </si>
   <si>
     <t>胡渣黑柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_UnshavenBlack.png</t>
-  </si>
-  <si>
     <t>Thin Cream</t>
   </si>
   <si>
     <t>瘦白柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_ThinCream.png</t>
-  </si>
-  <si>
     <t>Unshaven Cream</t>
   </si>
   <si>
     <t>胡渣白柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_UnshavenCream.png</t>
-  </si>
-  <si>
     <t>Thin Sesame</t>
   </si>
   <si>
     <t>瘦芝麻柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_ThinSesame.png</t>
-  </si>
-  <si>
     <t>Unshaven Sesame</t>
   </si>
   <si>
     <t>胡渣芝麻柴</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Shiba_UnshavenSesame.png</t>
-  </si>
-  <si>
     <t>Green Beret</t>
   </si>
   <si>
@@ -292,624 +247,228 @@
     <t>稀有</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\Beret_Green.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_Beret_Green.png</t>
+    <t>v1\Headwear\Beret_Green.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_Beret_Green.png</t>
   </si>
   <si>
     <t>Red Beret</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\Beret_Red.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_Beret_Red.png</t>
-  </si>
-  <si>
     <t>Gray Fedora Hat</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\FedoraHat_Gray.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_FedoraHat_Gray.png</t>
-  </si>
-  <si>
     <t>Maroon Fedora Hat</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\FedoraHat_Maroon.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_FedoraHat_Maroon.png</t>
-  </si>
-  <si>
     <t>Hole</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\Hole.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_Hole.png</t>
-  </si>
-  <si>
     <t>Lucky</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\Lucky.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_Lucky.png</t>
-  </si>
-  <si>
     <t>Black Magic Hat</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\MagicHat_Black.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_MagicHat_Black.png</t>
-  </si>
-  <si>
     <t>White Magic Hat</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\MagicHat_White.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_MagicHat_White.png</t>
-  </si>
-  <si>
     <t>Beige Sun Hat</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\SunHat_Beige.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_SunHat_Beige.png</t>
-  </si>
-  <si>
     <t>Blue Sun Hat</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Headwear\SunHat_Blue.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Headwear_SunHat_Blue.png</t>
-  </si>
-  <si>
     <t>3D Glasses</t>
   </si>
   <si>
     <t>Eyewear</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Eyewear\3DGlasses.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_3DGlasses.png</t>
-  </si>
-  <si>
     <t>Eye Patch</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Eyewear\EyePatch.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_EyePatch.png</t>
-  </si>
-  <si>
     <t>Black Monocle</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Eyewear\Monocle_black.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_Monocle_black.png</t>
-  </si>
-  <si>
     <t>Golden Monocle</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Eyewear\Monocle_golden.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_Monocle_golden.png</t>
-  </si>
-  <si>
     <t>Blade Sunglasses</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Eyewear\Sunglasses_Blade.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Eyewear_Sunglasses_Blade.png</t>
-  </si>
-  <si>
     <t>Male A</t>
   </si>
   <si>
-    <t>Hand</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\Hand\MaleA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Hand_MaleA.png</t>
+    <t>Arm</t>
   </si>
   <si>
     <t>Male B</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Hand\MaleB.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Hand_MaleB.png</t>
-  </si>
-  <si>
     <t>Male C</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Hand\MaleC.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Hand_MaleC.png</t>
-  </si>
-  <si>
     <t>Male D</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Hand\MaleD.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Hand_MaleD.png</t>
-  </si>
-  <si>
     <t>Baseball Jacket Black</t>
   </si>
   <si>
     <t>Clothes</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\BaseballJacket_Black.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BaseballJacket_Black.png</t>
-  </si>
-  <si>
     <t>Baseball Jacket Purple</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\BaseballJacket_Purple.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BaseballJacket_Purple.png</t>
-  </si>
-  <si>
     <t>Black Business Suit</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\BlackBusinessSuit_Black.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BlackBusinessSuit_Black.png</t>
-  </si>
-  <si>
     <t>Blue Shirt</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\BlueShirt_Cyan.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BlueShirt_Cyan.png</t>
-  </si>
-  <si>
     <t>Blue Striped Shirt</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\BlueStripedShirt_RegattaStripe.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_BlueStripedShirt_RegattaStripe.png</t>
-  </si>
-  <si>
     <t>Cream Shirt</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\CreamShirt_Beige.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_CreamShirt_Beige.png</t>
-  </si>
-  <si>
     <t>White Business Suit</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\WhiteBusinessSuit_LightGray.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_WhiteBusinessSuit_LightGray.png</t>
-  </si>
-  <si>
     <t>White Shirt</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Clothes\WhiteShirt_White.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Clothes_WhiteShirt_White.png</t>
-  </si>
-  <si>
     <t>Felt Emerald</t>
   </si>
   <si>
     <t>Table</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\FeltEmerald.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_FeltEmerald.png</t>
-  </si>
-  <si>
     <t>Full Tilt Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\FullTiltLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_FullTiltLike.png</t>
-  </si>
-  <si>
     <t>Hustler Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\HustlerLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_HustlerLike.png</t>
-  </si>
-  <si>
     <t>Les Ambassadeurs Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\LesAmbassadeursLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_LesAmbassadeursLike.png</t>
-  </si>
-  <si>
     <t>Maestral Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\MaestralLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_MaestralLike.png</t>
-  </si>
-  <si>
     <t>Mezcal Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\MezcalLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_MezcalLike.png</t>
-  </si>
-  <si>
     <t>Poker Go Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\PokerGoLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_PokerGoLike.png</t>
-  </si>
-  <si>
     <t>Pure Indigo</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\PureIndigo.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_PureIndigo.png</t>
-  </si>
-  <si>
     <t>Pure Purple</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\PurePurple.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_PurePurple.png</t>
-  </si>
-  <si>
     <t>Pure Teal</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\PureTeal.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_PureTeal.png</t>
-  </si>
-  <si>
     <t>The King of Hill Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Table\TheKingOfHillLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Table_TheKingOfHillLike.png</t>
-  </si>
-  <si>
     <t>Blue A</t>
   </si>
   <si>
     <t>Background</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\BlueA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_BlueA.png</t>
-  </si>
-  <si>
     <t>Brown A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\BrownA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_BrownA.png</t>
-  </si>
-  <si>
     <t>Brown B</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\BrownB.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_BrownB.png</t>
-  </si>
-  <si>
     <t>Gray A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\GrayA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_GrayA.png</t>
-  </si>
-  <si>
     <t>Gray B</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\GrayB.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_GrayB.png</t>
-  </si>
-  <si>
     <t>Green A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\GreenA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_GreenA.png</t>
-  </si>
-  <si>
     <t>Green B</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\GreenB.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_GreenB.png</t>
-  </si>
-  <si>
     <t>Highstakes Poker Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\HighstakesPokerLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_HighstakesPokerLike.png</t>
-  </si>
-  <si>
     <t>Orange A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\OrangeA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_OrangeA.png</t>
-  </si>
-  <si>
     <t>Part Poker Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\PartPokerLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_PartPokerLike.png</t>
-  </si>
-  <si>
     <t>Pink A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\PinkA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_PinkA.png</t>
-  </si>
-  <si>
     <t>Poker King Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\PokerKingLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_PokerKingLike.png</t>
-  </si>
-  <si>
     <t>Purple A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\PurpleA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_PurpleA.png</t>
-  </si>
-  <si>
     <t>Red A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\RedA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_RedA.png</t>
-  </si>
-  <si>
     <t>Red B</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\RedB.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_RedB.png</t>
-  </si>
-  <si>
     <t>Twitter Blue</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\TwitterBlue.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_TwitterBlue.png</t>
-  </si>
-  <si>
     <t>World Poker Tour Like</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\WorldPokerTourtLike.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_WorldPokerTourtLike.png</t>
-  </si>
-  <si>
     <t>Yellow A</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Background\YellowA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Background_YellowA.png</t>
-  </si>
-  <si>
     <t>A158UUA</t>
   </si>
   <si>
     <t>Accessory</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\A158UUA.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_A158UUA.png</t>
-  </si>
-  <si>
     <t>Anchor Tattoo</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\AnchorTattoo.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_AnchorTattoo.png</t>
-  </si>
-  <si>
     <t>F91UU</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\F91UU.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_F91UU.png</t>
-  </si>
-  <si>
     <t>Feng Shui Bracelet</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\FengShuiBracelet.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_FengShuiBracelet.png</t>
-  </si>
-  <si>
     <t>Good Luck Bracelet</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\GoodLuckBracelet.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_GoodLuckBracelet.png</t>
-  </si>
-  <si>
     <t>Hair</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\Hair.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_Hair.png</t>
-  </si>
-  <si>
     <t>Relax Driver Black</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\RelaxDriver_Black.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_RelaxDriver_Black.png</t>
-  </si>
-  <si>
     <t>Relax Driver Green</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\RelaxDriver_Green.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_RelaxDriver_Green.png</t>
-  </si>
-  <si>
     <t>Text Wristband Green</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\TextWristband_Green.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_TextWristband_Green.png</t>
-  </si>
-  <si>
     <t>Text Wristband Red</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\TextWristband_Red.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_TextWristband_Red.png</t>
-  </si>
-  <si>
     <t>WSOP Gold Bracelet</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Accessory\WSOPGoldBracelet.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\UI\ItemIcon\Accessory_WSOPGoldBracelet.png</t>
-  </si>
-  <si>
     <t>小狗本体</t>
   </si>
   <si>
@@ -961,6 +520,18 @@
     <t>玩家手部装饰</t>
   </si>
   <si>
+    <t>Treat</t>
+  </si>
+  <si>
+    <t>玩家嗜好品</t>
+  </si>
+  <si>
+    <t>CardBack</t>
+  </si>
+  <si>
+    <t>卡牌背面</t>
+  </si>
+  <si>
     <t>IconName</t>
   </si>
   <si>
@@ -1069,7 +640,7 @@
     <t>Eyes_Cute.png</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Red</t>
+    <t>v1\Shiba\Red</t>
   </si>
   <si>
     <t>Head_Chubby.png</t>
@@ -1102,19 +673,13 @@
     <t>Shiba_Black.png</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Black</t>
+    <t>v1\Shiba\Black</t>
   </si>
   <si>
     <t>Shiba_Cream.png</t>
   </si>
   <si>
-    <t>lucky-dog-rise\Assets\Shiba\Cream</t>
-  </si>
-  <si>
     <t>Shiba_Sesame.png</t>
-  </si>
-  <si>
-    <t>lucky-dog-rise\Assets\Shiba\Sesame</t>
   </si>
   <si>
     <t>Shiba_ThinRed.png</t>
@@ -1816,7 +1381,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1834,6 +1399,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2582,12 +2150,8 @@
       <c r="J6">
         <v>1001</v>
       </c>
-      <c r="K6" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" t="s">
-        <v>47</v>
-      </c>
+      <c r="K6"/>
+      <c r="L6"/>
       <c r="M6">
         <v>1002</v>
       </c>
@@ -2597,10 +2161,10 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>40</v>
@@ -2620,12 +2184,8 @@
       <c r="J7">
         <v>1001</v>
       </c>
-      <c r="K7" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" t="s">
-        <v>51</v>
-      </c>
+      <c r="K7"/>
+      <c r="L7"/>
       <c r="M7">
         <v>1003</v>
       </c>
@@ -2635,10 +2195,10 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
         <v>40</v>
@@ -2658,12 +2218,8 @@
       <c r="J8">
         <v>1001</v>
       </c>
-      <c r="K8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8" t="s">
-        <v>55</v>
-      </c>
+      <c r="K8"/>
+      <c r="L8"/>
       <c r="M8">
         <v>1004</v>
       </c>
@@ -2673,16 +2229,16 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -2696,12 +2252,8 @@
       <c r="J9">
         <v>1001</v>
       </c>
-      <c r="K9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9" t="s">
-        <v>59</v>
-      </c>
+      <c r="K9"/>
+      <c r="L9"/>
       <c r="M9">
         <v>1005</v>
       </c>
@@ -2711,16 +2263,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -2734,12 +2286,8 @@
       <c r="J10">
         <v>1001</v>
       </c>
-      <c r="K10" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" t="s">
-        <v>62</v>
-      </c>
+      <c r="K10"/>
+      <c r="L10"/>
       <c r="M10">
         <v>1006</v>
       </c>
@@ -2749,16 +2297,16 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
         <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -2772,12 +2320,8 @@
       <c r="J11">
         <v>1001</v>
       </c>
-      <c r="K11" t="s">
-        <v>65</v>
-      </c>
-      <c r="L11" t="s">
-        <v>66</v>
-      </c>
+      <c r="K11"/>
+      <c r="L11"/>
       <c r="M11">
         <v>1007</v>
       </c>
@@ -2787,16 +2331,16 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>40</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -2810,12 +2354,8 @@
       <c r="J12">
         <v>1001</v>
       </c>
-      <c r="K12" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" t="s">
-        <v>69</v>
-      </c>
+      <c r="K12"/>
+      <c r="L12"/>
       <c r="M12">
         <v>1008</v>
       </c>
@@ -2825,16 +2365,16 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -2848,12 +2388,8 @@
       <c r="J13">
         <v>1001</v>
       </c>
-      <c r="K13" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13" t="s">
-        <v>72</v>
-      </c>
+      <c r="K13"/>
+      <c r="L13"/>
       <c r="M13">
         <v>1009</v>
       </c>
@@ -2863,16 +2399,16 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
         <v>40</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -2886,12 +2422,8 @@
       <c r="J14">
         <v>1001</v>
       </c>
-      <c r="K14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L14" t="s">
-        <v>75</v>
-      </c>
+      <c r="K14"/>
+      <c r="L14"/>
       <c r="M14">
         <v>1010</v>
       </c>
@@ -2901,16 +2433,16 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -2924,12 +2456,8 @@
       <c r="J15">
         <v>1001</v>
       </c>
-      <c r="K15" t="s">
-        <v>54</v>
-      </c>
-      <c r="L15" t="s">
-        <v>78</v>
-      </c>
+      <c r="K15"/>
+      <c r="L15"/>
       <c r="M15">
         <v>1011</v>
       </c>
@@ -2939,16 +2467,16 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -2962,12 +2490,8 @@
       <c r="J16">
         <v>1001</v>
       </c>
-      <c r="K16" t="s">
-        <v>54</v>
-      </c>
-      <c r="L16" t="s">
-        <v>81</v>
-      </c>
+      <c r="K16"/>
+      <c r="L16"/>
       <c r="M16">
         <v>1012</v>
       </c>
@@ -2982,13 +2506,13 @@
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G18">
         <v>300</v>
@@ -3003,10 +2527,10 @@
         <v>1001</v>
       </c>
       <c r="K18" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="L18" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -3014,13 +2538,13 @@
         <v>2002</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G19">
         <v>300</v>
@@ -3033,12 +2557,6 @@
       </c>
       <c r="J19">
         <v>1001</v>
-      </c>
-      <c r="K19" t="s">
-        <v>88</v>
-      </c>
-      <c r="L19" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -3046,13 +2564,13 @@
         <v>2003</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G20">
         <v>300</v>
@@ -3065,12 +2583,6 @@
       </c>
       <c r="J20">
         <v>1001</v>
-      </c>
-      <c r="K20" t="s">
-        <v>91</v>
-      </c>
-      <c r="L20" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -3078,13 +2590,13 @@
         <v>2004</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G21">
         <v>300</v>
@@ -3097,12 +2609,6 @@
       </c>
       <c r="J21">
         <v>1001</v>
-      </c>
-      <c r="K21" t="s">
-        <v>94</v>
-      </c>
-      <c r="L21" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -3110,13 +2616,13 @@
         <v>2005</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G22">
         <v>300</v>
@@ -3129,12 +2635,6 @@
       </c>
       <c r="J22">
         <v>1001</v>
-      </c>
-      <c r="K22" t="s">
-        <v>97</v>
-      </c>
-      <c r="L22" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -3142,13 +2642,13 @@
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="E23" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G23">
         <v>300</v>
@@ -3161,12 +2661,6 @@
       </c>
       <c r="J23">
         <v>1001</v>
-      </c>
-      <c r="K23" t="s">
-        <v>100</v>
-      </c>
-      <c r="L23" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -3174,13 +2668,13 @@
         <v>2007</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="E24" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G24">
         <v>300</v>
@@ -3193,12 +2687,6 @@
       </c>
       <c r="J24">
         <v>1001</v>
-      </c>
-      <c r="K24" t="s">
-        <v>103</v>
-      </c>
-      <c r="L24" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -3206,13 +2694,13 @@
         <v>2008</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G25">
         <v>300</v>
@@ -3225,12 +2713,6 @@
       </c>
       <c r="J25">
         <v>1001</v>
-      </c>
-      <c r="K25" t="s">
-        <v>106</v>
-      </c>
-      <c r="L25" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -3238,13 +2720,13 @@
         <v>2009</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="E26" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G26">
         <v>300</v>
@@ -3257,12 +2739,6 @@
       </c>
       <c r="J26">
         <v>1001</v>
-      </c>
-      <c r="K26" t="s">
-        <v>109</v>
-      </c>
-      <c r="L26" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -3270,13 +2746,13 @@
         <v>2010</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G27">
         <v>300</v>
@@ -3289,12 +2765,6 @@
       </c>
       <c r="J27">
         <v>1001</v>
-      </c>
-      <c r="K27" t="s">
-        <v>112</v>
-      </c>
-      <c r="L27" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -3302,13 +2772,13 @@
         <v>3001</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="F28" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G28">
         <v>300</v>
@@ -3321,12 +2791,6 @@
       </c>
       <c r="J28">
         <v>1001</v>
-      </c>
-      <c r="K28" t="s">
-        <v>116</v>
-      </c>
-      <c r="L28" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -3334,13 +2798,13 @@
         <v>3002</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="E29" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="F29" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G29">
         <v>300</v>
@@ -3353,12 +2817,6 @@
       </c>
       <c r="J29">
         <v>1001</v>
-      </c>
-      <c r="K29" t="s">
-        <v>119</v>
-      </c>
-      <c r="L29" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -3366,13 +2824,13 @@
         <v>3003</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G30">
         <v>300</v>
@@ -3385,12 +2843,6 @@
       </c>
       <c r="J30">
         <v>1001</v>
-      </c>
-      <c r="K30" t="s">
-        <v>122</v>
-      </c>
-      <c r="L30" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -3398,13 +2850,13 @@
         <v>3004</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="F31" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G31">
         <v>300</v>
@@ -3417,12 +2869,6 @@
       </c>
       <c r="J31">
         <v>1001</v>
-      </c>
-      <c r="K31" t="s">
-        <v>125</v>
-      </c>
-      <c r="L31" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -3430,13 +2876,13 @@
         <v>3005</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="E32" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="F32" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G32">
         <v>300</v>
@@ -3450,25 +2896,19 @@
       <c r="J32">
         <v>1001</v>
       </c>
-      <c r="K32" t="s">
-        <v>128</v>
-      </c>
-      <c r="L32" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12">
+    </row>
+    <row r="33" spans="2:10">
       <c r="B33">
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="E33" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G33">
         <v>300</v>
@@ -3482,25 +2922,19 @@
       <c r="J33">
         <v>1001</v>
       </c>
-      <c r="K33" t="s">
-        <v>132</v>
-      </c>
-      <c r="L33" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12">
+    </row>
+    <row r="34" spans="2:10">
       <c r="B34">
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="E34" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G34">
         <v>300</v>
@@ -3514,25 +2948,19 @@
       <c r="J34">
         <v>1001</v>
       </c>
-      <c r="K34" t="s">
-        <v>135</v>
-      </c>
-      <c r="L34" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12">
+    </row>
+    <row r="35" spans="2:10">
       <c r="B35">
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>131</v>
+        <v>90</v>
+      </c>
+      <c r="E35" t="s">
+        <v>88</v>
       </c>
       <c r="F35" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G35">
         <v>300</v>
@@ -3546,25 +2974,19 @@
       <c r="J35">
         <v>1001</v>
       </c>
-      <c r="K35" t="s">
-        <v>138</v>
-      </c>
-      <c r="L35" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12">
+    </row>
+    <row r="36" spans="2:10">
       <c r="B36">
         <v>4004</v>
       </c>
       <c r="C36" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="E36" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G36">
         <v>300</v>
@@ -3578,25 +3000,19 @@
       <c r="J36">
         <v>1001</v>
       </c>
-      <c r="K36" t="s">
-        <v>141</v>
-      </c>
-      <c r="L36" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12">
+    </row>
+    <row r="37" spans="2:10">
       <c r="B37">
         <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="E37" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="F37" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G37">
         <v>300</v>
@@ -3610,25 +3026,19 @@
       <c r="J37">
         <v>1001</v>
       </c>
-      <c r="K37" t="s">
-        <v>145</v>
-      </c>
-      <c r="L37" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12">
+    </row>
+    <row r="38" spans="2:10">
       <c r="B38">
         <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="E38" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="F38" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G38">
         <v>300</v>
@@ -3642,25 +3052,19 @@
       <c r="J38">
         <v>1001</v>
       </c>
-      <c r="K38" t="s">
-        <v>148</v>
-      </c>
-      <c r="L38" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12">
+    </row>
+    <row r="39" spans="2:10">
       <c r="B39">
         <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="E39" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="F39" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G39">
         <v>300</v>
@@ -3674,25 +3078,19 @@
       <c r="J39">
         <v>1001</v>
       </c>
-      <c r="K39" t="s">
-        <v>151</v>
-      </c>
-      <c r="L39" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12">
+    </row>
+    <row r="40" spans="2:10">
       <c r="B40">
         <v>5004</v>
       </c>
       <c r="C40" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="E40" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="F40" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G40">
         <v>300</v>
@@ -3706,25 +3104,19 @@
       <c r="J40">
         <v>1001</v>
       </c>
-      <c r="K40" t="s">
-        <v>154</v>
-      </c>
-      <c r="L40" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12">
+    </row>
+    <row r="41" spans="2:10">
       <c r="B41">
         <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="E41" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="F41" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G41">
         <v>300</v>
@@ -3738,25 +3130,19 @@
       <c r="J41">
         <v>1001</v>
       </c>
-      <c r="K41" t="s">
-        <v>157</v>
-      </c>
-      <c r="L41" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12">
+    </row>
+    <row r="42" spans="2:10">
       <c r="B42">
         <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="E42" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="F42" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G42">
         <v>300</v>
@@ -3770,25 +3156,19 @@
       <c r="J42">
         <v>1001</v>
       </c>
-      <c r="K42" t="s">
-        <v>160</v>
-      </c>
-      <c r="L42" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12">
+    </row>
+    <row r="43" spans="2:10">
       <c r="B43">
         <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="E43" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="F43" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G43">
         <v>300</v>
@@ -3802,25 +3182,19 @@
       <c r="J43">
         <v>1001</v>
       </c>
-      <c r="K43" t="s">
-        <v>163</v>
-      </c>
-      <c r="L43" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12">
+    </row>
+    <row r="44" spans="2:10">
       <c r="B44">
         <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="F44" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G44">
         <v>300</v>
@@ -3834,25 +3208,19 @@
       <c r="J44">
         <v>1001</v>
       </c>
-      <c r="K44" t="s">
-        <v>166</v>
-      </c>
-      <c r="L44" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12">
+    </row>
+    <row r="45" spans="2:10">
       <c r="B45">
         <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="E45" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="F45" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G45">
         <v>300</v>
@@ -3866,25 +3234,19 @@
       <c r="J45">
         <v>1001</v>
       </c>
-      <c r="K45" t="s">
-        <v>170</v>
-      </c>
-      <c r="L45" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12">
+    </row>
+    <row r="46" spans="2:10">
       <c r="B46">
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>172</v>
+        <v>103</v>
       </c>
       <c r="E46" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="F46" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G46">
         <v>300</v>
@@ -3898,25 +3260,19 @@
       <c r="J46">
         <v>1001</v>
       </c>
-      <c r="K46" t="s">
-        <v>173</v>
-      </c>
-      <c r="L46" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12">
+    </row>
+    <row r="47" spans="2:10">
       <c r="B47">
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>175</v>
+        <v>104</v>
       </c>
       <c r="E47" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="F47" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G47">
         <v>300</v>
@@ -3930,25 +3286,19 @@
       <c r="J47">
         <v>1001</v>
       </c>
-      <c r="K47" t="s">
-        <v>176</v>
-      </c>
-      <c r="L47" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12">
+    </row>
+    <row r="48" spans="2:10">
       <c r="B48">
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>178</v>
+        <v>105</v>
       </c>
       <c r="E48" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="F48" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G48">
         <v>300</v>
@@ -3962,25 +3312,19 @@
       <c r="J48">
         <v>1001</v>
       </c>
-      <c r="K48" t="s">
-        <v>179</v>
-      </c>
-      <c r="L48" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="49" spans="2:12">
+    </row>
+    <row r="49" spans="2:10">
       <c r="B49">
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="E49" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="F49" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G49">
         <v>300</v>
@@ -3994,25 +3338,19 @@
       <c r="J49">
         <v>1001</v>
       </c>
-      <c r="K49" t="s">
-        <v>182</v>
-      </c>
-      <c r="L49" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="50" spans="2:12">
+    </row>
+    <row r="50" spans="2:10">
       <c r="B50">
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="E50" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="F50" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G50">
         <v>300</v>
@@ -4026,25 +3364,19 @@
       <c r="J50">
         <v>1001</v>
       </c>
-      <c r="K50" t="s">
-        <v>185</v>
-      </c>
-      <c r="L50" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="51" spans="2:12">
+    </row>
+    <row r="51" spans="2:10">
       <c r="B51">
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="E51" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="F51" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G51">
         <v>300</v>
@@ -4058,25 +3390,19 @@
       <c r="J51">
         <v>1001</v>
       </c>
-      <c r="K51" t="s">
-        <v>188</v>
-      </c>
-      <c r="L51" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="52" spans="2:12">
+    </row>
+    <row r="52" spans="2:10">
       <c r="B52">
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>190</v>
+        <v>109</v>
       </c>
       <c r="E52" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="F52" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G52">
         <v>300</v>
@@ -4090,25 +3416,19 @@
       <c r="J52">
         <v>1001</v>
       </c>
-      <c r="K52" t="s">
-        <v>191</v>
-      </c>
-      <c r="L52" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="53" spans="2:12">
+    </row>
+    <row r="53" spans="2:10">
       <c r="B53">
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>193</v>
+        <v>110</v>
       </c>
       <c r="E53" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="F53" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G53">
         <v>300</v>
@@ -4122,25 +3442,19 @@
       <c r="J53">
         <v>1001</v>
       </c>
-      <c r="K53" t="s">
-        <v>194</v>
-      </c>
-      <c r="L53" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="54" spans="2:12">
+    </row>
+    <row r="54" spans="2:10">
       <c r="B54">
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="E54" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="F54" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G54">
         <v>300</v>
@@ -4154,25 +3468,19 @@
       <c r="J54">
         <v>1001</v>
       </c>
-      <c r="K54" t="s">
-        <v>197</v>
-      </c>
-      <c r="L54" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="55" spans="2:12">
+    </row>
+    <row r="55" spans="2:10">
       <c r="B55">
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="E55" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="F55" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G55">
         <v>300</v>
@@ -4186,25 +3494,19 @@
       <c r="J55">
         <v>1001</v>
       </c>
-      <c r="K55" t="s">
-        <v>200</v>
-      </c>
-      <c r="L55" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="56" spans="2:12">
+    </row>
+    <row r="56" spans="2:10">
       <c r="B56">
         <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>202</v>
+        <v>113</v>
       </c>
       <c r="E56" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G56">
         <v>300</v>
@@ -4218,25 +3520,19 @@
       <c r="J56">
         <v>1001</v>
       </c>
-      <c r="K56" t="s">
-        <v>204</v>
-      </c>
-      <c r="L56" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="57" spans="2:12">
+    </row>
+    <row r="57" spans="2:10">
       <c r="B57">
         <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>206</v>
+        <v>115</v>
       </c>
       <c r="E57" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F57" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G57">
         <v>300</v>
@@ -4250,25 +3546,19 @@
       <c r="J57">
         <v>1001</v>
       </c>
-      <c r="K57" t="s">
-        <v>207</v>
-      </c>
-      <c r="L57" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12">
+    </row>
+    <row r="58" spans="2:10">
       <c r="B58">
         <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>209</v>
+        <v>116</v>
       </c>
       <c r="E58" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G58">
         <v>300</v>
@@ -4282,25 +3572,19 @@
       <c r="J58">
         <v>1001</v>
       </c>
-      <c r="K58" t="s">
-        <v>210</v>
-      </c>
-      <c r="L58" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="59" spans="2:12">
+    </row>
+    <row r="59" spans="2:10">
       <c r="B59">
         <v>7004</v>
       </c>
       <c r="C59" t="s">
-        <v>212</v>
+        <v>117</v>
       </c>
       <c r="E59" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G59">
         <v>300</v>
@@ -4314,25 +3598,19 @@
       <c r="J59">
         <v>1001</v>
       </c>
-      <c r="K59" t="s">
-        <v>213</v>
-      </c>
-      <c r="L59" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="60" spans="2:12">
+    </row>
+    <row r="60" spans="2:10">
       <c r="B60">
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="E60" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F60" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G60">
         <v>300</v>
@@ -4346,25 +3624,19 @@
       <c r="J60">
         <v>1001</v>
       </c>
-      <c r="K60" t="s">
-        <v>216</v>
-      </c>
-      <c r="L60" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12">
+    </row>
+    <row r="61" spans="2:10">
       <c r="B61">
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>218</v>
+        <v>119</v>
       </c>
       <c r="E61" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G61">
         <v>300</v>
@@ -4378,25 +3650,19 @@
       <c r="J61">
         <v>1001</v>
       </c>
-      <c r="K61" t="s">
-        <v>219</v>
-      </c>
-      <c r="L61" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="62" spans="2:12">
+    </row>
+    <row r="62" spans="2:10">
       <c r="B62">
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>221</v>
+        <v>120</v>
       </c>
       <c r="E62" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G62">
         <v>300</v>
@@ -4410,25 +3676,19 @@
       <c r="J62">
         <v>1001</v>
       </c>
-      <c r="K62" t="s">
-        <v>222</v>
-      </c>
-      <c r="L62" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="63" spans="2:12">
+    </row>
+    <row r="63" spans="2:10">
       <c r="B63">
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>224</v>
+        <v>121</v>
       </c>
       <c r="E63" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G63">
         <v>300</v>
@@ -4442,25 +3702,19 @@
       <c r="J63">
         <v>1001</v>
       </c>
-      <c r="K63" t="s">
-        <v>225</v>
-      </c>
-      <c r="L63" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="64" spans="2:12">
+    </row>
+    <row r="64" spans="2:10">
       <c r="B64">
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>227</v>
+        <v>122</v>
       </c>
       <c r="E64" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G64">
         <v>300</v>
@@ -4474,25 +3728,19 @@
       <c r="J64">
         <v>1001</v>
       </c>
-      <c r="K64" t="s">
-        <v>228</v>
-      </c>
-      <c r="L64" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="65" spans="2:12">
+    </row>
+    <row r="65" spans="2:10">
       <c r="B65">
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>230</v>
+        <v>123</v>
       </c>
       <c r="E65" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G65">
         <v>300</v>
@@ -4506,25 +3754,19 @@
       <c r="J65">
         <v>1001</v>
       </c>
-      <c r="K65" t="s">
-        <v>231</v>
-      </c>
-      <c r="L65" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="66" spans="2:12">
+    </row>
+    <row r="66" spans="2:10">
       <c r="B66">
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>233</v>
+        <v>124</v>
       </c>
       <c r="E66" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F66" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G66">
         <v>300</v>
@@ -4538,25 +3780,19 @@
       <c r="J66">
         <v>1001</v>
       </c>
-      <c r="K66" t="s">
-        <v>234</v>
-      </c>
-      <c r="L66" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12">
+    </row>
+    <row r="67" spans="2:10">
       <c r="B67">
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>236</v>
+        <v>125</v>
       </c>
       <c r="E67" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G67">
         <v>300</v>
@@ -4570,25 +3806,19 @@
       <c r="J67">
         <v>1001</v>
       </c>
-      <c r="K67" t="s">
-        <v>237</v>
-      </c>
-      <c r="L67" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="68" spans="2:12">
+    </row>
+    <row r="68" spans="2:10">
       <c r="B68">
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>239</v>
+        <v>126</v>
       </c>
       <c r="E68" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G68">
         <v>300</v>
@@ -4602,25 +3832,19 @@
       <c r="J68">
         <v>1001</v>
       </c>
-      <c r="K68" t="s">
-        <v>240</v>
-      </c>
-      <c r="L68" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="69" spans="2:12">
+    </row>
+    <row r="69" spans="2:10">
       <c r="B69">
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>242</v>
+        <v>127</v>
       </c>
       <c r="E69" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G69">
         <v>300</v>
@@ -4634,25 +3858,19 @@
       <c r="J69">
         <v>1001</v>
       </c>
-      <c r="K69" t="s">
-        <v>243</v>
-      </c>
-      <c r="L69" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="70" spans="2:12">
+    </row>
+    <row r="70" spans="2:10">
       <c r="B70">
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>245</v>
+        <v>128</v>
       </c>
       <c r="E70" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G70">
         <v>300</v>
@@ -4666,25 +3884,19 @@
       <c r="J70">
         <v>1001</v>
       </c>
-      <c r="K70" t="s">
-        <v>246</v>
-      </c>
-      <c r="L70" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="71" spans="2:12">
+    </row>
+    <row r="71" spans="2:10">
       <c r="B71">
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>248</v>
+        <v>129</v>
       </c>
       <c r="E71" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G71">
         <v>300</v>
@@ -4698,25 +3910,19 @@
       <c r="J71">
         <v>1001</v>
       </c>
-      <c r="K71" t="s">
-        <v>249</v>
-      </c>
-      <c r="L71" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="72" spans="2:12">
+    </row>
+    <row r="72" spans="2:10">
       <c r="B72">
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>251</v>
+        <v>130</v>
       </c>
       <c r="E72" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F72" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G72">
         <v>300</v>
@@ -4730,25 +3936,19 @@
       <c r="J72">
         <v>1001</v>
       </c>
-      <c r="K72" t="s">
-        <v>252</v>
-      </c>
-      <c r="L72" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="73" spans="2:12">
+    </row>
+    <row r="73" spans="2:10">
       <c r="B73">
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>254</v>
+        <v>131</v>
       </c>
       <c r="E73" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F73" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G73">
         <v>300</v>
@@ -4762,25 +3962,19 @@
       <c r="J73">
         <v>1001</v>
       </c>
-      <c r="K73" t="s">
-        <v>255</v>
-      </c>
-      <c r="L73" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="74" spans="2:12">
+    </row>
+    <row r="74" spans="2:10">
       <c r="B74">
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>257</v>
+        <v>132</v>
       </c>
       <c r="E74" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="F74" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G74">
         <v>300</v>
@@ -4794,25 +3988,19 @@
       <c r="J74">
         <v>1001</v>
       </c>
-      <c r="K74" t="s">
-        <v>259</v>
-      </c>
-      <c r="L74" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="75" spans="2:12">
+    </row>
+    <row r="75" spans="2:10">
       <c r="B75">
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>261</v>
+        <v>134</v>
       </c>
       <c r="E75" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="F75" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G75">
         <v>300</v>
@@ -4826,25 +4014,19 @@
       <c r="J75">
         <v>1001</v>
       </c>
-      <c r="K75" t="s">
-        <v>262</v>
-      </c>
-      <c r="L75" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="76" spans="2:12">
+    </row>
+    <row r="76" spans="2:10">
       <c r="B76">
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c r="E76" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="F76" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G76">
         <v>300</v>
@@ -4858,25 +4040,19 @@
       <c r="J76">
         <v>1001</v>
       </c>
-      <c r="K76" t="s">
-        <v>265</v>
-      </c>
-      <c r="L76" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="77" spans="2:12">
+    </row>
+    <row r="77" spans="2:10">
       <c r="B77">
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>267</v>
+        <v>136</v>
       </c>
       <c r="E77" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="F77" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G77">
         <v>300</v>
@@ -4890,25 +4066,19 @@
       <c r="J77">
         <v>1001</v>
       </c>
-      <c r="K77" t="s">
-        <v>268</v>
-      </c>
-      <c r="L77" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="78" spans="2:12">
+    </row>
+    <row r="78" spans="2:10">
       <c r="B78">
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>270</v>
+        <v>137</v>
       </c>
       <c r="E78" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="F78" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G78">
         <v>300</v>
@@ -4922,25 +4092,19 @@
       <c r="J78">
         <v>1001</v>
       </c>
-      <c r="K78" t="s">
-        <v>271</v>
-      </c>
-      <c r="L78" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="79" spans="2:12">
+    </row>
+    <row r="79" spans="2:10">
       <c r="B79">
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>273</v>
+        <v>138</v>
       </c>
       <c r="E79" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="F79" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G79">
         <v>300</v>
@@ -4954,25 +4118,19 @@
       <c r="J79">
         <v>1001</v>
       </c>
-      <c r="K79" t="s">
-        <v>274</v>
-      </c>
-      <c r="L79" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="80" spans="2:12">
+    </row>
+    <row r="80" spans="2:10">
       <c r="B80">
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>276</v>
+        <v>139</v>
       </c>
       <c r="E80" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="F80" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G80">
         <v>300</v>
@@ -4986,25 +4144,19 @@
       <c r="J80">
         <v>1001</v>
       </c>
-      <c r="K80" t="s">
-        <v>277</v>
-      </c>
-      <c r="L80" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="81" spans="2:12">
+    </row>
+    <row r="81" spans="2:10">
       <c r="B81">
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>279</v>
+        <v>140</v>
       </c>
       <c r="E81" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="F81" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G81">
         <v>300</v>
@@ -5018,25 +4170,19 @@
       <c r="J81">
         <v>1001</v>
       </c>
-      <c r="K81" t="s">
-        <v>280</v>
-      </c>
-      <c r="L81" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="82" spans="2:12">
+    </row>
+    <row r="82" spans="2:10">
       <c r="B82">
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>282</v>
+        <v>141</v>
       </c>
       <c r="E82" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="F82" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G82">
         <v>300</v>
@@ -5050,25 +4196,19 @@
       <c r="J82">
         <v>1001</v>
       </c>
-      <c r="K82" t="s">
-        <v>283</v>
-      </c>
-      <c r="L82" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="83" spans="2:12">
+    </row>
+    <row r="83" spans="2:10">
       <c r="B83">
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>285</v>
+        <v>142</v>
       </c>
       <c r="E83" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="F83" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G83">
         <v>300</v>
@@ -5082,25 +4222,19 @@
       <c r="J83">
         <v>1001</v>
       </c>
-      <c r="K83" t="s">
-        <v>286</v>
-      </c>
-      <c r="L83" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="84" spans="2:12">
+    </row>
+    <row r="84" spans="2:10">
       <c r="B84">
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>288</v>
+        <v>143</v>
       </c>
       <c r="E84" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="F84" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G84">
         <v>300</v>
@@ -5113,12 +4247,6 @@
       </c>
       <c r="J84">
         <v>1001</v>
-      </c>
-      <c r="K84" t="s">
-        <v>289</v>
-      </c>
-      <c r="L84" t="s">
-        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -5130,38 +4258,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:I9"/>
+  <dimension ref="B2:I11"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="11.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D2" s="2"/>
+      <c r="C2" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="6">
+        <v>1</v>
+      </c>
       <c r="G2" s="2" t="s">
-        <v>292</v>
+        <v>145</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D3" s="2"/>
+      <c r="B3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="6">
+        <v>2</v>
+      </c>
       <c r="G3" s="2" t="s">
-        <v>294</v>
+        <v>147</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>41</v>
@@ -5169,86 +4301,120 @@
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D4" s="2"/>
+      <c r="B4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="6">
+        <v>3</v>
+      </c>
       <c r="G4" s="2" t="s">
-        <v>296</v>
+        <v>149</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D5" s="2"/>
+      <c r="B5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="6">
+        <v>4</v>
+      </c>
       <c r="G5" s="2" t="s">
-        <v>298</v>
+        <v>151</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>299</v>
+        <v>152</v>
       </c>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="B6" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="6">
+        <v>5</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>301</v>
+        <v>154</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>302</v>
+        <v>155</v>
       </c>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D7" s="2"/>
+      <c r="B7" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="6">
+        <v>6</v>
+      </c>
       <c r="G7" s="2" t="s">
-        <v>304</v>
+        <v>157</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>305</v>
+        <v>158</v>
       </c>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="B8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="6">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" s="2"/>
+      <c r="B9" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D9" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D10" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="6">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5289,49 +4455,49 @@
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3" t="s">
-        <v>308</v>
+        <v>165</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>309</v>
+        <v>166</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>310</v>
+        <v>167</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>311</v>
+        <v>168</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>312</v>
+        <v>169</v>
       </c>
       <c r="I1" t="s">
-        <v>313</v>
+        <v>170</v>
       </c>
       <c r="J1" t="s">
-        <v>314</v>
+        <v>171</v>
       </c>
       <c r="K1" t="s">
-        <v>315</v>
+        <v>172</v>
       </c>
       <c r="L1" t="s">
-        <v>316</v>
+        <v>173</v>
       </c>
       <c r="M1" t="s">
-        <v>317</v>
+        <v>174</v>
       </c>
       <c r="N1" t="s">
-        <v>318</v>
+        <v>175</v>
       </c>
       <c r="O1" t="s">
-        <v>319</v>
+        <v>176</v>
       </c>
       <c r="P1" t="s">
-        <v>320</v>
+        <v>177</v>
       </c>
       <c r="Q1" t="s">
-        <v>321</v>
+        <v>178</v>
       </c>
       <c r="R1" t="s">
-        <v>322</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -5396,10 +4562,10 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>323</v>
+        <v>180</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>323</v>
+        <v>180</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -5412,52 +4578,52 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>324</v>
+        <v>181</v>
       </c>
       <c r="D4" t="s">
-        <v>325</v>
+        <v>182</v>
       </c>
       <c r="E4" t="s">
-        <v>326</v>
+        <v>183</v>
       </c>
       <c r="F4" t="s">
-        <v>327</v>
+        <v>184</v>
       </c>
       <c r="G4" t="s">
-        <v>328</v>
+        <v>185</v>
       </c>
       <c r="H4" t="s">
-        <v>329</v>
+        <v>186</v>
       </c>
       <c r="I4" t="s">
-        <v>330</v>
+        <v>187</v>
       </c>
       <c r="J4" t="s">
-        <v>331</v>
+        <v>188</v>
       </c>
       <c r="K4" t="s">
-        <v>332</v>
+        <v>189</v>
       </c>
       <c r="L4" t="s">
-        <v>333</v>
+        <v>190</v>
       </c>
       <c r="M4" t="s">
-        <v>334</v>
+        <v>191</v>
       </c>
       <c r="N4" t="s">
-        <v>335</v>
+        <v>192</v>
       </c>
       <c r="O4" t="s">
-        <v>336</v>
+        <v>193</v>
       </c>
       <c r="P4" t="s">
-        <v>337</v>
+        <v>194</v>
       </c>
       <c r="Q4" t="s">
-        <v>338</v>
+        <v>195</v>
       </c>
       <c r="R4" t="s">
-        <v>339</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -5465,52 +4631,52 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>340</v>
+        <v>197</v>
       </c>
       <c r="D5" t="s">
-        <v>341</v>
+        <v>198</v>
       </c>
       <c r="E5" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="F5" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="G5" t="s">
-        <v>344</v>
+        <v>201</v>
       </c>
       <c r="H5" t="s">
-        <v>345</v>
+        <v>202</v>
       </c>
       <c r="I5" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="J5" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="K5" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="L5" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="M5" t="s">
-        <v>349</v>
+        <v>206</v>
       </c>
       <c r="N5" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="O5" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="P5" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="Q5" t="s">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="R5" t="s">
-        <v>353</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -5521,49 +4687,49 @@
         <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>354</v>
+        <v>211</v>
       </c>
       <c r="E6" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="F6" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="G6" t="s">
-        <v>355</v>
+        <v>212</v>
       </c>
       <c r="H6" t="s">
-        <v>345</v>
+        <v>202</v>
       </c>
       <c r="I6" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="J6" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="K6" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="L6" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="M6" t="s">
-        <v>349</v>
+        <v>206</v>
       </c>
       <c r="N6" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="O6" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="P6" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="Q6" t="s">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="R6" t="s">
-        <v>353</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -5571,52 +4737,50 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>356</v>
+        <v>213</v>
       </c>
       <c r="E7" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="F7" t="s">
-        <v>351</v>
-      </c>
-      <c r="G7" t="s">
-        <v>357</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="G7"/>
       <c r="H7" t="s">
-        <v>345</v>
+        <v>202</v>
       </c>
       <c r="I7" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="J7" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="K7" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="L7" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="M7" t="s">
-        <v>349</v>
+        <v>206</v>
       </c>
       <c r="N7" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="O7" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="P7" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="Q7" t="s">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="R7" t="s">
-        <v>353</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -5624,52 +4788,50 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>358</v>
+        <v>214</v>
       </c>
       <c r="E8" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="F8" t="s">
-        <v>349</v>
-      </c>
-      <c r="G8" t="s">
-        <v>359</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="G8"/>
       <c r="H8" t="s">
-        <v>345</v>
+        <v>202</v>
       </c>
       <c r="I8" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="J8" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="K8" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="L8" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="M8" t="s">
-        <v>349</v>
+        <v>206</v>
       </c>
       <c r="N8" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="O8" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="P8" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="Q8" t="s">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="R8" t="s">
-        <v>353</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -5677,52 +4839,50 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>360</v>
+        <v>215</v>
       </c>
       <c r="E9" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="F9" t="s">
-        <v>351</v>
-      </c>
-      <c r="G9" t="s">
-        <v>344</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="G9"/>
       <c r="H9" t="s">
-        <v>361</v>
+        <v>216</v>
       </c>
       <c r="I9" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="J9" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="K9" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="L9" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="M9" t="s">
-        <v>349</v>
+        <v>206</v>
       </c>
       <c r="N9" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="O9" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="P9" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="Q9" t="s">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="R9" t="s">
-        <v>353</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -5730,52 +4890,50 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>362</v>
+        <v>217</v>
       </c>
       <c r="E10" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="F10" t="s">
-        <v>343</v>
-      </c>
-      <c r="G10" t="s">
-        <v>344</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G10"/>
       <c r="H10" t="s">
-        <v>363</v>
+        <v>218</v>
       </c>
       <c r="I10" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="J10" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="K10" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="L10" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="M10" t="s">
-        <v>349</v>
+        <v>206</v>
       </c>
       <c r="N10" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="O10" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="P10" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="Q10" t="s">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="R10" t="s">
-        <v>353</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -5783,52 +4941,50 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>364</v>
+        <v>219</v>
       </c>
       <c r="E11" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="F11" t="s">
-        <v>353</v>
-      </c>
-      <c r="G11" t="s">
-        <v>355</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="G11"/>
       <c r="H11" t="s">
-        <v>361</v>
+        <v>216</v>
       </c>
       <c r="I11" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="J11" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="K11" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="L11" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="M11" t="s">
-        <v>349</v>
+        <v>206</v>
       </c>
       <c r="N11" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="O11" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="P11" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="Q11" t="s">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="R11" t="s">
-        <v>353</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -5836,52 +4992,50 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>365</v>
+        <v>220</v>
       </c>
       <c r="E12" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="F12" t="s">
-        <v>343</v>
-      </c>
-      <c r="G12" t="s">
-        <v>355</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G12"/>
       <c r="H12" t="s">
-        <v>363</v>
+        <v>218</v>
       </c>
       <c r="I12" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="J12" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="K12" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="L12" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="M12" t="s">
-        <v>349</v>
+        <v>206</v>
       </c>
       <c r="N12" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="O12" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="P12" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="Q12" t="s">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="R12" t="s">
-        <v>353</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -5889,52 +5043,50 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>366</v>
+        <v>221</v>
       </c>
       <c r="E13" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="F13" t="s">
-        <v>353</v>
-      </c>
-      <c r="G13" t="s">
-        <v>357</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="G13"/>
       <c r="H13" t="s">
-        <v>361</v>
+        <v>216</v>
       </c>
       <c r="I13" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="J13" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="K13" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="L13" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="M13" t="s">
-        <v>349</v>
+        <v>206</v>
       </c>
       <c r="N13" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="O13" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="P13" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="Q13" t="s">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="R13" t="s">
-        <v>353</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -5942,52 +5094,50 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>367</v>
+        <v>222</v>
       </c>
       <c r="E14" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="F14" t="s">
-        <v>343</v>
-      </c>
-      <c r="G14" t="s">
-        <v>357</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G14"/>
       <c r="H14" t="s">
-        <v>363</v>
+        <v>218</v>
       </c>
       <c r="I14" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="J14" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="K14" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="L14" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="M14" t="s">
-        <v>349</v>
+        <v>206</v>
       </c>
       <c r="N14" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="O14" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="P14" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="Q14" t="s">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="R14" t="s">
-        <v>353</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -5995,52 +5145,50 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>368</v>
+        <v>223</v>
       </c>
       <c r="E15" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="F15" t="s">
-        <v>343</v>
-      </c>
-      <c r="G15" t="s">
-        <v>359</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G15"/>
       <c r="H15" t="s">
-        <v>361</v>
+        <v>216</v>
       </c>
       <c r="I15" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="J15" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="K15" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="L15" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="M15" t="s">
-        <v>349</v>
+        <v>206</v>
       </c>
       <c r="N15" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="O15" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="P15" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="Q15" t="s">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="R15" t="s">
-        <v>353</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -6048,52 +5196,50 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>369</v>
+        <v>224</v>
       </c>
       <c r="D16" t="s">
-        <v>370</v>
+        <v>225</v>
       </c>
       <c r="E16" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="F16" t="s">
-        <v>352</v>
-      </c>
-      <c r="G16" t="s">
-        <v>359</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="G16"/>
       <c r="H16" t="s">
-        <v>363</v>
+        <v>218</v>
       </c>
       <c r="I16" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="J16" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="K16" t="s">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="L16" t="s">
-        <v>348</v>
+        <v>205</v>
       </c>
       <c r="M16" t="s">
-        <v>349</v>
+        <v>206</v>
       </c>
       <c r="N16" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="O16" t="s">
-        <v>350</v>
+        <v>207</v>
       </c>
       <c r="P16" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="Q16" t="s">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="R16" t="s">
-        <v>353</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -6121,10 +5267,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>371</v>
+        <v>226</v>
       </c>
       <c r="D1" t="s">
-        <v>372</v>
+        <v>227</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
@@ -6138,7 +5284,7 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>373</v>
+        <v>228</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -6155,10 +5301,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>374</v>
+        <v>229</v>
       </c>
       <c r="D3" t="s">
-        <v>375</v>
+        <v>230</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>36</v>
@@ -6254,7 +5400,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>231</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>19</v>
@@ -6270,39 +5416,39 @@
     <row r="2" spans="1:5">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>377</v>
+        <v>232</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>378</v>
+        <v>233</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>379</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>380</v>
+        <v>235</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>381</v>
+        <v>236</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>382</v>
+        <v>237</v>
       </c>
       <c r="D3" s="3">
         <v>0.5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>383</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>384</v>
+        <v>239</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>385</v>
+        <v>240</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
@@ -6311,7 +5457,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>386</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:5">

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="DogSkin" sheetId="2" r:id="rId3"/>
     <sheet name="BlindBox" sheetId="4" r:id="rId4"/>
     <sheet name="GameDevelopConfig" sheetId="5" r:id="rId5"/>
+    <sheet name="PayTable" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="587">
   <si>
     <t>##var</t>
   </si>
@@ -54,7 +55,13 @@
     <t>BlindBoxWeight</t>
   </si>
   <si>
-    <t>isUnique</t>
+    <t>IsUnique</t>
+  </si>
+  <si>
+    <t>HiddenRegionFlag</t>
+  </si>
+  <si>
+    <t>SafeResourceId</t>
   </si>
   <si>
     <t>BlindBoxId</t>
@@ -87,6 +94,9 @@
     <t>bool</t>
   </si>
   <si>
+    <t>EHiddenRegionFlag</t>
+  </si>
+  <si>
     <t>list,string</t>
   </si>
   <si>
@@ -99,7 +109,16 @@
     <t>排序权重，数字越大约靠前</t>
   </si>
   <si>
+    <t>盲盒权重</t>
+  </si>
+  <si>
     <t>非唯一的物品可以重复获得</t>
+  </si>
+  <si>
+    <t>在哪些国家无法抽到</t>
+  </si>
+  <si>
+    <t>直播模式或者安全模式开启状态下，需要替换成和谐资源，该替换规则高于国家规则</t>
   </si>
   <si>
     <t>所属盲盒的id，相同id的物品在同一个组里进行随机</t>
@@ -133,12 +152,12 @@
     <t>排序权重</t>
   </si>
   <si>
-    <t>盲盒权重</t>
-  </si>
-  <si>
     <t>是否唯一</t>
   </si>
   <si>
+    <t>安全替换资源id</t>
+  </si>
+  <si>
     <t>随机组id</t>
   </si>
   <si>
@@ -151,6 +170,9 @@
     <t>皮肤id</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>Red</t>
   </si>
   <si>
@@ -175,18 +197,36 @@
     <t>黑柴</t>
   </si>
   <si>
+    <t>v1\Assets\Shiba\Black\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Black.png</t>
+  </si>
+  <si>
     <t>Cream</t>
   </si>
   <si>
     <t>白柴</t>
   </si>
   <si>
+    <t>v1\Assets\Shiba\Cream\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Cream.png</t>
+  </si>
+  <si>
     <t>Sesame</t>
   </si>
   <si>
     <t>胡麻柴</t>
   </si>
   <si>
+    <t>v1\Assets\Shiba\Sesame\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Sesame.png</t>
+  </si>
+  <si>
     <t>Thin Red</t>
   </si>
   <si>
@@ -196,51 +236,78 @@
     <t>传说</t>
   </si>
   <si>
+    <t>v1\ItemIcon\Shiba_ThinRed.png</t>
+  </si>
+  <si>
     <t>Unshaven Red</t>
   </si>
   <si>
     <t>胡渣赤柴</t>
   </si>
   <si>
+    <t>v1\ItemIcon\Shiba_UnshavenRed.png</t>
+  </si>
+  <si>
     <t>Thin Black</t>
   </si>
   <si>
     <t>瘦黑柴</t>
   </si>
   <si>
+    <t>v1\ItemIcon\Shiba_ThinBlack.png</t>
+  </si>
+  <si>
     <t>Unshaven Black</t>
   </si>
   <si>
     <t>胡渣黑柴</t>
   </si>
   <si>
+    <t>v1\ItemIcon\Shiba_UnshavenBlack.png</t>
+  </si>
+  <si>
     <t>Thin Cream</t>
   </si>
   <si>
     <t>瘦白柴</t>
   </si>
   <si>
+    <t>v1\ItemIcon\Shiba_ThinCream.png</t>
+  </si>
+  <si>
     <t>Unshaven Cream</t>
   </si>
   <si>
     <t>胡渣白柴</t>
   </si>
   <si>
+    <t>v1\ItemIcon\Shiba_UnshavenCream.png</t>
+  </si>
+  <si>
     <t>Thin Sesame</t>
   </si>
   <si>
     <t>瘦芝麻柴</t>
   </si>
   <si>
+    <t>v1\ItemIcon\Shiba_ThinSesame.png</t>
+  </si>
+  <si>
     <t>Unshaven Sesame</t>
   </si>
   <si>
     <t>胡渣芝麻柴</t>
   </si>
   <si>
+    <t>v1\ItemIcon\Shiba_UnshavenSesame.png</t>
+  </si>
+  <si>
     <t>Green Beret</t>
   </si>
   <si>
+    <t>绿色贝雷帽</t>
+  </si>
+  <si>
     <t>Headwear</t>
   </si>
   <si>
@@ -256,244 +323,1048 @@
     <t>Red Beret</t>
   </si>
   <si>
+    <t>红色贝雷帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\Beret_Red.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_Beret_Red.png</t>
+  </si>
+  <si>
     <t>Gray Fedora Hat</t>
   </si>
   <si>
+    <t>灰色软呢帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\FedoraHat_Gray.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_FedoraHat_Gray.png</t>
+  </si>
+  <si>
     <t>Maroon Fedora Hat</t>
   </si>
   <si>
+    <t>栗色软呢帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\FedoraHat_Maroon.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_FedoraHat_Maroon.png</t>
+  </si>
+  <si>
     <t>Hole</t>
   </si>
   <si>
+    <t>洞洞帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\Hole.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_Hole.png</t>
+  </si>
+  <si>
     <t>Lucky</t>
   </si>
   <si>
+    <t>幸运帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\Lucky.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_Lucky.png</t>
+  </si>
+  <si>
     <t>Black Magic Hat</t>
   </si>
   <si>
+    <t>黑色魔术帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\MagicHat_Black.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_MagicHat_Black.png</t>
+  </si>
+  <si>
     <t>White Magic Hat</t>
   </si>
   <si>
+    <t>白色魔术帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\MagicHat_White.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_MagicHat_White.png</t>
+  </si>
+  <si>
     <t>Beige Sun Hat</t>
   </si>
   <si>
+    <t>米色太阳帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\SunHat_Beige.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_SunHat_Beige.png</t>
+  </si>
+  <si>
     <t>Blue Sun Hat</t>
   </si>
   <si>
+    <t>蓝色太阳帽</t>
+  </si>
+  <si>
+    <t>v1\Headwear\SunHat_Blue.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Headwear_SunHat_Blue.png</t>
+  </si>
+  <si>
     <t>3D Glasses</t>
   </si>
   <si>
+    <t>3D眼镜</t>
+  </si>
+  <si>
     <t>Eyewear</t>
   </si>
   <si>
+    <t>v1\Eyewear\3DGlasses.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Eyewear_3DGlasses.png</t>
+  </si>
+  <si>
     <t>Eye Patch</t>
   </si>
   <si>
+    <t>海盗眼罩</t>
+  </si>
+  <si>
+    <t>v1\Eyewear\EyePatch.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Eyewear_EyePatch.png</t>
+  </si>
+  <si>
     <t>Black Monocle</t>
   </si>
   <si>
+    <t>黑色单片镜</t>
+  </si>
+  <si>
+    <t>v1\Eyewear\Monocle_black.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Eyewear_Monocle_black.png</t>
+  </si>
+  <si>
     <t>Golden Monocle</t>
   </si>
   <si>
+    <t>金色单片镜</t>
+  </si>
+  <si>
+    <t>v1\Eyewear\Monocle_golden.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Eyewear_Monocle_golden.png</t>
+  </si>
+  <si>
     <t>Blade Sunglasses</t>
   </si>
   <si>
+    <t>刀锋墨镜</t>
+  </si>
+  <si>
+    <t>v1\Eyewear\Sunglasses_Blade.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Eyewear_Sunglasses_Blade.png</t>
+  </si>
+  <si>
     <t>Male A</t>
   </si>
   <si>
+    <t>男性手臂A</t>
+  </si>
+  <si>
     <t>Arm</t>
   </si>
   <si>
+    <t>全球</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\MaleA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Hand_MaleA.png</t>
+  </si>
+  <si>
     <t>Male B</t>
   </si>
   <si>
+    <t>男性手臂B</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\MaleB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Hand_MaleB.png</t>
+  </si>
+  <si>
     <t>Male C</t>
   </si>
   <si>
+    <t>男性手臂C</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\MaleC.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Hand_MaleC.png</t>
+  </si>
+  <si>
     <t>Male D</t>
   </si>
   <si>
+    <t>男性手臂D</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\MaleD.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Hand_MaleD.png</t>
+  </si>
+  <si>
     <t>Baseball Jacket Black</t>
   </si>
   <si>
+    <t>黑色棒球夹克</t>
+  </si>
+  <si>
     <t>Clothes</t>
   </si>
   <si>
+    <t>v1\Player\Clothes\BaseballJacket_Black.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_BaseballJacket_Black.png</t>
+  </si>
+  <si>
     <t>Baseball Jacket Purple</t>
   </si>
   <si>
+    <t>紫色棒球夹克</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\BaseballJacket_Purple.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_BaseballJacket_Purple.png</t>
+  </si>
+  <si>
     <t>Black Business Suit</t>
   </si>
   <si>
+    <t>黑色西装</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\BlackBusinessSuit_Black.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_BlackBusinessSuit_Black.png</t>
+  </si>
+  <si>
     <t>Blue Shirt</t>
   </si>
   <si>
+    <t>蓝色衬衫</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\BlueShirt_Cyan.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_BlueShirt_Cyan.png</t>
+  </si>
+  <si>
     <t>Blue Striped Shirt</t>
   </si>
   <si>
+    <t>蓝色条纹衬衫</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\BlueStripedShirt_RegattaStripe.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_BlueStripedShirt_RegattaStripe.png</t>
+  </si>
+  <si>
     <t>Cream Shirt</t>
   </si>
   <si>
+    <t>米色衬衫</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\CreamShirt_Beige.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_CreamShirt_Beige.png</t>
+  </si>
+  <si>
     <t>White Business Suit</t>
   </si>
   <si>
+    <t>白色西装</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\WhiteBusinessSuit_LightGray.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_WhiteBusinessSuit_LightGray.png</t>
+  </si>
+  <si>
     <t>White Shirt</t>
   </si>
   <si>
+    <t>白色衬衫</t>
+  </si>
+  <si>
+    <t>v1\Player\Clothes\WhiteShirt_White.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Clothes_WhiteShirt_White.png</t>
+  </si>
+  <si>
     <t>Felt Emerald</t>
   </si>
   <si>
+    <t>翡翠绿桌布</t>
+  </si>
+  <si>
     <t>Table</t>
   </si>
   <si>
+    <t>v1\Table\FeltEmerald.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_FeltEmerald.png</t>
+  </si>
+  <si>
     <t>Full Tilt Like</t>
   </si>
   <si>
+    <t>Full Tilt风格</t>
+  </si>
+  <si>
+    <t>v1\Table\FullTiltLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_FullTiltLike.png</t>
+  </si>
+  <si>
     <t>Hustler Like</t>
   </si>
   <si>
+    <t>Hustler风格</t>
+  </si>
+  <si>
+    <t>v1\Table\HustlerLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_HustlerLike.png</t>
+  </si>
+  <si>
     <t>Les Ambassadeurs Like</t>
   </si>
   <si>
+    <t>Les Ambassadeurs风格</t>
+  </si>
+  <si>
+    <t>v1\Table\LesAmbassadeursLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_LesAmbassadeursLike.png</t>
+  </si>
+  <si>
     <t>Maestral Like</t>
   </si>
   <si>
+    <t>Maestral风格</t>
+  </si>
+  <si>
+    <t>v1\Table\MaestralLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_MaestralLike.png</t>
+  </si>
+  <si>
     <t>Mezcal Like</t>
   </si>
   <si>
+    <t>Mezcal风格</t>
+  </si>
+  <si>
+    <t>v1\Table\MezcalLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_MezcalLike.png</t>
+  </si>
+  <si>
     <t>Poker Go Like</t>
   </si>
   <si>
+    <t>Poker Go风格</t>
+  </si>
+  <si>
+    <t>v1\Table\PokerGoLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_PokerGoLike.png</t>
+  </si>
+  <si>
     <t>Pure Indigo</t>
   </si>
   <si>
+    <t>纯靛蓝</t>
+  </si>
+  <si>
+    <t>v1\Table\PureIndigo.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_PureIndigo.png</t>
+  </si>
+  <si>
     <t>Pure Purple</t>
   </si>
   <si>
+    <t>纯紫色</t>
+  </si>
+  <si>
+    <t>v1\Table\PurePurple.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_PurePurple.png</t>
+  </si>
+  <si>
     <t>Pure Teal</t>
   </si>
   <si>
+    <t>纯青色</t>
+  </si>
+  <si>
+    <t>v1\Table\PureTeal.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_PureTeal.png</t>
+  </si>
+  <si>
     <t>The King of Hill Like</t>
   </si>
   <si>
+    <t>King of Hill风格</t>
+  </si>
+  <si>
+    <t>v1\Table\TheKingOfHillLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Table_TheKingOfHillLike.png</t>
+  </si>
+  <si>
     <t>Blue A</t>
   </si>
   <si>
+    <t>蓝色A</t>
+  </si>
+  <si>
     <t>Background</t>
   </si>
   <si>
+    <t>v1\Background\BlueA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_BlueA.png</t>
+  </si>
+  <si>
     <t>Brown A</t>
   </si>
   <si>
+    <t>棕色A</t>
+  </si>
+  <si>
+    <t>v1\Background\BrownA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_BrownA.png</t>
+  </si>
+  <si>
     <t>Brown B</t>
   </si>
   <si>
+    <t>棕色B</t>
+  </si>
+  <si>
+    <t>v1\Background\BrownB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_BrownB.png</t>
+  </si>
+  <si>
     <t>Gray A</t>
   </si>
   <si>
+    <t>灰色A</t>
+  </si>
+  <si>
+    <t>v1\Background\GrayA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_GrayA.png</t>
+  </si>
+  <si>
     <t>Gray B</t>
   </si>
   <si>
+    <t>灰色B</t>
+  </si>
+  <si>
+    <t>v1\Background\GrayB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_GrayB.png</t>
+  </si>
+  <si>
     <t>Green A</t>
   </si>
   <si>
+    <t>绿色A</t>
+  </si>
+  <si>
+    <t>v1\Background\GreenA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_GreenA.png</t>
+  </si>
+  <si>
     <t>Green B</t>
   </si>
   <si>
+    <t>绿色B</t>
+  </si>
+  <si>
+    <t>v1\Background\GreenB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_GreenB.png</t>
+  </si>
+  <si>
     <t>Highstakes Poker Like</t>
   </si>
   <si>
+    <t>Highstakes Poker风格</t>
+  </si>
+  <si>
+    <t>v1\Background\HighstakesPokerLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_HighstakesPokerLike.png</t>
+  </si>
+  <si>
     <t>Orange A</t>
   </si>
   <si>
+    <t>橙色A</t>
+  </si>
+  <si>
+    <t>v1\Background\OrangeA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_OrangeA.png</t>
+  </si>
+  <si>
     <t>Part Poker Like</t>
   </si>
   <si>
+    <t>Part Poker风格</t>
+  </si>
+  <si>
+    <t>v1\Background\PartPokerLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_PartPokerLike.png</t>
+  </si>
+  <si>
     <t>Pink A</t>
   </si>
   <si>
+    <t>粉色A</t>
+  </si>
+  <si>
+    <t>v1\Background\PinkA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_PinkA.png</t>
+  </si>
+  <si>
     <t>Poker King Like</t>
   </si>
   <si>
+    <t>Poker King风格</t>
+  </si>
+  <si>
+    <t>v1\Background\PokerKingLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_PokerKingLike.png</t>
+  </si>
+  <si>
     <t>Purple A</t>
   </si>
   <si>
+    <t>紫色A</t>
+  </si>
+  <si>
+    <t>v1\Background\PurpleA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_PurpleA.png</t>
+  </si>
+  <si>
     <t>Red A</t>
   </si>
   <si>
+    <t>红色A</t>
+  </si>
+  <si>
+    <t>v1\Background\RedA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_RedA.png</t>
+  </si>
+  <si>
     <t>Red B</t>
   </si>
   <si>
+    <t>红色B</t>
+  </si>
+  <si>
+    <t>v1\Background\RedB.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_RedB.png</t>
+  </si>
+  <si>
     <t>Twitter Blue</t>
   </si>
   <si>
+    <t>Twitter蓝</t>
+  </si>
+  <si>
+    <t>v1\Background\TwitterBlue.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_TwitterBlue.png</t>
+  </si>
+  <si>
     <t>World Poker Tour Like</t>
   </si>
   <si>
+    <t>World Poker Tour风格</t>
+  </si>
+  <si>
+    <t>v1\Background\WorldPokerTourtLike.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_WorldPokerTourtLike.png</t>
+  </si>
+  <si>
     <t>Yellow A</t>
   </si>
   <si>
+    <t>黄色A</t>
+  </si>
+  <si>
+    <t>v1\Background\YellowA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Background_YellowA.png</t>
+  </si>
+  <si>
     <t>A158UUA</t>
   </si>
   <si>
     <t>Accessory</t>
   </si>
   <si>
+    <t>v1\Player\Accessory\A158UUA.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_A158UUA.png</t>
+  </si>
+  <si>
     <t>Anchor Tattoo</t>
   </si>
   <si>
+    <t>锚纹身</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\AnchorTattoo.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_AnchorTattoo.png</t>
+  </si>
+  <si>
     <t>F91UU</t>
   </si>
   <si>
+    <t>v1\Player\Accessory\F91UU.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_F91UU.png</t>
+  </si>
+  <si>
     <t>Feng Shui Bracelet</t>
   </si>
   <si>
+    <t>风水手链</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\FengShuiBracelet.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_FengShuiBracelet.png</t>
+  </si>
+  <si>
     <t>Good Luck Bracelet</t>
   </si>
   <si>
+    <t>好运手链</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\GoodLuckBracelet.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_GoodLuckBracelet.png</t>
+  </si>
+  <si>
     <t>Hair</t>
   </si>
   <si>
+    <t>体毛</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\Hair.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_Hair.png</t>
+  </si>
+  <si>
     <t>Relax Driver Black</t>
   </si>
   <si>
+    <t>黑色Relax Driver</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\RelaxDriver_Black.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_RelaxDriver_Black.png</t>
+  </si>
+  <si>
     <t>Relax Driver Green</t>
   </si>
   <si>
+    <t>绿色Relax Driver</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\RelaxDriver_Green.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_RelaxDriver_Green.png</t>
+  </si>
+  <si>
     <t>Text Wristband Green</t>
   </si>
   <si>
+    <t>绿色文字腕带</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\TextWristband_Green.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_TextWristband_Green.png</t>
+  </si>
+  <si>
     <t>Text Wristband Red</t>
   </si>
   <si>
+    <t>红色文字腕带</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\TextWristband_Red.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_TextWristband_Red.png</t>
+  </si>
+  <si>
     <t>WSOP Gold Bracelet</t>
   </si>
   <si>
+    <t>WSOP金手链</t>
+  </si>
+  <si>
+    <t>v1\Player\Accessory\WSOPGoldBracelet.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Accessory_WSOPGoldBracelet.png</t>
+  </si>
+  <si>
+    <t>Black Tea</t>
+  </si>
+  <si>
+    <t>红茶</t>
+  </si>
+  <si>
+    <t>Treat</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>v1\Treat\BlackTea.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_BlackTea.png</t>
+  </si>
+  <si>
+    <t>Bordeaux</t>
+  </si>
+  <si>
+    <t>波尔多</t>
+  </si>
+  <si>
+    <t>沙特阿拉伯,阿联酋,马来西亚,印尼</t>
+  </si>
+  <si>
+    <t>v1\Treat\Bordeaux.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Bordeaux.png</t>
+  </si>
+  <si>
+    <t>一些国家不允许饮酒，替换成水</t>
+  </si>
+  <si>
+    <t>Burgundy</t>
+  </si>
+  <si>
+    <t>勃艮第</t>
+  </si>
+  <si>
+    <t>v1\Treat\Burgundy.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Burgundy.png</t>
+  </si>
+  <si>
+    <t>Chardonnay</t>
+  </si>
+  <si>
+    <t>霞多丽</t>
+  </si>
+  <si>
+    <t>v1\Treat\Chardonnay.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Chardonnay.png</t>
+  </si>
+  <si>
+    <t>Shot Glass</t>
+  </si>
+  <si>
+    <t>子弹杯</t>
+  </si>
+  <si>
+    <t>v1\Treat\ShotGlass.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_ShotGlass.png</t>
+  </si>
+  <si>
+    <t>Tulip</t>
+  </si>
+  <si>
+    <t>郁金香杯</t>
+  </si>
+  <si>
+    <t>v1\Treat\Tulip.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Tulip.png</t>
+  </si>
+  <si>
+    <t>Tumbler</t>
+  </si>
+  <si>
+    <t>平底杯</t>
+  </si>
+  <si>
+    <t>v1\Treat\Tumbler.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Tumbler.png</t>
+  </si>
+  <si>
+    <t>Vintage</t>
+  </si>
+  <si>
+    <t>年份酒</t>
+  </si>
+  <si>
+    <t>v1\Treat\Vintage.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Vintage.png</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>凉白开</t>
+  </si>
+  <si>
+    <t>v1\Treat\Water.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Water.png</t>
+  </si>
+  <si>
+    <t>Whisky</t>
+  </si>
+  <si>
+    <t>威士忌</t>
+  </si>
+  <si>
+    <t>v1\Treat\Whisky.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_Whisky.png</t>
+  </si>
+  <si>
+    <t>Whisky Cigar</t>
+  </si>
+  <si>
+    <t>威士忌雪茄</t>
+  </si>
+  <si>
+    <t>v1\Treat\WhiskyCagar.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Treat_WhiskyCagar.png</t>
+  </si>
+  <si>
+    <t>Basic Card Back</t>
+  </si>
+  <si>
+    <t>基础背</t>
+  </si>
+  <si>
+    <t>CardBack</t>
+  </si>
+  <si>
+    <t>v1\Card\CardBack\Basic.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\CardBack_Basic.png</t>
+  </si>
+  <si>
+    <t>Kibble Card Face</t>
+  </si>
+  <si>
+    <t>狗粮卡面</t>
+  </si>
+  <si>
+    <t>CardFace</t>
+  </si>
+  <si>
+    <t>v1\Card\CardFace\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\CardFace_Classic.png</t>
+  </si>
+  <si>
+    <t>开发阶段先临时用经典卡面</t>
+  </si>
+  <si>
+    <t>Classic Card Face</t>
+  </si>
+  <si>
+    <t>经典卡面</t>
+  </si>
+  <si>
     <t>小狗本体</t>
   </si>
   <si>
     <t>Legendary</t>
   </si>
   <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>在全部国家隐藏</t>
+  </si>
+  <si>
     <t>小狗头部装饰</t>
   </si>
   <si>
     <t>Epic</t>
   </si>
   <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>沙特阿拉伯</t>
+  </si>
+  <si>
+    <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
+  </si>
+  <si>
     <t>小狗眼部装饰</t>
   </si>
   <si>
     <t>Rare</t>
   </si>
   <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>阿联酋</t>
+  </si>
+  <si>
+    <t>United Arab Emirates赌博/宗教/酒精/色情</t>
+  </si>
+  <si>
     <t>手臂层的装饰</t>
   </si>
   <si>
     <t>Common</t>
   </si>
   <si>
-    <t>普通</t>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>伊朗</t>
+  </si>
+  <si>
+    <t>Iran宗教/进化论/赌博/政治/西方文化</t>
   </si>
   <si>
     <t>玩家手臂衣服</t>
@@ -505,6 +1376,15 @@
     <t>特殊1</t>
   </si>
   <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>巴基斯坦</t>
+  </si>
+  <si>
+    <t>Pakistan国家形象/政治</t>
+  </si>
+  <si>
     <t>桌布</t>
   </si>
   <si>
@@ -514,24 +1394,81 @@
     <t>特殊2</t>
   </si>
   <si>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>马来西亚</t>
+  </si>
+  <si>
+    <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
+  </si>
+  <si>
     <t>背景</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>印尼</t>
+  </si>
+  <si>
+    <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
+  </si>
+  <si>
     <t>玩家手部装饰</t>
   </si>
   <si>
-    <t>Treat</t>
+    <t>RU</t>
+  </si>
+  <si>
+    <t>俄罗斯</t>
+  </si>
+  <si>
+    <t>Russia赌博/LGBTQ/极端主义</t>
   </si>
   <si>
     <t>玩家嗜好品</t>
   </si>
   <si>
-    <t>CardBack</t>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>中国</t>
+  </si>
+  <si>
+    <t>China赌博/暴力/血腥/色情</t>
   </si>
   <si>
     <t>卡牌背面</t>
   </si>
   <si>
+    <t>KP</t>
+  </si>
+  <si>
+    <t>朝鲜</t>
+  </si>
+  <si>
+    <t>North Korea国际制裁/政治</t>
+  </si>
+  <si>
+    <t>SY</t>
+  </si>
+  <si>
+    <t>叙利亚</t>
+  </si>
+  <si>
+    <t>Syria国际制裁/政治/宗教</t>
+  </si>
+  <si>
+    <t>CU</t>
+  </si>
+  <si>
+    <t>古巴</t>
+  </si>
+  <si>
+    <t>Cuba国际制裁/政治</t>
+  </si>
+  <si>
     <t>IconName</t>
   </si>
   <si>
@@ -679,9 +1616,15 @@
     <t>Shiba_Cream.png</t>
   </si>
   <si>
+    <t>v1\Shiba\Cream</t>
+  </si>
+  <si>
     <t>Shiba_Sesame.png</t>
   </si>
   <si>
+    <t>v1\Shiba\Sesame</t>
+  </si>
+  <si>
     <t>Shiba_ThinRed.png</t>
   </si>
   <si>
@@ -742,25 +1685,118 @@
     <t>描述</t>
   </si>
   <si>
-    <t>GoldInheritanceRatio</t>
-  </si>
-  <si>
-    <t>金币继承比例</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>旅程失败时保留的金币比例</t>
-  </si>
-  <si>
-    <t>DrawCountPerTurn</t>
-  </si>
-  <si>
-    <t>每回合抽牌数</t>
-  </si>
-  <si>
-    <t>抽牌阶段从牌库抽取的张数</t>
+    <t>IsSafeMode</t>
+  </si>
+  <si>
+    <t>直播模式</t>
+  </si>
+  <si>
+    <t>直播模式下/安全模式下，某些图片资源会背替换成和谐版，例如烟酒</t>
+  </si>
+  <si>
+    <t>PayoutMultiplier</t>
+  </si>
+  <si>
+    <t>OriginalName</t>
+  </si>
+  <si>
+    <t>SafeName_EN</t>
+  </si>
+  <si>
+    <t>SafeName_CN</t>
+  </si>
+  <si>
+    <t>赔率</t>
+  </si>
+  <si>
+    <t>原始名称</t>
+  </si>
+  <si>
+    <t>安全英文</t>
+  </si>
+  <si>
+    <t>安全中文</t>
+  </si>
+  <si>
+    <t>Jacks or Better</t>
+  </si>
+  <si>
+    <t>Top Dogs</t>
+  </si>
+  <si>
+    <t>好犬优选</t>
+  </si>
+  <si>
+    <t>Two Pair</t>
+  </si>
+  <si>
+    <t>Twin Pairs</t>
+  </si>
+  <si>
+    <t>双犬配对</t>
+  </si>
+  <si>
+    <t>Three of a Kind</t>
+  </si>
+  <si>
+    <t>Triple Pals</t>
+  </si>
+  <si>
+    <t>三犬同行</t>
+  </si>
+  <si>
+    <t>Straight</t>
+  </si>
+  <si>
+    <t>Chain Walk</t>
+  </si>
+  <si>
+    <t>顺位犬链</t>
+  </si>
+  <si>
+    <t>Flush</t>
+  </si>
+  <si>
+    <t>Matching Den</t>
+  </si>
+  <si>
+    <t>同色犬舍</t>
+  </si>
+  <si>
+    <t>Full House</t>
+  </si>
+  <si>
+    <t>Puppy Party</t>
+  </si>
+  <si>
+    <t>狗狗满堂</t>
+  </si>
+  <si>
+    <t>Four of a Kind</t>
+  </si>
+  <si>
+    <t>Dog Squad</t>
+  </si>
+  <si>
+    <t>四犬成团</t>
+  </si>
+  <si>
+    <t>Straight Flush</t>
+  </si>
+  <si>
+    <t>Purebred Strike</t>
+  </si>
+  <si>
+    <t>纯种犬连击</t>
+  </si>
+  <si>
+    <t>Royal Flush</t>
+  </si>
+  <si>
+    <t>Royal Feast</t>
+  </si>
+  <si>
+    <t>皇家狗粮</t>
   </si>
 </sst>
 </file>
@@ -1381,14 +2417,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1397,11 +2427,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1928,29 +2961,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
-    <col min="3" max="3" width="12.9166666666667" customWidth="1"/>
-    <col min="4" max="4" width="13.25" customWidth="1"/>
-    <col min="8" max="8" width="11.0833333333333" customWidth="1"/>
-    <col min="10" max="10" width="9.91666666666667" customWidth="1"/>
-    <col min="11" max="11" width="44" customWidth="1"/>
-    <col min="12" max="12" width="55.9166666666667" customWidth="1"/>
-    <col min="13" max="13" width="15.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="20.4166666666667" customWidth="1"/>
+    <col min="4" max="4" width="20.0833333333333" customWidth="1"/>
+    <col min="8" max="8" width="14.3333333333333" customWidth="1"/>
+    <col min="10" max="11" width="17.5833333333333" customWidth="1"/>
+    <col min="12" max="12" width="9.91666666666667" customWidth="1"/>
+    <col min="13" max="13" width="44" customWidth="1"/>
+    <col min="14" max="14" width="55.9166666666667" customWidth="1"/>
+    <col min="15" max="15" width="15.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
+      <c r="D1" s="1"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -1978,127 +3012,157 @@
       <c r="M1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1"/>
       <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="5" customFormat="1" ht="104.4" spans="1:13">
-      <c r="A3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>20</v>
+      <c r="O2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" s="5" customFormat="1" ht="104.4" spans="1:16">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="I3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="I4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>41</v>
+      </c>
+      <c r="N4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O4" t="s">
+        <v>43</v>
+      </c>
+      <c r="P4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>200</v>
@@ -2109,34 +3173,34 @@
       <c r="I5" t="b">
         <v>1</v>
       </c>
-      <c r="J5">
-        <v>1001</v>
-      </c>
-      <c r="K5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>49</v>
+      </c>
+      <c r="N5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O5">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G6">
         <v>200</v>
@@ -2147,30 +3211,34 @@
       <c r="I6" t="b">
         <v>1</v>
       </c>
-      <c r="J6">
-        <v>1001</v>
-      </c>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6">
+      <c r="L6">
+        <v>1001</v>
+      </c>
+      <c r="M6" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6">
         <v>1002</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:16">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s">
         <v>47</v>
       </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G7">
         <v>200</v>
@@ -2181,30 +3249,34 @@
       <c r="I7" t="b">
         <v>1</v>
       </c>
-      <c r="J7">
-        <v>1001</v>
-      </c>
-      <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7">
+      <c r="L7">
+        <v>1001</v>
+      </c>
+      <c r="M7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7">
         <v>1003</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:16">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
         <v>48</v>
-      </c>
-      <c r="D8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
       </c>
       <c r="G8">
         <v>200</v>
@@ -2215,30 +3287,34 @@
       <c r="I8" t="b">
         <v>1</v>
       </c>
-      <c r="J8">
-        <v>1001</v>
-      </c>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8">
+      <c r="L8">
+        <v>1001</v>
+      </c>
+      <c r="M8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" t="s">
+        <v>62</v>
+      </c>
+      <c r="O8">
         <v>1004</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:16">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -2249,30 +3325,34 @@
       <c r="I9" t="b">
         <v>1</v>
       </c>
-      <c r="J9">
-        <v>1001</v>
-      </c>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9">
+      <c r="L9">
+        <v>1001</v>
+      </c>
+      <c r="M9" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" t="s">
+        <v>66</v>
+      </c>
+      <c r="O9">
         <v>1005</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:16">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -2283,30 +3363,34 @@
       <c r="I10" t="b">
         <v>1</v>
       </c>
-      <c r="J10">
-        <v>1001</v>
-      </c>
-      <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10">
+      <c r="L10">
+        <v>1001</v>
+      </c>
+      <c r="M10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O10">
         <v>1006</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:16">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -2317,30 +3401,34 @@
       <c r="I11" t="b">
         <v>1</v>
       </c>
-      <c r="J11">
-        <v>1001</v>
-      </c>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11">
+      <c r="L11">
+        <v>1001</v>
+      </c>
+      <c r="M11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" t="s">
+        <v>72</v>
+      </c>
+      <c r="O11">
         <v>1007</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:16">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -2351,30 +3439,34 @@
       <c r="I12" t="b">
         <v>1</v>
       </c>
-      <c r="J12">
-        <v>1001</v>
-      </c>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12">
+      <c r="L12">
+        <v>1001</v>
+      </c>
+      <c r="M12" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" t="s">
+        <v>75</v>
+      </c>
+      <c r="O12">
         <v>1008</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:16">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -2385,30 +3477,34 @@
       <c r="I13" t="b">
         <v>1</v>
       </c>
-      <c r="J13">
-        <v>1001</v>
-      </c>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13">
+      <c r="L13">
+        <v>1001</v>
+      </c>
+      <c r="M13" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" t="s">
+        <v>78</v>
+      </c>
+      <c r="O13">
         <v>1009</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:16">
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -2419,30 +3515,34 @@
       <c r="I14" t="b">
         <v>1</v>
       </c>
-      <c r="J14">
-        <v>1001</v>
-      </c>
-      <c r="K14"/>
-      <c r="L14"/>
-      <c r="M14">
+      <c r="L14">
+        <v>1001</v>
+      </c>
+      <c r="M14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" t="s">
+        <v>81</v>
+      </c>
+      <c r="O14">
         <v>1010</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:16">
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -2453,30 +3553,34 @@
       <c r="I15" t="b">
         <v>1</v>
       </c>
-      <c r="J15">
-        <v>1001</v>
-      </c>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15">
+      <c r="L15">
+        <v>1001</v>
+      </c>
+      <c r="M15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" t="s">
+        <v>84</v>
+      </c>
+      <c r="O15">
         <v>1011</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:16">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" t="s">
         <v>65</v>
-      </c>
-      <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" t="s">
-        <v>52</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -2487,32 +3591,39 @@
       <c r="I16" t="b">
         <v>1</v>
       </c>
-      <c r="J16">
-        <v>1001</v>
-      </c>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16">
+      <c r="L16">
+        <v>1001</v>
+      </c>
+      <c r="M16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" t="s">
+        <v>87</v>
+      </c>
+      <c r="O16">
         <v>1012</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="B18">
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G18">
         <v>300</v>
@@ -2523,28 +3634,31 @@
       <c r="I18" t="b">
         <v>0</v>
       </c>
-      <c r="J18">
-        <v>1001</v>
-      </c>
-      <c r="K18" t="s">
-        <v>70</v>
-      </c>
-      <c r="L18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="L18">
+        <v>1001</v>
+      </c>
+      <c r="M18" t="s">
+        <v>92</v>
+      </c>
+      <c r="N18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="B19">
         <v>2002</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>94</v>
+      </c>
+      <c r="D19" t="s">
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G19">
         <v>300</v>
@@ -2555,22 +3669,31 @@
       <c r="I19" t="b">
         <v>0</v>
       </c>
-      <c r="J19">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="L19">
+        <v>1001</v>
+      </c>
+      <c r="M19" t="s">
+        <v>96</v>
+      </c>
+      <c r="N19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="B20">
         <v>2003</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
+        <v>99</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F20" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G20">
         <v>300</v>
@@ -2581,22 +3704,31 @@
       <c r="I20" t="b">
         <v>0</v>
       </c>
-      <c r="J20">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="L20">
+        <v>1001</v>
+      </c>
+      <c r="M20" t="s">
+        <v>100</v>
+      </c>
+      <c r="N20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="B21">
         <v>2004</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G21">
         <v>300</v>
@@ -2607,22 +3739,31 @@
       <c r="I21" t="b">
         <v>0</v>
       </c>
-      <c r="J21">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="L21">
+        <v>1001</v>
+      </c>
+      <c r="M21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="B22">
         <v>2005</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>106</v>
+      </c>
+      <c r="D22" t="s">
+        <v>107</v>
       </c>
       <c r="E22" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G22">
         <v>300</v>
@@ -2633,22 +3774,31 @@
       <c r="I22" t="b">
         <v>0</v>
       </c>
-      <c r="J22">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="L22">
+        <v>1001</v>
+      </c>
+      <c r="M22" t="s">
+        <v>108</v>
+      </c>
+      <c r="N22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="B23">
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>111</v>
       </c>
       <c r="E23" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F23" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G23">
         <v>300</v>
@@ -2659,22 +3809,31 @@
       <c r="I23" t="b">
         <v>0</v>
       </c>
-      <c r="J23">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="L23">
+        <v>1001</v>
+      </c>
+      <c r="M23" t="s">
+        <v>112</v>
+      </c>
+      <c r="N23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="B24">
         <v>2007</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>114</v>
+      </c>
+      <c r="D24" t="s">
+        <v>115</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F24" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G24">
         <v>300</v>
@@ -2685,22 +3844,31 @@
       <c r="I24" t="b">
         <v>0</v>
       </c>
-      <c r="J24">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="L24">
+        <v>1001</v>
+      </c>
+      <c r="M24" t="s">
+        <v>116</v>
+      </c>
+      <c r="N24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="B25">
         <v>2008</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>118</v>
+      </c>
+      <c r="D25" t="s">
+        <v>119</v>
       </c>
       <c r="E25" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F25" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G25">
         <v>300</v>
@@ -2711,22 +3879,31 @@
       <c r="I25" t="b">
         <v>0</v>
       </c>
-      <c r="J25">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="L25">
+        <v>1001</v>
+      </c>
+      <c r="M25" t="s">
+        <v>120</v>
+      </c>
+      <c r="N25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="B26">
         <v>2009</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>122</v>
+      </c>
+      <c r="D26" t="s">
+        <v>123</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F26" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G26">
         <v>300</v>
@@ -2737,22 +3914,31 @@
       <c r="I26" t="b">
         <v>0</v>
       </c>
-      <c r="J26">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="L26">
+        <v>1001</v>
+      </c>
+      <c r="M26" t="s">
+        <v>124</v>
+      </c>
+      <c r="N26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="B27">
         <v>2010</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>126</v>
+      </c>
+      <c r="D27" t="s">
+        <v>127</v>
       </c>
       <c r="E27" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F27" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G27">
         <v>300</v>
@@ -2763,22 +3949,31 @@
       <c r="I27" t="b">
         <v>0</v>
       </c>
-      <c r="J27">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="L27">
+        <v>1001</v>
+      </c>
+      <c r="M27" t="s">
+        <v>128</v>
+      </c>
+      <c r="N27" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="B28">
         <v>3001</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>130</v>
+      </c>
+      <c r="D28" t="s">
+        <v>131</v>
       </c>
       <c r="E28" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="F28" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G28">
         <v>300</v>
@@ -2789,22 +3984,31 @@
       <c r="I28" t="b">
         <v>0</v>
       </c>
-      <c r="J28">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="L28">
+        <v>1001</v>
+      </c>
+      <c r="M28" t="s">
+        <v>133</v>
+      </c>
+      <c r="N28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="B29">
         <v>3002</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>135</v>
+      </c>
+      <c r="D29" t="s">
+        <v>136</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="F29" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G29">
         <v>300</v>
@@ -2815,22 +4019,31 @@
       <c r="I29" t="b">
         <v>0</v>
       </c>
-      <c r="J29">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="L29">
+        <v>1001</v>
+      </c>
+      <c r="M29" t="s">
+        <v>137</v>
+      </c>
+      <c r="N29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="B30">
         <v>3003</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>139</v>
+      </c>
+      <c r="D30" t="s">
+        <v>140</v>
       </c>
       <c r="E30" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G30">
         <v>300</v>
@@ -2841,22 +4054,31 @@
       <c r="I30" t="b">
         <v>0</v>
       </c>
-      <c r="J30">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="L30">
+        <v>1001</v>
+      </c>
+      <c r="M30" t="s">
+        <v>141</v>
+      </c>
+      <c r="N30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="B31">
         <v>3004</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>143</v>
+      </c>
+      <c r="D31" t="s">
+        <v>144</v>
       </c>
       <c r="E31" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="F31" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G31">
         <v>300</v>
@@ -2867,22 +4089,31 @@
       <c r="I31" t="b">
         <v>0</v>
       </c>
-      <c r="J31">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="L31">
+        <v>1001</v>
+      </c>
+      <c r="M31" t="s">
+        <v>145</v>
+      </c>
+      <c r="N31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="B32">
         <v>3005</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>147</v>
+      </c>
+      <c r="D32" t="s">
+        <v>148</v>
       </c>
       <c r="E32" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="F32" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G32">
         <v>300</v>
@@ -2893,25 +4124,34 @@
       <c r="I32" t="b">
         <v>0</v>
       </c>
-      <c r="J32">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10">
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="s">
+        <v>149</v>
+      </c>
+      <c r="N32" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
       <c r="B33">
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>151</v>
+      </c>
+      <c r="D33" t="s">
+        <v>152</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="F33" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G33">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2919,25 +4159,37 @@
       <c r="I33" t="b">
         <v>1</v>
       </c>
-      <c r="J33">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10">
+      <c r="J33" t="s">
+        <v>154</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="s">
+        <v>155</v>
+      </c>
+      <c r="N33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
       <c r="B34">
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>157</v>
+      </c>
+      <c r="D34" t="s">
+        <v>158</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="F34" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G34">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2945,25 +4197,37 @@
       <c r="I34" t="b">
         <v>1</v>
       </c>
-      <c r="J34">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10">
+      <c r="J34" t="s">
+        <v>154</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="s">
+        <v>159</v>
+      </c>
+      <c r="N34" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14">
       <c r="B35">
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>161</v>
+      </c>
+      <c r="D35" t="s">
+        <v>162</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="F35" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G35">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -2971,25 +4235,37 @@
       <c r="I35" t="b">
         <v>1</v>
       </c>
-      <c r="J35">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10">
+      <c r="J35" t="s">
+        <v>154</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="s">
+        <v>163</v>
+      </c>
+      <c r="N35" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14">
       <c r="B36">
         <v>4004</v>
       </c>
       <c r="C36" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" t="s">
+        <v>166</v>
+      </c>
+      <c r="E36" t="s">
+        <v>153</v>
+      </c>
+      <c r="F36" t="s">
         <v>91</v>
       </c>
-      <c r="E36" t="s">
-        <v>88</v>
-      </c>
-      <c r="F36" t="s">
-        <v>69</v>
-      </c>
       <c r="G36">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -2997,22 +4273,34 @@
       <c r="I36" t="b">
         <v>1</v>
       </c>
-      <c r="J36">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10">
+      <c r="J36" t="s">
+        <v>154</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="s">
+        <v>167</v>
+      </c>
+      <c r="N36" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14">
       <c r="B37">
         <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>169</v>
+      </c>
+      <c r="D37" t="s">
+        <v>170</v>
       </c>
       <c r="E37" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="F37" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G37">
         <v>300</v>
@@ -3023,22 +4311,31 @@
       <c r="I37" t="b">
         <v>0</v>
       </c>
-      <c r="J37">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10">
+      <c r="L37">
+        <v>1001</v>
+      </c>
+      <c r="M37" t="s">
+        <v>172</v>
+      </c>
+      <c r="N37" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14">
       <c r="B38">
         <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>174</v>
+      </c>
+      <c r="D38" t="s">
+        <v>175</v>
       </c>
       <c r="E38" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="F38" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G38">
         <v>300</v>
@@ -3049,22 +4346,31 @@
       <c r="I38" t="b">
         <v>0</v>
       </c>
-      <c r="J38">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10">
+      <c r="L38">
+        <v>1001</v>
+      </c>
+      <c r="M38" t="s">
+        <v>176</v>
+      </c>
+      <c r="N38" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14">
       <c r="B39">
         <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>178</v>
+      </c>
+      <c r="D39" t="s">
+        <v>179</v>
       </c>
       <c r="E39" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="F39" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G39">
         <v>300</v>
@@ -3075,22 +4381,31 @@
       <c r="I39" t="b">
         <v>0</v>
       </c>
-      <c r="J39">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10">
+      <c r="L39">
+        <v>1001</v>
+      </c>
+      <c r="M39" t="s">
+        <v>180</v>
+      </c>
+      <c r="N39" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14">
       <c r="B40">
         <v>5004</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>182</v>
+      </c>
+      <c r="D40" t="s">
+        <v>183</v>
       </c>
       <c r="E40" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="F40" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G40">
         <v>300</v>
@@ -3101,22 +4416,31 @@
       <c r="I40" t="b">
         <v>0</v>
       </c>
-      <c r="J40">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10">
+      <c r="L40">
+        <v>1001</v>
+      </c>
+      <c r="M40" t="s">
+        <v>184</v>
+      </c>
+      <c r="N40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14">
       <c r="B41">
         <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>186</v>
+      </c>
+      <c r="D41" t="s">
+        <v>187</v>
       </c>
       <c r="E41" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="F41" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G41">
         <v>300</v>
@@ -3127,22 +4451,31 @@
       <c r="I41" t="b">
         <v>0</v>
       </c>
-      <c r="J41">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10">
+      <c r="L41">
+        <v>1001</v>
+      </c>
+      <c r="M41" t="s">
+        <v>188</v>
+      </c>
+      <c r="N41" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14">
       <c r="B42">
         <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>190</v>
+      </c>
+      <c r="D42" t="s">
+        <v>191</v>
       </c>
       <c r="E42" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="F42" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G42">
         <v>300</v>
@@ -3153,22 +4486,31 @@
       <c r="I42" t="b">
         <v>0</v>
       </c>
-      <c r="J42">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10">
+      <c r="L42">
+        <v>1001</v>
+      </c>
+      <c r="M42" t="s">
+        <v>192</v>
+      </c>
+      <c r="N42" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14">
       <c r="B43">
         <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>194</v>
+      </c>
+      <c r="D43" t="s">
+        <v>195</v>
       </c>
       <c r="E43" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="F43" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G43">
         <v>300</v>
@@ -3179,22 +4521,31 @@
       <c r="I43" t="b">
         <v>0</v>
       </c>
-      <c r="J43">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10">
+      <c r="L43">
+        <v>1001</v>
+      </c>
+      <c r="M43" t="s">
+        <v>196</v>
+      </c>
+      <c r="N43" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14">
       <c r="B44">
         <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>198</v>
+      </c>
+      <c r="D44" t="s">
+        <v>199</v>
       </c>
       <c r="E44" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="F44" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G44">
         <v>300</v>
@@ -3205,22 +4556,31 @@
       <c r="I44" t="b">
         <v>0</v>
       </c>
-      <c r="J44">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10">
+      <c r="L44">
+        <v>1001</v>
+      </c>
+      <c r="M44" t="s">
+        <v>200</v>
+      </c>
+      <c r="N44" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14">
       <c r="B45">
         <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>202</v>
+      </c>
+      <c r="D45" t="s">
+        <v>203</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F45" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G45">
         <v>300</v>
@@ -3231,22 +4591,31 @@
       <c r="I45" t="b">
         <v>0</v>
       </c>
-      <c r="J45">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10">
+      <c r="L45">
+        <v>1001</v>
+      </c>
+      <c r="M45" t="s">
+        <v>205</v>
+      </c>
+      <c r="N45" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14">
       <c r="B46">
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
+        <v>207</v>
+      </c>
+      <c r="D46" t="s">
+        <v>208</v>
       </c>
       <c r="E46" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F46" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G46">
         <v>300</v>
@@ -3257,22 +4626,31 @@
       <c r="I46" t="b">
         <v>0</v>
       </c>
-      <c r="J46">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10">
+      <c r="L46">
+        <v>1001</v>
+      </c>
+      <c r="M46" t="s">
+        <v>209</v>
+      </c>
+      <c r="N46" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14">
       <c r="B47">
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>104</v>
+        <v>211</v>
+      </c>
+      <c r="D47" t="s">
+        <v>212</v>
       </c>
       <c r="E47" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F47" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G47">
         <v>300</v>
@@ -3283,22 +4661,31 @@
       <c r="I47" t="b">
         <v>0</v>
       </c>
-      <c r="J47">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10">
+      <c r="L47">
+        <v>1001</v>
+      </c>
+      <c r="M47" t="s">
+        <v>213</v>
+      </c>
+      <c r="N47" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14">
       <c r="B48">
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>105</v>
+        <v>215</v>
+      </c>
+      <c r="D48" t="s">
+        <v>216</v>
       </c>
       <c r="E48" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F48" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G48">
         <v>300</v>
@@ -3309,22 +4696,31 @@
       <c r="I48" t="b">
         <v>0</v>
       </c>
-      <c r="J48">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10">
+      <c r="L48">
+        <v>1001</v>
+      </c>
+      <c r="M48" t="s">
+        <v>217</v>
+      </c>
+      <c r="N48" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14">
       <c r="B49">
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>219</v>
+      </c>
+      <c r="D49" t="s">
+        <v>220</v>
       </c>
       <c r="E49" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F49" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G49">
         <v>300</v>
@@ -3335,22 +4731,31 @@
       <c r="I49" t="b">
         <v>0</v>
       </c>
-      <c r="J49">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10">
+      <c r="L49">
+        <v>1001</v>
+      </c>
+      <c r="M49" t="s">
+        <v>221</v>
+      </c>
+      <c r="N49" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14">
       <c r="B50">
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
+        <v>223</v>
+      </c>
+      <c r="D50" t="s">
+        <v>224</v>
       </c>
       <c r="E50" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F50" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G50">
         <v>300</v>
@@ -3361,22 +4766,31 @@
       <c r="I50" t="b">
         <v>0</v>
       </c>
-      <c r="J50">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10">
+      <c r="L50">
+        <v>1001</v>
+      </c>
+      <c r="M50" t="s">
+        <v>225</v>
+      </c>
+      <c r="N50" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14">
       <c r="B51">
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>108</v>
+        <v>227</v>
+      </c>
+      <c r="D51" t="s">
+        <v>228</v>
       </c>
       <c r="E51" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F51" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G51">
         <v>300</v>
@@ -3387,22 +4801,31 @@
       <c r="I51" t="b">
         <v>0</v>
       </c>
-      <c r="J51">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10">
+      <c r="L51">
+        <v>1001</v>
+      </c>
+      <c r="M51" t="s">
+        <v>229</v>
+      </c>
+      <c r="N51" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14">
       <c r="B52">
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>109</v>
+        <v>231</v>
+      </c>
+      <c r="D52" t="s">
+        <v>232</v>
       </c>
       <c r="E52" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F52" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G52">
         <v>300</v>
@@ -3413,22 +4836,31 @@
       <c r="I52" t="b">
         <v>0</v>
       </c>
-      <c r="J52">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10">
+      <c r="L52">
+        <v>1001</v>
+      </c>
+      <c r="M52" t="s">
+        <v>233</v>
+      </c>
+      <c r="N52" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14">
       <c r="B53">
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>110</v>
+        <v>235</v>
+      </c>
+      <c r="D53" t="s">
+        <v>236</v>
       </c>
       <c r="E53" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F53" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G53">
         <v>300</v>
@@ -3439,22 +4871,31 @@
       <c r="I53" t="b">
         <v>0</v>
       </c>
-      <c r="J53">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10">
+      <c r="L53">
+        <v>1001</v>
+      </c>
+      <c r="M53" t="s">
+        <v>237</v>
+      </c>
+      <c r="N53" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14">
       <c r="B54">
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>111</v>
+        <v>239</v>
+      </c>
+      <c r="D54" t="s">
+        <v>240</v>
       </c>
       <c r="E54" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F54" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G54">
         <v>300</v>
@@ -3465,22 +4906,31 @@
       <c r="I54" t="b">
         <v>0</v>
       </c>
-      <c r="J54">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10">
+      <c r="L54">
+        <v>1001</v>
+      </c>
+      <c r="M54" t="s">
+        <v>241</v>
+      </c>
+      <c r="N54" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14">
       <c r="B55">
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>243</v>
+      </c>
+      <c r="D55" t="s">
+        <v>244</v>
       </c>
       <c r="E55" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F55" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G55">
         <v>300</v>
@@ -3491,22 +4941,31 @@
       <c r="I55" t="b">
         <v>0</v>
       </c>
-      <c r="J55">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10">
+      <c r="L55">
+        <v>1001</v>
+      </c>
+      <c r="M55" t="s">
+        <v>245</v>
+      </c>
+      <c r="N55" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14">
       <c r="B56">
         <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>113</v>
+        <v>247</v>
+      </c>
+      <c r="D56" t="s">
+        <v>248</v>
       </c>
       <c r="E56" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F56" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G56">
         <v>300</v>
@@ -3517,22 +4976,31 @@
       <c r="I56" t="b">
         <v>0</v>
       </c>
-      <c r="J56">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10">
+      <c r="L56">
+        <v>1001</v>
+      </c>
+      <c r="M56" t="s">
+        <v>250</v>
+      </c>
+      <c r="N56" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14">
       <c r="B57">
         <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>115</v>
+        <v>252</v>
+      </c>
+      <c r="D57" t="s">
+        <v>253</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F57" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G57">
         <v>300</v>
@@ -3543,22 +5011,31 @@
       <c r="I57" t="b">
         <v>0</v>
       </c>
-      <c r="J57">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10">
+      <c r="L57">
+        <v>1001</v>
+      </c>
+      <c r="M57" t="s">
+        <v>254</v>
+      </c>
+      <c r="N57" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14">
       <c r="B58">
         <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>116</v>
+        <v>256</v>
+      </c>
+      <c r="D58" t="s">
+        <v>257</v>
       </c>
       <c r="E58" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F58" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G58">
         <v>300</v>
@@ -3569,22 +5046,31 @@
       <c r="I58" t="b">
         <v>0</v>
       </c>
-      <c r="J58">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10">
+      <c r="L58">
+        <v>1001</v>
+      </c>
+      <c r="M58" t="s">
+        <v>258</v>
+      </c>
+      <c r="N58" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14">
       <c r="B59">
         <v>7004</v>
       </c>
       <c r="C59" t="s">
-        <v>117</v>
+        <v>260</v>
+      </c>
+      <c r="D59" t="s">
+        <v>261</v>
       </c>
       <c r="E59" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F59" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G59">
         <v>300</v>
@@ -3595,22 +5081,31 @@
       <c r="I59" t="b">
         <v>0</v>
       </c>
-      <c r="J59">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10">
+      <c r="L59">
+        <v>1001</v>
+      </c>
+      <c r="M59" t="s">
+        <v>262</v>
+      </c>
+      <c r="N59" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14">
       <c r="B60">
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>264</v>
+      </c>
+      <c r="D60" t="s">
+        <v>265</v>
       </c>
       <c r="E60" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F60" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G60">
         <v>300</v>
@@ -3621,22 +5116,31 @@
       <c r="I60" t="b">
         <v>0</v>
       </c>
-      <c r="J60">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10">
+      <c r="L60">
+        <v>1001</v>
+      </c>
+      <c r="M60" t="s">
+        <v>266</v>
+      </c>
+      <c r="N60" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14">
       <c r="B61">
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>119</v>
+        <v>268</v>
+      </c>
+      <c r="D61" t="s">
+        <v>269</v>
       </c>
       <c r="E61" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F61" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G61">
         <v>300</v>
@@ -3647,22 +5151,31 @@
       <c r="I61" t="b">
         <v>0</v>
       </c>
-      <c r="J61">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10">
+      <c r="L61">
+        <v>1001</v>
+      </c>
+      <c r="M61" t="s">
+        <v>270</v>
+      </c>
+      <c r="N61" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14">
       <c r="B62">
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>120</v>
+        <v>272</v>
+      </c>
+      <c r="D62" t="s">
+        <v>273</v>
       </c>
       <c r="E62" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F62" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G62">
         <v>300</v>
@@ -3673,22 +5186,31 @@
       <c r="I62" t="b">
         <v>0</v>
       </c>
-      <c r="J62">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10">
+      <c r="L62">
+        <v>1001</v>
+      </c>
+      <c r="M62" t="s">
+        <v>274</v>
+      </c>
+      <c r="N62" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14">
       <c r="B63">
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>121</v>
+        <v>276</v>
+      </c>
+      <c r="D63" t="s">
+        <v>277</v>
       </c>
       <c r="E63" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F63" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G63">
         <v>300</v>
@@ -3699,22 +5221,31 @@
       <c r="I63" t="b">
         <v>0</v>
       </c>
-      <c r="J63">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10">
+      <c r="L63">
+        <v>1001</v>
+      </c>
+      <c r="M63" t="s">
+        <v>278</v>
+      </c>
+      <c r="N63" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14">
       <c r="B64">
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>280</v>
+      </c>
+      <c r="D64" t="s">
+        <v>281</v>
       </c>
       <c r="E64" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F64" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G64">
         <v>300</v>
@@ -3725,22 +5256,31 @@
       <c r="I64" t="b">
         <v>0</v>
       </c>
-      <c r="J64">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10">
+      <c r="L64">
+        <v>1001</v>
+      </c>
+      <c r="M64" t="s">
+        <v>282</v>
+      </c>
+      <c r="N64" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14">
       <c r="B65">
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>123</v>
+        <v>284</v>
+      </c>
+      <c r="D65" t="s">
+        <v>285</v>
       </c>
       <c r="E65" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F65" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G65">
         <v>300</v>
@@ -3751,22 +5291,31 @@
       <c r="I65" t="b">
         <v>0</v>
       </c>
-      <c r="J65">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10">
+      <c r="L65">
+        <v>1001</v>
+      </c>
+      <c r="M65" t="s">
+        <v>286</v>
+      </c>
+      <c r="N65" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14">
       <c r="B66">
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>124</v>
+        <v>288</v>
+      </c>
+      <c r="D66" t="s">
+        <v>289</v>
       </c>
       <c r="E66" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F66" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G66">
         <v>300</v>
@@ -3777,22 +5326,31 @@
       <c r="I66" t="b">
         <v>0</v>
       </c>
-      <c r="J66">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10">
+      <c r="L66">
+        <v>1001</v>
+      </c>
+      <c r="M66" t="s">
+        <v>290</v>
+      </c>
+      <c r="N66" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14">
       <c r="B67">
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>125</v>
+        <v>292</v>
+      </c>
+      <c r="D67" t="s">
+        <v>293</v>
       </c>
       <c r="E67" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F67" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G67">
         <v>300</v>
@@ -3803,22 +5361,31 @@
       <c r="I67" t="b">
         <v>0</v>
       </c>
-      <c r="J67">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10">
+      <c r="L67">
+        <v>1001</v>
+      </c>
+      <c r="M67" t="s">
+        <v>294</v>
+      </c>
+      <c r="N67" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14">
       <c r="B68">
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>126</v>
+        <v>296</v>
+      </c>
+      <c r="D68" t="s">
+        <v>297</v>
       </c>
       <c r="E68" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F68" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G68">
         <v>300</v>
@@ -3829,22 +5396,31 @@
       <c r="I68" t="b">
         <v>0</v>
       </c>
-      <c r="J68">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10">
+      <c r="L68">
+        <v>1001</v>
+      </c>
+      <c r="M68" t="s">
+        <v>298</v>
+      </c>
+      <c r="N68" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14">
       <c r="B69">
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>127</v>
+        <v>300</v>
+      </c>
+      <c r="D69" t="s">
+        <v>301</v>
       </c>
       <c r="E69" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F69" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G69">
         <v>300</v>
@@ -3855,22 +5431,31 @@
       <c r="I69" t="b">
         <v>0</v>
       </c>
-      <c r="J69">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10">
+      <c r="L69">
+        <v>1001</v>
+      </c>
+      <c r="M69" t="s">
+        <v>302</v>
+      </c>
+      <c r="N69" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14">
       <c r="B70">
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>128</v>
+        <v>304</v>
+      </c>
+      <c r="D70" t="s">
+        <v>305</v>
       </c>
       <c r="E70" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F70" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G70">
         <v>300</v>
@@ -3881,22 +5466,31 @@
       <c r="I70" t="b">
         <v>0</v>
       </c>
-      <c r="J70">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10">
+      <c r="L70">
+        <v>1001</v>
+      </c>
+      <c r="M70" t="s">
+        <v>306</v>
+      </c>
+      <c r="N70" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14">
       <c r="B71">
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>129</v>
+        <v>308</v>
+      </c>
+      <c r="D71" t="s">
+        <v>309</v>
       </c>
       <c r="E71" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F71" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G71">
         <v>300</v>
@@ -3907,22 +5501,31 @@
       <c r="I71" t="b">
         <v>0</v>
       </c>
-      <c r="J71">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10">
+      <c r="L71">
+        <v>1001</v>
+      </c>
+      <c r="M71" t="s">
+        <v>310</v>
+      </c>
+      <c r="N71" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14">
       <c r="B72">
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>130</v>
+        <v>312</v>
+      </c>
+      <c r="D72" t="s">
+        <v>313</v>
       </c>
       <c r="E72" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F72" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G72">
         <v>300</v>
@@ -3933,22 +5536,31 @@
       <c r="I72" t="b">
         <v>0</v>
       </c>
-      <c r="J72">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10">
+      <c r="L72">
+        <v>1001</v>
+      </c>
+      <c r="M72" t="s">
+        <v>314</v>
+      </c>
+      <c r="N72" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14">
       <c r="B73">
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>131</v>
+        <v>316</v>
+      </c>
+      <c r="D73" t="s">
+        <v>317</v>
       </c>
       <c r="E73" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="F73" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G73">
         <v>300</v>
@@ -3959,22 +5571,31 @@
       <c r="I73" t="b">
         <v>0</v>
       </c>
-      <c r="J73">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10">
+      <c r="L73">
+        <v>1001</v>
+      </c>
+      <c r="M73" t="s">
+        <v>318</v>
+      </c>
+      <c r="N73" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14">
       <c r="B74">
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>132</v>
+        <v>320</v>
+      </c>
+      <c r="D74" t="s">
+        <v>320</v>
       </c>
       <c r="E74" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="F74" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G74">
         <v>300</v>
@@ -3985,22 +5606,31 @@
       <c r="I74" t="b">
         <v>0</v>
       </c>
-      <c r="J74">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10">
+      <c r="L74">
+        <v>1001</v>
+      </c>
+      <c r="M74" t="s">
+        <v>322</v>
+      </c>
+      <c r="N74" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14">
       <c r="B75">
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>134</v>
+        <v>324</v>
+      </c>
+      <c r="D75" t="s">
+        <v>325</v>
       </c>
       <c r="E75" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="F75" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G75">
         <v>300</v>
@@ -4011,22 +5641,31 @@
       <c r="I75" t="b">
         <v>0</v>
       </c>
-      <c r="J75">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10">
+      <c r="L75">
+        <v>1001</v>
+      </c>
+      <c r="M75" t="s">
+        <v>326</v>
+      </c>
+      <c r="N75" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14">
       <c r="B76">
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>135</v>
+        <v>328</v>
+      </c>
+      <c r="D76" t="s">
+        <v>328</v>
       </c>
       <c r="E76" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="F76" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G76">
         <v>300</v>
@@ -4037,22 +5676,31 @@
       <c r="I76" t="b">
         <v>0</v>
       </c>
-      <c r="J76">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10">
+      <c r="L76">
+        <v>1001</v>
+      </c>
+      <c r="M76" t="s">
+        <v>329</v>
+      </c>
+      <c r="N76" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14">
       <c r="B77">
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>136</v>
+        <v>331</v>
+      </c>
+      <c r="D77" t="s">
+        <v>332</v>
       </c>
       <c r="E77" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="F77" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G77">
         <v>300</v>
@@ -4063,22 +5711,31 @@
       <c r="I77" t="b">
         <v>0</v>
       </c>
-      <c r="J77">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10">
+      <c r="L77">
+        <v>1001</v>
+      </c>
+      <c r="M77" t="s">
+        <v>333</v>
+      </c>
+      <c r="N77" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14">
       <c r="B78">
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>137</v>
+        <v>335</v>
+      </c>
+      <c r="D78" t="s">
+        <v>336</v>
       </c>
       <c r="E78" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="F78" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G78">
         <v>300</v>
@@ -4089,22 +5746,31 @@
       <c r="I78" t="b">
         <v>0</v>
       </c>
-      <c r="J78">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10">
+      <c r="L78">
+        <v>1001</v>
+      </c>
+      <c r="M78" t="s">
+        <v>337</v>
+      </c>
+      <c r="N78" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14">
       <c r="B79">
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>138</v>
+        <v>339</v>
+      </c>
+      <c r="D79" t="s">
+        <v>340</v>
       </c>
       <c r="E79" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="F79" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G79">
         <v>300</v>
@@ -4115,22 +5781,31 @@
       <c r="I79" t="b">
         <v>0</v>
       </c>
-      <c r="J79">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10">
+      <c r="L79">
+        <v>1001</v>
+      </c>
+      <c r="M79" t="s">
+        <v>341</v>
+      </c>
+      <c r="N79" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14">
       <c r="B80">
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>139</v>
+        <v>343</v>
+      </c>
+      <c r="D80" t="s">
+        <v>344</v>
       </c>
       <c r="E80" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="F80" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G80">
         <v>300</v>
@@ -4141,22 +5816,31 @@
       <c r="I80" t="b">
         <v>0</v>
       </c>
-      <c r="J80">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10">
+      <c r="L80">
+        <v>1001</v>
+      </c>
+      <c r="M80" t="s">
+        <v>345</v>
+      </c>
+      <c r="N80" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="81" spans="2:16">
       <c r="B81">
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>140</v>
+        <v>347</v>
+      </c>
+      <c r="D81" t="s">
+        <v>348</v>
       </c>
       <c r="E81" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="F81" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G81">
         <v>300</v>
@@ -4167,22 +5851,31 @@
       <c r="I81" t="b">
         <v>0</v>
       </c>
-      <c r="J81">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10">
+      <c r="L81">
+        <v>1001</v>
+      </c>
+      <c r="M81" t="s">
+        <v>349</v>
+      </c>
+      <c r="N81" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="82" spans="2:16">
       <c r="B82">
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>141</v>
+        <v>351</v>
+      </c>
+      <c r="D82" t="s">
+        <v>352</v>
       </c>
       <c r="E82" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="F82" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G82">
         <v>300</v>
@@ -4193,22 +5886,31 @@
       <c r="I82" t="b">
         <v>0</v>
       </c>
-      <c r="J82">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10">
+      <c r="L82">
+        <v>1001</v>
+      </c>
+      <c r="M82" t="s">
+        <v>353</v>
+      </c>
+      <c r="N82" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="83" spans="2:16">
       <c r="B83">
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>142</v>
+        <v>355</v>
+      </c>
+      <c r="D83" t="s">
+        <v>356</v>
       </c>
       <c r="E83" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="F83" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G83">
         <v>300</v>
@@ -4219,22 +5921,31 @@
       <c r="I83" t="b">
         <v>0</v>
       </c>
-      <c r="J83">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10">
+      <c r="L83">
+        <v>1001</v>
+      </c>
+      <c r="M83" t="s">
+        <v>357</v>
+      </c>
+      <c r="N83" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="84" spans="2:16">
       <c r="B84">
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>143</v>
+        <v>359</v>
+      </c>
+      <c r="D84" t="s">
+        <v>360</v>
       </c>
       <c r="E84" t="s">
-        <v>133</v>
+        <v>321</v>
       </c>
       <c r="F84" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G84">
         <v>300</v>
@@ -4245,8 +5956,591 @@
       <c r="I84" t="b">
         <v>0</v>
       </c>
-      <c r="J84">
-        <v>1001</v>
+      <c r="L84">
+        <v>1001</v>
+      </c>
+      <c r="M84" t="s">
+        <v>361</v>
+      </c>
+      <c r="N84" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="85" spans="2:16">
+      <c r="B85">
+        <v>9001</v>
+      </c>
+      <c r="C85" t="s">
+        <v>363</v>
+      </c>
+      <c r="D85" t="s">
+        <v>364</v>
+      </c>
+      <c r="E85" t="s">
+        <v>365</v>
+      </c>
+      <c r="F85" t="s">
+        <v>366</v>
+      </c>
+      <c r="G85">
+        <v>300</v>
+      </c>
+      <c r="H85">
+        <v>300</v>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>1001</v>
+      </c>
+      <c r="M85" t="s">
+        <v>367</v>
+      </c>
+      <c r="N85" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="86" spans="2:16">
+      <c r="B86">
+        <v>9002</v>
+      </c>
+      <c r="C86" t="s">
+        <v>369</v>
+      </c>
+      <c r="D86" t="s">
+        <v>370</v>
+      </c>
+      <c r="E86" t="s">
+        <v>365</v>
+      </c>
+      <c r="F86" t="s">
+        <v>91</v>
+      </c>
+      <c r="G86">
+        <v>300</v>
+      </c>
+      <c r="H86">
+        <v>300</v>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" t="s">
+        <v>371</v>
+      </c>
+      <c r="K86">
+        <v>9009</v>
+      </c>
+      <c r="L86">
+        <v>1001</v>
+      </c>
+      <c r="M86" t="s">
+        <v>372</v>
+      </c>
+      <c r="N86" t="s">
+        <v>373</v>
+      </c>
+      <c r="P86" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="87" spans="2:16">
+      <c r="B87">
+        <v>9003</v>
+      </c>
+      <c r="C87" t="s">
+        <v>375</v>
+      </c>
+      <c r="D87" t="s">
+        <v>376</v>
+      </c>
+      <c r="E87" t="s">
+        <v>365</v>
+      </c>
+      <c r="F87" t="s">
+        <v>91</v>
+      </c>
+      <c r="G87">
+        <v>300</v>
+      </c>
+      <c r="H87">
+        <v>300</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" t="s">
+        <v>371</v>
+      </c>
+      <c r="K87">
+        <v>9009</v>
+      </c>
+      <c r="L87">
+        <v>1001</v>
+      </c>
+      <c r="M87" t="s">
+        <v>377</v>
+      </c>
+      <c r="N87" t="s">
+        <v>378</v>
+      </c>
+      <c r="P87" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="88" spans="2:16">
+      <c r="B88">
+        <v>9004</v>
+      </c>
+      <c r="C88" t="s">
+        <v>379</v>
+      </c>
+      <c r="D88" t="s">
+        <v>380</v>
+      </c>
+      <c r="E88" t="s">
+        <v>365</v>
+      </c>
+      <c r="F88" t="s">
+        <v>91</v>
+      </c>
+      <c r="G88">
+        <v>300</v>
+      </c>
+      <c r="H88">
+        <v>300</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" t="s">
+        <v>371</v>
+      </c>
+      <c r="K88">
+        <v>9009</v>
+      </c>
+      <c r="L88">
+        <v>1001</v>
+      </c>
+      <c r="M88" t="s">
+        <v>381</v>
+      </c>
+      <c r="N88" t="s">
+        <v>382</v>
+      </c>
+      <c r="P88" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="89" spans="2:16">
+      <c r="B89">
+        <v>9005</v>
+      </c>
+      <c r="C89" t="s">
+        <v>383</v>
+      </c>
+      <c r="D89" t="s">
+        <v>384</v>
+      </c>
+      <c r="E89" t="s">
+        <v>365</v>
+      </c>
+      <c r="F89" t="s">
+        <v>91</v>
+      </c>
+      <c r="G89">
+        <v>300</v>
+      </c>
+      <c r="H89">
+        <v>300</v>
+      </c>
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" t="s">
+        <v>371</v>
+      </c>
+      <c r="K89">
+        <v>9009</v>
+      </c>
+      <c r="L89">
+        <v>1001</v>
+      </c>
+      <c r="M89" t="s">
+        <v>385</v>
+      </c>
+      <c r="N89" t="s">
+        <v>386</v>
+      </c>
+      <c r="P89" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="90" spans="2:16">
+      <c r="B90">
+        <v>9006</v>
+      </c>
+      <c r="C90" t="s">
+        <v>387</v>
+      </c>
+      <c r="D90" t="s">
+        <v>388</v>
+      </c>
+      <c r="E90" t="s">
+        <v>365</v>
+      </c>
+      <c r="F90" t="s">
+        <v>91</v>
+      </c>
+      <c r="G90">
+        <v>300</v>
+      </c>
+      <c r="H90">
+        <v>300</v>
+      </c>
+      <c r="I90" t="b">
+        <v>0</v>
+      </c>
+      <c r="J90" t="s">
+        <v>371</v>
+      </c>
+      <c r="K90">
+        <v>9009</v>
+      </c>
+      <c r="L90">
+        <v>1001</v>
+      </c>
+      <c r="M90" t="s">
+        <v>389</v>
+      </c>
+      <c r="N90" t="s">
+        <v>390</v>
+      </c>
+      <c r="P90" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="91" spans="2:16">
+      <c r="B91">
+        <v>9007</v>
+      </c>
+      <c r="C91" t="s">
+        <v>391</v>
+      </c>
+      <c r="D91" t="s">
+        <v>392</v>
+      </c>
+      <c r="E91" t="s">
+        <v>365</v>
+      </c>
+      <c r="F91" t="s">
+        <v>91</v>
+      </c>
+      <c r="G91">
+        <v>300</v>
+      </c>
+      <c r="H91">
+        <v>300</v>
+      </c>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+      <c r="J91" t="s">
+        <v>371</v>
+      </c>
+      <c r="K91">
+        <v>9009</v>
+      </c>
+      <c r="L91">
+        <v>1001</v>
+      </c>
+      <c r="M91" t="s">
+        <v>393</v>
+      </c>
+      <c r="N91" t="s">
+        <v>394</v>
+      </c>
+      <c r="P91" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="92" spans="2:16">
+      <c r="B92">
+        <v>9008</v>
+      </c>
+      <c r="C92" t="s">
+        <v>395</v>
+      </c>
+      <c r="D92" t="s">
+        <v>396</v>
+      </c>
+      <c r="E92" t="s">
+        <v>365</v>
+      </c>
+      <c r="F92" t="s">
+        <v>91</v>
+      </c>
+      <c r="G92">
+        <v>300</v>
+      </c>
+      <c r="H92">
+        <v>300</v>
+      </c>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" t="s">
+        <v>371</v>
+      </c>
+      <c r="K92">
+        <v>9009</v>
+      </c>
+      <c r="L92">
+        <v>1001</v>
+      </c>
+      <c r="M92" t="s">
+        <v>397</v>
+      </c>
+      <c r="N92" t="s">
+        <v>398</v>
+      </c>
+      <c r="P92" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="93" spans="2:16">
+      <c r="B93">
+        <v>9009</v>
+      </c>
+      <c r="C93" t="s">
+        <v>399</v>
+      </c>
+      <c r="D93" t="s">
+        <v>400</v>
+      </c>
+      <c r="E93" t="s">
+        <v>365</v>
+      </c>
+      <c r="F93" t="s">
+        <v>91</v>
+      </c>
+      <c r="G93">
+        <v>300</v>
+      </c>
+      <c r="H93">
+        <v>300</v>
+      </c>
+      <c r="I93" t="b">
+        <v>1</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93" t="s">
+        <v>401</v>
+      </c>
+      <c r="N93" t="s">
+        <v>402</v>
+      </c>
+      <c r="P93" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="94" spans="2:16">
+      <c r="B94">
+        <v>9010</v>
+      </c>
+      <c r="C94" t="s">
+        <v>403</v>
+      </c>
+      <c r="D94" t="s">
+        <v>404</v>
+      </c>
+      <c r="E94" t="s">
+        <v>365</v>
+      </c>
+      <c r="F94" t="s">
+        <v>91</v>
+      </c>
+      <c r="G94">
+        <v>300</v>
+      </c>
+      <c r="H94">
+        <v>300</v>
+      </c>
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+      <c r="J94" t="s">
+        <v>371</v>
+      </c>
+      <c r="K94">
+        <v>9009</v>
+      </c>
+      <c r="L94">
+        <v>1001</v>
+      </c>
+      <c r="M94" t="s">
+        <v>405</v>
+      </c>
+      <c r="N94" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="95" spans="2:16">
+      <c r="B95">
+        <v>9011</v>
+      </c>
+      <c r="C95" t="s">
+        <v>407</v>
+      </c>
+      <c r="D95" t="s">
+        <v>408</v>
+      </c>
+      <c r="E95" t="s">
+        <v>365</v>
+      </c>
+      <c r="F95" t="s">
+        <v>91</v>
+      </c>
+      <c r="G95">
+        <v>300</v>
+      </c>
+      <c r="H95">
+        <v>300</v>
+      </c>
+      <c r="I95" t="b">
+        <v>0</v>
+      </c>
+      <c r="J95" t="s">
+        <v>371</v>
+      </c>
+      <c r="K95">
+        <v>9009</v>
+      </c>
+      <c r="L95">
+        <v>1001</v>
+      </c>
+      <c r="M95" t="s">
+        <v>409</v>
+      </c>
+      <c r="N95" t="s">
+        <v>410</v>
+      </c>
+      <c r="P95" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="96" spans="2:16">
+      <c r="B96">
+        <v>10001</v>
+      </c>
+      <c r="C96" t="s">
+        <v>411</v>
+      </c>
+      <c r="D96" t="s">
+        <v>412</v>
+      </c>
+      <c r="E96" t="s">
+        <v>413</v>
+      </c>
+      <c r="F96" t="s">
+        <v>366</v>
+      </c>
+      <c r="G96">
+        <v>300</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96" t="b">
+        <v>1</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96" t="s">
+        <v>414</v>
+      </c>
+      <c r="N96" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="97" spans="2:16">
+      <c r="B97">
+        <v>11001</v>
+      </c>
+      <c r="C97" t="s">
+        <v>416</v>
+      </c>
+      <c r="D97" t="s">
+        <v>417</v>
+      </c>
+      <c r="E97" t="s">
+        <v>418</v>
+      </c>
+      <c r="F97" t="s">
+        <v>366</v>
+      </c>
+      <c r="G97">
+        <v>300</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97" t="b">
+        <v>1</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97" t="s">
+        <v>419</v>
+      </c>
+      <c r="N97" t="s">
+        <v>420</v>
+      </c>
+      <c r="P97" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="98" spans="2:16">
+      <c r="B98">
+        <v>11002</v>
+      </c>
+      <c r="C98" t="s">
+        <v>422</v>
+      </c>
+      <c r="D98" t="s">
+        <v>423</v>
+      </c>
+      <c r="E98" t="s">
+        <v>418</v>
+      </c>
+      <c r="F98" t="s">
+        <v>366</v>
+      </c>
+      <c r="G98">
+        <v>300</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98" t="b">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>11001</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98" t="s">
+        <v>419</v>
+      </c>
+      <c r="N98" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -4258,162 +6552,311 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:I11"/>
+  <dimension ref="B2:M13"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="11.4166666666667" customWidth="1"/>
+    <col min="11" max="11" width="12.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9">
-      <c r="B2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D2" s="6">
+    <row r="2" spans="2:13">
+      <c r="B2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="D2" s="4">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="2:9">
-      <c r="B3" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="G2" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="L2" s="4">
+        <v>1</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13">
+      <c r="B3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="4">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="2:9">
-      <c r="B4" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="G3" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="L3" s="4">
+        <v>2</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13">
+      <c r="B4" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="D4" s="4">
         <v>3</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="2:9">
-      <c r="B5" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="G4" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="L4" s="4">
         <v>4</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="M4" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D6" s="6">
+      <c r="C5" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D5" s="4">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="L5" s="4">
+        <v>8</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D6" s="4">
         <v>5</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="G6" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="L6" s="4">
+        <v>16</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="D7" s="4">
         <v>6</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="B8" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="G7" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="L7" s="4">
+        <v>32</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="D8" s="4">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="J8" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="L8" s="4">
+        <v>64</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="D9" s="4">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="B10" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="J9" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="L9" s="4">
+        <v>128</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="D10" s="4">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="2:9">
-      <c r="B11" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="J10" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="L10" s="4">
+        <v>256</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="D11" s="4">
         <v>10</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="L11" s="4">
+        <v>512</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="J12" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="L12" s="4">
+        <v>1024</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="J13" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="L13" s="4">
+        <v>2048</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -4447,183 +6890,183 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>169</v>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>481</v>
       </c>
       <c r="I1" t="s">
-        <v>170</v>
+        <v>482</v>
       </c>
       <c r="J1" t="s">
-        <v>171</v>
+        <v>483</v>
       </c>
       <c r="K1" t="s">
-        <v>172</v>
+        <v>484</v>
       </c>
       <c r="L1" t="s">
-        <v>173</v>
+        <v>485</v>
       </c>
       <c r="M1" t="s">
-        <v>174</v>
+        <v>486</v>
       </c>
       <c r="N1" t="s">
-        <v>175</v>
+        <v>487</v>
       </c>
       <c r="O1" t="s">
-        <v>176</v>
+        <v>488</v>
       </c>
       <c r="P1" t="s">
-        <v>177</v>
+        <v>489</v>
       </c>
       <c r="Q1" t="s">
-        <v>178</v>
+        <v>490</v>
       </c>
       <c r="R1" t="s">
-        <v>179</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>14</v>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="34.8" spans="1:18">
-      <c r="A3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="4" t="s">
-        <v>19</v>
+      <c r="A4" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>493</v>
       </c>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>494</v>
       </c>
       <c r="E4" t="s">
-        <v>183</v>
+        <v>495</v>
       </c>
       <c r="F4" t="s">
-        <v>184</v>
+        <v>496</v>
       </c>
       <c r="G4" t="s">
-        <v>185</v>
+        <v>497</v>
       </c>
       <c r="H4" t="s">
-        <v>186</v>
+        <v>498</v>
       </c>
       <c r="I4" t="s">
-        <v>187</v>
+        <v>499</v>
       </c>
       <c r="J4" t="s">
-        <v>188</v>
+        <v>500</v>
       </c>
       <c r="K4" t="s">
-        <v>189</v>
+        <v>501</v>
       </c>
       <c r="L4" t="s">
-        <v>190</v>
+        <v>502</v>
       </c>
       <c r="M4" t="s">
-        <v>191</v>
+        <v>503</v>
       </c>
       <c r="N4" t="s">
-        <v>192</v>
+        <v>504</v>
       </c>
       <c r="O4" t="s">
-        <v>193</v>
+        <v>505</v>
       </c>
       <c r="P4" t="s">
-        <v>194</v>
+        <v>506</v>
       </c>
       <c r="Q4" t="s">
-        <v>195</v>
+        <v>507</v>
       </c>
       <c r="R4" t="s">
-        <v>196</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -4631,52 +7074,52 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>197</v>
+        <v>509</v>
       </c>
       <c r="D5" t="s">
-        <v>198</v>
+        <v>510</v>
       </c>
       <c r="E5" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="F5" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="G5" t="s">
-        <v>201</v>
+        <v>513</v>
       </c>
       <c r="H5" t="s">
-        <v>202</v>
+        <v>514</v>
       </c>
       <c r="I5" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
       <c r="J5" t="s">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="K5" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="L5" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="M5" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="N5" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="O5" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="P5" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="Q5" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="R5" t="s">
-        <v>210</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -4684,52 +7127,52 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>211</v>
+        <v>523</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="G6" t="s">
-        <v>212</v>
+        <v>524</v>
       </c>
       <c r="H6" t="s">
-        <v>202</v>
+        <v>514</v>
       </c>
       <c r="I6" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
       <c r="J6" t="s">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="K6" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="L6" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="M6" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="N6" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="O6" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="P6" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="Q6" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="R6" t="s">
-        <v>210</v>
+        <v>522</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -4737,50 +7180,52 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>213</v>
+        <v>525</v>
       </c>
       <c r="E7" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="F7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G7"/>
+        <v>520</v>
+      </c>
+      <c r="G7" t="s">
+        <v>526</v>
+      </c>
       <c r="H7" t="s">
-        <v>202</v>
+        <v>514</v>
       </c>
       <c r="I7" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
       <c r="J7" t="s">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="K7" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="L7" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="M7" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="N7" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="O7" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="Q7" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="R7" t="s">
-        <v>210</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -4788,50 +7233,52 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>214</v>
+        <v>527</v>
       </c>
       <c r="E8" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="F8" t="s">
-        <v>206</v>
-      </c>
-      <c r="G8"/>
+        <v>518</v>
+      </c>
+      <c r="G8" t="s">
+        <v>528</v>
+      </c>
       <c r="H8" t="s">
-        <v>202</v>
+        <v>514</v>
       </c>
       <c r="I8" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
       <c r="J8" t="s">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="K8" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="L8" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="M8" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="N8" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="O8" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="P8" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="Q8" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="R8" t="s">
-        <v>210</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -4839,50 +7286,52 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>215</v>
+        <v>529</v>
       </c>
       <c r="E9" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="F9" t="s">
-        <v>208</v>
-      </c>
-      <c r="G9"/>
+        <v>520</v>
+      </c>
+      <c r="G9" t="s">
+        <v>513</v>
+      </c>
       <c r="H9" t="s">
-        <v>216</v>
+        <v>530</v>
       </c>
       <c r="I9" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
       <c r="J9" t="s">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="K9" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="L9" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="M9" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="N9" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="O9" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="P9" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="Q9" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="R9" t="s">
-        <v>210</v>
+        <v>522</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -4890,50 +7339,52 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>217</v>
+        <v>531</v>
       </c>
       <c r="E10" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="F10" t="s">
-        <v>200</v>
-      </c>
-      <c r="G10"/>
+        <v>512</v>
+      </c>
+      <c r="G10" t="s">
+        <v>513</v>
+      </c>
       <c r="H10" t="s">
-        <v>218</v>
+        <v>532</v>
       </c>
       <c r="I10" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
       <c r="J10" t="s">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="K10" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="L10" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="M10" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="N10" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="O10" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="P10" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="Q10" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="R10" t="s">
-        <v>210</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -4941,50 +7392,52 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>219</v>
+        <v>533</v>
       </c>
       <c r="E11" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="F11" t="s">
-        <v>210</v>
-      </c>
-      <c r="G11"/>
+        <v>522</v>
+      </c>
+      <c r="G11" t="s">
+        <v>524</v>
+      </c>
       <c r="H11" t="s">
-        <v>216</v>
+        <v>530</v>
       </c>
       <c r="I11" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
       <c r="J11" t="s">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="K11" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="L11" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="M11" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="N11" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="O11" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="P11" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="Q11" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="R11" t="s">
-        <v>210</v>
+        <v>522</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -4992,50 +7445,52 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>220</v>
+        <v>534</v>
       </c>
       <c r="E12" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="F12" t="s">
-        <v>200</v>
-      </c>
-      <c r="G12"/>
+        <v>512</v>
+      </c>
+      <c r="G12" t="s">
+        <v>524</v>
+      </c>
       <c r="H12" t="s">
-        <v>218</v>
+        <v>532</v>
       </c>
       <c r="I12" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
       <c r="J12" t="s">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="K12" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="L12" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="M12" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="N12" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="O12" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="P12" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="Q12" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="R12" t="s">
-        <v>210</v>
+        <v>522</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -5043,50 +7498,52 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>221</v>
+        <v>535</v>
       </c>
       <c r="E13" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="F13" t="s">
-        <v>210</v>
-      </c>
-      <c r="G13"/>
+        <v>522</v>
+      </c>
+      <c r="G13" t="s">
+        <v>526</v>
+      </c>
       <c r="H13" t="s">
-        <v>216</v>
+        <v>530</v>
       </c>
       <c r="I13" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
       <c r="J13" t="s">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="K13" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="L13" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="M13" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="N13" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="O13" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="P13" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="Q13" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="R13" t="s">
-        <v>210</v>
+        <v>522</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -5094,50 +7551,52 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>222</v>
+        <v>536</v>
       </c>
       <c r="E14" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="F14" t="s">
-        <v>200</v>
-      </c>
-      <c r="G14"/>
+        <v>512</v>
+      </c>
+      <c r="G14" t="s">
+        <v>526</v>
+      </c>
       <c r="H14" t="s">
-        <v>218</v>
+        <v>532</v>
       </c>
       <c r="I14" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
       <c r="J14" t="s">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="K14" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="L14" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="M14" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="N14" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="O14" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="P14" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="Q14" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="R14" t="s">
-        <v>210</v>
+        <v>522</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -5145,50 +7604,52 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>223</v>
+        <v>537</v>
       </c>
       <c r="E15" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="F15" t="s">
-        <v>200</v>
-      </c>
-      <c r="G15"/>
+        <v>512</v>
+      </c>
+      <c r="G15" t="s">
+        <v>528</v>
+      </c>
       <c r="H15" t="s">
-        <v>216</v>
+        <v>530</v>
       </c>
       <c r="I15" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
       <c r="J15" t="s">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="K15" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="L15" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="M15" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="N15" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="O15" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="P15" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="Q15" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="R15" t="s">
-        <v>210</v>
+        <v>522</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -5196,50 +7657,52 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>224</v>
+        <v>538</v>
       </c>
       <c r="D16" t="s">
-        <v>225</v>
+        <v>539</v>
       </c>
       <c r="E16" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="F16" t="s">
-        <v>209</v>
-      </c>
-      <c r="G16"/>
+        <v>521</v>
+      </c>
+      <c r="G16" t="s">
+        <v>528</v>
+      </c>
       <c r="H16" t="s">
-        <v>218</v>
+        <v>532</v>
       </c>
       <c r="I16" t="s">
-        <v>203</v>
+        <v>515</v>
       </c>
       <c r="J16" t="s">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="K16" t="s">
-        <v>199</v>
+        <v>511</v>
       </c>
       <c r="L16" t="s">
-        <v>205</v>
+        <v>517</v>
       </c>
       <c r="M16" t="s">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="N16" t="s">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="O16" t="s">
-        <v>207</v>
+        <v>519</v>
       </c>
       <c r="P16" t="s">
-        <v>208</v>
+        <v>520</v>
       </c>
       <c r="Q16" t="s">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="R16" t="s">
-        <v>210</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -5260,54 +7723,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>226</v>
+        <v>540</v>
       </c>
       <c r="D1" t="s">
-        <v>227</v>
+        <v>541</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>542</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>26</v>
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>543</v>
       </c>
       <c r="D3" t="s">
-        <v>230</v>
+        <v>544</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5397,120 +7860,352 @@
   <sheetPr/>
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="56.0833333333333" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="3" max="3" width="14.8333333333333" customWidth="1"/>
+    <col min="4" max="4" width="13.75" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="12.9166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E1" t="s">
+        <v>554</v>
+      </c>
+      <c r="F1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>556</v>
+      </c>
+      <c r="D4" t="s">
+        <v>557</v>
+      </c>
+      <c r="E4" t="s">
+        <v>558</v>
+      </c>
+      <c r="F4" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>560</v>
+      </c>
+      <c r="E5" t="s">
+        <v>561</v>
+      </c>
+      <c r="F5" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6" t="s">
+        <v>563</v>
+      </c>
+      <c r="E6" t="s">
+        <v>564</v>
+      </c>
+      <c r="F6" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7">
+        <v>150</v>
+      </c>
+      <c r="D7" t="s">
+        <v>566</v>
+      </c>
+      <c r="E7" t="s">
+        <v>567</v>
+      </c>
+      <c r="F7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8">
+        <v>200</v>
+      </c>
+      <c r="D8" t="s">
+        <v>569</v>
+      </c>
+      <c r="E8" t="s">
+        <v>570</v>
+      </c>
+      <c r="F8" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9">
+        <v>300</v>
+      </c>
+      <c r="D9" t="s">
+        <v>572</v>
+      </c>
+      <c r="E9" t="s">
+        <v>573</v>
+      </c>
+      <c r="F9" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10">
+        <v>450</v>
+      </c>
+      <c r="D10" t="s">
+        <v>575</v>
+      </c>
+      <c r="E10" t="s">
+        <v>576</v>
+      </c>
+      <c r="F10" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+      <c r="D11" t="s">
+        <v>578</v>
+      </c>
+      <c r="E11" t="s">
+        <v>579</v>
+      </c>
+      <c r="F11" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12">
+        <v>2500</v>
+      </c>
+      <c r="D12" t="s">
+        <v>581</v>
+      </c>
+      <c r="E12" t="s">
+        <v>582</v>
+      </c>
+      <c r="F12" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13">
+        <v>12500</v>
+      </c>
+      <c r="D13" t="s">
+        <v>584</v>
+      </c>
+      <c r="E13" t="s">
+        <v>585</v>
+      </c>
+      <c r="F13" t="s">
+        <v>586</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13451"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -1151,7 +1151,7 @@
     <t>波尔多</t>
   </si>
   <si>
-    <t>沙特阿拉伯,阿联酋,马来西亚,印尼</t>
+    <t>沙特阿拉伯|阿联酋|马来西亚|印尼</t>
   </si>
   <si>
     <t>v1\Treat\Bordeaux.png</t>
@@ -2967,7 +2967,8 @@
     <col min="3" max="3" width="20.4166666666667" customWidth="1"/>
     <col min="4" max="4" width="20.0833333333333" customWidth="1"/>
     <col min="8" max="8" width="14.3333333333333" customWidth="1"/>
-    <col min="10" max="11" width="17.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="67.75" customWidth="1"/>
+    <col min="11" max="11" width="17.5833333333333" customWidth="1"/>
     <col min="12" max="12" width="9.91666666666667" customWidth="1"/>
     <col min="13" max="13" width="44" customWidth="1"/>
     <col min="14" max="14" width="55.9166666666667" customWidth="1"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="BlindBox" sheetId="4" r:id="rId4"/>
     <sheet name="GameDevelopConfig" sheetId="5" r:id="rId5"/>
     <sheet name="PayTable" sheetId="6" r:id="rId6"/>
+    <sheet name="Rarity" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="592">
   <si>
     <t>##var</t>
   </si>
@@ -128,7 +129,7 @@
 拿到字符串后需要自行转义
 该字段为列表，可以跨行填写多个
 要注意，也可以是tres文件
-由于小狗皮肤由多个文件组成，因此直接填写文件夹目录</t>
+由于小狗皮肤由多个文件组成，因此直接填写文件夹目录，卡面也是填文件夹</t>
   </si>
   <si>
     <t>在背包内显示的图标</t>
@@ -185,7 +186,7 @@
     <t>史诗</t>
   </si>
   <si>
-    <t>v1\Assets\Shiba\Red\</t>
+    <t>v1\Shiba\Red\</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_Red.png</t>
@@ -197,7 +198,7 @@
     <t>黑柴</t>
   </si>
   <si>
-    <t>v1\Assets\Shiba\Black\</t>
+    <t>v1\Shiba\Black\</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_Black.png</t>
@@ -209,7 +210,7 @@
     <t>白柴</t>
   </si>
   <si>
-    <t>v1\Assets\Shiba\Cream\</t>
+    <t>v1\Shiba\Cream\</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_Cream.png</t>
@@ -221,7 +222,7 @@
     <t>胡麻柴</t>
   </si>
   <si>
-    <t>v1\Assets\Shiba\Sesame\</t>
+    <t>v1\Shiba\Sesame\</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_Sesame.png</t>
@@ -1295,21 +1296,24 @@
     <t>CardFace</t>
   </si>
   <si>
-    <t>v1\Card\CardFace\</t>
+    <t>v1\Card\CardFace\Classic\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\CardFace_Kibble.png</t>
+  </si>
+  <si>
+    <t>开发阶段先临时用经典卡面</t>
+  </si>
+  <si>
+    <t>Classic Card Face</t>
+  </si>
+  <si>
+    <t>经典卡面</t>
   </si>
   <si>
     <t>v1\ItemIcon\CardFace_Classic.png</t>
   </si>
   <si>
-    <t>开发阶段先临时用经典卡面</t>
-  </si>
-  <si>
-    <t>Classic Card Face</t>
-  </si>
-  <si>
-    <t>经典卡面</t>
-  </si>
-  <si>
     <t>小狗本体</t>
   </si>
   <si>
@@ -1797,6 +1801,18 @@
   </si>
   <si>
     <t>皇家狗粮</t>
+  </si>
+  <si>
+    <t>FrameAssetPath</t>
+  </si>
+  <si>
+    <t>PlateAssetPath</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Legendary.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Legendary.png</t>
   </si>
 </sst>
 </file>
@@ -2427,14 +2443,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2967,7 +2983,7 @@
     <col min="3" max="3" width="20.4166666666667" customWidth="1"/>
     <col min="4" max="4" width="20.0833333333333" customWidth="1"/>
     <col min="8" max="8" width="14.3333333333333" customWidth="1"/>
-    <col min="10" max="10" width="67.75" customWidth="1"/>
+    <col min="10" max="10" width="27.4166666666667" customWidth="1"/>
     <col min="11" max="11" width="17.5833333333333" customWidth="1"/>
     <col min="12" max="12" width="9.91666666666667" customWidth="1"/>
     <col min="13" max="13" width="44" customWidth="1"/>
@@ -3065,7 +3081,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="5" customFormat="1" ht="104.4" spans="1:16">
+    <row r="3" s="3" customFormat="1" ht="121.8" spans="1:16">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -3074,28 +3090,28 @@
       <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6541,7 +6557,7 @@
         <v>419</v>
       </c>
       <c r="N98" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -6565,20 +6581,20 @@
         <v>47</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>65</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>154</v>
@@ -6587,7 +6603,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="2:13">
@@ -6595,29 +6611,29 @@
         <v>90</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D3" s="4">
         <v>2</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>48</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L3" s="4">
         <v>2</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="2:13">
@@ -6625,29 +6641,29 @@
         <v>132</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>91</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L4" s="4">
         <v>4</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="2:13">
@@ -6655,29 +6671,29 @@
         <v>153</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D5" s="4">
         <v>4</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>366</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L5" s="4">
         <v>8</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="2:13">
@@ -6685,29 +6701,29 @@
         <v>171</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D6" s="4">
         <v>5</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L6" s="4">
         <v>16</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="2:13">
@@ -6715,29 +6731,29 @@
         <v>204</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D7" s="4">
         <v>6</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L7" s="4">
         <v>32</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" spans="2:13">
@@ -6745,22 +6761,22 @@
         <v>249</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D8" s="4">
         <v>7</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L8" s="4">
         <v>64</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" spans="2:13">
@@ -6768,22 +6784,22 @@
         <v>321</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D9" s="4">
         <v>8</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L9" s="4">
         <v>128</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" spans="2:13">
@@ -6791,22 +6807,22 @@
         <v>365</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D10" s="4">
         <v>9</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L10" s="4">
         <v>256</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" spans="2:13">
@@ -6814,50 +6830,50 @@
         <v>413</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D11" s="4">
         <v>10</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L11" s="4">
         <v>512</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" spans="2:13">
       <c r="J12" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L12" s="4">
         <v>1024</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="J13" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L13" s="4">
         <v>2048</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -6899,49 +6915,49 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Q1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="R1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -7006,10 +7022,10 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -7022,52 +7038,52 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Q4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="R4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -7075,52 +7091,52 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F5" t="s">
+        <v>513</v>
+      </c>
+      <c r="G5" t="s">
+        <v>514</v>
+      </c>
+      <c r="H5" t="s">
+        <v>515</v>
+      </c>
+      <c r="I5" t="s">
+        <v>516</v>
+      </c>
+      <c r="J5" t="s">
+        <v>517</v>
+      </c>
+      <c r="K5" t="s">
         <v>512</v>
       </c>
-      <c r="G5" t="s">
+      <c r="L5" t="s">
+        <v>518</v>
+      </c>
+      <c r="M5" t="s">
+        <v>519</v>
+      </c>
+      <c r="N5" t="s">
         <v>513</v>
       </c>
-      <c r="H5" t="s">
-        <v>514</v>
-      </c>
-      <c r="I5" t="s">
-        <v>515</v>
-      </c>
-      <c r="J5" t="s">
-        <v>516</v>
-      </c>
-      <c r="K5" t="s">
-        <v>511</v>
-      </c>
-      <c r="L5" t="s">
-        <v>517</v>
-      </c>
-      <c r="M5" t="s">
-        <v>518</v>
-      </c>
-      <c r="N5" t="s">
-        <v>512</v>
-      </c>
       <c r="O5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -7131,49 +7147,49 @@
         <v>52</v>
       </c>
       <c r="D6" t="s">
+        <v>524</v>
+      </c>
+      <c r="E6" t="s">
+        <v>512</v>
+      </c>
+      <c r="F6" t="s">
+        <v>520</v>
+      </c>
+      <c r="G6" t="s">
+        <v>525</v>
+      </c>
+      <c r="H6" t="s">
+        <v>515</v>
+      </c>
+      <c r="I6" t="s">
+        <v>516</v>
+      </c>
+      <c r="J6" t="s">
+        <v>517</v>
+      </c>
+      <c r="K6" t="s">
+        <v>512</v>
+      </c>
+      <c r="L6" t="s">
+        <v>518</v>
+      </c>
+      <c r="M6" t="s">
+        <v>519</v>
+      </c>
+      <c r="N6" t="s">
+        <v>513</v>
+      </c>
+      <c r="O6" t="s">
+        <v>520</v>
+      </c>
+      <c r="P6" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>522</v>
+      </c>
+      <c r="R6" t="s">
         <v>523</v>
-      </c>
-      <c r="E6" t="s">
-        <v>511</v>
-      </c>
-      <c r="F6" t="s">
-        <v>519</v>
-      </c>
-      <c r="G6" t="s">
-        <v>524</v>
-      </c>
-      <c r="H6" t="s">
-        <v>514</v>
-      </c>
-      <c r="I6" t="s">
-        <v>515</v>
-      </c>
-      <c r="J6" t="s">
-        <v>516</v>
-      </c>
-      <c r="K6" t="s">
-        <v>511</v>
-      </c>
-      <c r="L6" t="s">
-        <v>517</v>
-      </c>
-      <c r="M6" t="s">
-        <v>518</v>
-      </c>
-      <c r="N6" t="s">
-        <v>512</v>
-      </c>
-      <c r="O6" t="s">
-        <v>519</v>
-      </c>
-      <c r="P6" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>521</v>
-      </c>
-      <c r="R6" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -7184,49 +7200,49 @@
         <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G7" t="s">
+        <v>527</v>
+      </c>
+      <c r="H7" t="s">
+        <v>515</v>
+      </c>
+      <c r="I7" t="s">
+        <v>516</v>
+      </c>
+      <c r="J7" t="s">
+        <v>517</v>
+      </c>
+      <c r="K7" t="s">
+        <v>512</v>
+      </c>
+      <c r="L7" t="s">
+        <v>518</v>
+      </c>
+      <c r="M7" t="s">
+        <v>519</v>
+      </c>
+      <c r="N7" t="s">
+        <v>513</v>
+      </c>
+      <c r="O7" t="s">
         <v>520</v>
       </c>
-      <c r="G7" t="s">
-        <v>526</v>
-      </c>
-      <c r="H7" t="s">
-        <v>514</v>
-      </c>
-      <c r="I7" t="s">
-        <v>515</v>
-      </c>
-      <c r="J7" t="s">
-        <v>516</v>
-      </c>
-      <c r="K7" t="s">
-        <v>511</v>
-      </c>
-      <c r="L7" t="s">
-        <v>517</v>
-      </c>
-      <c r="M7" t="s">
-        <v>518</v>
-      </c>
-      <c r="N7" t="s">
-        <v>512</v>
-      </c>
-      <c r="O7" t="s">
-        <v>519</v>
-      </c>
       <c r="P7" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -7237,49 +7253,49 @@
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E8" t="s">
+        <v>518</v>
+      </c>
+      <c r="F8" t="s">
+        <v>519</v>
+      </c>
+      <c r="G8" t="s">
+        <v>529</v>
+      </c>
+      <c r="H8" t="s">
+        <v>515</v>
+      </c>
+      <c r="I8" t="s">
+        <v>516</v>
+      </c>
+      <c r="J8" t="s">
         <v>517</v>
       </c>
-      <c r="F8" t="s">
+      <c r="K8" t="s">
+        <v>512</v>
+      </c>
+      <c r="L8" t="s">
         <v>518</v>
       </c>
-      <c r="G8" t="s">
-        <v>528</v>
-      </c>
-      <c r="H8" t="s">
-        <v>514</v>
-      </c>
-      <c r="I8" t="s">
-        <v>515</v>
-      </c>
-      <c r="J8" t="s">
-        <v>516</v>
-      </c>
-      <c r="K8" t="s">
-        <v>511</v>
-      </c>
-      <c r="L8" t="s">
-        <v>517</v>
-      </c>
       <c r="M8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N8" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -7290,49 +7306,49 @@
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F9" t="s">
+        <v>521</v>
+      </c>
+      <c r="G9" t="s">
+        <v>514</v>
+      </c>
+      <c r="H9" t="s">
+        <v>531</v>
+      </c>
+      <c r="I9" t="s">
+        <v>516</v>
+      </c>
+      <c r="J9" t="s">
+        <v>517</v>
+      </c>
+      <c r="K9" t="s">
+        <v>512</v>
+      </c>
+      <c r="L9" t="s">
+        <v>518</v>
+      </c>
+      <c r="M9" t="s">
+        <v>519</v>
+      </c>
+      <c r="N9" t="s">
+        <v>513</v>
+      </c>
+      <c r="O9" t="s">
         <v>520</v>
       </c>
-      <c r="G9" t="s">
-        <v>513</v>
-      </c>
-      <c r="H9" t="s">
-        <v>530</v>
-      </c>
-      <c r="I9" t="s">
-        <v>515</v>
-      </c>
-      <c r="J9" t="s">
-        <v>516</v>
-      </c>
-      <c r="K9" t="s">
-        <v>511</v>
-      </c>
-      <c r="L9" t="s">
-        <v>517</v>
-      </c>
-      <c r="M9" t="s">
-        <v>518</v>
-      </c>
-      <c r="N9" t="s">
-        <v>512</v>
-      </c>
-      <c r="O9" t="s">
-        <v>519</v>
-      </c>
       <c r="P9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -7343,49 +7359,49 @@
         <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E10" t="s">
+        <v>518</v>
+      </c>
+      <c r="F10" t="s">
+        <v>513</v>
+      </c>
+      <c r="G10" t="s">
+        <v>514</v>
+      </c>
+      <c r="H10" t="s">
+        <v>533</v>
+      </c>
+      <c r="I10" t="s">
+        <v>516</v>
+      </c>
+      <c r="J10" t="s">
         <v>517</v>
       </c>
-      <c r="F10" t="s">
+      <c r="K10" t="s">
         <v>512</v>
       </c>
-      <c r="G10" t="s">
+      <c r="L10" t="s">
+        <v>518</v>
+      </c>
+      <c r="M10" t="s">
+        <v>519</v>
+      </c>
+      <c r="N10" t="s">
         <v>513</v>
       </c>
-      <c r="H10" t="s">
-        <v>532</v>
-      </c>
-      <c r="I10" t="s">
-        <v>515</v>
-      </c>
-      <c r="J10" t="s">
-        <v>516</v>
-      </c>
-      <c r="K10" t="s">
-        <v>511</v>
-      </c>
-      <c r="L10" t="s">
-        <v>517</v>
-      </c>
-      <c r="M10" t="s">
-        <v>518</v>
-      </c>
-      <c r="N10" t="s">
-        <v>512</v>
-      </c>
       <c r="O10" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -7396,49 +7412,49 @@
         <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F11" t="s">
+        <v>523</v>
+      </c>
+      <c r="G11" t="s">
+        <v>525</v>
+      </c>
+      <c r="H11" t="s">
+        <v>531</v>
+      </c>
+      <c r="I11" t="s">
+        <v>516</v>
+      </c>
+      <c r="J11" t="s">
+        <v>517</v>
+      </c>
+      <c r="K11" t="s">
+        <v>512</v>
+      </c>
+      <c r="L11" t="s">
+        <v>518</v>
+      </c>
+      <c r="M11" t="s">
+        <v>519</v>
+      </c>
+      <c r="N11" t="s">
+        <v>513</v>
+      </c>
+      <c r="O11" t="s">
+        <v>520</v>
+      </c>
+      <c r="P11" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q11" t="s">
         <v>522</v>
       </c>
-      <c r="G11" t="s">
-        <v>524</v>
-      </c>
-      <c r="H11" t="s">
-        <v>530</v>
-      </c>
-      <c r="I11" t="s">
-        <v>515</v>
-      </c>
-      <c r="J11" t="s">
-        <v>516</v>
-      </c>
-      <c r="K11" t="s">
-        <v>511</v>
-      </c>
-      <c r="L11" t="s">
-        <v>517</v>
-      </c>
-      <c r="M11" t="s">
-        <v>518</v>
-      </c>
-      <c r="N11" t="s">
-        <v>512</v>
-      </c>
-      <c r="O11" t="s">
-        <v>519</v>
-      </c>
-      <c r="P11" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>521</v>
-      </c>
       <c r="R11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -7449,49 +7465,49 @@
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F12" t="s">
+        <v>513</v>
+      </c>
+      <c r="G12" t="s">
+        <v>525</v>
+      </c>
+      <c r="H12" t="s">
+        <v>533</v>
+      </c>
+      <c r="I12" t="s">
+        <v>516</v>
+      </c>
+      <c r="J12" t="s">
+        <v>517</v>
+      </c>
+      <c r="K12" t="s">
         <v>512</v>
       </c>
-      <c r="G12" t="s">
-        <v>524</v>
-      </c>
-      <c r="H12" t="s">
-        <v>532</v>
-      </c>
-      <c r="I12" t="s">
-        <v>515</v>
-      </c>
-      <c r="J12" t="s">
-        <v>516</v>
-      </c>
-      <c r="K12" t="s">
-        <v>511</v>
-      </c>
       <c r="L12" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N12" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q12" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -7502,49 +7518,49 @@
         <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E13" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F13" t="s">
+        <v>523</v>
+      </c>
+      <c r="G13" t="s">
+        <v>527</v>
+      </c>
+      <c r="H13" t="s">
+        <v>531</v>
+      </c>
+      <c r="I13" t="s">
+        <v>516</v>
+      </c>
+      <c r="J13" t="s">
+        <v>517</v>
+      </c>
+      <c r="K13" t="s">
+        <v>512</v>
+      </c>
+      <c r="L13" t="s">
+        <v>518</v>
+      </c>
+      <c r="M13" t="s">
+        <v>519</v>
+      </c>
+      <c r="N13" t="s">
+        <v>513</v>
+      </c>
+      <c r="O13" t="s">
+        <v>520</v>
+      </c>
+      <c r="P13" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q13" t="s">
         <v>522</v>
       </c>
-      <c r="G13" t="s">
-        <v>526</v>
-      </c>
-      <c r="H13" t="s">
-        <v>530</v>
-      </c>
-      <c r="I13" t="s">
-        <v>515</v>
-      </c>
-      <c r="J13" t="s">
-        <v>516</v>
-      </c>
-      <c r="K13" t="s">
-        <v>511</v>
-      </c>
-      <c r="L13" t="s">
-        <v>517</v>
-      </c>
-      <c r="M13" t="s">
-        <v>518</v>
-      </c>
-      <c r="N13" t="s">
-        <v>512</v>
-      </c>
-      <c r="O13" t="s">
-        <v>519</v>
-      </c>
-      <c r="P13" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>521</v>
-      </c>
       <c r="R13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -7555,49 +7571,49 @@
         <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E14" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F14" t="s">
+        <v>513</v>
+      </c>
+      <c r="G14" t="s">
+        <v>527</v>
+      </c>
+      <c r="H14" t="s">
+        <v>533</v>
+      </c>
+      <c r="I14" t="s">
+        <v>516</v>
+      </c>
+      <c r="J14" t="s">
+        <v>517</v>
+      </c>
+      <c r="K14" t="s">
         <v>512</v>
       </c>
-      <c r="G14" t="s">
-        <v>526</v>
-      </c>
-      <c r="H14" t="s">
-        <v>532</v>
-      </c>
-      <c r="I14" t="s">
-        <v>515</v>
-      </c>
-      <c r="J14" t="s">
-        <v>516</v>
-      </c>
-      <c r="K14" t="s">
-        <v>511</v>
-      </c>
       <c r="L14" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M14" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N14" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O14" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P14" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q14" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R14" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -7608,49 +7624,49 @@
         <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E15" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F15" t="s">
+        <v>513</v>
+      </c>
+      <c r="G15" t="s">
+        <v>529</v>
+      </c>
+      <c r="H15" t="s">
+        <v>531</v>
+      </c>
+      <c r="I15" t="s">
+        <v>516</v>
+      </c>
+      <c r="J15" t="s">
+        <v>517</v>
+      </c>
+      <c r="K15" t="s">
         <v>512</v>
       </c>
-      <c r="G15" t="s">
-        <v>528</v>
-      </c>
-      <c r="H15" t="s">
-        <v>530</v>
-      </c>
-      <c r="I15" t="s">
-        <v>515</v>
-      </c>
-      <c r="J15" t="s">
-        <v>516</v>
-      </c>
-      <c r="K15" t="s">
-        <v>511</v>
-      </c>
       <c r="L15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M15" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N15" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q15" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -7658,52 +7674,52 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D16" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E16" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F16" t="s">
+        <v>522</v>
+      </c>
+      <c r="G16" t="s">
+        <v>529</v>
+      </c>
+      <c r="H16" t="s">
+        <v>533</v>
+      </c>
+      <c r="I16" t="s">
+        <v>516</v>
+      </c>
+      <c r="J16" t="s">
+        <v>517</v>
+      </c>
+      <c r="K16" t="s">
+        <v>512</v>
+      </c>
+      <c r="L16" t="s">
+        <v>518</v>
+      </c>
+      <c r="M16" t="s">
+        <v>519</v>
+      </c>
+      <c r="N16" t="s">
+        <v>513</v>
+      </c>
+      <c r="O16" t="s">
+        <v>520</v>
+      </c>
+      <c r="P16" t="s">
         <v>521</v>
       </c>
-      <c r="G16" t="s">
-        <v>528</v>
-      </c>
-      <c r="H16" t="s">
-        <v>532</v>
-      </c>
-      <c r="I16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J16" t="s">
-        <v>516</v>
-      </c>
-      <c r="K16" t="s">
-        <v>511</v>
-      </c>
-      <c r="L16" t="s">
-        <v>517</v>
-      </c>
-      <c r="M16" t="s">
-        <v>518</v>
-      </c>
-      <c r="N16" t="s">
-        <v>512</v>
-      </c>
-      <c r="O16" t="s">
-        <v>519</v>
-      </c>
-      <c r="P16" t="s">
-        <v>520</v>
-      </c>
       <c r="Q16" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R16" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -7731,10 +7747,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -7748,7 +7764,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -7765,12 +7781,12 @@
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D3" t="s">
-        <v>544</v>
-      </c>
-      <c r="E3" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7867,8 +7883,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>545</v>
+      <c r="A1" s="5" t="s">
+        <v>546</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>22</v>
@@ -7882,24 +7898,24 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3"/>
+      <c r="A2" s="5"/>
       <c r="B2" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>19</v>
@@ -7908,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7996,16 +8012,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8043,16 +8059,16 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8063,13 +8079,13 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8080,13 +8096,13 @@
         <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8097,13 +8113,13 @@
         <v>150</v>
       </c>
       <c r="D7" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F7" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8114,13 +8130,13 @@
         <v>200</v>
       </c>
       <c r="D8" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F8" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8131,13 +8147,13 @@
         <v>300</v>
       </c>
       <c r="D9" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E9" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F9" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8148,13 +8164,13 @@
         <v>450</v>
       </c>
       <c r="D10" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F10" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8165,13 +8181,13 @@
         <v>1000</v>
       </c>
       <c r="D11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8182,13 +8198,13 @@
         <v>2500</v>
       </c>
       <c r="D12" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -8199,13 +8215,165 @@
         <v>12500</v>
       </c>
       <c r="D13" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E13" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F13" t="s">
-        <v>586</v>
+        <v>587</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="5.25" customWidth="1"/>
+    <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
+    <col min="5" max="5" width="28.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="39.3333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>588</v>
+      </c>
+      <c r="F1" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" t="s">
+        <v>590</v>
+      </c>
+      <c r="F5" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="604">
   <si>
     <t>##var</t>
   </si>
@@ -1809,10 +1809,46 @@
     <t>PlateAssetPath</t>
   </si>
   <si>
+    <t>边框</t>
+  </si>
+  <si>
+    <t>底板</t>
+  </si>
+  <si>
     <t>UI\ItemUI\Frame_Legendary.png</t>
   </si>
   <si>
     <t>UI\ItemUI\Plate_Legendary.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Epic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Epic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Rare.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Rare.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Common.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Common.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Special1.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Special1.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Special2.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Special2.png</t>
   </si>
 </sst>
 </file>
@@ -8303,6 +8339,12 @@
       <c r="D4" t="s">
         <v>36</v>
       </c>
+      <c r="E4" t="s">
+        <v>590</v>
+      </c>
+      <c r="F4" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5">
@@ -8315,10 +8357,10 @@
         <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F5" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8331,6 +8373,12 @@
       <c r="D6" s="4" t="s">
         <v>48</v>
       </c>
+      <c r="E6" t="s">
+        <v>594</v>
+      </c>
+      <c r="F6" t="s">
+        <v>595</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7">
@@ -8342,6 +8390,12 @@
       <c r="D7" s="4" t="s">
         <v>91</v>
       </c>
+      <c r="E7" t="s">
+        <v>596</v>
+      </c>
+      <c r="F7" t="s">
+        <v>597</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8">
@@ -8353,6 +8407,12 @@
       <c r="D8" s="4" t="s">
         <v>366</v>
       </c>
+      <c r="E8" t="s">
+        <v>598</v>
+      </c>
+      <c r="F8" t="s">
+        <v>599</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9">
@@ -8364,6 +8424,12 @@
       <c r="D9" s="4" t="s">
         <v>446</v>
       </c>
+      <c r="E9" t="s">
+        <v>600</v>
+      </c>
+      <c r="F9" t="s">
+        <v>601</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10">
@@ -8374,6 +8440,12 @@
       </c>
       <c r="D10" s="4" t="s">
         <v>452</v>
+      </c>
+      <c r="E10" t="s">
+        <v>602</v>
+      </c>
+      <c r="F10" t="s">
+        <v>603</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -13,7 +13,7 @@
     <sheet name="BlindBox" sheetId="4" r:id="rId4"/>
     <sheet name="GameDevelopConfig" sheetId="5" r:id="rId5"/>
     <sheet name="PayTable" sheetId="6" r:id="rId6"/>
-    <sheet name="Rarity" sheetId="7" r:id="rId7"/>
+    <sheet name="RarityUI" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
     <t>ItemType</t>
   </si>
   <si>
-    <t>Rarity</t>
+    <t>ItemRarity</t>
   </si>
   <si>
     <t>SortOrder</t>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="6"/>
+    <workbookView windowWidth="29868" windowHeight="13451"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -4639,13 +4639,13 @@
         <v>300</v>
       </c>
       <c r="H45">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="M45" t="s">
         <v>205</v>
@@ -5129,13 +5129,13 @@
         <v>300</v>
       </c>
       <c r="H59">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="M59" t="s">
         <v>262</v>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,7 @@
     <sheet name="GameDevelopConfig" sheetId="5" r:id="rId5"/>
     <sheet name="PayTable" sheetId="6" r:id="rId6"/>
     <sheet name="RarityUI" sheetId="7" r:id="rId7"/>
+    <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="615">
   <si>
     <t>##var</t>
   </si>
@@ -107,7 +108,7 @@
     <t>内部名称方便记忆</t>
   </si>
   <si>
-    <t>排序权重，数字越大约靠前</t>
+    <t>排序权重，数字越小约靠前</t>
   </si>
   <si>
     <t>盲盒权重</t>
@@ -1455,6 +1456,9 @@
     <t>North Korea国际制裁/政治</t>
   </si>
   <si>
+    <t>卡面</t>
+  </si>
+  <si>
     <t>SY</t>
   </si>
   <si>
@@ -1849,6 +1853,36 @@
   </si>
   <si>
     <t>UI\ItemUI\Plate_Special2.png</t>
+  </si>
+  <si>
+    <t>TabName</t>
+  </si>
+  <si>
+    <t>*ItemTypeList</t>
+  </si>
+  <si>
+    <t>list,EItemType</t>
+  </si>
+  <si>
+    <t>包含类型</t>
+  </si>
+  <si>
+    <t>在标签栏的顺序</t>
+  </si>
+  <si>
+    <t>Hat</t>
+  </si>
+  <si>
+    <t>Eye</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>Theme</t>
+  </si>
+  <si>
+    <t>Card</t>
   </si>
 </sst>
 </file>
@@ -2479,11 +2513,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3117,7 +3151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" ht="121.8" spans="1:16">
+    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:16">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -3126,28 +3160,28 @@
       <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6613,303 +6647,312 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="3">
         <v>1</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="3" spans="2:13">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>2</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="3">
         <v>2</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="4" spans="2:13">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>3</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="3">
         <v>4</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="3" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="3">
         <v>8</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>5</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4" t="s">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="3">
         <v>16</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="7" spans="2:13">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>6</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4" t="s">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="3">
         <v>32</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="8" spans="2:13">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>7</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="3">
         <v>64</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="9" spans="2:13">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>8</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="3">
         <v>128</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="10" spans="2:13">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>9</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="3">
         <v>256</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="11" spans="2:13">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>10</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11" s="3">
         <v>512</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="3" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="12" spans="2:13">
-      <c r="J12" s="4" t="s">
+      <c r="B12" t="s">
+        <v>418</v>
+      </c>
+      <c r="C12" t="s">
         <v>472</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="L12" s="4">
+      <c r="K12" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="L12" s="3">
         <v>1024</v>
       </c>
-      <c r="M12" s="4" t="s">
-        <v>474</v>
+      <c r="M12" s="3" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="13" spans="2:13">
-      <c r="J13" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="K13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="L13" s="4">
+      <c r="K13" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="L13" s="3">
         <v>2048</v>
       </c>
-      <c r="M13" s="4" t="s">
-        <v>477</v>
+      <c r="M13" s="3" t="s">
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -6951,49 +6994,49 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Q1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="R1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -7058,10 +7101,10 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -7074,52 +7117,52 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="Q4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="R4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -7127,52 +7170,52 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F5" t="s">
+        <v>514</v>
+      </c>
+      <c r="G5" t="s">
+        <v>515</v>
+      </c>
+      <c r="H5" t="s">
+        <v>516</v>
+      </c>
+      <c r="I5" t="s">
+        <v>517</v>
+      </c>
+      <c r="J5" t="s">
+        <v>518</v>
+      </c>
+      <c r="K5" t="s">
         <v>513</v>
       </c>
-      <c r="G5" t="s">
+      <c r="L5" t="s">
+        <v>519</v>
+      </c>
+      <c r="M5" t="s">
+        <v>520</v>
+      </c>
+      <c r="N5" t="s">
         <v>514</v>
       </c>
-      <c r="H5" t="s">
-        <v>515</v>
-      </c>
-      <c r="I5" t="s">
-        <v>516</v>
-      </c>
-      <c r="J5" t="s">
-        <v>517</v>
-      </c>
-      <c r="K5" t="s">
-        <v>512</v>
-      </c>
-      <c r="L5" t="s">
-        <v>518</v>
-      </c>
-      <c r="M5" t="s">
-        <v>519</v>
-      </c>
-      <c r="N5" t="s">
-        <v>513</v>
-      </c>
       <c r="O5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="R5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -7183,49 +7226,49 @@
         <v>52</v>
       </c>
       <c r="D6" t="s">
+        <v>525</v>
+      </c>
+      <c r="E6" t="s">
+        <v>513</v>
+      </c>
+      <c r="F6" t="s">
+        <v>521</v>
+      </c>
+      <c r="G6" t="s">
+        <v>526</v>
+      </c>
+      <c r="H6" t="s">
+        <v>516</v>
+      </c>
+      <c r="I6" t="s">
+        <v>517</v>
+      </c>
+      <c r="J6" t="s">
+        <v>518</v>
+      </c>
+      <c r="K6" t="s">
+        <v>513</v>
+      </c>
+      <c r="L6" t="s">
+        <v>519</v>
+      </c>
+      <c r="M6" t="s">
+        <v>520</v>
+      </c>
+      <c r="N6" t="s">
+        <v>514</v>
+      </c>
+      <c r="O6" t="s">
+        <v>521</v>
+      </c>
+      <c r="P6" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>523</v>
+      </c>
+      <c r="R6" t="s">
         <v>524</v>
-      </c>
-      <c r="E6" t="s">
-        <v>512</v>
-      </c>
-      <c r="F6" t="s">
-        <v>520</v>
-      </c>
-      <c r="G6" t="s">
-        <v>525</v>
-      </c>
-      <c r="H6" t="s">
-        <v>515</v>
-      </c>
-      <c r="I6" t="s">
-        <v>516</v>
-      </c>
-      <c r="J6" t="s">
-        <v>517</v>
-      </c>
-      <c r="K6" t="s">
-        <v>512</v>
-      </c>
-      <c r="L6" t="s">
-        <v>518</v>
-      </c>
-      <c r="M6" t="s">
-        <v>519</v>
-      </c>
-      <c r="N6" t="s">
-        <v>513</v>
-      </c>
-      <c r="O6" t="s">
-        <v>520</v>
-      </c>
-      <c r="P6" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>522</v>
-      </c>
-      <c r="R6" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -7236,49 +7279,49 @@
         <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E7" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F7" t="s">
+        <v>522</v>
+      </c>
+      <c r="G7" t="s">
+        <v>528</v>
+      </c>
+      <c r="H7" t="s">
+        <v>516</v>
+      </c>
+      <c r="I7" t="s">
+        <v>517</v>
+      </c>
+      <c r="J7" t="s">
+        <v>518</v>
+      </c>
+      <c r="K7" t="s">
+        <v>513</v>
+      </c>
+      <c r="L7" t="s">
+        <v>519</v>
+      </c>
+      <c r="M7" t="s">
+        <v>520</v>
+      </c>
+      <c r="N7" t="s">
+        <v>514</v>
+      </c>
+      <c r="O7" t="s">
         <v>521</v>
       </c>
-      <c r="G7" t="s">
-        <v>527</v>
-      </c>
-      <c r="H7" t="s">
-        <v>515</v>
-      </c>
-      <c r="I7" t="s">
-        <v>516</v>
-      </c>
-      <c r="J7" t="s">
-        <v>517</v>
-      </c>
-      <c r="K7" t="s">
-        <v>512</v>
-      </c>
-      <c r="L7" t="s">
-        <v>518</v>
-      </c>
-      <c r="M7" t="s">
-        <v>519</v>
-      </c>
-      <c r="N7" t="s">
-        <v>513</v>
-      </c>
-      <c r="O7" t="s">
-        <v>520</v>
-      </c>
       <c r="P7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="R7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -7289,49 +7332,49 @@
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E8" t="s">
+        <v>519</v>
+      </c>
+      <c r="F8" t="s">
+        <v>520</v>
+      </c>
+      <c r="G8" t="s">
+        <v>530</v>
+      </c>
+      <c r="H8" t="s">
+        <v>516</v>
+      </c>
+      <c r="I8" t="s">
+        <v>517</v>
+      </c>
+      <c r="J8" t="s">
         <v>518</v>
       </c>
-      <c r="F8" t="s">
+      <c r="K8" t="s">
+        <v>513</v>
+      </c>
+      <c r="L8" t="s">
         <v>519</v>
       </c>
-      <c r="G8" t="s">
-        <v>529</v>
-      </c>
-      <c r="H8" t="s">
-        <v>515</v>
-      </c>
-      <c r="I8" t="s">
-        <v>516</v>
-      </c>
-      <c r="J8" t="s">
-        <v>517</v>
-      </c>
-      <c r="K8" t="s">
-        <v>512</v>
-      </c>
-      <c r="L8" t="s">
-        <v>518</v>
-      </c>
       <c r="M8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N8" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="R8" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -7342,49 +7385,49 @@
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F9" t="s">
+        <v>522</v>
+      </c>
+      <c r="G9" t="s">
+        <v>515</v>
+      </c>
+      <c r="H9" t="s">
+        <v>532</v>
+      </c>
+      <c r="I9" t="s">
+        <v>517</v>
+      </c>
+      <c r="J9" t="s">
+        <v>518</v>
+      </c>
+      <c r="K9" t="s">
+        <v>513</v>
+      </c>
+      <c r="L9" t="s">
+        <v>519</v>
+      </c>
+      <c r="M9" t="s">
+        <v>520</v>
+      </c>
+      <c r="N9" t="s">
+        <v>514</v>
+      </c>
+      <c r="O9" t="s">
         <v>521</v>
       </c>
-      <c r="G9" t="s">
-        <v>514</v>
-      </c>
-      <c r="H9" t="s">
-        <v>531</v>
-      </c>
-      <c r="I9" t="s">
-        <v>516</v>
-      </c>
-      <c r="J9" t="s">
-        <v>517</v>
-      </c>
-      <c r="K9" t="s">
-        <v>512</v>
-      </c>
-      <c r="L9" t="s">
-        <v>518</v>
-      </c>
-      <c r="M9" t="s">
-        <v>519</v>
-      </c>
-      <c r="N9" t="s">
-        <v>513</v>
-      </c>
-      <c r="O9" t="s">
-        <v>520</v>
-      </c>
       <c r="P9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="R9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -7395,49 +7438,49 @@
         <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E10" t="s">
+        <v>519</v>
+      </c>
+      <c r="F10" t="s">
+        <v>514</v>
+      </c>
+      <c r="G10" t="s">
+        <v>515</v>
+      </c>
+      <c r="H10" t="s">
+        <v>534</v>
+      </c>
+      <c r="I10" t="s">
+        <v>517</v>
+      </c>
+      <c r="J10" t="s">
         <v>518</v>
       </c>
-      <c r="F10" t="s">
+      <c r="K10" t="s">
         <v>513</v>
       </c>
-      <c r="G10" t="s">
+      <c r="L10" t="s">
+        <v>519</v>
+      </c>
+      <c r="M10" t="s">
+        <v>520</v>
+      </c>
+      <c r="N10" t="s">
         <v>514</v>
       </c>
-      <c r="H10" t="s">
-        <v>533</v>
-      </c>
-      <c r="I10" t="s">
-        <v>516</v>
-      </c>
-      <c r="J10" t="s">
-        <v>517</v>
-      </c>
-      <c r="K10" t="s">
-        <v>512</v>
-      </c>
-      <c r="L10" t="s">
-        <v>518</v>
-      </c>
-      <c r="M10" t="s">
-        <v>519</v>
-      </c>
-      <c r="N10" t="s">
-        <v>513</v>
-      </c>
       <c r="O10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="R10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -7448,49 +7491,49 @@
         <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F11" t="s">
+        <v>524</v>
+      </c>
+      <c r="G11" t="s">
+        <v>526</v>
+      </c>
+      <c r="H11" t="s">
+        <v>532</v>
+      </c>
+      <c r="I11" t="s">
+        <v>517</v>
+      </c>
+      <c r="J11" t="s">
+        <v>518</v>
+      </c>
+      <c r="K11" t="s">
+        <v>513</v>
+      </c>
+      <c r="L11" t="s">
+        <v>519</v>
+      </c>
+      <c r="M11" t="s">
+        <v>520</v>
+      </c>
+      <c r="N11" t="s">
+        <v>514</v>
+      </c>
+      <c r="O11" t="s">
+        <v>521</v>
+      </c>
+      <c r="P11" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q11" t="s">
         <v>523</v>
       </c>
-      <c r="G11" t="s">
-        <v>525</v>
-      </c>
-      <c r="H11" t="s">
-        <v>531</v>
-      </c>
-      <c r="I11" t="s">
-        <v>516</v>
-      </c>
-      <c r="J11" t="s">
-        <v>517</v>
-      </c>
-      <c r="K11" t="s">
-        <v>512</v>
-      </c>
-      <c r="L11" t="s">
-        <v>518</v>
-      </c>
-      <c r="M11" t="s">
-        <v>519</v>
-      </c>
-      <c r="N11" t="s">
-        <v>513</v>
-      </c>
-      <c r="O11" t="s">
-        <v>520</v>
-      </c>
-      <c r="P11" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>522</v>
-      </c>
       <c r="R11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -7501,49 +7544,49 @@
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E12" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F12" t="s">
+        <v>514</v>
+      </c>
+      <c r="G12" t="s">
+        <v>526</v>
+      </c>
+      <c r="H12" t="s">
+        <v>534</v>
+      </c>
+      <c r="I12" t="s">
+        <v>517</v>
+      </c>
+      <c r="J12" t="s">
+        <v>518</v>
+      </c>
+      <c r="K12" t="s">
         <v>513</v>
       </c>
-      <c r="G12" t="s">
-        <v>525</v>
-      </c>
-      <c r="H12" t="s">
-        <v>533</v>
-      </c>
-      <c r="I12" t="s">
-        <v>516</v>
-      </c>
-      <c r="J12" t="s">
-        <v>517</v>
-      </c>
-      <c r="K12" t="s">
-        <v>512</v>
-      </c>
       <c r="L12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N12" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P12" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q12" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="R12" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -7554,49 +7597,49 @@
         <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F13" t="s">
+        <v>524</v>
+      </c>
+      <c r="G13" t="s">
+        <v>528</v>
+      </c>
+      <c r="H13" t="s">
+        <v>532</v>
+      </c>
+      <c r="I13" t="s">
+        <v>517</v>
+      </c>
+      <c r="J13" t="s">
+        <v>518</v>
+      </c>
+      <c r="K13" t="s">
+        <v>513</v>
+      </c>
+      <c r="L13" t="s">
+        <v>519</v>
+      </c>
+      <c r="M13" t="s">
+        <v>520</v>
+      </c>
+      <c r="N13" t="s">
+        <v>514</v>
+      </c>
+      <c r="O13" t="s">
+        <v>521</v>
+      </c>
+      <c r="P13" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q13" t="s">
         <v>523</v>
       </c>
-      <c r="G13" t="s">
-        <v>527</v>
-      </c>
-      <c r="H13" t="s">
-        <v>531</v>
-      </c>
-      <c r="I13" t="s">
-        <v>516</v>
-      </c>
-      <c r="J13" t="s">
-        <v>517</v>
-      </c>
-      <c r="K13" t="s">
-        <v>512</v>
-      </c>
-      <c r="L13" t="s">
-        <v>518</v>
-      </c>
-      <c r="M13" t="s">
-        <v>519</v>
-      </c>
-      <c r="N13" t="s">
-        <v>513</v>
-      </c>
-      <c r="O13" t="s">
-        <v>520</v>
-      </c>
-      <c r="P13" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>522</v>
-      </c>
       <c r="R13" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -7607,49 +7650,49 @@
         <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E14" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F14" t="s">
+        <v>514</v>
+      </c>
+      <c r="G14" t="s">
+        <v>528</v>
+      </c>
+      <c r="H14" t="s">
+        <v>534</v>
+      </c>
+      <c r="I14" t="s">
+        <v>517</v>
+      </c>
+      <c r="J14" t="s">
+        <v>518</v>
+      </c>
+      <c r="K14" t="s">
         <v>513</v>
       </c>
-      <c r="G14" t="s">
-        <v>527</v>
-      </c>
-      <c r="H14" t="s">
-        <v>533</v>
-      </c>
-      <c r="I14" t="s">
-        <v>516</v>
-      </c>
-      <c r="J14" t="s">
-        <v>517</v>
-      </c>
-      <c r="K14" t="s">
-        <v>512</v>
-      </c>
       <c r="L14" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M14" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N14" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O14" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P14" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q14" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="R14" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -7660,49 +7703,49 @@
         <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E15" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F15" t="s">
+        <v>514</v>
+      </c>
+      <c r="G15" t="s">
+        <v>530</v>
+      </c>
+      <c r="H15" t="s">
+        <v>532</v>
+      </c>
+      <c r="I15" t="s">
+        <v>517</v>
+      </c>
+      <c r="J15" t="s">
+        <v>518</v>
+      </c>
+      <c r="K15" t="s">
         <v>513</v>
       </c>
-      <c r="G15" t="s">
-        <v>529</v>
-      </c>
-      <c r="H15" t="s">
-        <v>531</v>
-      </c>
-      <c r="I15" t="s">
-        <v>516</v>
-      </c>
-      <c r="J15" t="s">
-        <v>517</v>
-      </c>
-      <c r="K15" t="s">
-        <v>512</v>
-      </c>
       <c r="L15" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N15" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P15" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="R15" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -7710,52 +7753,52 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D16" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E16" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F16" t="s">
+        <v>523</v>
+      </c>
+      <c r="G16" t="s">
+        <v>530</v>
+      </c>
+      <c r="H16" t="s">
+        <v>534</v>
+      </c>
+      <c r="I16" t="s">
+        <v>517</v>
+      </c>
+      <c r="J16" t="s">
+        <v>518</v>
+      </c>
+      <c r="K16" t="s">
+        <v>513</v>
+      </c>
+      <c r="L16" t="s">
+        <v>519</v>
+      </c>
+      <c r="M16" t="s">
+        <v>520</v>
+      </c>
+      <c r="N16" t="s">
+        <v>514</v>
+      </c>
+      <c r="O16" t="s">
+        <v>521</v>
+      </c>
+      <c r="P16" t="s">
         <v>522</v>
       </c>
-      <c r="G16" t="s">
-        <v>529</v>
-      </c>
-      <c r="H16" t="s">
-        <v>533</v>
-      </c>
-      <c r="I16" t="s">
-        <v>516</v>
-      </c>
-      <c r="J16" t="s">
-        <v>517</v>
-      </c>
-      <c r="K16" t="s">
-        <v>512</v>
-      </c>
-      <c r="L16" t="s">
-        <v>518</v>
-      </c>
-      <c r="M16" t="s">
-        <v>519</v>
-      </c>
-      <c r="N16" t="s">
-        <v>513</v>
-      </c>
-      <c r="O16" t="s">
-        <v>520</v>
-      </c>
-      <c r="P16" t="s">
-        <v>521</v>
-      </c>
       <c r="Q16" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="R16" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -7783,10 +7826,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -7800,7 +7843,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -7817,12 +7860,12 @@
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D3" t="s">
-        <v>545</v>
-      </c>
-      <c r="E3" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7920,60 +7963,60 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="B1" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5"/>
-      <c r="B2" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>549</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="C3" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="4"/>
+      <c r="C4" s="3"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="4"/>
+      <c r="C5" s="3"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
@@ -7986,7 +8029,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="4"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
@@ -7999,7 +8042,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="4"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
@@ -8011,14 +8054,14 @@
     <row r="11" spans="1:5">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="4"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="4"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
@@ -8048,16 +8091,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8095,16 +8138,16 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8115,13 +8158,13 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F5" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8132,13 +8175,13 @@
         <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8149,13 +8192,13 @@
         <v>150</v>
       </c>
       <c r="D7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E7" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F7" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8166,13 +8209,13 @@
         <v>200</v>
       </c>
       <c r="D8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E8" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F8" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8183,13 +8226,13 @@
         <v>300</v>
       </c>
       <c r="D9" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E9" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F9" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8200,13 +8243,13 @@
         <v>450</v>
       </c>
       <c r="D10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E10" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F10" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8217,13 +8260,13 @@
         <v>1000</v>
       </c>
       <c r="D11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8234,13 +8277,13 @@
         <v>2500</v>
       </c>
       <c r="D12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -8251,13 +8294,13 @@
         <v>12500</v>
       </c>
       <c r="D13" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E13" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F13" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -8292,10 +8335,10 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8324,7 +8367,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -8340,113 +8383,330 @@
         <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F5" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F6" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F7" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>366</v>
       </c>
       <c r="E8" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>446</v>
       </c>
       <c r="E9" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F9" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>452</v>
       </c>
       <c r="E10" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F10" t="s">
-        <v>603</v>
-      </c>
+        <v>604</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="21.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>605</v>
+      </c>
+      <c r="D1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>608</v>
+      </c>
+      <c r="E3" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4">
+        <v>1001</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5">
+        <v>1002</v>
+      </c>
+      <c r="C5" t="s">
+        <v>610</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6">
+        <v>1003</v>
+      </c>
+      <c r="C6" t="s">
+        <v>611</v>
+      </c>
+      <c r="D6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7">
+        <v>1004</v>
+      </c>
+      <c r="C7" t="s">
+        <v>612</v>
+      </c>
+      <c r="D7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="D8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="D9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10">
+        <v>1005</v>
+      </c>
+      <c r="C10" t="s">
+        <v>613</v>
+      </c>
+      <c r="D10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="D11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="D12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13">
+        <v>1006</v>
+      </c>
+      <c r="C13" t="s">
+        <v>614</v>
+      </c>
+      <c r="D13" t="s">
+        <v>413</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="D14" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="3:4">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="3:4">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="3:4">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="3:4">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="3:4">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="3:4">
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="3:4">
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="3:4">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" spans="3:4">
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -1858,7 +1858,7 @@
     <t>TabName</t>
   </si>
   <si>
-    <t>*ItemTypeList</t>
+    <t>*TabItemTypeList</t>
   </si>
   <si>
     <t>list,EItemType</t>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="7"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="618">
   <si>
     <t>##var</t>
   </si>
@@ -1492,10 +1492,13 @@
     <t>Head</t>
   </si>
   <si>
-    <t>ClawLucky_Left_Back</t>
-  </si>
-  <si>
-    <t>ClawLucky_Right_Palms</t>
+    <t>Claw_Left_Back</t>
+  </si>
+  <si>
+    <t>Claw_Right_Palms</t>
+  </si>
+  <si>
+    <t>Tongue_Regular</t>
   </si>
   <si>
     <t>Ears_Happy</t>
@@ -1549,6 +1552,9 @@
     <t>狗右爪</t>
   </si>
   <si>
+    <t>舌头</t>
+  </si>
+  <si>
     <t>高兴耳朵</t>
   </si>
   <si>
@@ -1591,10 +1597,13 @@
     <t>Head_Chubby.png</t>
   </si>
   <si>
-    <t>Claw_Lucky_Left.tres</t>
-  </si>
-  <si>
-    <t>Claw_Lucky_Right.tres</t>
+    <t>Claw_Lucky_Left.png</t>
+  </si>
+  <si>
+    <t>Claw_Lucky_Right.png</t>
+  </si>
+  <si>
+    <t>Tongue_Regular.png</t>
   </si>
   <si>
     <t>Ears_Plane.png</t>
@@ -6964,28 +6973,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
     <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
     <col min="4" max="6" width="21.9166666666667" customWidth="1"/>
-    <col min="7" max="7" width="30.1666666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
     <col min="8" max="8" width="16.5833333333333" customWidth="1"/>
     <col min="9" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="10" width="20.8333333333333" customWidth="1"/>
-    <col min="11" max="11" width="14.5" customWidth="1"/>
-    <col min="12" max="12" width="13.4166666666667" customWidth="1"/>
-    <col min="13" max="13" width="14.3333333333333" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="14.8333333333333" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="15.4166666666667" customWidth="1"/>
-    <col min="18" max="18" width="13.4166666666667" customWidth="1"/>
+    <col min="10" max="11" width="20.8333333333333" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="13.4166666666667" customWidth="1"/>
+    <col min="14" max="14" width="14.3333333333333" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="14.8333333333333" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="15.4166666666667" customWidth="1"/>
+    <col min="19" max="19" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7038,8 +7047,11 @@
       <c r="R1" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="S1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -7092,8 +7104,11 @@
       <c r="R2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" ht="34.8" spans="1:18">
+      <c r="S2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="34.8" spans="1:19">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -7101,15 +7116,15 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:19">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -7117,108 +7132,114 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Q4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="R4" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>511</v>
+      </c>
+      <c r="S4" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D5" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E5" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G5" t="s">
+        <v>517</v>
+      </c>
+      <c r="H5" t="s">
+        <v>518</v>
+      </c>
+      <c r="I5" t="s">
+        <v>519</v>
+      </c>
+      <c r="J5" t="s">
+        <v>520</v>
+      </c>
+      <c r="K5" t="s">
+        <v>521</v>
+      </c>
+      <c r="L5" t="s">
         <v>515</v>
       </c>
-      <c r="H5" t="s">
+      <c r="M5" t="s">
+        <v>522</v>
+      </c>
+      <c r="N5" t="s">
+        <v>523</v>
+      </c>
+      <c r="O5" t="s">
         <v>516</v>
       </c>
-      <c r="I5" t="s">
-        <v>517</v>
-      </c>
-      <c r="J5" t="s">
-        <v>518</v>
-      </c>
-      <c r="K5" t="s">
-        <v>513</v>
-      </c>
-      <c r="L5" t="s">
-        <v>519</v>
-      </c>
-      <c r="M5" t="s">
-        <v>520</v>
-      </c>
-      <c r="N5" t="s">
-        <v>514</v>
-      </c>
-      <c r="O5" t="s">
-        <v>521</v>
-      </c>
       <c r="P5" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Q5" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="R5" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>526</v>
+      </c>
+      <c r="S5" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -7226,52 +7247,55 @@
         <v>52</v>
       </c>
       <c r="D6" t="s">
+        <v>528</v>
+      </c>
+      <c r="E6" t="s">
+        <v>515</v>
+      </c>
+      <c r="F6" t="s">
+        <v>524</v>
+      </c>
+      <c r="G6" t="s">
+        <v>529</v>
+      </c>
+      <c r="H6" t="s">
+        <v>518</v>
+      </c>
+      <c r="I6" t="s">
+        <v>519</v>
+      </c>
+      <c r="J6" t="s">
+        <v>520</v>
+      </c>
+      <c r="K6" t="s">
+        <v>521</v>
+      </c>
+      <c r="L6" t="s">
+        <v>515</v>
+      </c>
+      <c r="M6" t="s">
+        <v>522</v>
+      </c>
+      <c r="N6" t="s">
+        <v>523</v>
+      </c>
+      <c r="O6" t="s">
+        <v>516</v>
+      </c>
+      <c r="P6" t="s">
+        <v>524</v>
+      </c>
+      <c r="Q6" t="s">
         <v>525</v>
       </c>
-      <c r="E6" t="s">
-        <v>513</v>
-      </c>
-      <c r="F6" t="s">
-        <v>521</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="R6" t="s">
         <v>526</v>
       </c>
-      <c r="H6" t="s">
-        <v>516</v>
-      </c>
-      <c r="I6" t="s">
-        <v>517</v>
-      </c>
-      <c r="J6" t="s">
-        <v>518</v>
-      </c>
-      <c r="K6" t="s">
-        <v>513</v>
-      </c>
-      <c r="L6" t="s">
-        <v>519</v>
-      </c>
-      <c r="M6" t="s">
-        <v>520</v>
-      </c>
-      <c r="N6" t="s">
-        <v>514</v>
-      </c>
-      <c r="O6" t="s">
-        <v>521</v>
-      </c>
-      <c r="P6" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>523</v>
-      </c>
-      <c r="R6" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="S6" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -7279,52 +7303,55 @@
         <v>56</v>
       </c>
       <c r="D7" t="s">
+        <v>530</v>
+      </c>
+      <c r="E7" t="s">
+        <v>515</v>
+      </c>
+      <c r="F7" t="s">
+        <v>525</v>
+      </c>
+      <c r="G7" t="s">
+        <v>531</v>
+      </c>
+      <c r="H7" t="s">
+        <v>518</v>
+      </c>
+      <c r="I7" t="s">
+        <v>519</v>
+      </c>
+      <c r="J7" t="s">
+        <v>520</v>
+      </c>
+      <c r="K7" t="s">
+        <v>521</v>
+      </c>
+      <c r="L7" t="s">
+        <v>515</v>
+      </c>
+      <c r="M7" t="s">
+        <v>522</v>
+      </c>
+      <c r="N7" t="s">
+        <v>523</v>
+      </c>
+      <c r="O7" t="s">
+        <v>516</v>
+      </c>
+      <c r="P7" t="s">
+        <v>524</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>525</v>
+      </c>
+      <c r="R7" t="s">
+        <v>526</v>
+      </c>
+      <c r="S7" t="s">
         <v>527</v>
       </c>
-      <c r="E7" t="s">
-        <v>513</v>
-      </c>
-      <c r="F7" t="s">
-        <v>522</v>
-      </c>
-      <c r="G7" t="s">
-        <v>528</v>
-      </c>
-      <c r="H7" t="s">
-        <v>516</v>
-      </c>
-      <c r="I7" t="s">
-        <v>517</v>
-      </c>
-      <c r="J7" t="s">
-        <v>518</v>
-      </c>
-      <c r="K7" t="s">
-        <v>513</v>
-      </c>
-      <c r="L7" t="s">
-        <v>519</v>
-      </c>
-      <c r="M7" t="s">
-        <v>520</v>
-      </c>
-      <c r="N7" t="s">
-        <v>514</v>
-      </c>
-      <c r="O7" t="s">
-        <v>521</v>
-      </c>
-      <c r="P7" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>523</v>
-      </c>
-      <c r="R7" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+    </row>
+    <row r="8" spans="1:19">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -7332,52 +7359,55 @@
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E8" t="s">
+        <v>522</v>
+      </c>
+      <c r="F8" t="s">
+        <v>523</v>
+      </c>
+      <c r="G8" t="s">
+        <v>533</v>
+      </c>
+      <c r="H8" t="s">
+        <v>518</v>
+      </c>
+      <c r="I8" t="s">
         <v>519</v>
       </c>
-      <c r="F8" t="s">
+      <c r="J8" t="s">
         <v>520</v>
       </c>
-      <c r="G8" t="s">
-        <v>530</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="K8" t="s">
+        <v>521</v>
+      </c>
+      <c r="L8" t="s">
+        <v>515</v>
+      </c>
+      <c r="M8" t="s">
+        <v>522</v>
+      </c>
+      <c r="N8" t="s">
+        <v>523</v>
+      </c>
+      <c r="O8" t="s">
         <v>516</v>
       </c>
-      <c r="I8" t="s">
-        <v>517</v>
-      </c>
-      <c r="J8" t="s">
-        <v>518</v>
-      </c>
-      <c r="K8" t="s">
-        <v>513</v>
-      </c>
-      <c r="L8" t="s">
-        <v>519</v>
-      </c>
-      <c r="M8" t="s">
-        <v>520</v>
-      </c>
-      <c r="N8" t="s">
-        <v>514</v>
-      </c>
-      <c r="O8" t="s">
-        <v>521</v>
-      </c>
       <c r="P8" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Q8" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="R8" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+        <v>526</v>
+      </c>
+      <c r="S8" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -7385,52 +7415,55 @@
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E9" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F9" t="s">
+        <v>525</v>
+      </c>
+      <c r="G9" t="s">
+        <v>517</v>
+      </c>
+      <c r="H9" t="s">
+        <v>535</v>
+      </c>
+      <c r="I9" t="s">
+        <v>519</v>
+      </c>
+      <c r="J9" t="s">
+        <v>520</v>
+      </c>
+      <c r="K9" t="s">
+        <v>521</v>
+      </c>
+      <c r="L9" t="s">
+        <v>515</v>
+      </c>
+      <c r="M9" t="s">
         <v>522</v>
       </c>
-      <c r="G9" t="s">
-        <v>515</v>
-      </c>
-      <c r="H9" t="s">
-        <v>532</v>
-      </c>
-      <c r="I9" t="s">
-        <v>517</v>
-      </c>
-      <c r="J9" t="s">
-        <v>518</v>
-      </c>
-      <c r="K9" t="s">
-        <v>513</v>
-      </c>
-      <c r="L9" t="s">
-        <v>519</v>
-      </c>
-      <c r="M9" t="s">
-        <v>520</v>
-      </c>
       <c r="N9" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="O9" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="P9" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Q9" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="R9" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+        <v>526</v>
+      </c>
+      <c r="S9" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -7438,52 +7471,55 @@
         <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E10" t="s">
+        <v>522</v>
+      </c>
+      <c r="F10" t="s">
+        <v>516</v>
+      </c>
+      <c r="G10" t="s">
+        <v>517</v>
+      </c>
+      <c r="H10" t="s">
+        <v>537</v>
+      </c>
+      <c r="I10" t="s">
         <v>519</v>
       </c>
-      <c r="F10" t="s">
-        <v>514</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="J10" t="s">
+        <v>520</v>
+      </c>
+      <c r="K10" t="s">
+        <v>521</v>
+      </c>
+      <c r="L10" t="s">
         <v>515</v>
       </c>
-      <c r="H10" t="s">
-        <v>534</v>
-      </c>
-      <c r="I10" t="s">
-        <v>517</v>
-      </c>
-      <c r="J10" t="s">
-        <v>518</v>
-      </c>
-      <c r="K10" t="s">
-        <v>513</v>
-      </c>
-      <c r="L10" t="s">
-        <v>519</v>
-      </c>
       <c r="M10" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N10" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="O10" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="P10" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Q10" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="R10" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+        <v>526</v>
+      </c>
+      <c r="S10" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="B11">
         <v>1007</v>
       </c>
@@ -7491,52 +7527,55 @@
         <v>71</v>
       </c>
       <c r="D11" t="s">
+        <v>538</v>
+      </c>
+      <c r="E11" t="s">
+        <v>515</v>
+      </c>
+      <c r="F11" t="s">
+        <v>527</v>
+      </c>
+      <c r="G11" t="s">
+        <v>529</v>
+      </c>
+      <c r="H11" t="s">
         <v>535</v>
       </c>
-      <c r="E11" t="s">
-        <v>513</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="I11" t="s">
+        <v>519</v>
+      </c>
+      <c r="J11" t="s">
+        <v>520</v>
+      </c>
+      <c r="K11" t="s">
+        <v>521</v>
+      </c>
+      <c r="L11" t="s">
+        <v>515</v>
+      </c>
+      <c r="M11" t="s">
+        <v>522</v>
+      </c>
+      <c r="N11" t="s">
+        <v>523</v>
+      </c>
+      <c r="O11" t="s">
+        <v>516</v>
+      </c>
+      <c r="P11" t="s">
         <v>524</v>
       </c>
-      <c r="G11" t="s">
+      <c r="Q11" t="s">
+        <v>525</v>
+      </c>
+      <c r="R11" t="s">
         <v>526</v>
       </c>
-      <c r="H11" t="s">
-        <v>532</v>
-      </c>
-      <c r="I11" t="s">
-        <v>517</v>
-      </c>
-      <c r="J11" t="s">
-        <v>518</v>
-      </c>
-      <c r="K11" t="s">
-        <v>513</v>
-      </c>
-      <c r="L11" t="s">
-        <v>519</v>
-      </c>
-      <c r="M11" t="s">
-        <v>520</v>
-      </c>
-      <c r="N11" t="s">
-        <v>514</v>
-      </c>
-      <c r="O11" t="s">
-        <v>521</v>
-      </c>
-      <c r="P11" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>523</v>
-      </c>
-      <c r="R11" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="S11" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="B12">
         <v>1008</v>
       </c>
@@ -7544,52 +7583,55 @@
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E12" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F12" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G12" t="s">
+        <v>529</v>
+      </c>
+      <c r="H12" t="s">
+        <v>537</v>
+      </c>
+      <c r="I12" t="s">
+        <v>519</v>
+      </c>
+      <c r="J12" t="s">
+        <v>520</v>
+      </c>
+      <c r="K12" t="s">
+        <v>521</v>
+      </c>
+      <c r="L12" t="s">
+        <v>515</v>
+      </c>
+      <c r="M12" t="s">
+        <v>522</v>
+      </c>
+      <c r="N12" t="s">
+        <v>523</v>
+      </c>
+      <c r="O12" t="s">
+        <v>516</v>
+      </c>
+      <c r="P12" t="s">
+        <v>524</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>525</v>
+      </c>
+      <c r="R12" t="s">
         <v>526</v>
       </c>
-      <c r="H12" t="s">
-        <v>534</v>
-      </c>
-      <c r="I12" t="s">
-        <v>517</v>
-      </c>
-      <c r="J12" t="s">
-        <v>518</v>
-      </c>
-      <c r="K12" t="s">
-        <v>513</v>
-      </c>
-      <c r="L12" t="s">
-        <v>519</v>
-      </c>
-      <c r="M12" t="s">
-        <v>520</v>
-      </c>
-      <c r="N12" t="s">
-        <v>514</v>
-      </c>
-      <c r="O12" t="s">
-        <v>521</v>
-      </c>
-      <c r="P12" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>523</v>
-      </c>
-      <c r="R12" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="S12" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="B13">
         <v>1009</v>
       </c>
@@ -7597,52 +7639,55 @@
         <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E13" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F13" t="s">
+        <v>527</v>
+      </c>
+      <c r="G13" t="s">
+        <v>531</v>
+      </c>
+      <c r="H13" t="s">
+        <v>535</v>
+      </c>
+      <c r="I13" t="s">
+        <v>519</v>
+      </c>
+      <c r="J13" t="s">
+        <v>520</v>
+      </c>
+      <c r="K13" t="s">
+        <v>521</v>
+      </c>
+      <c r="L13" t="s">
+        <v>515</v>
+      </c>
+      <c r="M13" t="s">
+        <v>522</v>
+      </c>
+      <c r="N13" t="s">
+        <v>523</v>
+      </c>
+      <c r="O13" t="s">
+        <v>516</v>
+      </c>
+      <c r="P13" t="s">
         <v>524</v>
       </c>
-      <c r="G13" t="s">
-        <v>528</v>
-      </c>
-      <c r="H13" t="s">
-        <v>532</v>
-      </c>
-      <c r="I13" t="s">
-        <v>517</v>
-      </c>
-      <c r="J13" t="s">
-        <v>518</v>
-      </c>
-      <c r="K13" t="s">
-        <v>513</v>
-      </c>
-      <c r="L13" t="s">
-        <v>519</v>
-      </c>
-      <c r="M13" t="s">
-        <v>520</v>
-      </c>
-      <c r="N13" t="s">
-        <v>514</v>
-      </c>
-      <c r="O13" t="s">
-        <v>521</v>
-      </c>
-      <c r="P13" t="s">
-        <v>522</v>
-      </c>
       <c r="Q13" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="R13" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>526</v>
+      </c>
+      <c r="S13" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="B14">
         <v>1010</v>
       </c>
@@ -7650,52 +7695,55 @@
         <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E14" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F14" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G14" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="H14" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="I14" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J14" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K14" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="L14" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="M14" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N14" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="O14" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="P14" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Q14" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="R14" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+        <v>526</v>
+      </c>
+      <c r="S14" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="B15">
         <v>1011</v>
       </c>
@@ -7703,102 +7751,108 @@
         <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E15" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F15" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G15" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="H15" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I15" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J15" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K15" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="L15" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="M15" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N15" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="O15" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="P15" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Q15" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="R15" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+        <v>526</v>
+      </c>
+      <c r="S15" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D16" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E16" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F16" t="s">
+        <v>526</v>
+      </c>
+      <c r="G16" t="s">
+        <v>533</v>
+      </c>
+      <c r="H16" t="s">
+        <v>537</v>
+      </c>
+      <c r="I16" t="s">
+        <v>519</v>
+      </c>
+      <c r="J16" t="s">
+        <v>520</v>
+      </c>
+      <c r="K16" t="s">
+        <v>521</v>
+      </c>
+      <c r="L16" t="s">
+        <v>515</v>
+      </c>
+      <c r="M16" t="s">
+        <v>522</v>
+      </c>
+      <c r="N16" t="s">
         <v>523</v>
       </c>
-      <c r="G16" t="s">
-        <v>530</v>
-      </c>
-      <c r="H16" t="s">
-        <v>534</v>
-      </c>
-      <c r="I16" t="s">
-        <v>517</v>
-      </c>
-      <c r="J16" t="s">
-        <v>518</v>
-      </c>
-      <c r="K16" t="s">
-        <v>513</v>
-      </c>
-      <c r="L16" t="s">
-        <v>519</v>
-      </c>
-      <c r="M16" t="s">
-        <v>520</v>
-      </c>
-      <c r="N16" t="s">
-        <v>514</v>
-      </c>
       <c r="O16" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="P16" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Q16" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="R16" t="s">
-        <v>524</v>
+        <v>526</v>
+      </c>
+      <c r="S16" t="s">
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -7826,10 +7880,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -7843,7 +7897,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -7860,10 +7914,10 @@
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D3" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>42</v>
@@ -7963,7 +8017,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>22</v>
@@ -7979,22 +8033,22 @@
     <row r="2" spans="1:5">
       <c r="A2" s="5"/>
       <c r="B2" s="3" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>19</v>
@@ -8003,7 +8057,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8091,16 +8145,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="F1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8138,16 +8192,16 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D4" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E4" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F4" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8158,13 +8212,13 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E5" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="F5" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8175,13 +8229,13 @@
         <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E6" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F6" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8192,13 +8246,13 @@
         <v>150</v>
       </c>
       <c r="D7" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E7" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="F7" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8209,13 +8263,13 @@
         <v>200</v>
       </c>
       <c r="D8" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E8" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="F8" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8226,13 +8280,13 @@
         <v>300</v>
       </c>
       <c r="D9" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E9" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F9" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8243,13 +8297,13 @@
         <v>450</v>
       </c>
       <c r="D10" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E10" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="F10" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8260,13 +8314,13 @@
         <v>1000</v>
       </c>
       <c r="D11" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E11" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F11" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8277,13 +8331,13 @@
         <v>2500</v>
       </c>
       <c r="D12" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E12" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="F12" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -8294,13 +8348,13 @@
         <v>12500</v>
       </c>
       <c r="D13" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E13" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F13" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
   </sheetData>
@@ -8335,10 +8389,10 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8383,10 +8437,10 @@
         <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F4" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8400,10 +8454,10 @@
         <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="F5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8417,10 +8471,10 @@
         <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="F6" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8434,10 +8488,10 @@
         <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="F7" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8451,10 +8505,10 @@
         <v>366</v>
       </c>
       <c r="E8" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="F8" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8468,10 +8522,10 @@
         <v>446</v>
       </c>
       <c r="E9" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F9" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8485,10 +8539,10 @@
         <v>452</v>
       </c>
       <c r="E10" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F10" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -8516,10 +8570,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E1" t="s">
         <v>5</v>
@@ -8536,7 +8590,7 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -8553,10 +8607,10 @@
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E3" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8578,7 +8632,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D5" t="s">
         <v>90</v>
@@ -8592,7 +8646,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D6" t="s">
         <v>132</v>
@@ -8606,7 +8660,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D7" t="s">
         <v>153</v>
@@ -8630,7 +8684,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D10" t="s">
         <v>204</v>
@@ -8654,7 +8708,7 @@
         <v>1006</v>
       </c>
       <c r="C13" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D13" t="s">
         <v>413</v>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -15,6 +15,7 @@
     <sheet name="PayTable" sheetId="6" r:id="rId6"/>
     <sheet name="RarityUI" sheetId="7" r:id="rId7"/>
     <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
+    <sheet name="DogReaction" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="679">
   <si>
     <t>##var</t>
   </si>
@@ -1327,6 +1328,12 @@
     <t>在全部国家隐藏</t>
   </si>
   <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
     <t>小狗头部装饰</t>
   </si>
   <si>
@@ -1342,6 +1349,12 @@
     <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
   </si>
   <si>
+    <t>Serious</t>
+  </si>
+  <si>
+    <t>严肃</t>
+  </si>
+  <si>
     <t>小狗眼部装饰</t>
   </si>
   <si>
@@ -1357,6 +1370,12 @@
     <t>United Arab Emirates赌博/宗教/酒精/色情</t>
   </si>
   <si>
+    <t>Bored</t>
+  </si>
+  <si>
+    <t>无聊</t>
+  </si>
+  <si>
     <t>手臂层的装饰</t>
   </si>
   <si>
@@ -1372,6 +1391,12 @@
     <t>Iran宗教/进化论/赌博/政治/西方文化</t>
   </si>
   <si>
+    <t>Wink</t>
+  </si>
+  <si>
+    <t>媚眼</t>
+  </si>
+  <si>
     <t>玩家手臂衣服</t>
   </si>
   <si>
@@ -1390,6 +1415,12 @@
     <t>Pakistan国家形象/政治</t>
   </si>
   <si>
+    <t>Excited</t>
+  </si>
+  <si>
+    <t>兴奋</t>
+  </si>
+  <si>
     <t>桌布</t>
   </si>
   <si>
@@ -1408,6 +1439,12 @@
     <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
   </si>
   <si>
+    <t>Starstruck</t>
+  </si>
+  <si>
+    <t>崇拜</t>
+  </si>
+  <si>
     <t>背景</t>
   </si>
   <si>
@@ -1420,6 +1457,12 @@
     <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
   </si>
   <si>
+    <t>Silent</t>
+  </si>
+  <si>
+    <t>沉默</t>
+  </si>
+  <si>
     <t>玩家手部装饰</t>
   </si>
   <si>
@@ -1432,6 +1475,12 @@
     <t>Russia赌博/LGBTQ/极端主义</t>
   </si>
   <si>
+    <t>Reject</t>
+  </si>
+  <si>
+    <t>拒绝</t>
+  </si>
+  <si>
     <t>玩家嗜好品</t>
   </si>
   <si>
@@ -1714,6 +1763,9 @@
     <t>PayoutMultiplier</t>
   </si>
   <si>
+    <t>HandRank</t>
+  </si>
+  <si>
     <t>OriginalName</t>
   </si>
   <si>
@@ -1723,6 +1775,9 @@
     <t>SafeName_CN</t>
   </si>
   <si>
+    <t>EHandRank</t>
+  </si>
+  <si>
     <t>赔率</t>
   </si>
   <si>
@@ -1735,6 +1790,9 @@
     <t>安全中文</t>
   </si>
   <si>
+    <t>JacksOrBetter</t>
+  </si>
+  <si>
     <t>Jacks or Better</t>
   </si>
   <si>
@@ -1744,6 +1802,9 @@
     <t>好犬优选</t>
   </si>
   <si>
+    <t>TwoPair</t>
+  </si>
+  <si>
     <t>Two Pair</t>
   </si>
   <si>
@@ -1753,6 +1814,9 @@
     <t>双犬配对</t>
   </si>
   <si>
+    <t>ThreeOfAKind</t>
+  </si>
+  <si>
     <t>Three of a Kind</t>
   </si>
   <si>
@@ -1780,6 +1844,9 @@
     <t>同色犬舍</t>
   </si>
   <si>
+    <t>FullHouse</t>
+  </si>
+  <si>
     <t>Full House</t>
   </si>
   <si>
@@ -1789,6 +1856,9 @@
     <t>狗狗满堂</t>
   </si>
   <si>
+    <t>FourOfAKind</t>
+  </si>
+  <si>
     <t>Four of a Kind</t>
   </si>
   <si>
@@ -1798,6 +1868,9 @@
     <t>四犬成团</t>
   </si>
   <si>
+    <t>StraightFlush</t>
+  </si>
+  <si>
     <t>Straight Flush</t>
   </si>
   <si>
@@ -1807,6 +1880,9 @@
     <t>纯种犬连击</t>
   </si>
   <si>
+    <t>RoyalFlush</t>
+  </si>
+  <si>
     <t>Royal Flush</t>
   </si>
   <si>
@@ -1892,6 +1968,114 @@
   </si>
   <si>
     <t>Card</t>
+  </si>
+  <si>
+    <t>？</t>
+  </si>
+  <si>
+    <t>枚举</t>
+  </si>
+  <si>
+    <t>注释</t>
+  </si>
+  <si>
+    <t>引用枚举</t>
+  </si>
+  <si>
+    <t>耳朵资源</t>
+  </si>
+  <si>
+    <t>眼睛资源</t>
+  </si>
+  <si>
+    <t>头饰变化</t>
+  </si>
+  <si>
+    <t>戴上眼镜</t>
+  </si>
+  <si>
+    <t>左爪子</t>
+  </si>
+  <si>
+    <t>右爪子</t>
+  </si>
+  <si>
+    <t>手背</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>手心，摆手</t>
+  </si>
+  <si>
+    <t>WaitingForBet</t>
+  </si>
+  <si>
+    <t>等待下注</t>
+  </si>
+  <si>
+    <t>默认，该品种狗默认表情</t>
+  </si>
+  <si>
+    <t>Dealt</t>
+  </si>
+  <si>
+    <t>已发牌</t>
+  </si>
+  <si>
+    <t>严肃，面无表情</t>
+  </si>
+  <si>
+    <t>Holding</t>
+  </si>
+  <si>
+    <t>选牌中</t>
+  </si>
+  <si>
+    <t>严肃，面无表情，等待玩家询问，如果玩家进行了询问，再作出相应的预测表情。如果玩家又更改了选牌，则作出拒绝回答的表情。如果玩家再次询问，则作出拒绝回答的动作。</t>
+  </si>
+  <si>
+    <t>Drawing</t>
+  </si>
+  <si>
+    <t>补牌中</t>
+  </si>
+  <si>
+    <t>Settled</t>
+  </si>
+  <si>
+    <t>结算</t>
+  </si>
+  <si>
+    <t>根据牌型优劣作出相应表情</t>
+  </si>
+  <si>
+    <t>高对</t>
+  </si>
+  <si>
+    <t>两对</t>
+  </si>
+  <si>
+    <t>三条</t>
+  </si>
+  <si>
+    <t>顺子</t>
+  </si>
+  <si>
+    <t>同花</t>
+  </si>
+  <si>
+    <t>葫芦</t>
+  </si>
+  <si>
+    <t>四条</t>
+  </si>
+  <si>
+    <t>同花顺</t>
+  </si>
+  <si>
+    <t>皇家同花顺</t>
   </si>
 </sst>
 </file>
@@ -2512,7 +2696,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2521,6 +2705,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3160,7 +3347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:16">
+    <row r="3" s="5" customFormat="1" ht="121.8" spans="1:16">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -3169,28 +3356,28 @@
       <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6648,320 +6835,335 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:M13"/>
+  <dimension ref="B2:P13"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="11.4166666666667" customWidth="1"/>
-    <col min="11" max="11" width="12.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="12.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13">
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="2:16">
+      <c r="B2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="D2" s="3">
+      <c r="E2" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="L2" s="3">
-        <v>1</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="3" spans="2:13">
-      <c r="B3" s="3" t="s">
+      <c r="O2" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16">
+      <c r="B3" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="C3" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="L3" s="3">
-        <v>2</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13">
-      <c r="B4" s="3" t="s">
+      <c r="K3" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16">
+      <c r="B4" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="D4" s="3">
-        <v>3</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="L4" s="3">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="J4" s="4">
         <v>4</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="3" t="s">
+      <c r="K4" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16">
+      <c r="B5" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="D5" s="3">
-        <v>4</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="C5" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="L5" s="3">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="J5" s="4">
         <v>8</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13">
-      <c r="B6" s="3" t="s">
+      <c r="K5" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16">
+      <c r="B6" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="D6" s="3">
-        <v>5</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="L6" s="3">
+      <c r="C6" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="J6" s="4">
         <v>16</v>
       </c>
-      <c r="M6" s="3" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="3" t="s">
+      <c r="K6" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16">
+      <c r="B7" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="D7" s="3">
-        <v>6</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="L7" s="3">
+      <c r="C7" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="J7" s="4">
         <v>32</v>
       </c>
-      <c r="M7" s="3" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="3" t="s">
+      <c r="K7" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16">
+      <c r="B8" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="D8" s="3">
-        <v>7</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="C8" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="J8" s="4">
         <v>64</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="3" t="s">
+      <c r="K8" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16">
+      <c r="B9" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="D9" s="3">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="C9" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J9" s="4">
         <v>128</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13">
-      <c r="B10" s="3" t="s">
+      <c r="K9" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16">
+      <c r="B10" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="D10" s="3">
-        <v>9</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="C10" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="J10" s="4">
         <v>256</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="3" t="s">
+      <c r="K10" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16">
+      <c r="B11" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="D11" s="3">
-        <v>10</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="L11" s="3">
+      <c r="C11" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J11" s="4">
         <v>512</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13">
+      <c r="K11" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16">
       <c r="B12" t="s">
         <v>418</v>
       </c>
       <c r="C12" t="s">
-        <v>472</v>
-      </c>
-      <c r="D12">
-        <v>11</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="L12" s="3">
+        <v>488</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="J12" s="4">
         <v>1024</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="J13" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="L13" s="3">
+      <c r="K12" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16">
+      <c r="H13" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="J13" s="4">
         <v>2048</v>
       </c>
-      <c r="M13" s="3" t="s">
-        <v>478</v>
+      <c r="K13" s="4" t="s">
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -7003,52 +7205,52 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="I1" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="J1" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="K1" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="L1" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="M1" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="N1" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="O1" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="P1" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="Q1" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="R1" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="S1" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -7116,10 +7318,10 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -7132,55 +7334,55 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="D4" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="E4" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="F4" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="G4" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="H4" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="I4" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="J4" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="K4" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
       <c r="L4" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="M4" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="N4" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="O4" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="P4" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="Q4" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="R4" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="S4" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -7188,55 +7390,55 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="D5" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="E5" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="F5" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="G5" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="H5" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="I5" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="J5" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="K5" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="L5" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="M5" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="N5" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="O5" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="P5" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="Q5" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="R5" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="S5" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -7247,52 +7449,52 @@
         <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="E6" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="F6" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="G6" t="s">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="H6" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="I6" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="J6" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="K6" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="L6" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="M6" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="N6" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="O6" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="P6" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="Q6" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="R6" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="S6" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -7303,52 +7505,52 @@
         <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="E7" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="F7" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="G7" t="s">
+        <v>547</v>
+      </c>
+      <c r="H7" t="s">
+        <v>534</v>
+      </c>
+      <c r="I7" t="s">
+        <v>535</v>
+      </c>
+      <c r="J7" t="s">
+        <v>536</v>
+      </c>
+      <c r="K7" t="s">
+        <v>537</v>
+      </c>
+      <c r="L7" t="s">
         <v>531</v>
       </c>
-      <c r="H7" t="s">
-        <v>518</v>
-      </c>
-      <c r="I7" t="s">
-        <v>519</v>
-      </c>
-      <c r="J7" t="s">
-        <v>520</v>
-      </c>
-      <c r="K7" t="s">
-        <v>521</v>
-      </c>
-      <c r="L7" t="s">
-        <v>515</v>
-      </c>
       <c r="M7" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="N7" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="O7" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="P7" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="Q7" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="R7" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="S7" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -7359,52 +7561,52 @@
         <v>60</v>
       </c>
       <c r="D8" t="s">
+        <v>548</v>
+      </c>
+      <c r="E8" t="s">
+        <v>538</v>
+      </c>
+      <c r="F8" t="s">
+        <v>539</v>
+      </c>
+      <c r="G8" t="s">
+        <v>549</v>
+      </c>
+      <c r="H8" t="s">
+        <v>534</v>
+      </c>
+      <c r="I8" t="s">
+        <v>535</v>
+      </c>
+      <c r="J8" t="s">
+        <v>536</v>
+      </c>
+      <c r="K8" t="s">
+        <v>537</v>
+      </c>
+      <c r="L8" t="s">
+        <v>531</v>
+      </c>
+      <c r="M8" t="s">
+        <v>538</v>
+      </c>
+      <c r="N8" t="s">
+        <v>539</v>
+      </c>
+      <c r="O8" t="s">
         <v>532</v>
       </c>
-      <c r="E8" t="s">
-        <v>522</v>
-      </c>
-      <c r="F8" t="s">
-        <v>523</v>
-      </c>
-      <c r="G8" t="s">
-        <v>533</v>
-      </c>
-      <c r="H8" t="s">
-        <v>518</v>
-      </c>
-      <c r="I8" t="s">
-        <v>519</v>
-      </c>
-      <c r="J8" t="s">
-        <v>520</v>
-      </c>
-      <c r="K8" t="s">
-        <v>521</v>
-      </c>
-      <c r="L8" t="s">
-        <v>515</v>
-      </c>
-      <c r="M8" t="s">
-        <v>522</v>
-      </c>
-      <c r="N8" t="s">
-        <v>523</v>
-      </c>
-      <c r="O8" t="s">
-        <v>516</v>
-      </c>
       <c r="P8" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="Q8" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="R8" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="S8" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -7415,52 +7617,52 @@
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="E9" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="F9" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="G9" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="H9" t="s">
+        <v>551</v>
+      </c>
+      <c r="I9" t="s">
         <v>535</v>
       </c>
-      <c r="I9" t="s">
-        <v>519</v>
-      </c>
       <c r="J9" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="K9" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="L9" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="M9" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="N9" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="O9" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="P9" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="Q9" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="R9" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="S9" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -7471,52 +7673,52 @@
         <v>68</v>
       </c>
       <c r="D10" t="s">
+        <v>552</v>
+      </c>
+      <c r="E10" t="s">
+        <v>538</v>
+      </c>
+      <c r="F10" t="s">
+        <v>532</v>
+      </c>
+      <c r="G10" t="s">
+        <v>533</v>
+      </c>
+      <c r="H10" t="s">
+        <v>553</v>
+      </c>
+      <c r="I10" t="s">
+        <v>535</v>
+      </c>
+      <c r="J10" t="s">
         <v>536</v>
       </c>
-      <c r="E10" t="s">
-        <v>522</v>
-      </c>
-      <c r="F10" t="s">
-        <v>516</v>
-      </c>
-      <c r="G10" t="s">
-        <v>517</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="K10" t="s">
         <v>537</v>
       </c>
-      <c r="I10" t="s">
-        <v>519</v>
-      </c>
-      <c r="J10" t="s">
-        <v>520</v>
-      </c>
-      <c r="K10" t="s">
-        <v>521</v>
-      </c>
       <c r="L10" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="M10" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="N10" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="O10" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="P10" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="Q10" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="R10" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="S10" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -7527,52 +7729,52 @@
         <v>71</v>
       </c>
       <c r="D11" t="s">
+        <v>554</v>
+      </c>
+      <c r="E11" t="s">
+        <v>531</v>
+      </c>
+      <c r="F11" t="s">
+        <v>543</v>
+      </c>
+      <c r="G11" t="s">
+        <v>545</v>
+      </c>
+      <c r="H11" t="s">
+        <v>551</v>
+      </c>
+      <c r="I11" t="s">
+        <v>535</v>
+      </c>
+      <c r="J11" t="s">
+        <v>536</v>
+      </c>
+      <c r="K11" t="s">
+        <v>537</v>
+      </c>
+      <c r="L11" t="s">
+        <v>531</v>
+      </c>
+      <c r="M11" t="s">
         <v>538</v>
       </c>
-      <c r="E11" t="s">
-        <v>515</v>
-      </c>
-      <c r="F11" t="s">
-        <v>527</v>
-      </c>
-      <c r="G11" t="s">
-        <v>529</v>
-      </c>
-      <c r="H11" t="s">
-        <v>535</v>
-      </c>
-      <c r="I11" t="s">
-        <v>519</v>
-      </c>
-      <c r="J11" t="s">
-        <v>520</v>
-      </c>
-      <c r="K11" t="s">
-        <v>521</v>
-      </c>
-      <c r="L11" t="s">
-        <v>515</v>
-      </c>
-      <c r="M11" t="s">
-        <v>522</v>
-      </c>
       <c r="N11" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="O11" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="P11" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="Q11" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="R11" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="S11" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -7583,52 +7785,52 @@
         <v>74</v>
       </c>
       <c r="D12" t="s">
+        <v>555</v>
+      </c>
+      <c r="E12" t="s">
+        <v>531</v>
+      </c>
+      <c r="F12" t="s">
+        <v>532</v>
+      </c>
+      <c r="G12" t="s">
+        <v>545</v>
+      </c>
+      <c r="H12" t="s">
+        <v>553</v>
+      </c>
+      <c r="I12" t="s">
+        <v>535</v>
+      </c>
+      <c r="J12" t="s">
+        <v>536</v>
+      </c>
+      <c r="K12" t="s">
+        <v>537</v>
+      </c>
+      <c r="L12" t="s">
+        <v>531</v>
+      </c>
+      <c r="M12" t="s">
+        <v>538</v>
+      </c>
+      <c r="N12" t="s">
         <v>539</v>
       </c>
-      <c r="E12" t="s">
-        <v>515</v>
-      </c>
-      <c r="F12" t="s">
-        <v>516</v>
-      </c>
-      <c r="G12" t="s">
-        <v>529</v>
-      </c>
-      <c r="H12" t="s">
-        <v>537</v>
-      </c>
-      <c r="I12" t="s">
-        <v>519</v>
-      </c>
-      <c r="J12" t="s">
-        <v>520</v>
-      </c>
-      <c r="K12" t="s">
-        <v>521</v>
-      </c>
-      <c r="L12" t="s">
-        <v>515</v>
-      </c>
-      <c r="M12" t="s">
-        <v>522</v>
-      </c>
-      <c r="N12" t="s">
-        <v>523</v>
-      </c>
       <c r="O12" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="P12" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="Q12" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="R12" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="S12" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -7639,52 +7841,52 @@
         <v>77</v>
       </c>
       <c r="D13" t="s">
+        <v>556</v>
+      </c>
+      <c r="E13" t="s">
+        <v>531</v>
+      </c>
+      <c r="F13" t="s">
+        <v>543</v>
+      </c>
+      <c r="G13" t="s">
+        <v>547</v>
+      </c>
+      <c r="H13" t="s">
+        <v>551</v>
+      </c>
+      <c r="I13" t="s">
+        <v>535</v>
+      </c>
+      <c r="J13" t="s">
+        <v>536</v>
+      </c>
+      <c r="K13" t="s">
+        <v>537</v>
+      </c>
+      <c r="L13" t="s">
+        <v>531</v>
+      </c>
+      <c r="M13" t="s">
+        <v>538</v>
+      </c>
+      <c r="N13" t="s">
+        <v>539</v>
+      </c>
+      <c r="O13" t="s">
+        <v>532</v>
+      </c>
+      <c r="P13" t="s">
         <v>540</v>
       </c>
-      <c r="E13" t="s">
-        <v>515</v>
-      </c>
-      <c r="F13" t="s">
-        <v>527</v>
-      </c>
-      <c r="G13" t="s">
-        <v>531</v>
-      </c>
-      <c r="H13" t="s">
-        <v>535</v>
-      </c>
-      <c r="I13" t="s">
-        <v>519</v>
-      </c>
-      <c r="J13" t="s">
-        <v>520</v>
-      </c>
-      <c r="K13" t="s">
-        <v>521</v>
-      </c>
-      <c r="L13" t="s">
-        <v>515</v>
-      </c>
-      <c r="M13" t="s">
-        <v>522</v>
-      </c>
-      <c r="N13" t="s">
-        <v>523</v>
-      </c>
-      <c r="O13" t="s">
-        <v>516</v>
-      </c>
-      <c r="P13" t="s">
-        <v>524</v>
-      </c>
       <c r="Q13" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="R13" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="S13" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -7695,52 +7897,52 @@
         <v>80</v>
       </c>
       <c r="D14" t="s">
+        <v>557</v>
+      </c>
+      <c r="E14" t="s">
+        <v>531</v>
+      </c>
+      <c r="F14" t="s">
+        <v>532</v>
+      </c>
+      <c r="G14" t="s">
+        <v>547</v>
+      </c>
+      <c r="H14" t="s">
+        <v>553</v>
+      </c>
+      <c r="I14" t="s">
+        <v>535</v>
+      </c>
+      <c r="J14" t="s">
+        <v>536</v>
+      </c>
+      <c r="K14" t="s">
+        <v>537</v>
+      </c>
+      <c r="L14" t="s">
+        <v>531</v>
+      </c>
+      <c r="M14" t="s">
+        <v>538</v>
+      </c>
+      <c r="N14" t="s">
+        <v>539</v>
+      </c>
+      <c r="O14" t="s">
+        <v>532</v>
+      </c>
+      <c r="P14" t="s">
+        <v>540</v>
+      </c>
+      <c r="Q14" t="s">
         <v>541</v>
       </c>
-      <c r="E14" t="s">
-        <v>515</v>
-      </c>
-      <c r="F14" t="s">
-        <v>516</v>
-      </c>
-      <c r="G14" t="s">
-        <v>531</v>
-      </c>
-      <c r="H14" t="s">
-        <v>537</v>
-      </c>
-      <c r="I14" t="s">
-        <v>519</v>
-      </c>
-      <c r="J14" t="s">
-        <v>520</v>
-      </c>
-      <c r="K14" t="s">
-        <v>521</v>
-      </c>
-      <c r="L14" t="s">
-        <v>515</v>
-      </c>
-      <c r="M14" t="s">
-        <v>522</v>
-      </c>
-      <c r="N14" t="s">
-        <v>523</v>
-      </c>
-      <c r="O14" t="s">
-        <v>516</v>
-      </c>
-      <c r="P14" t="s">
-        <v>524</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>525</v>
-      </c>
       <c r="R14" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="S14" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -7751,52 +7953,52 @@
         <v>83</v>
       </c>
       <c r="D15" t="s">
+        <v>558</v>
+      </c>
+      <c r="E15" t="s">
+        <v>531</v>
+      </c>
+      <c r="F15" t="s">
+        <v>532</v>
+      </c>
+      <c r="G15" t="s">
+        <v>549</v>
+      </c>
+      <c r="H15" t="s">
+        <v>551</v>
+      </c>
+      <c r="I15" t="s">
+        <v>535</v>
+      </c>
+      <c r="J15" t="s">
+        <v>536</v>
+      </c>
+      <c r="K15" t="s">
+        <v>537</v>
+      </c>
+      <c r="L15" t="s">
+        <v>531</v>
+      </c>
+      <c r="M15" t="s">
+        <v>538</v>
+      </c>
+      <c r="N15" t="s">
+        <v>539</v>
+      </c>
+      <c r="O15" t="s">
+        <v>532</v>
+      </c>
+      <c r="P15" t="s">
+        <v>540</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>541</v>
+      </c>
+      <c r="R15" t="s">
         <v>542</v>
       </c>
-      <c r="E15" t="s">
-        <v>515</v>
-      </c>
-      <c r="F15" t="s">
-        <v>516</v>
-      </c>
-      <c r="G15" t="s">
-        <v>533</v>
-      </c>
-      <c r="H15" t="s">
-        <v>535</v>
-      </c>
-      <c r="I15" t="s">
-        <v>519</v>
-      </c>
-      <c r="J15" t="s">
-        <v>520</v>
-      </c>
-      <c r="K15" t="s">
-        <v>521</v>
-      </c>
-      <c r="L15" t="s">
-        <v>515</v>
-      </c>
-      <c r="M15" t="s">
-        <v>522</v>
-      </c>
-      <c r="N15" t="s">
-        <v>523</v>
-      </c>
-      <c r="O15" t="s">
-        <v>516</v>
-      </c>
-      <c r="P15" t="s">
-        <v>524</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>525</v>
-      </c>
-      <c r="R15" t="s">
-        <v>526</v>
-      </c>
       <c r="S15" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -7804,55 +8006,55 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
+        <v>559</v>
+      </c>
+      <c r="D16" t="s">
+        <v>560</v>
+      </c>
+      <c r="E16" t="s">
+        <v>531</v>
+      </c>
+      <c r="F16" t="s">
+        <v>542</v>
+      </c>
+      <c r="G16" t="s">
+        <v>549</v>
+      </c>
+      <c r="H16" t="s">
+        <v>553</v>
+      </c>
+      <c r="I16" t="s">
+        <v>535</v>
+      </c>
+      <c r="J16" t="s">
+        <v>536</v>
+      </c>
+      <c r="K16" t="s">
+        <v>537</v>
+      </c>
+      <c r="L16" t="s">
+        <v>531</v>
+      </c>
+      <c r="M16" t="s">
+        <v>538</v>
+      </c>
+      <c r="N16" t="s">
+        <v>539</v>
+      </c>
+      <c r="O16" t="s">
+        <v>532</v>
+      </c>
+      <c r="P16" t="s">
+        <v>540</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>541</v>
+      </c>
+      <c r="R16" t="s">
+        <v>542</v>
+      </c>
+      <c r="S16" t="s">
         <v>543</v>
-      </c>
-      <c r="D16" t="s">
-        <v>544</v>
-      </c>
-      <c r="E16" t="s">
-        <v>515</v>
-      </c>
-      <c r="F16" t="s">
-        <v>526</v>
-      </c>
-      <c r="G16" t="s">
-        <v>533</v>
-      </c>
-      <c r="H16" t="s">
-        <v>537</v>
-      </c>
-      <c r="I16" t="s">
-        <v>519</v>
-      </c>
-      <c r="J16" t="s">
-        <v>520</v>
-      </c>
-      <c r="K16" t="s">
-        <v>521</v>
-      </c>
-      <c r="L16" t="s">
-        <v>515</v>
-      </c>
-      <c r="M16" t="s">
-        <v>522</v>
-      </c>
-      <c r="N16" t="s">
-        <v>523</v>
-      </c>
-      <c r="O16" t="s">
-        <v>516</v>
-      </c>
-      <c r="P16" t="s">
-        <v>524</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>525</v>
-      </c>
-      <c r="R16" t="s">
-        <v>526</v>
-      </c>
-      <c r="S16" t="s">
-        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -7880,10 +8082,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>545</v>
+        <v>561</v>
       </c>
       <c r="D1" t="s">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -7897,7 +8099,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -7914,12 +8116,12 @@
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="D3" t="s">
-        <v>549</v>
-      </c>
-      <c r="E3" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -8016,61 +8218,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="5"/>
-      <c r="B2" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>553</v>
+      <c r="A2" s="6"/>
+      <c r="B2" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="C3" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>556</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="3"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="3"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
@@ -8083,7 +8285,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="3"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
@@ -8096,7 +8298,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="3"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
@@ -8108,14 +8310,14 @@
     <row r="11" spans="1:5">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="3"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="3"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
@@ -8128,16 +8330,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="14.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="12.9166666666667" customWidth="1"/>
+    <col min="4" max="4" width="12.5833333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.75" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8145,19 +8348,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>557</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="E1" t="s">
-        <v>559</v>
+        <v>573</v>
+      </c>
+      <c r="D1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>575</v>
       </c>
       <c r="F1" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>576</v>
+      </c>
+      <c r="G1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -8167,24 +8373,27 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -8192,169 +8401,196 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>561</v>
-      </c>
-      <c r="D4" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="E4" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
       <c r="F4" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>581</v>
+      </c>
+      <c r="G4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" t="s">
-        <v>565</v>
+      <c r="D5" s="3" t="s">
+        <v>583</v>
       </c>
       <c r="E5" t="s">
-        <v>566</v>
+        <v>584</v>
       </c>
       <c r="F5" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>585</v>
+      </c>
+      <c r="G5" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" t="s">
-        <v>568</v>
+      <c r="D6" s="3" t="s">
+        <v>587</v>
       </c>
       <c r="E6" t="s">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="F6" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>589</v>
+      </c>
+      <c r="G6" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7">
         <v>150</v>
       </c>
-      <c r="D7" t="s">
-        <v>571</v>
+      <c r="D7" s="3" t="s">
+        <v>591</v>
       </c>
       <c r="E7" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="F7" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>593</v>
+      </c>
+      <c r="G7" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8">
         <v>200</v>
       </c>
-      <c r="D8" t="s">
-        <v>574</v>
+      <c r="D8" s="3" t="s">
+        <v>595</v>
       </c>
       <c r="E8" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="F8" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>596</v>
+      </c>
+      <c r="G8" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" t="s">
-        <v>577</v>
+      <c r="D9" s="3" t="s">
+        <v>598</v>
       </c>
       <c r="E9" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="F9" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>599</v>
+      </c>
+      <c r="G9" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10">
         <v>450</v>
       </c>
-      <c r="D10" t="s">
-        <v>580</v>
+      <c r="D10" s="3" t="s">
+        <v>601</v>
       </c>
       <c r="E10" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="F10" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>603</v>
+      </c>
+      <c r="G10" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11">
         <v>1000</v>
       </c>
-      <c r="D11" t="s">
-        <v>583</v>
+      <c r="D11" s="3" t="s">
+        <v>605</v>
       </c>
       <c r="E11" t="s">
-        <v>584</v>
+        <v>606</v>
       </c>
       <c r="F11" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>607</v>
+      </c>
+      <c r="G11" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12">
         <v>2500</v>
       </c>
-      <c r="D12" t="s">
-        <v>586</v>
+      <c r="D12" s="3" t="s">
+        <v>609</v>
       </c>
       <c r="E12" t="s">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="F12" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>611</v>
+      </c>
+      <c r="G12" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13">
         <v>12500</v>
       </c>
-      <c r="D13" t="s">
-        <v>589</v>
+      <c r="D13" s="3" t="s">
+        <v>613</v>
       </c>
       <c r="E13" t="s">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="F13" t="s">
-        <v>591</v>
+        <v>615</v>
+      </c>
+      <c r="G13" t="s">
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -8389,10 +8625,10 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="F1" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8421,7 +8657,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="4"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -8437,112 +8673,112 @@
         <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="F4" t="s">
-        <v>595</v>
+        <v>620</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="F5" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>598</v>
+        <v>623</v>
       </c>
       <c r="F6" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="F7" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="C8" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>366</v>
       </c>
       <c r="E8" t="s">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="F8" t="s">
-        <v>603</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>446</v>
+      <c r="C9" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>454</v>
       </c>
       <c r="E9" t="s">
-        <v>604</v>
+        <v>629</v>
       </c>
       <c r="F9" t="s">
-        <v>605</v>
+        <v>630</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>452</v>
+      <c r="C10" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>462</v>
       </c>
       <c r="E10" t="s">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="F10" t="s">
-        <v>607</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -8570,10 +8806,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="D1" t="s">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="E1" t="s">
         <v>5</v>
@@ -8590,7 +8826,7 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>610</v>
+        <v>635</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -8607,10 +8843,10 @@
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="E3" t="s">
-        <v>612</v>
+        <v>637</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8632,7 +8868,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>613</v>
+        <v>638</v>
       </c>
       <c r="D5" t="s">
         <v>90</v>
@@ -8646,7 +8882,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>614</v>
+        <v>639</v>
       </c>
       <c r="D6" t="s">
         <v>132</v>
@@ -8660,7 +8896,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>615</v>
+        <v>640</v>
       </c>
       <c r="D7" t="s">
         <v>153</v>
@@ -8684,7 +8920,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>616</v>
+        <v>641</v>
       </c>
       <c r="D10" t="s">
         <v>204</v>
@@ -8708,7 +8944,7 @@
         <v>1006</v>
       </c>
       <c r="C13" t="s">
-        <v>617</v>
+        <v>642</v>
       </c>
       <c r="D13" t="s">
         <v>413</v>
@@ -8723,44 +8959,665 @@
       </c>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="3:4">
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="4" max="5" width="12.9166666666667" customWidth="1"/>
+    <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
+    <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
+    <col min="8" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="13" width="9.58333333333333" customWidth="1"/>
+    <col min="20" max="20" width="12.9166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>643</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>644</v>
+      </c>
+      <c r="D4" t="s">
+        <v>645</v>
+      </c>
+      <c r="E4" t="s">
+        <v>646</v>
+      </c>
+      <c r="F4" t="s">
+        <v>645</v>
+      </c>
+      <c r="G4" t="s">
+        <v>647</v>
+      </c>
+      <c r="H4" t="s">
+        <v>648</v>
+      </c>
+      <c r="I4" t="s">
+        <v>649</v>
+      </c>
+      <c r="J4" t="s">
+        <v>650</v>
+      </c>
+      <c r="K4" t="s">
+        <v>651</v>
+      </c>
+      <c r="L4" t="s">
+        <v>652</v>
+      </c>
+      <c r="M4" t="s">
+        <v>520</v>
+      </c>
+      <c r="N4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D5" t="s">
+        <v>430</v>
+      </c>
+      <c r="G5" t="s">
+        <v>430</v>
+      </c>
+      <c r="H5" t="s">
+        <v>430</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>653</v>
+      </c>
+      <c r="L5" t="s">
+        <v>653</v>
+      </c>
+      <c r="M5" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G6" t="s">
+        <v>503</v>
+      </c>
+      <c r="H6" t="s">
+        <v>506</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>653</v>
+      </c>
+      <c r="L6" t="s">
+        <v>653</v>
+      </c>
+      <c r="M6" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D7" t="s">
+        <v>444</v>
+      </c>
+      <c r="G7" t="s">
+        <v>504</v>
+      </c>
+      <c r="H7" t="s">
+        <v>505</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>653</v>
+      </c>
+      <c r="L7" t="s">
+        <v>653</v>
+      </c>
+      <c r="M7" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D8" t="s">
+        <v>451</v>
+      </c>
+      <c r="G8" t="s">
+        <v>503</v>
+      </c>
+      <c r="H8" t="s">
+        <v>510</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>653</v>
+      </c>
+      <c r="L8" t="s">
+        <v>653</v>
+      </c>
+      <c r="M8" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D9" t="s">
+        <v>459</v>
+      </c>
+      <c r="G9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H9" t="s">
+        <v>507</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>653</v>
+      </c>
+      <c r="L9" t="s">
+        <v>653</v>
+      </c>
+      <c r="M9" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D10" t="s">
+        <v>467</v>
+      </c>
+      <c r="G10" t="s">
+        <v>503</v>
+      </c>
+      <c r="H10" t="s">
+        <v>508</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>653</v>
+      </c>
+      <c r="L10" t="s">
+        <v>653</v>
+      </c>
+      <c r="M10" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D11" t="s">
+        <v>473</v>
+      </c>
+      <c r="G11" t="s">
+        <v>504</v>
+      </c>
+      <c r="H11" t="s">
+        <v>505</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>653</v>
+      </c>
+      <c r="L11" t="s">
+        <v>653</v>
+      </c>
+      <c r="M11" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D12" t="s">
+        <v>479</v>
+      </c>
+      <c r="G12" t="s">
+        <v>504</v>
+      </c>
+      <c r="H12" t="s">
+        <v>509</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>655</v>
+      </c>
+      <c r="L12" t="s">
+        <v>655</v>
+      </c>
+      <c r="M12" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16">
+        <v>2001</v>
+      </c>
+      <c r="C16" t="s">
+        <v>656</v>
+      </c>
+      <c r="D16" t="s">
+        <v>657</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F16" t="s">
+        <v>430</v>
+      </c>
+      <c r="N16" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17">
+        <v>2002</v>
+      </c>
+      <c r="C17" t="s">
+        <v>659</v>
+      </c>
+      <c r="D17" t="s">
+        <v>660</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F17" t="s">
+        <v>437</v>
+      </c>
+      <c r="N17" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18">
+        <v>2003</v>
+      </c>
+      <c r="C18" t="s">
+        <v>662</v>
+      </c>
+      <c r="D18" t="s">
+        <v>663</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F18" t="s">
+        <v>437</v>
+      </c>
+      <c r="N18" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19">
+        <v>2004</v>
+      </c>
+      <c r="C19" t="s">
+        <v>665</v>
+      </c>
+      <c r="D19" t="s">
+        <v>666</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F19" t="s">
+        <v>437</v>
+      </c>
+      <c r="N19" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20">
+        <v>2005</v>
+      </c>
+      <c r="C20" t="s">
+        <v>667</v>
+      </c>
+      <c r="D20" t="s">
+        <v>668</v>
+      </c>
+      <c r="N20" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23">
+        <v>3001</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F23" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24">
+        <v>3002</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="F24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25">
+        <v>3003</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="F25" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26">
+        <v>3004</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="F26" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27">
+        <v>3005</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="F27" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28">
+        <v>3006</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="F28" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29">
+        <v>3007</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F29" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30">
+        <v>3008</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F30" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31">
+        <v>3009</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F31" t="s">
+        <v>467</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="681">
   <si>
     <t>##var</t>
   </si>
@@ -2067,6 +2067,12 @@
   </si>
   <si>
     <t>葫芦</t>
+  </si>
+  <si>
+    <t>哈气</t>
+  </si>
+  <si>
+    <t>舌头上下略微移动</t>
   </si>
   <si>
     <t>四条</t>
@@ -2696,7 +2702,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2705,9 +2711,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3347,7 +3350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="5" customFormat="1" ht="121.8" spans="1:16">
+    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:16">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -3356,28 +3359,28 @@
       <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="4" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6843,29 +6846,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="3">
         <v>1</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>428</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -6876,29 +6879,29 @@
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="3">
         <v>2</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>435</v>
       </c>
       <c r="O3" s="3" t="s">
@@ -6909,29 +6912,29 @@
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>4</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>442</v>
       </c>
       <c r="O4" s="3" t="s">
@@ -6942,29 +6945,29 @@
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>8</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>449</v>
       </c>
       <c r="O5" s="3" t="s">
@@ -6975,29 +6978,29 @@
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>16</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>457</v>
       </c>
       <c r="O6" s="3" t="s">
@@ -7008,29 +7011,29 @@
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="3">
         <v>32</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>465</v>
       </c>
       <c r="O7" s="3" t="s">
@@ -7041,22 +7044,22 @@
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <v>64</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>471</v>
       </c>
       <c r="O8" s="3" t="s">
@@ -7067,22 +7070,22 @@
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="3">
         <v>128</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>477</v>
       </c>
       <c r="O9" s="3" t="s">
@@ -7093,42 +7096,42 @@
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="3">
         <v>256</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="3">
         <v>512</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>487</v>
       </c>
     </row>
@@ -7139,30 +7142,30 @@
       <c r="C12" t="s">
         <v>488</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="3">
         <v>1024</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="3">
         <v>2048</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>494</v>
       </c>
     </row>
@@ -8121,7 +8124,7 @@
       <c r="D3" t="s">
         <v>565</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>42</v>
       </c>
     </row>
@@ -8218,30 +8221,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="6"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>569</v>
       </c>
     </row>
@@ -8252,7 +8255,7 @@
       <c r="B3" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="b">
@@ -8265,14 +8268,14 @@
     <row r="4" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="4"/>
+      <c r="C4" s="3"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="4"/>
+      <c r="C5" s="3"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
@@ -8285,7 +8288,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="4"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
@@ -8298,7 +8301,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="4"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
@@ -8310,14 +8313,14 @@
     <row r="11" spans="1:5">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="4"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="4"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
@@ -8657,7 +8660,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -8683,10 +8686,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E5" t="s">
@@ -8700,10 +8703,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E6" t="s">
@@ -8717,10 +8720,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E7" t="s">
@@ -8734,10 +8737,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>366</v>
       </c>
       <c r="E8" t="s">
@@ -8751,10 +8754,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>454</v>
       </c>
       <c r="E9" t="s">
@@ -8768,10 +8771,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>462</v>
       </c>
       <c r="E10" t="s">
@@ -8959,44 +8962,44 @@
       </c>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" spans="3:4">
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9567,6 +9570,12 @@
       <c r="F28" t="s">
         <v>459</v>
       </c>
+      <c r="M28" t="s">
+        <v>676</v>
+      </c>
+      <c r="N28" t="s">
+        <v>677</v>
+      </c>
     </row>
     <row r="29" spans="2:14">
       <c r="B29">
@@ -9576,7 +9585,7 @@
         <v>605</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>466</v>
@@ -9593,7 +9602,7 @@
         <v>609</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>466</v>
@@ -9610,13 +9619,19 @@
         <v>613</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>466</v>
       </c>
       <c r="F31" t="s">
         <v>467</v>
+      </c>
+      <c r="M31" t="s">
+        <v>676</v>
+      </c>
+      <c r="N31" t="s">
+        <v>677</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="705">
   <si>
     <t>##var</t>
   </si>
@@ -1970,7 +1970,13 @@
     <t>Card</t>
   </si>
   <si>
-    <t>？</t>
+    <t>DogReactionTrigger</t>
+  </si>
+  <si>
+    <t>EDogReactionTrigger</t>
+  </si>
+  <si>
+    <t>复用引用枚举所对应的美术资源参数。其自身的值可以Override引用的值</t>
   </si>
   <si>
     <t>枚举</t>
@@ -2012,7 +2018,7 @@
     <t>WaitingForBet</t>
   </si>
   <si>
-    <t>等待下注</t>
+    <t>等待下注时</t>
   </si>
   <si>
     <t>默认，该品种狗默认表情</t>
@@ -2021,52 +2027,109 @@
     <t>Dealt</t>
   </si>
   <si>
-    <t>已发牌</t>
+    <t>等待玩家选牌</t>
+  </si>
+  <si>
+    <t>WaitingForHint</t>
+  </si>
+  <si>
+    <t>玩家选牌中等待询问时</t>
+  </si>
+  <si>
+    <t>严肃，面无表情，等待玩家询问</t>
+  </si>
+  <si>
+    <t>HintResult</t>
+  </si>
+  <si>
+    <t>展示询问结果</t>
+  </si>
+  <si>
+    <t>Bespoke</t>
+  </si>
+  <si>
+    <t>约定</t>
+  </si>
+  <si>
+    <t>如果玩家进行了询问，再作出相应的预测表情。</t>
+  </si>
+  <si>
+    <t>HintExhausted</t>
+  </si>
+  <si>
+    <t>询问机会用尽</t>
+  </si>
+  <si>
+    <t>如果玩家又更改了选牌，则作出拒绝回答的表情。</t>
+  </si>
+  <si>
+    <t>RefuseHint</t>
+  </si>
+  <si>
+    <t>拒绝询问</t>
+  </si>
+  <si>
+    <t>如果玩家再次询问，则作出拒绝回答的动作。</t>
+  </si>
+  <si>
+    <t>Drawing</t>
+  </si>
+  <si>
+    <t>补牌中</t>
   </si>
   <si>
     <t>严肃，面无表情</t>
   </si>
   <si>
-    <t>Holding</t>
-  </si>
-  <si>
-    <t>选牌中</t>
-  </si>
-  <si>
-    <t>严肃，面无表情，等待玩家询问，如果玩家进行了询问，再作出相应的预测表情。如果玩家又更改了选牌，则作出拒绝回答的表情。如果玩家再次询问，则作出拒绝回答的动作。</t>
-  </si>
-  <si>
-    <t>Drawing</t>
-  </si>
-  <si>
-    <t>补牌中</t>
-  </si>
-  <si>
     <t>Settled</t>
   </si>
   <si>
-    <t>结算</t>
+    <t>看到结算结果</t>
   </si>
   <si>
     <t>根据牌型优劣作出相应表情</t>
   </si>
   <si>
-    <t>高对</t>
-  </si>
-  <si>
-    <t>两对</t>
-  </si>
-  <si>
-    <t>三条</t>
-  </si>
-  <si>
-    <t>顺子</t>
-  </si>
-  <si>
-    <t>同花</t>
-  </si>
-  <si>
-    <t>葫芦</t>
+    <t>SawNothing</t>
+  </si>
+  <si>
+    <t>看到坏牌</t>
+  </si>
+  <si>
+    <t>SawJacksOrBetter</t>
+  </si>
+  <si>
+    <t>看到高对</t>
+  </si>
+  <si>
+    <t>SawTwoPair</t>
+  </si>
+  <si>
+    <t>看到两对</t>
+  </si>
+  <si>
+    <t>SawThreeOfAKind</t>
+  </si>
+  <si>
+    <t>看到三条</t>
+  </si>
+  <si>
+    <t>SawStraight</t>
+  </si>
+  <si>
+    <t>看到顺子</t>
+  </si>
+  <si>
+    <t>SawFlush</t>
+  </si>
+  <si>
+    <t>看到同花</t>
+  </si>
+  <si>
+    <t>SawFullHouse</t>
+  </si>
+  <si>
+    <t>看到葫芦</t>
   </si>
   <si>
     <t>哈气</t>
@@ -2075,13 +2138,22 @@
     <t>舌头上下略微移动</t>
   </si>
   <si>
-    <t>四条</t>
-  </si>
-  <si>
-    <t>同花顺</t>
-  </si>
-  <si>
-    <t>皇家同花顺</t>
+    <t>SawFourOfAKind</t>
+  </si>
+  <si>
+    <t>看到四条</t>
+  </si>
+  <si>
+    <t>SawStraightFlush</t>
+  </si>
+  <si>
+    <t>看到同花顺</t>
+  </si>
+  <si>
+    <t>SawRoyalFlush</t>
+  </si>
+  <si>
+    <t>看到皇家同花顺</t>
   </si>
 </sst>
 </file>
@@ -2702,7 +2774,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2711,6 +2783,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3350,7 +3428,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" ht="121.8" spans="1:16">
+    <row r="3" s="6" customFormat="1" ht="121.8" spans="1:16">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -3359,28 +3437,28 @@
       <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6846,292 +6924,292 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="5">
         <v>1</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="5" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="5">
         <v>2</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="5" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="5">
         <v>4</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="5" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="5">
         <v>8</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="O5" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="P5" s="5" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="5">
         <v>16</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="O6" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="P6" s="5" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="5">
         <v>32</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="O7" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="P7" s="5" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="5">
         <v>64</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="O8" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="P8" s="5" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="5">
         <v>128</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="O9" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="P9" s="5" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="5">
         <v>256</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="5" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="5">
         <v>512</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="5" t="s">
         <v>487</v>
       </c>
     </row>
@@ -7142,30 +7220,30 @@
       <c r="C12" t="s">
         <v>488</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="5">
         <v>1024</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="5" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="5">
         <v>2048</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="K13" s="5" t="s">
         <v>494</v>
       </c>
     </row>
@@ -8124,7 +8202,7 @@
       <c r="D3" t="s">
         <v>565</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="6" t="s">
         <v>42</v>
       </c>
     </row>
@@ -8221,30 +8299,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="5"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="7"/>
+      <c r="B2" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>569</v>
       </c>
     </row>
@@ -8255,7 +8333,7 @@
       <c r="B3" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="b">
@@ -8268,14 +8346,14 @@
     <row r="4" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="3"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="3"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
@@ -8288,7 +8366,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="3"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
@@ -8301,7 +8379,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="3"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
@@ -8313,14 +8391,14 @@
     <row r="11" spans="1:5">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="3"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="3"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
@@ -8423,7 +8501,7 @@
       <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>583</v>
       </c>
       <c r="E5" t="s">
@@ -8443,7 +8521,7 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>587</v>
       </c>
       <c r="E6" t="s">
@@ -8463,7 +8541,7 @@
       <c r="C7">
         <v>150</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="5" t="s">
         <v>591</v>
       </c>
       <c r="E7" t="s">
@@ -8483,7 +8561,7 @@
       <c r="C8">
         <v>200</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>595</v>
       </c>
       <c r="E8" t="s">
@@ -8503,7 +8581,7 @@
       <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>598</v>
       </c>
       <c r="E9" t="s">
@@ -8523,7 +8601,7 @@
       <c r="C10">
         <v>450</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>601</v>
       </c>
       <c r="E10" t="s">
@@ -8543,7 +8621,7 @@
       <c r="C11">
         <v>1000</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="5" t="s">
         <v>605</v>
       </c>
       <c r="E11" t="s">
@@ -8563,7 +8641,7 @@
       <c r="C12">
         <v>2500</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>609</v>
       </c>
       <c r="E12" t="s">
@@ -8583,7 +8661,7 @@
       <c r="C13">
         <v>12500</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="5" t="s">
         <v>613</v>
       </c>
       <c r="E13" t="s">
@@ -8660,7 +8738,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="4"/>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -8686,10 +8764,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E5" t="s">
@@ -8703,10 +8781,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E6" t="s">
@@ -8720,10 +8798,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="5" t="s">
         <v>91</v>
       </c>
       <c r="E7" t="s">
@@ -8737,10 +8815,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>366</v>
       </c>
       <c r="E8" t="s">
@@ -8754,10 +8832,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>454</v>
       </c>
       <c r="E9" t="s">
@@ -8771,10 +8849,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>462</v>
       </c>
       <c r="E10" t="s">
@@ -8962,44 +9040,44 @@
       </c>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
     </row>
     <row r="32" spans="3:4">
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9010,11 +9088,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
-    <col min="3" max="3" width="13.25" customWidth="1"/>
-    <col min="4" max="5" width="12.9166666666667" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="18.1666666666667" customWidth="1"/>
     <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
     <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
     <col min="8" max="10" width="11.5" customWidth="1"/>
@@ -9030,7 +9109,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -9041,10 +9120,10 @@
         <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>644</v>
       </c>
       <c r="E2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
@@ -9068,12 +9147,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" ht="69.6" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
+      <c r="E3" s="3" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
@@ -9083,34 +9165,34 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D4" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E4" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="F4" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="G4" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="H4" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="I4" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="J4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="K4" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="L4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M4" t="s">
         <v>520</v>
@@ -9123,10 +9205,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>430</v>
       </c>
       <c r="G5" t="s">
@@ -9142,23 +9224,23 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M5" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>437</v>
       </c>
       <c r="G6" t="s">
@@ -9174,23 +9256,23 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L6" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M6" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>444</v>
       </c>
       <c r="G7" t="s">
@@ -9206,23 +9288,23 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L7" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M7" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>451</v>
       </c>
       <c r="G8" t="s">
@@ -9238,23 +9320,23 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M8" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="4" t="s">
         <v>459</v>
       </c>
       <c r="G9" t="s">
@@ -9270,23 +9352,23 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L9" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M9" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="4" t="s">
         <v>467</v>
       </c>
       <c r="G10" t="s">
@@ -9302,23 +9384,23 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M10" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="4" t="s">
         <v>473</v>
       </c>
       <c r="G11" t="s">
@@ -9334,23 +9416,23 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M11" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="4" t="s">
         <v>479</v>
       </c>
       <c r="G12" t="s">
@@ -9366,137 +9448,237 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L12" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M12" t="s">
-        <v>654</v>
+        <v>656</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="B13">
+        <v>2001</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F13" t="s">
+        <v>430</v>
+      </c>
+      <c r="N13" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="B14">
+        <v>2002</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F14" t="s">
+        <v>430</v>
+      </c>
+      <c r="N14" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15">
+        <v>2003</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="F15" t="s">
+        <v>437</v>
+      </c>
+      <c r="N15" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="B16">
-        <v>2001</v>
-      </c>
-      <c r="C16" t="s">
-        <v>656</v>
-      </c>
-      <c r="D16" t="s">
-        <v>657</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>429</v>
+        <v>2004</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>668</v>
       </c>
       <c r="F16" t="s">
-        <v>430</v>
+        <v>669</v>
       </c>
       <c r="N16" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
     </row>
     <row r="17" spans="2:14">
       <c r="B17">
-        <v>2002</v>
-      </c>
-      <c r="C17" t="s">
-        <v>659</v>
-      </c>
-      <c r="D17" t="s">
-        <v>660</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="F17" t="s">
-        <v>437</v>
+        <v>2005</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>473</v>
       </c>
       <c r="N17" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
     </row>
     <row r="18" spans="2:14">
       <c r="B18">
-        <v>2003</v>
-      </c>
-      <c r="C18" t="s">
-        <v>662</v>
-      </c>
-      <c r="D18" t="s">
-        <v>663</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="F18" t="s">
-        <v>437</v>
+        <v>2006</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>479</v>
       </c>
       <c r="N18" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="19" spans="2:14">
       <c r="B19">
-        <v>2004</v>
-      </c>
-      <c r="C19" t="s">
-        <v>665</v>
-      </c>
-      <c r="D19" t="s">
-        <v>666</v>
-      </c>
-      <c r="E19" s="3" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>436</v>
       </c>
       <c r="F19" t="s">
         <v>437</v>
       </c>
       <c r="N19" t="s">
-        <v>661</v>
+        <v>679</v>
       </c>
     </row>
     <row r="20" spans="2:14">
       <c r="B20">
-        <v>2005</v>
-      </c>
-      <c r="C20" t="s">
-        <v>667</v>
-      </c>
-      <c r="D20" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="E20" t="s">
         <v>668</v>
       </c>
+      <c r="F20" t="s">
+        <v>669</v>
+      </c>
       <c r="N20" t="s">
-        <v>669</v>
+        <v>682</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21">
+        <v>3001</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F21" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22">
+        <v>3002</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F22" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="23" spans="2:14">
       <c r="B23">
-        <v>3001</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>443</v>
+        <v>3003</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>450</v>
       </c>
       <c r="F23" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="2:14">
       <c r="B24">
-        <v>3002</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="E24" s="3" t="s">
+        <v>3004</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>450</v>
       </c>
       <c r="F24" t="s">
@@ -9505,32 +9687,32 @@
     </row>
     <row r="25" spans="2:14">
       <c r="B25">
-        <v>3003</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>450</v>
+        <v>3005</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>458</v>
       </c>
       <c r="F25" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="26" spans="2:14">
       <c r="B26">
-        <v>3004</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="E26" s="3" t="s">
+        <v>3006</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>458</v>
       </c>
       <c r="F26" t="s">
@@ -9539,55 +9721,55 @@
     </row>
     <row r="27" spans="2:14">
       <c r="B27">
-        <v>3005</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>674</v>
-      </c>
-      <c r="E27" s="3" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>458</v>
       </c>
       <c r="F27" t="s">
         <v>459</v>
       </c>
+      <c r="M27" t="s">
+        <v>697</v>
+      </c>
+      <c r="N27" t="s">
+        <v>698</v>
+      </c>
     </row>
     <row r="28" spans="2:14">
       <c r="B28">
-        <v>3006</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>458</v>
+        <v>3008</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>466</v>
       </c>
       <c r="F28" t="s">
-        <v>459</v>
-      </c>
-      <c r="M28" t="s">
-        <v>676</v>
-      </c>
-      <c r="N28" t="s">
-        <v>677</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" spans="2:14">
       <c r="B29">
-        <v>3007</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="E29" s="3" t="s">
+        <v>3009</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>466</v>
       </c>
       <c r="F29" t="s">
@@ -9596,42 +9778,25 @@
     </row>
     <row r="30" spans="2:14">
       <c r="B30">
-        <v>3008</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="E30" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>466</v>
       </c>
       <c r="F30" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="31" spans="2:14">
-      <c r="B31">
-        <v>3009</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="F31" t="s">
-        <v>467</v>
-      </c>
-      <c r="M31" t="s">
-        <v>676</v>
-      </c>
-      <c r="N31" t="s">
-        <v>677</v>
+      <c r="M30" t="s">
+        <v>697</v>
+      </c>
+      <c r="N30" t="s">
+        <v>698</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="715">
   <si>
     <t>##var</t>
   </si>
@@ -1973,10 +1973,40 @@
     <t>DogReactionTrigger</t>
   </si>
   <si>
+    <t>AssetRef</t>
+  </si>
+  <si>
+    <t>EarAsset</t>
+  </si>
+  <si>
+    <t>EyeAsset</t>
+  </si>
+  <si>
+    <t>OverrideHeadwear</t>
+  </si>
+  <si>
+    <t>WearGlasses</t>
+  </si>
+  <si>
+    <t>LeftPawAnimation</t>
+  </si>
+  <si>
+    <t>RightPawAnimation</t>
+  </si>
+  <si>
+    <t>TongueAnimation</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
     <t>EDogReactionTrigger</t>
   </si>
   <si>
     <t>复用引用枚举所对应的美术资源参数。其自身的值可以Override引用的值</t>
+  </si>
+  <si>
+    <t>有些表情需要临时更换头饰，例如被打晕的时候头上转的星星。但目前版本没有</t>
   </si>
   <si>
     <t>枚举</t>
@@ -2774,7 +2804,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2789,12 +2819,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3428,7 +3452,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="6" customFormat="1" ht="121.8" spans="1:16">
+    <row r="3" s="3" customFormat="1" ht="121.8" spans="1:16">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -3437,28 +3461,28 @@
       <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6924,292 +6948,292 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="4" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>4</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>8</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="4" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>16</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="P6" s="4" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>32</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="P7" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <v>64</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="P8" s="4" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>128</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="P9" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>256</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>512</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="4" t="s">
         <v>487</v>
       </c>
     </row>
@@ -7220,30 +7244,30 @@
       <c r="C12" t="s">
         <v>488</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>1024</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="4" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="4">
         <v>2048</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>494</v>
       </c>
     </row>
@@ -8202,7 +8226,7 @@
       <c r="D3" t="s">
         <v>565</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -8299,30 +8323,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="7"/>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>569</v>
       </c>
     </row>
@@ -8333,7 +8357,7 @@
       <c r="B3" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="b">
@@ -8346,14 +8370,14 @@
     <row r="4" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="5"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="5"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
@@ -8366,7 +8390,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="5"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
@@ -8379,7 +8403,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="5"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
@@ -8391,14 +8415,14 @@
     <row r="11" spans="1:5">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="5"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="5"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
@@ -8501,7 +8525,7 @@
       <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>583</v>
       </c>
       <c r="E5" t="s">
@@ -8521,7 +8545,7 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>587</v>
       </c>
       <c r="E6" t="s">
@@ -8541,7 +8565,7 @@
       <c r="C7">
         <v>150</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>591</v>
       </c>
       <c r="E7" t="s">
@@ -8561,7 +8585,7 @@
       <c r="C8">
         <v>200</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>595</v>
       </c>
       <c r="E8" t="s">
@@ -8581,7 +8605,7 @@
       <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>598</v>
       </c>
       <c r="E9" t="s">
@@ -8601,7 +8625,7 @@
       <c r="C10">
         <v>450</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>601</v>
       </c>
       <c r="E10" t="s">
@@ -8621,7 +8645,7 @@
       <c r="C11">
         <v>1000</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>605</v>
       </c>
       <c r="E11" t="s">
@@ -8641,7 +8665,7 @@
       <c r="C12">
         <v>2500</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>609</v>
       </c>
       <c r="E12" t="s">
@@ -8661,7 +8685,7 @@
       <c r="C13">
         <v>12500</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>613</v>
       </c>
       <c r="E13" t="s">
@@ -8738,7 +8762,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="6"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -8764,10 +8788,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E5" t="s">
@@ -8781,10 +8805,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>48</v>
       </c>
       <c r="E6" t="s">
@@ -8798,10 +8822,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E7" t="s">
@@ -8815,10 +8839,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>366</v>
       </c>
       <c r="E8" t="s">
@@ -8832,10 +8856,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>454</v>
       </c>
       <c r="E9" t="s">
@@ -8849,10 +8873,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>462</v>
       </c>
       <c r="E10" t="s">
@@ -9040,44 +9064,44 @@
       </c>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="3:4">
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9111,6 +9135,33 @@
       <c r="C1" s="1" t="s">
         <v>643</v>
       </c>
+      <c r="E1" t="s">
+        <v>644</v>
+      </c>
+      <c r="G1" t="s">
+        <v>645</v>
+      </c>
+      <c r="H1" t="s">
+        <v>646</v>
+      </c>
+      <c r="I1" t="s">
+        <v>647</v>
+      </c>
+      <c r="J1" t="s">
+        <v>648</v>
+      </c>
+      <c r="K1" t="s">
+        <v>649</v>
+      </c>
+      <c r="L1" t="s">
+        <v>650</v>
+      </c>
+      <c r="M1" t="s">
+        <v>651</v>
+      </c>
+      <c r="N1" t="s">
+        <v>652</v>
+      </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
@@ -9120,10 +9171,10 @@
         <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="E2" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
@@ -9132,7 +9183,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -9146,15 +9197,21 @@
       <c r="M2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" ht="69.6" spans="1:14">
+      <c r="N2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="104.4" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="E3" s="3" t="s">
-        <v>645</v>
+        <v>654</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -9165,34 +9222,34 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="D4" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="E4" t="s">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="F4" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="G4" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="H4" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="I4" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="J4" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="K4" t="s">
-        <v>653</v>
+        <v>663</v>
       </c>
       <c r="L4" t="s">
-        <v>654</v>
+        <v>664</v>
       </c>
       <c r="M4" t="s">
         <v>520</v>
@@ -9217,20 +9274,18 @@
       <c r="H5" t="s">
         <v>430</v>
       </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
+      <c r="I5"/>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="L5" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="M5" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -9249,20 +9304,18 @@
       <c r="H6" t="s">
         <v>506</v>
       </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
+      <c r="I6"/>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="L6" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="M6" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -9281,20 +9334,18 @@
       <c r="H7" t="s">
         <v>505</v>
       </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
+      <c r="I7"/>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="L7" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="M7" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -9313,20 +9364,18 @@
       <c r="H8" t="s">
         <v>510</v>
       </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
+      <c r="I8"/>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="L8" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="M8" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -9345,20 +9394,18 @@
       <c r="H9" t="s">
         <v>507</v>
       </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
+      <c r="I9"/>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="L9" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="M9" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -9377,20 +9424,18 @@
       <c r="H10" t="s">
         <v>508</v>
       </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
+      <c r="I10"/>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="L10" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="M10" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -9409,20 +9454,18 @@
       <c r="H11" t="s">
         <v>505</v>
       </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
+      <c r="I11"/>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="L11" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="M11" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -9441,20 +9484,18 @@
       <c r="H12" t="s">
         <v>509</v>
       </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
+      <c r="I12"/>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="L12" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="M12" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -9462,19 +9503,19 @@
         <v>2001</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="E13" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>429</v>
       </c>
       <c r="F13" t="s">
         <v>430</v>
       </c>
       <c r="N13" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -9482,19 +9523,19 @@
         <v>2002</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="E14" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>429</v>
       </c>
       <c r="F14" t="s">
         <v>430</v>
       </c>
       <c r="N14" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -9502,19 +9543,19 @@
         <v>2003</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>664</v>
-      </c>
-      <c r="E15" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>436</v>
       </c>
       <c r="F15" t="s">
         <v>437</v>
       </c>
       <c r="N15" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -9522,19 +9563,19 @@
         <v>2004</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>668</v>
+        <v>677</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>678</v>
       </c>
       <c r="F16" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="N16" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -9542,10 +9583,10 @@
         <v>2005</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>472</v>
@@ -9554,7 +9595,7 @@
         <v>473</v>
       </c>
       <c r="N17" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -9562,10 +9603,10 @@
         <v>2006</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>478</v>
@@ -9574,7 +9615,7 @@
         <v>479</v>
       </c>
       <c r="N18" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -9582,19 +9623,19 @@
         <v>2007</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="E19" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>436</v>
       </c>
       <c r="F19" t="s">
         <v>437</v>
       </c>
       <c r="N19" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -9602,19 +9643,19 @@
         <v>2008</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="E20" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="F20" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="N20" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -9622,12 +9663,12 @@
         <v>3001</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="E21" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>443</v>
       </c>
       <c r="F21" t="s">
@@ -9639,12 +9680,12 @@
         <v>3002</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="E22" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>443</v>
       </c>
       <c r="F22" t="s">
@@ -9656,12 +9697,12 @@
         <v>3003</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="E23" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>450</v>
       </c>
       <c r="F23" t="s">
@@ -9673,12 +9714,12 @@
         <v>3004</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="E24" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>450</v>
       </c>
       <c r="F24" t="s">
@@ -9690,12 +9731,12 @@
         <v>3005</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="E25" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>458</v>
       </c>
       <c r="F25" t="s">
@@ -9707,12 +9748,12 @@
         <v>3006</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="E26" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>458</v>
       </c>
       <c r="F26" t="s">
@@ -9724,22 +9765,22 @@
         <v>3007</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="E27" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>458</v>
       </c>
       <c r="F27" t="s">
         <v>459</v>
       </c>
       <c r="M27" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="N27" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
     </row>
     <row r="28" spans="2:14">
@@ -9747,12 +9788,12 @@
         <v>3008</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>700</v>
-      </c>
-      <c r="E28" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>466</v>
       </c>
       <c r="F28" t="s">
@@ -9764,12 +9805,12 @@
         <v>3009</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>702</v>
-      </c>
-      <c r="E29" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>466</v>
       </c>
       <c r="F29" t="s">
@@ -9781,22 +9822,22 @@
         <v>3010</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>704</v>
-      </c>
-      <c r="E30" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>466</v>
       </c>
       <c r="F30" t="s">
         <v>467</v>
       </c>
       <c r="M30" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="N30" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -9274,7 +9274,6 @@
       <c r="H5" t="s">
         <v>430</v>
       </c>
-      <c r="I5"/>
       <c r="J5" t="b">
         <v>0</v>
       </c>
@@ -9304,7 +9303,6 @@
       <c r="H6" t="s">
         <v>506</v>
       </c>
-      <c r="I6"/>
       <c r="J6" t="b">
         <v>0</v>
       </c>
@@ -9334,7 +9332,6 @@
       <c r="H7" t="s">
         <v>505</v>
       </c>
-      <c r="I7"/>
       <c r="J7" t="b">
         <v>0</v>
       </c>
@@ -9364,7 +9361,6 @@
       <c r="H8" t="s">
         <v>510</v>
       </c>
-      <c r="I8"/>
       <c r="J8" t="b">
         <v>0</v>
       </c>
@@ -9394,7 +9390,6 @@
       <c r="H9" t="s">
         <v>507</v>
       </c>
-      <c r="I9"/>
       <c r="J9" t="b">
         <v>0</v>
       </c>
@@ -9424,7 +9419,6 @@
       <c r="H10" t="s">
         <v>508</v>
       </c>
-      <c r="I10"/>
       <c r="J10" t="b">
         <v>0</v>
       </c>
@@ -9454,7 +9448,6 @@
       <c r="H11" t="s">
         <v>505</v>
       </c>
-      <c r="I11"/>
       <c r="J11" t="b">
         <v>1</v>
       </c>
@@ -9484,7 +9477,6 @@
       <c r="H12" t="s">
         <v>509</v>
       </c>
-      <c r="I12"/>
       <c r="J12" t="b">
         <v>1</v>
       </c>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="5"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -16,6 +16,7 @@
     <sheet name="RarityUI" sheetId="7" r:id="rId7"/>
     <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
     <sheet name="DogReaction" sheetId="9" r:id="rId9"/>
+    <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="717">
   <si>
     <t>##var</t>
   </si>
@@ -2184,6 +2185,12 @@
   </si>
   <si>
     <t>看到皇家同花顺</t>
+  </si>
+  <si>
+    <t>CanUnequip</t>
+  </si>
+  <si>
+    <t>可脱光吗</t>
   </si>
 </sst>
 </file>
@@ -6937,6 +6944,144 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="11.1666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" t="s">
+        <v>413</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="9"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
     <sheet name="DogReaction" sheetId="9" r:id="rId9"/>
     <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId10"/>
+    <sheet name="DesktopActivityState" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="748">
   <si>
     <t>##var</t>
   </si>
@@ -2191,6 +2192,99 @@
   </si>
   <si>
     <t>可脱光吗</t>
+  </si>
+  <si>
+    <t>StateName</t>
+  </si>
+  <si>
+    <t>MinInputEventsPerMinute</t>
+  </si>
+  <si>
+    <t>MaxInputEventsPerMinute</t>
+  </si>
+  <si>
+    <t>MinDurationSeconds</t>
+  </si>
+  <si>
+    <t>CooldownSeconds</t>
+  </si>
+  <si>
+    <t>EnableTongueFeedback</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>行 ID</t>
+  </si>
+  <si>
+    <t>状态名，给人看的</t>
+  </si>
+  <si>
+    <t>最近一段时间估算输入频率下限</t>
+  </si>
+  <si>
+    <t>输入频率上限，0表示无上限</t>
+  </si>
+  <si>
+    <t>连续满足多久后才切换到该状态，防抖动</t>
+  </si>
+  <si>
+    <t>切换到该状态后至少保持多久</t>
+  </si>
+  <si>
+    <t>要播放的狗狗表现</t>
+  </si>
+  <si>
+    <t>该状态下是否启用吐舌反馈</t>
+  </si>
+  <si>
+    <t>多条规则命中时用，数字越大优先级越高</t>
+  </si>
+  <si>
+    <t>状态名</t>
+  </si>
+  <si>
+    <t>输入频率下限</t>
+  </si>
+  <si>
+    <t>输入频率上限</t>
+  </si>
+  <si>
+    <t>最小持续时间(秒)</t>
+  </si>
+  <si>
+    <t>冷却时间(秒)</t>
+  </si>
+  <si>
+    <t>狗表现触发</t>
+  </si>
+  <si>
+    <t>启用吐舌反馈</t>
+  </si>
+  <si>
+    <t>优先级</t>
+  </si>
+  <si>
+    <t>Idle</t>
+  </si>
+  <si>
+    <t>挂机空闲，测试阶段为了快速测试，先调成10秒进入，后续记得改长一些</t>
+  </si>
+  <si>
+    <t>Casual</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Focused</t>
+  </si>
+  <si>
+    <t>HighEnergy</t>
   </si>
 </sst>
 </file>
@@ -2815,13 +2909,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3370,16 +3464,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -3415,16 +3509,16 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="1"/>
+      <c r="D2" s="2"/>
       <c r="E2" t="s">
         <v>17</v>
       </c>
@@ -3459,51 +3553,51 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" ht="121.8" spans="1:16">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:16">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E4" t="s">
@@ -6956,7 +7050,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -6967,24 +7061,24 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>716</v>
       </c>
     </row>
@@ -7074,6 +7168,299 @@
       </c>
       <c r="C15" t="b">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="4.5" customWidth="1"/>
+    <col min="3" max="3" width="10.5833333333333" customWidth="1"/>
+    <col min="4" max="4" width="22.9166666666667" customWidth="1"/>
+    <col min="5" max="5" width="23.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="18.75" customWidth="1"/>
+    <col min="7" max="7" width="16.75" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="21.0833333333333" customWidth="1"/>
+    <col min="10" max="10" width="7.25" customWidth="1"/>
+    <col min="11" max="11" width="59.3333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>717</v>
+      </c>
+      <c r="D1" t="s">
+        <v>718</v>
+      </c>
+      <c r="E1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F1" t="s">
+        <v>720</v>
+      </c>
+      <c r="G1" t="s">
+        <v>721</v>
+      </c>
+      <c r="H1" t="s">
+        <v>643</v>
+      </c>
+      <c r="I1" t="s">
+        <v>722</v>
+      </c>
+      <c r="J1" t="s">
+        <v>723</v>
+      </c>
+      <c r="K1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>724</v>
+      </c>
+      <c r="G2" t="s">
+        <v>724</v>
+      </c>
+      <c r="H2" t="s">
+        <v>653</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="87" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>734</v>
+      </c>
+      <c r="D4" t="s">
+        <v>735</v>
+      </c>
+      <c r="E4" t="s">
+        <v>736</v>
+      </c>
+      <c r="F4" t="s">
+        <v>737</v>
+      </c>
+      <c r="G4" t="s">
+        <v>738</v>
+      </c>
+      <c r="H4" t="s">
+        <v>739</v>
+      </c>
+      <c r="I4" t="s">
+        <v>740</v>
+      </c>
+      <c r="J4" t="s">
+        <v>741</v>
+      </c>
+      <c r="K4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>742</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>443</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>744</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>80</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>429</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>746</v>
+      </c>
+      <c r="D7">
+        <v>81</v>
+      </c>
+      <c r="E7">
+        <v>180</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s">
+        <v>458</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>747</v>
+      </c>
+      <c r="D8">
+        <v>181</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>466</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8" t="s">
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -7447,26 +7834,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>499</v>
       </c>
       <c r="I1" t="s">
@@ -7504,80 +7891,80 @@
       </c>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" ht="34.8" spans="1:19">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B4" t="s">
@@ -8325,10 +8712,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -8342,10 +8729,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
@@ -8359,10 +8746,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C3" t="s">
@@ -8371,7 +8758,7 @@
       <c r="D3" t="s">
         <v>565</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -8496,80 +8883,80 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>571</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="A10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8591,10 +8978,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -8603,7 +8990,7 @@
       <c r="D1" t="s">
         <v>574</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>575</v>
       </c>
       <c r="F1" t="s">
@@ -8614,10 +9001,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
@@ -8626,7 +9013,7 @@
       <c r="D2" t="s">
         <v>578</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
@@ -8637,11 +9024,11 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -8862,13 +9249,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -8882,13 +9269,13 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D2" t="s">
@@ -8902,12 +9289,12 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -9049,10 +9436,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -9066,10 +9453,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
@@ -9083,10 +9470,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C3" t="s">
@@ -9271,13 +9658,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>643</v>
       </c>
       <c r="E1" t="s">
@@ -9309,13 +9696,13 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>653</v>
       </c>
       <c r="E2" t="s">
@@ -9347,15 +9734,15 @@
       </c>
     </row>
     <row r="3" ht="104.4" spans="1:14">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="E3" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="E3" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>655</v>
       </c>
     </row>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -2254,10 +2254,10 @@
     <t>输入频率上限</t>
   </si>
   <si>
-    <t>最小持续时间(秒)</t>
-  </si>
-  <si>
-    <t>冷却时间(秒)</t>
+    <t>切换状态阈值</t>
+  </si>
+  <si>
+    <t>状态最小持续时间</t>
   </si>
   <si>
     <t>狗表现触发</t>
@@ -7352,7 +7352,7 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5" t="s">
         <v>443</v>
@@ -7381,7 +7381,7 @@
         <v>80</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -7416,7 +7416,7 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H7" t="s">
         <v>458</v>
@@ -7445,10 +7445,10 @@
         <v>0</v>
       </c>
       <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
         <v>3</v>
-      </c>
-      <c r="G8">
-        <v>8</v>
       </c>
       <c r="H8" t="s">
         <v>466</v>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="10"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="749">
   <si>
     <t>##var</t>
   </si>
@@ -1988,6 +1988,9 @@
   </si>
   <si>
     <t>WearGlasses</t>
+  </si>
+  <si>
+    <t>ShowEquippedEyewearByDefault</t>
   </si>
   <si>
     <t>LeftPawAnimation</t>
@@ -7057,7 +7060,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -7079,7 +7082,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7203,31 +7206,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1" t="s">
         <v>643</v>
       </c>
       <c r="I1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="K1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7247,13 +7250,13 @@
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I2" t="s">
         <v>19</v>
@@ -7270,31 +7273,31 @@
         <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>44</v>
@@ -7308,28 +7311,28 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="I4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="J4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="K4" t="s">
         <v>44</v>
@@ -7340,7 +7343,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -7364,7 +7367,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -7372,7 +7375,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7396,7 +7399,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -7404,7 +7407,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -7428,7 +7431,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -7436,7 +7439,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -7460,7 +7463,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -9644,7 +9647,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="19" customWidth="1"/>
@@ -9653,11 +9656,12 @@
     <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
     <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
     <col min="8" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="13" width="9.58333333333333" customWidth="1"/>
-    <col min="20" max="20" width="12.9166666666667" customWidth="1"/>
+    <col min="11" max="11" width="29.25" customWidth="1"/>
+    <col min="12" max="14" width="9.58333333333333" customWidth="1"/>
+    <col min="21" max="21" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9694,8 +9698,11 @@
       <c r="N1" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -9703,10 +9710,10 @@
         <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
@@ -9720,9 +9727,6 @@
       <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
-        <v>16</v>
-      </c>
       <c r="L2" t="s">
         <v>16</v>
       </c>
@@ -9732,21 +9736,24 @@
       <c r="N2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" ht="104.4" spans="1:14">
+      <c r="O2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="104.4" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -9754,43 +9761,43 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E4" t="s">
+        <v>659</v>
+      </c>
+      <c r="F4" t="s">
         <v>658</v>
       </c>
-      <c r="F4" t="s">
-        <v>657</v>
-      </c>
       <c r="G4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H4" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="I4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="J4" t="s">
-        <v>662</v>
-      </c>
-      <c r="K4" t="s">
         <v>663</v>
       </c>
       <c r="L4" t="s">
         <v>664</v>
       </c>
       <c r="M4" t="s">
+        <v>665</v>
+      </c>
+      <c r="N4" t="s">
         <v>520</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="B5">
         <v>1001</v>
       </c>
@@ -9809,17 +9816,17 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
-      <c r="K5" t="s">
-        <v>665</v>
-      </c>
       <c r="L5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M5" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="N5" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -9838,17 +9845,17 @@
       <c r="J6" t="b">
         <v>0</v>
       </c>
-      <c r="K6" t="s">
-        <v>665</v>
-      </c>
       <c r="L6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M6" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="N6" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -9867,17 +9874,17 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
-      <c r="K7" t="s">
-        <v>665</v>
-      </c>
       <c r="L7" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M7" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="N7" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -9896,17 +9903,17 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
-      <c r="K8" t="s">
-        <v>665</v>
-      </c>
       <c r="L8" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M8" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="N8" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -9925,17 +9932,17 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
-      <c r="K9" t="s">
-        <v>665</v>
-      </c>
       <c r="L9" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M9" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="N9" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -9954,17 +9961,17 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
-      <c r="K10" t="s">
-        <v>665</v>
-      </c>
       <c r="L10" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M10" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="N10" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="B11">
         <v>1007</v>
       </c>
@@ -9983,17 +9990,17 @@
       <c r="J11" t="b">
         <v>1</v>
       </c>
-      <c r="K11" t="s">
-        <v>665</v>
-      </c>
       <c r="L11" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M11" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="N11" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="B12">
         <v>1008</v>
       </c>
@@ -10012,25 +10019,25 @@
       <c r="J12" t="b">
         <v>1</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
+        <v>668</v>
+      </c>
+      <c r="M12" t="s">
+        <v>668</v>
+      </c>
+      <c r="N12" t="s">
         <v>667</v>
       </c>
-      <c r="L12" t="s">
-        <v>667</v>
-      </c>
-      <c r="M12" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+    </row>
+    <row r="13" spans="1:15">
       <c r="B13">
         <v>2001</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>429</v>
@@ -10038,19 +10045,19 @@
       <c r="F13" t="s">
         <v>430</v>
       </c>
-      <c r="N13" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="B14">
         <v>2002</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>429</v>
@@ -10058,19 +10065,19 @@
       <c r="F14" t="s">
         <v>430</v>
       </c>
-      <c r="N14" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="B15">
         <v>2003</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>436</v>
@@ -10078,39 +10085,39 @@
       <c r="F15" t="s">
         <v>437</v>
       </c>
-      <c r="N15" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="B16">
         <v>2004</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F16" t="s">
-        <v>679</v>
-      </c>
-      <c r="N16" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="17" spans="2:14">
+      <c r="O16" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15">
       <c r="B17">
         <v>2005</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>472</v>
@@ -10118,19 +10125,19 @@
       <c r="F17" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="N17" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
+      <c r="O17" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15">
       <c r="B18">
         <v>2006</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>478</v>
@@ -10138,19 +10145,19 @@
       <c r="F18" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="N18" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14">
+      <c r="O18" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15">
       <c r="B19">
         <v>2007</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>436</v>
@@ -10158,39 +10165,39 @@
       <c r="F19" t="s">
         <v>437</v>
       </c>
-      <c r="N19" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14">
+      <c r="O19" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15">
       <c r="B20">
         <v>2008</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E20" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F20" t="s">
-        <v>679</v>
-      </c>
-      <c r="N20" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14">
+        <v>680</v>
+      </c>
+      <c r="O20" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15">
       <c r="B21">
         <v>3001</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>443</v>
@@ -10199,15 +10206,15 @@
         <v>444</v>
       </c>
     </row>
-    <row r="22" spans="2:14">
+    <row r="22" spans="2:15">
       <c r="B22">
         <v>3002</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>443</v>
@@ -10216,15 +10223,15 @@
         <v>444</v>
       </c>
     </row>
-    <row r="23" spans="2:14">
+    <row r="23" spans="2:15">
       <c r="B23">
         <v>3003</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>450</v>
@@ -10233,15 +10240,15 @@
         <v>451</v>
       </c>
     </row>
-    <row r="24" spans="2:14">
+    <row r="24" spans="2:15">
       <c r="B24">
         <v>3004</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>450</v>
@@ -10250,15 +10257,15 @@
         <v>451</v>
       </c>
     </row>
-    <row r="25" spans="2:14">
+    <row r="25" spans="2:15">
       <c r="B25">
         <v>3005</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>458</v>
@@ -10267,15 +10274,15 @@
         <v>459</v>
       </c>
     </row>
-    <row r="26" spans="2:14">
+    <row r="26" spans="2:15">
       <c r="B26">
         <v>3006</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>458</v>
@@ -10284,15 +10291,15 @@
         <v>459</v>
       </c>
     </row>
-    <row r="27" spans="2:14">
+    <row r="27" spans="2:15">
       <c r="B27">
         <v>3007</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>458</v>
@@ -10300,22 +10307,22 @@
       <c r="F27" t="s">
         <v>459</v>
       </c>
-      <c r="M27" t="s">
-        <v>707</v>
-      </c>
       <c r="N27" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="28" spans="2:14">
+      <c r="O27" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15">
       <c r="B28">
         <v>3008</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>466</v>
@@ -10324,15 +10331,15 @@
         <v>467</v>
       </c>
     </row>
-    <row r="29" spans="2:14">
+    <row r="29" spans="2:15">
       <c r="B29">
         <v>3009</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>466</v>
@@ -10341,15 +10348,15 @@
         <v>467</v>
       </c>
     </row>
-    <row r="30" spans="2:14">
+    <row r="30" spans="2:15">
       <c r="B30">
         <v>3010</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>466</v>
@@ -10357,11 +10364,11 @@
       <c r="F30" t="s">
         <v>467</v>
       </c>
-      <c r="M30" t="s">
-        <v>707</v>
-      </c>
       <c r="N30" t="s">
         <v>708</v>
+      </c>
+      <c r="O30" t="s">
+        <v>709</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="GameDevelopConfig" sheetId="5" r:id="rId1"/>
-    <sheet name="枚举示例" sheetId="3" r:id="rId2"/>
-    <sheet name="PayTable" sheetId="6" r:id="rId3"/>
+    <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
+    <sheet name="PayTable" sheetId="6" r:id="rId2"/>
+    <sheet name="GameDevelopConfig" sheetId="5" r:id="rId3"/>
     <sheet name="DogSkin" sheetId="2" r:id="rId4"/>
     <sheet name="RarityUI" sheetId="7" r:id="rId5"/>
     <sheet name="DogReaction" sheetId="9" r:id="rId6"/>
@@ -33,17 +33,458 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="361">
+  <si>
+    <t>Dog</t>
+  </si>
+  <si>
+    <t>小狗本体</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>传说</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>全球</t>
+  </si>
+  <si>
+    <t>在全部国家隐藏</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
+    <t>Headwear</t>
+  </si>
+  <si>
+    <t>小狗头部装饰</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>史诗</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>沙特阿拉伯</t>
+  </si>
+  <si>
+    <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
+  </si>
+  <si>
+    <t>Serious</t>
+  </si>
+  <si>
+    <t>严肃</t>
+  </si>
+  <si>
+    <t>Eyewear</t>
+  </si>
+  <si>
+    <t>小狗眼部装饰</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>稀有</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>阿联酋</t>
+  </si>
+  <si>
+    <t>United Arab Emirates赌博/宗教/酒精/色情</t>
+  </si>
+  <si>
+    <t>Bored</t>
+  </si>
+  <si>
+    <t>无聊</t>
+  </si>
+  <si>
+    <t>Arm</t>
+  </si>
+  <si>
+    <t>手臂层的装饰</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>伊朗</t>
+  </si>
+  <si>
+    <t>Iran宗教/进化论/赌博/政治/西方文化</t>
+  </si>
+  <si>
+    <t>Wink</t>
+  </si>
+  <si>
+    <t>媚眼</t>
+  </si>
+  <si>
+    <t>Clothes</t>
+  </si>
+  <si>
+    <t>玩家手臂衣服</t>
+  </si>
+  <si>
+    <t>Special1</t>
+  </si>
+  <si>
+    <t>特殊1</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>巴基斯坦</t>
+  </si>
+  <si>
+    <t>Pakistan国家形象/政治</t>
+  </si>
+  <si>
+    <t>Excited</t>
+  </si>
+  <si>
+    <t>兴奋</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>桌布</t>
+  </si>
+  <si>
+    <t>Special2</t>
+  </si>
+  <si>
+    <t>特殊2</t>
+  </si>
+  <si>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>马来西亚</t>
+  </si>
+  <si>
+    <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
+  </si>
+  <si>
+    <t>Starstruck</t>
+  </si>
+  <si>
+    <t>崇拜</t>
+  </si>
+  <si>
+    <t>Background</t>
+  </si>
+  <si>
+    <t>背景</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>印尼</t>
+  </si>
+  <si>
+    <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
+  </si>
+  <si>
+    <t>Silent</t>
+  </si>
+  <si>
+    <t>沉默</t>
+  </si>
+  <si>
+    <t>Accessory</t>
+  </si>
+  <si>
+    <t>玩家手部装饰</t>
+  </si>
+  <si>
+    <t>RU</t>
+  </si>
+  <si>
+    <t>俄罗斯</t>
+  </si>
+  <si>
+    <t>Russia赌博/LGBTQ/极端主义</t>
+  </si>
+  <si>
+    <t>Reject</t>
+  </si>
+  <si>
+    <t>拒绝</t>
+  </si>
+  <si>
+    <t>Refreshment</t>
+  </si>
+  <si>
+    <t>消耗品</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>中国</t>
+  </si>
+  <si>
+    <t>China赌博/暴力/血腥/色情</t>
+  </si>
+  <si>
+    <t>CardBack</t>
+  </si>
+  <si>
+    <t>卡背</t>
+  </si>
+  <si>
+    <t>KP</t>
+  </si>
+  <si>
+    <t>朝鲜</t>
+  </si>
+  <si>
+    <t>North Korea国际制裁/政治</t>
+  </si>
+  <si>
+    <t>CardFace</t>
+  </si>
+  <si>
+    <t>卡面</t>
+  </si>
+  <si>
+    <t>SY</t>
+  </si>
+  <si>
+    <t>叙利亚</t>
+  </si>
+  <si>
+    <t>Syria国际制裁/政治/宗教</t>
+  </si>
+  <si>
+    <t>CU</t>
+  </si>
+  <si>
+    <t>古巴</t>
+  </si>
+  <si>
+    <t>Cuba国际制裁/政治</t>
+  </si>
+  <si>
+    <t>Initial</t>
+  </si>
+  <si>
+    <t>初始拥有</t>
+  </si>
+  <si>
+    <t>DecorationBlindBox</t>
+  </si>
+  <si>
+    <t>装扮盲盒产出</t>
+  </si>
+  <si>
+    <t>RefreshmentBlindBox</t>
+  </si>
+  <si>
+    <t>消耗品盲盒产出</t>
+  </si>
+  <si>
+    <t>EventReward</t>
+  </si>
+  <si>
+    <t>活动产出</t>
+  </si>
+  <si>
+    <t>Retired</t>
+  </si>
+  <si>
+    <t>已下架</t>
+  </si>
+  <si>
+    <t>DebugOnly</t>
+  </si>
+  <si>
+    <t>仅调试</t>
+  </si>
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>PayoutMultiplier</t>
+  </si>
+  <si>
+    <t>HandRank</t>
+  </si>
+  <si>
+    <t>OriginalName</t>
+  </si>
+  <si>
+    <t>SafeName_EN</t>
+  </si>
+  <si>
+    <t>SafeName_CN</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>EHandRank</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>赔率</t>
+  </si>
+  <si>
+    <t>原始名称</t>
+  </si>
+  <si>
+    <t>安全英文</t>
+  </si>
+  <si>
+    <t>安全中文</t>
+  </si>
+  <si>
+    <t>JacksOrBetter</t>
+  </si>
+  <si>
+    <t>Jacks or Better</t>
+  </si>
+  <si>
+    <t>Top Dogs</t>
+  </si>
+  <si>
+    <t>好犬优选</t>
+  </si>
+  <si>
+    <t>TwoPair</t>
+  </si>
+  <si>
+    <t>Two Pair</t>
+  </si>
+  <si>
+    <t>Twin Pairs</t>
+  </si>
+  <si>
+    <t>双犬配对</t>
+  </si>
+  <si>
+    <t>ThreeOfAKind</t>
+  </si>
+  <si>
+    <t>Three of a Kind</t>
+  </si>
+  <si>
+    <t>Triple Pals</t>
+  </si>
+  <si>
+    <t>三犬同行</t>
+  </si>
+  <si>
+    <t>Straight</t>
+  </si>
+  <si>
+    <t>Chain Walk</t>
+  </si>
+  <si>
+    <t>顺位犬链</t>
+  </si>
+  <si>
+    <t>Flush</t>
+  </si>
+  <si>
+    <t>Matching Den</t>
+  </si>
+  <si>
+    <t>同色犬舍</t>
+  </si>
+  <si>
+    <t>FullHouse</t>
+  </si>
+  <si>
+    <t>Full House</t>
+  </si>
+  <si>
+    <t>Puppy Party</t>
+  </si>
+  <si>
+    <t>狗狗满堂</t>
+  </si>
+  <si>
+    <t>FourOfAKind</t>
+  </si>
+  <si>
+    <t>Four of a Kind</t>
+  </si>
+  <si>
+    <t>Dog Squad</t>
+  </si>
+  <si>
+    <t>四犬成团</t>
+  </si>
+  <si>
+    <t>StraightFlush</t>
+  </si>
+  <si>
+    <t>Straight Flush</t>
+  </si>
+  <si>
+    <t>Purebred Strike</t>
+  </si>
+  <si>
+    <t>纯种犬连击</t>
+  </si>
+  <si>
+    <t>RoyalFlush</t>
+  </si>
+  <si>
+    <t>Royal Flush</t>
+  </si>
+  <si>
+    <t>Royal Feast</t>
+  </si>
+  <si>
+    <t>皇家狗粮</t>
+  </si>
   <si>
     <t>##column#var</t>
   </si>
   <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
     <t>名称</t>
   </si>
   <si>
@@ -74,447 +515,6 @@
     <t>盲盒消耗筹码倍率</t>
   </si>
   <si>
-    <t>Dog</t>
-  </si>
-  <si>
-    <t>小狗本体</t>
-  </si>
-  <si>
-    <t>Legendary</t>
-  </si>
-  <si>
-    <t>传说</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>全球</t>
-  </si>
-  <si>
-    <t>在全部国家隐藏</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>默认</t>
-  </si>
-  <si>
-    <t>Headwear</t>
-  </si>
-  <si>
-    <t>小狗头部装饰</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>史诗</t>
-  </si>
-  <si>
-    <t>SA</t>
-  </si>
-  <si>
-    <t>沙特阿拉伯</t>
-  </si>
-  <si>
-    <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
-  </si>
-  <si>
-    <t>Serious</t>
-  </si>
-  <si>
-    <t>严肃</t>
-  </si>
-  <si>
-    <t>Eyewear</t>
-  </si>
-  <si>
-    <t>小狗眼部装饰</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>稀有</t>
-  </si>
-  <si>
-    <t>AE</t>
-  </si>
-  <si>
-    <t>阿联酋</t>
-  </si>
-  <si>
-    <t>United Arab Emirates赌博/宗教/酒精/色情</t>
-  </si>
-  <si>
-    <t>Bored</t>
-  </si>
-  <si>
-    <t>无聊</t>
-  </si>
-  <si>
-    <t>Arm</t>
-  </si>
-  <si>
-    <t>手臂层的装饰</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>普通</t>
-  </si>
-  <si>
-    <t>IR</t>
-  </si>
-  <si>
-    <t>伊朗</t>
-  </si>
-  <si>
-    <t>Iran宗教/进化论/赌博/政治/西方文化</t>
-  </si>
-  <si>
-    <t>Wink</t>
-  </si>
-  <si>
-    <t>媚眼</t>
-  </si>
-  <si>
-    <t>Clothes</t>
-  </si>
-  <si>
-    <t>玩家手臂衣服</t>
-  </si>
-  <si>
-    <t>Special1</t>
-  </si>
-  <si>
-    <t>特殊1</t>
-  </si>
-  <si>
-    <t>PK</t>
-  </si>
-  <si>
-    <t>巴基斯坦</t>
-  </si>
-  <si>
-    <t>Pakistan国家形象/政治</t>
-  </si>
-  <si>
-    <t>Excited</t>
-  </si>
-  <si>
-    <t>兴奋</t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
-    <t>桌布</t>
-  </si>
-  <si>
-    <t>Special2</t>
-  </si>
-  <si>
-    <t>特殊2</t>
-  </si>
-  <si>
-    <t>MY</t>
-  </si>
-  <si>
-    <t>马来西亚</t>
-  </si>
-  <si>
-    <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
-  </si>
-  <si>
-    <t>Starstruck</t>
-  </si>
-  <si>
-    <t>崇拜</t>
-  </si>
-  <si>
-    <t>Background</t>
-  </si>
-  <si>
-    <t>背景</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>印尼</t>
-  </si>
-  <si>
-    <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
-  </si>
-  <si>
-    <t>Silent</t>
-  </si>
-  <si>
-    <t>沉默</t>
-  </si>
-  <si>
-    <t>Accessory</t>
-  </si>
-  <si>
-    <t>玩家手部装饰</t>
-  </si>
-  <si>
-    <t>RU</t>
-  </si>
-  <si>
-    <t>俄罗斯</t>
-  </si>
-  <si>
-    <t>Russia赌博/LGBTQ/极端主义</t>
-  </si>
-  <si>
-    <t>Reject</t>
-  </si>
-  <si>
-    <t>拒绝</t>
-  </si>
-  <si>
-    <t>Refreshment</t>
-  </si>
-  <si>
-    <t>消耗品</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>中国</t>
-  </si>
-  <si>
-    <t>China赌博/暴力/血腥/色情</t>
-  </si>
-  <si>
-    <t>CardBack</t>
-  </si>
-  <si>
-    <t>卡背</t>
-  </si>
-  <si>
-    <t>KP</t>
-  </si>
-  <si>
-    <t>朝鲜</t>
-  </si>
-  <si>
-    <t>North Korea国际制裁/政治</t>
-  </si>
-  <si>
-    <t>CardFace</t>
-  </si>
-  <si>
-    <t>卡面</t>
-  </si>
-  <si>
-    <t>SY</t>
-  </si>
-  <si>
-    <t>叙利亚</t>
-  </si>
-  <si>
-    <t>Syria国际制裁/政治/宗教</t>
-  </si>
-  <si>
-    <t>CU</t>
-  </si>
-  <si>
-    <t>古巴</t>
-  </si>
-  <si>
-    <t>Cuba国际制裁/政治</t>
-  </si>
-  <si>
-    <t>Initial</t>
-  </si>
-  <si>
-    <t>初始拥有</t>
-  </si>
-  <si>
-    <t>DecorationBlindBox</t>
-  </si>
-  <si>
-    <t>装扮盲盒产出</t>
-  </si>
-  <si>
-    <t>RefreshmentBlindBox</t>
-  </si>
-  <si>
-    <t>消耗品盲盒产出</t>
-  </si>
-  <si>
-    <t>EventReward</t>
-  </si>
-  <si>
-    <t>活动产出</t>
-  </si>
-  <si>
-    <t>Retired</t>
-  </si>
-  <si>
-    <t>已下架</t>
-  </si>
-  <si>
-    <t>DebugOnly</t>
-  </si>
-  <si>
-    <t>仅调试</t>
-  </si>
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>PayoutMultiplier</t>
-  </si>
-  <si>
-    <t>HandRank</t>
-  </si>
-  <si>
-    <t>OriginalName</t>
-  </si>
-  <si>
-    <t>SafeName_EN</t>
-  </si>
-  <si>
-    <t>SafeName_CN</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>EHandRank</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>赔率</t>
-  </si>
-  <si>
-    <t>原始名称</t>
-  </si>
-  <si>
-    <t>安全英文</t>
-  </si>
-  <si>
-    <t>安全中文</t>
-  </si>
-  <si>
-    <t>JacksOrBetter</t>
-  </si>
-  <si>
-    <t>Jacks or Better</t>
-  </si>
-  <si>
-    <t>Top Dogs</t>
-  </si>
-  <si>
-    <t>好犬优选</t>
-  </si>
-  <si>
-    <t>TwoPair</t>
-  </si>
-  <si>
-    <t>Two Pair</t>
-  </si>
-  <si>
-    <t>Twin Pairs</t>
-  </si>
-  <si>
-    <t>双犬配对</t>
-  </si>
-  <si>
-    <t>ThreeOfAKind</t>
-  </si>
-  <si>
-    <t>Three of a Kind</t>
-  </si>
-  <si>
-    <t>Triple Pals</t>
-  </si>
-  <si>
-    <t>三犬同行</t>
-  </si>
-  <si>
-    <t>Straight</t>
-  </si>
-  <si>
-    <t>Chain Walk</t>
-  </si>
-  <si>
-    <t>顺位犬链</t>
-  </si>
-  <si>
-    <t>Flush</t>
-  </si>
-  <si>
-    <t>Matching Den</t>
-  </si>
-  <si>
-    <t>同色犬舍</t>
-  </si>
-  <si>
-    <t>FullHouse</t>
-  </si>
-  <si>
-    <t>Full House</t>
-  </si>
-  <si>
-    <t>Puppy Party</t>
-  </si>
-  <si>
-    <t>狗狗满堂</t>
-  </si>
-  <si>
-    <t>FourOfAKind</t>
-  </si>
-  <si>
-    <t>Four of a Kind</t>
-  </si>
-  <si>
-    <t>Dog Squad</t>
-  </si>
-  <si>
-    <t>四犬成团</t>
-  </si>
-  <si>
-    <t>StraightFlush</t>
-  </si>
-  <si>
-    <t>Straight Flush</t>
-  </si>
-  <si>
-    <t>Purebred Strike</t>
-  </si>
-  <si>
-    <t>纯种犬连击</t>
-  </si>
-  <si>
-    <t>RoyalFlush</t>
-  </si>
-  <si>
-    <t>Royal Flush</t>
-  </si>
-  <si>
-    <t>Royal Feast</t>
-  </si>
-  <si>
-    <t>皇家狗粮</t>
-  </si>
-  <si>
     <t>IconName</t>
   </si>
   <si>
@@ -822,9 +822,6 @@
   </si>
   <si>
     <t>WearGlasses</t>
-  </si>
-  <si>
-    <t>ShowEquippedEyewearByDefault</t>
   </si>
   <si>
     <t>LeftPawAnimation</t>
@@ -2283,123 +2280,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="18.75" customWidth="1"/>
-    <col min="2" max="2" width="15.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="56.0833333333333" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="5"/>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="B2:P23"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
@@ -2410,374 +2290,374 @@
   <sheetData>
     <row r="2" spans="2:16">
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J2" s="4">
         <v>1</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:16">
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J3" s="4">
         <v>2</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:16">
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J4" s="4">
         <v>4</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="2:16">
       <c r="B5" s="4" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="J5" s="4">
         <v>8</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="2:16">
       <c r="B6" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="J6" s="4">
         <v>16</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:16">
       <c r="B7" s="4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="J7" s="4">
         <v>32</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="2:16">
       <c r="B8" s="4" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="J8" s="4">
         <v>64</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="4" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="J9" s="4">
         <v>128</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="J10" s="4">
         <v>256</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="4" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="J11" s="4">
         <v>512</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="4" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J12" s="4">
         <v>1024</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="H13" s="4" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="J13" s="4">
         <v>2048</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="4" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="B19" s="4" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="4" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" s="4" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="4" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="B23" s="4" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2666,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G13"/>
@@ -2801,75 +2681,75 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="F1" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="G1" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="G2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="F4" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="G4" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2880,16 +2760,16 @@
         <v>50</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="F5" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="G5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2900,16 +2780,16 @@
         <v>100</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="F6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="G6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2920,16 +2800,16 @@
         <v>150</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="F7" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="G7" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2940,16 +2820,16 @@
         <v>200</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F8" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="G8" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2960,16 +2840,16 @@
         <v>300</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F9" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="G9" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2980,16 +2860,16 @@
         <v>450</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F10" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="G10" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3000,16 +2880,16 @@
         <v>1000</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F11" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="G11" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3020,16 +2900,16 @@
         <v>2500</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="F12" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="G12" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3040,17 +2920,134 @@
         <v>12500</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E13" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="18.75" customWidth="1"/>
+    <col min="2" max="2" width="15.0833333333333" customWidth="1"/>
+    <col min="5" max="5" width="56.0833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="5"/>
+      <c r="B2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E13" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F13" t="s">
+      <c r="B4" t="s">
         <v>158</v>
       </c>
-      <c r="G13" t="s">
+      <c r="C4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>159</v>
       </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3084,10 +3081,10 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
@@ -3141,64 +3138,64 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" ht="34.8" spans="1:19">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3214,10 +3211,10 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="3" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
         <v>177</v>
@@ -3963,10 +3960,10 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>236</v>
@@ -3983,27 +3980,27 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
         <v>240</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4011,10 +4008,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
         <v>241</v>
@@ -4034,10 +4031,10 @@
         <v>1001</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E5" t="s">
         <v>245</v>
@@ -4051,10 +4048,10 @@
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>247</v>
@@ -4068,10 +4065,10 @@
         <v>1003</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
         <v>249</v>
@@ -4085,10 +4082,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
         <v>251</v>
@@ -4102,10 +4099,10 @@
         <v>1005</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
         <v>253</v>
@@ -4119,10 +4116,10 @@
         <v>1006</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>255</v>
@@ -4140,7 +4137,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="19" customWidth="1"/>
@@ -4149,17 +4146,16 @@
     <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
     <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
     <col min="8" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="11" width="29.25" customWidth="1"/>
-    <col min="12" max="14" width="9.58333333333333" customWidth="1"/>
-    <col min="21" max="21" width="12.9166666666667" customWidth="1"/>
+    <col min="11" max="13" width="9.58333333333333" customWidth="1"/>
+    <col min="20" max="20" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>257</v>
@@ -4191,143 +4187,140 @@
       <c r="N1" t="s">
         <v>266</v>
       </c>
-      <c r="O1" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J2" t="s">
         <v>268</v>
       </c>
-      <c r="E2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" t="s">
-        <v>269</v>
+      <c r="K2" t="s">
+        <v>108</v>
       </c>
       <c r="L2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="M2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="N2" t="s">
-        <v>120</v>
-      </c>
-      <c r="O2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" ht="104.4" spans="1:15">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" ht="104.4" spans="1:14">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="I3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>272</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>273</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>272</v>
+      </c>
+      <c r="G4" t="s">
         <v>274</v>
       </c>
-      <c r="F4" t="s">
-        <v>273</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>275</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>276</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>277</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>278</v>
       </c>
       <c r="L4" t="s">
         <v>279</v>
       </c>
       <c r="M4" t="s">
+        <v>185</v>
+      </c>
+      <c r="N4" t="s">
         <v>280</v>
       </c>
-      <c r="N4" t="s">
-        <v>185</v>
-      </c>
-      <c r="O4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+    </row>
+    <row r="5" spans="1:14">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
+      <c r="K5" t="s">
+        <v>281</v>
+      </c>
       <c r="L5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M5" t="s">
         <v>282</v>
       </c>
-      <c r="N5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+    </row>
+    <row r="6" spans="1:14">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
         <v>168</v>
@@ -4338,25 +4331,25 @@
       <c r="J6" t="b">
         <v>0</v>
       </c>
+      <c r="K6" t="s">
+        <v>281</v>
+      </c>
       <c r="L6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M6" t="s">
         <v>282</v>
       </c>
-      <c r="N6" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+    </row>
+    <row r="7" spans="1:14">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
         <v>169</v>
@@ -4367,25 +4360,25 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
+      <c r="K7" t="s">
+        <v>281</v>
+      </c>
       <c r="L7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M7" t="s">
         <v>282</v>
       </c>
-      <c r="N7" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+    </row>
+    <row r="8" spans="1:14">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
         <v>168</v>
@@ -4396,25 +4389,25 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
+      <c r="K8" t="s">
+        <v>281</v>
+      </c>
       <c r="L8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M8" t="s">
         <v>282</v>
       </c>
-      <c r="N8" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+    </row>
+    <row r="9" spans="1:14">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
         <v>168</v>
@@ -4425,25 +4418,25 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
+      <c r="K9" t="s">
+        <v>281</v>
+      </c>
       <c r="L9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M9" t="s">
         <v>282</v>
       </c>
-      <c r="N9" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+    </row>
+    <row r="10" spans="1:14">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
         <v>168</v>
@@ -4454,25 +4447,25 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
+      <c r="K10" t="s">
+        <v>281</v>
+      </c>
       <c r="L10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M10" t="s">
         <v>282</v>
       </c>
-      <c r="N10" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+    </row>
+    <row r="11" spans="1:14">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
         <v>169</v>
@@ -4483,25 +4476,25 @@
       <c r="J11" t="b">
         <v>1</v>
       </c>
+      <c r="K11" t="s">
+        <v>281</v>
+      </c>
       <c r="L11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M11" t="s">
         <v>282</v>
       </c>
-      <c r="N11" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+    </row>
+    <row r="12" spans="1:14">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G12" t="s">
         <v>169</v>
@@ -4512,356 +4505,356 @@
       <c r="J12" t="b">
         <v>1</v>
       </c>
+      <c r="K12" t="s">
+        <v>283</v>
+      </c>
       <c r="L12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M12" t="s">
-        <v>284</v>
-      </c>
-      <c r="N12" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="B13">
         <v>2001</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" t="s">
         <v>286</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+    </row>
+    <row r="14" spans="1:14">
       <c r="B14">
         <v>2002</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>289</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>8</v>
+      </c>
+      <c r="N14" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="B15">
         <v>2003</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
         <v>291</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" t="s">
-        <v>30</v>
-      </c>
-      <c r="O15" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+    </row>
+    <row r="16" spans="1:14">
       <c r="B16">
         <v>2004</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" t="s">
         <v>295</v>
       </c>
-      <c r="F16" t="s">
+      <c r="N16" t="s">
         <v>296</v>
       </c>
-      <c r="O16" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15">
+    </row>
+    <row r="17" spans="2:14">
       <c r="B17">
         <v>2005</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17" t="s">
         <v>299</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="O17" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15">
+    </row>
+    <row r="18" spans="2:14">
       <c r="B18">
         <v>2006</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="N18" t="s">
         <v>302</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="O18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15">
+    </row>
+    <row r="19" spans="2:14">
       <c r="B19">
         <v>2007</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
         <v>305</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" t="s">
-        <v>30</v>
-      </c>
-      <c r="O19" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15">
+    </row>
+    <row r="20" spans="2:14">
       <c r="B20">
         <v>2008</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" t="s">
+        <v>294</v>
+      </c>
+      <c r="F20" t="s">
+        <v>295</v>
+      </c>
+      <c r="N20" t="s">
         <v>308</v>
       </c>
-      <c r="E20" t="s">
-        <v>295</v>
-      </c>
-      <c r="F20" t="s">
-        <v>296</v>
-      </c>
-      <c r="O20" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15">
+    </row>
+    <row r="21" spans="2:14">
       <c r="B21">
         <v>3001</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>311</v>
-      </c>
       <c r="E21" s="4" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
       <c r="B22">
         <v>3002</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>313</v>
-      </c>
       <c r="E22" s="4" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
       <c r="B23">
         <v>3003</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>315</v>
-      </c>
       <c r="E23" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
       <c r="B24">
         <v>3004</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>317</v>
-      </c>
       <c r="E24" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
       <c r="B25">
         <v>3005</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>319</v>
-      </c>
       <c r="E25" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
       <c r="B26">
         <v>3006</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>321</v>
-      </c>
       <c r="E26" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
       <c r="B27">
         <v>3007</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="E27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" t="s">
+        <v>44</v>
+      </c>
+      <c r="M27" t="s">
         <v>323</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
       </c>
       <c r="N27" t="s">
         <v>324</v>
       </c>
-      <c r="O27" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15">
+    </row>
+    <row r="28" spans="2:14">
       <c r="B28">
         <v>3008</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>327</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
       <c r="B29">
         <v>3009</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>329</v>
-      </c>
       <c r="E29" s="4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="F29" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
       <c r="B30">
         <v>3010</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>331</v>
-      </c>
       <c r="E30" s="4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>53</v>
+      </c>
+      <c r="M30" t="s">
+        <v>323</v>
       </c>
       <c r="N30" t="s">
         <v>324</v>
-      </c>
-      <c r="O30" t="s">
-        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -4891,142 +4884,142 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D1" t="s">
         <v>332</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>333</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>334</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>335</v>
-      </c>
-      <c r="G1" t="s">
-        <v>336</v>
       </c>
       <c r="H1" t="s">
         <v>257</v>
       </c>
       <c r="I1" t="s">
+        <v>336</v>
+      </c>
+      <c r="J1" t="s">
         <v>337</v>
       </c>
-      <c r="J1" t="s">
-        <v>338</v>
-      </c>
       <c r="K1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>155</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>155</v>
       </c>
       <c r="H2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I2" t="s">
         <v>268</v>
       </c>
-      <c r="I2" t="s">
-        <v>269</v>
-      </c>
       <c r="J2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="K2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" ht="87" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
+        <v>347</v>
+      </c>
+      <c r="D4" t="s">
         <v>348</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>349</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>350</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>351</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>352</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>353</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>354</v>
       </c>
-      <c r="J4" t="s">
-        <v>355</v>
-      </c>
       <c r="K4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -5034,7 +5027,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5049,7 +5042,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -5058,7 +5051,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -5066,7 +5059,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -5081,7 +5074,7 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -5090,7 +5083,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -5098,7 +5091,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -5113,7 +5106,7 @@
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -5122,7 +5115,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -5130,7 +5123,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -5145,7 +5138,7 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -5154,7 +5147,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="5"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -2944,7 +2944,7 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="18.75" customWidth="1"/>
+    <col min="1" max="1" width="21.9166666666667" customWidth="1"/>
     <col min="2" max="2" width="15.0833333333333" customWidth="1"/>
     <col min="5" max="5" width="56.0833333333333" customWidth="1"/>
   </cols>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="717" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -497,13 +497,13 @@
     <t>BlindBoxTimeScale</t>
   </si>
   <si>
-    <t>盲盒时间倍率</t>
+    <t>等待盲盒时间倍率</t>
   </si>
   <si>
     <t>float</t>
   </si>
   <si>
-    <t>盲盒调度时间倍率，开发时填1,playtest时填5,正式上线填10</t>
+    <t>等待盲盒到达时间的倍率，开发时填1,playtest时填5,正式上线填10，数字越大等待时间越久</t>
   </si>
   <si>
     <t>BlindBoxCostScale</t>
@@ -2946,7 +2946,7 @@
   <cols>
     <col min="1" max="1" width="21.9166666666667" customWidth="1"/>
     <col min="2" max="2" width="15.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="56.0833333333333" customWidth="1"/>
+    <col min="5" max="5" width="70.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="717" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="717" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="368">
   <si>
     <t>Dog</t>
   </si>
@@ -770,28 +770,49 @@
     <t>底板</t>
   </si>
   <si>
+    <t>UI\ItemUI\Frame_Common.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Common.png</t>
+  </si>
+  <si>
+    <t>Unommon</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Unommon.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Unommon.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Rare.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Rare.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Epic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Epic.png</t>
+  </si>
+  <si>
     <t>UI\ItemUI\Frame_Legendary.png</t>
   </si>
   <si>
     <t>UI\ItemUI\Plate_Legendary.png</t>
   </si>
   <si>
-    <t>UI\ItemUI\Frame_Epic.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Plate_Epic.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Frame_Rare.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Plate_Rare.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Frame_Common.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Plate_Common.png</t>
+    <t>Mythic</t>
+  </si>
+  <si>
+    <t>神话</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Mythic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Mythic.png</t>
   </si>
   <si>
     <t>UI\ItemUI\Frame_Special1.png</t>
@@ -3949,7 +3970,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="5.25" customWidth="1"/>
@@ -4031,10 +4052,10 @@
         <v>1001</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>245</v>
@@ -4048,16 +4069,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>11</v>
+        <v>247</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4071,10 +4092,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4082,16 +4103,16 @@
         <v>1004</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4099,33 +4120,67 @@
         <v>1005</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D10" t="s">
+        <v>257</v>
+      </c>
+      <c r="E10" t="s">
+        <v>258</v>
+      </c>
+      <c r="F10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11">
+        <v>2001</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>260</v>
+      </c>
+      <c r="F11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12">
+        <v>2002</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E10" t="s">
-        <v>255</v>
-      </c>
-      <c r="F10" t="s">
-        <v>256</v>
+      <c r="E12" t="s">
+        <v>262</v>
+      </c>
+      <c r="F12" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4158,34 +4213,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="E1" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="G1" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="H1" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="I1" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J1" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="K1" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="L1" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="M1" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="N1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -4196,10 +4251,10 @@
         <v>106</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E2" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="G2" t="s">
         <v>108</v>
@@ -4211,7 +4266,7 @@
         <v>108</v>
       </c>
       <c r="J2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="K2" t="s">
         <v>108</v>
@@ -4233,10 +4288,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -4247,40 +4302,40 @@
         <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="E4" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="F4" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="G4" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="H4" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="I4" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="J4" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K4" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="L4" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="M4" t="s">
         <v>185</v>
       </c>
       <c r="N4" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -4303,13 +4358,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="L5" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="M5" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -4332,13 +4387,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="L6" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="M6" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4361,13 +4416,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="L7" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="M7" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4390,13 +4445,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="L8" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="M8" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4419,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="L9" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="M9" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4448,13 +4503,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="L10" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="M10" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4477,13 +4532,13 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="L11" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="M11" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4506,13 +4561,13 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="L12" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="M12" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4520,10 +4575,10 @@
         <v>2001</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>7</v>
@@ -4532,7 +4587,7 @@
         <v>8</v>
       </c>
       <c r="N13" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -4540,10 +4595,10 @@
         <v>2002</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -4552,7 +4607,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4560,10 +4615,10 @@
         <v>2003</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>16</v>
@@ -4572,7 +4627,7 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4580,19 +4635,19 @@
         <v>2004</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="F16" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="N16" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -4600,10 +4655,10 @@
         <v>2005</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>59</v>
@@ -4612,7 +4667,7 @@
         <v>60</v>
       </c>
       <c r="N17" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -4620,10 +4675,10 @@
         <v>2006</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>66</v>
@@ -4632,7 +4687,7 @@
         <v>67</v>
       </c>
       <c r="N18" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -4640,10 +4695,10 @@
         <v>2007</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>16</v>
@@ -4652,7 +4707,7 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -4660,19 +4715,19 @@
         <v>2008</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E20" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="F20" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="N20" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -4680,10 +4735,10 @@
         <v>3001</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>25</v>
@@ -4697,10 +4752,10 @@
         <v>3002</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>25</v>
@@ -4714,10 +4769,10 @@
         <v>3003</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>34</v>
@@ -4731,10 +4786,10 @@
         <v>3004</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>34</v>
@@ -4748,10 +4803,10 @@
         <v>3005</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>43</v>
@@ -4765,10 +4820,10 @@
         <v>3006</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>43</v>
@@ -4782,10 +4837,10 @@
         <v>3007</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>43</v>
@@ -4794,10 +4849,10 @@
         <v>44</v>
       </c>
       <c r="M27" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N27" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" spans="2:14">
@@ -4805,10 +4860,10 @@
         <v>3008</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>52</v>
@@ -4822,10 +4877,10 @@
         <v>3009</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>52</v>
@@ -4839,10 +4894,10 @@
         <v>3010</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>52</v>
@@ -4851,10 +4906,10 @@
         <v>53</v>
       </c>
       <c r="M30" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N30" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -4890,31 +4945,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="D1" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="E1" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F1" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="G1" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="H1" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="I1" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="J1" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="K1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -4940,10 +4995,10 @@
         <v>155</v>
       </c>
       <c r="H2" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="I2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="J2" t="s">
         <v>106</v>
@@ -4957,34 +5012,34 @@
         <v>109</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -4995,31 +5050,31 @@
         <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D4" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E4" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="F4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="G4" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="H4" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="I4" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="J4" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="K4" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -5027,7 +5082,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5051,7 +5106,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -5059,7 +5114,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -5083,7 +5138,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -5091,7 +5146,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -5115,7 +5170,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -5123,7 +5178,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -5147,7 +5202,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -779,10 +779,10 @@
     <t>Unommon</t>
   </si>
   <si>
-    <t>UI\ItemUI\Frame_Unommon.png</t>
-  </si>
-  <si>
-    <t>UI\ItemUI\Plate_Unommon.png</t>
+    <t>UI\ItemUI\Frame_Uncommon.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Uncommon.png</t>
   </si>
   <si>
     <t>UI\ItemUI\Frame_Rare.png</t>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="717" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="369">
   <si>
     <t>Dog</t>
   </si>
@@ -522,6 +522,9 @@
   </si>
   <si>
     <t>DefaultEyes</t>
+  </si>
+  <si>
+    <t>DefaultTongue</t>
   </si>
   <si>
     <t>FolderPath</t>
@@ -3079,28 +3082,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
     <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
-    <col min="4" max="6" width="21.9166666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.5" customWidth="1"/>
-    <col min="8" max="8" width="16.5833333333333" customWidth="1"/>
-    <col min="9" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="11" width="20.8333333333333" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="13" max="13" width="13.4166666666667" customWidth="1"/>
-    <col min="14" max="14" width="14.3333333333333" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="14.8333333333333" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="15.4166666666667" customWidth="1"/>
-    <col min="19" max="19" width="13.4166666666667" customWidth="1"/>
+    <col min="4" max="7" width="21.9166666666667" customWidth="1"/>
+    <col min="8" max="8" width="15.5" customWidth="1"/>
+    <col min="9" max="9" width="16.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="18.5" customWidth="1"/>
+    <col min="11" max="12" width="20.8333333333333" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
+    <col min="14" max="14" width="13.4166666666667" customWidth="1"/>
+    <col min="15" max="15" width="14.3333333333333" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="14.8333333333333" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="15.4166666666667" customWidth="1"/>
+    <col min="20" max="20" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
@@ -3123,7 +3126,7 @@
       <c r="H1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>165</v>
       </c>
       <c r="J1" t="s">
@@ -3156,8 +3159,11 @@
       <c r="S1" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="2" t="s">
         <v>105</v>
       </c>
@@ -3213,8 +3219,11 @@
       <c r="S2" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="3" ht="34.8" spans="1:19">
+      <c r="T2" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" ht="34.8" spans="1:20">
       <c r="A3" s="3" t="s">
         <v>109</v>
       </c>
@@ -3222,15 +3231,16 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" s="3" t="s">
         <v>109</v>
       </c>
@@ -3238,18 +3248,15 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F4" t="s">
-        <v>180</v>
-      </c>
-      <c r="G4" t="s">
         <v>181</v>
       </c>
       <c r="H4" t="s">
@@ -3288,25 +3295,28 @@
       <c r="S4" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="T4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G5" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="H5" t="s">
         <v>199</v>
@@ -3321,19 +3331,19 @@
         <v>202</v>
       </c>
       <c r="L5" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N5" t="s">
         <v>204</v>
       </c>
       <c r="O5" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P5" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Q5" t="s">
         <v>206</v>
@@ -3344,28 +3354,31 @@
       <c r="S5" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G6" t="s">
-        <v>211</v>
+        <v>168</v>
       </c>
       <c r="H6" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="I6" t="s">
         <v>200</v>
@@ -3377,19 +3390,19 @@
         <v>202</v>
       </c>
       <c r="L6" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M6" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N6" t="s">
         <v>204</v>
       </c>
       <c r="O6" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P6" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Q6" t="s">
         <v>206</v>
@@ -3400,28 +3413,31 @@
       <c r="S6" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G7" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="H7" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="I7" t="s">
         <v>200</v>
@@ -3433,19 +3449,19 @@
         <v>202</v>
       </c>
       <c r="L7" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M7" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N7" t="s">
         <v>204</v>
       </c>
       <c r="O7" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P7" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Q7" t="s">
         <v>206</v>
@@ -3456,28 +3472,31 @@
       <c r="S7" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="T7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G8" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="H8" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="I8" t="s">
         <v>200</v>
@@ -3489,19 +3508,19 @@
         <v>202</v>
       </c>
       <c r="L8" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M8" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N8" t="s">
         <v>204</v>
       </c>
       <c r="O8" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P8" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Q8" t="s">
         <v>206</v>
@@ -3512,31 +3531,34 @@
       <c r="S8" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="T8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G9" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="H9" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="I9" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="J9" t="s">
         <v>201</v>
@@ -3545,19 +3567,19 @@
         <v>202</v>
       </c>
       <c r="L9" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M9" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N9" t="s">
         <v>204</v>
       </c>
       <c r="O9" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P9" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Q9" t="s">
         <v>206</v>
@@ -3568,31 +3590,34 @@
       <c r="S9" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="T9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G10" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="H10" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="I10" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="J10" t="s">
         <v>201</v>
@@ -3601,19 +3626,19 @@
         <v>202</v>
       </c>
       <c r="L10" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M10" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N10" t="s">
         <v>204</v>
       </c>
       <c r="O10" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P10" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Q10" t="s">
         <v>206</v>
@@ -3624,31 +3649,34 @@
       <c r="S10" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="T10" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G11" t="s">
-        <v>211</v>
+        <v>168</v>
       </c>
       <c r="H11" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="I11" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="J11" t="s">
         <v>201</v>
@@ -3657,19 +3685,19 @@
         <v>202</v>
       </c>
       <c r="L11" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M11" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N11" t="s">
         <v>204</v>
       </c>
       <c r="O11" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P11" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Q11" t="s">
         <v>206</v>
@@ -3680,31 +3708,34 @@
       <c r="S11" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="T11" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G12" t="s">
-        <v>211</v>
+        <v>168</v>
       </c>
       <c r="H12" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="I12" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="J12" t="s">
         <v>201</v>
@@ -3713,19 +3744,19 @@
         <v>202</v>
       </c>
       <c r="L12" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M12" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N12" t="s">
         <v>204</v>
       </c>
       <c r="O12" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P12" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Q12" t="s">
         <v>206</v>
@@ -3736,31 +3767,34 @@
       <c r="S12" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="T12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G13" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="H13" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="I13" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="J13" t="s">
         <v>201</v>
@@ -3769,19 +3803,19 @@
         <v>202</v>
       </c>
       <c r="L13" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M13" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N13" t="s">
         <v>204</v>
       </c>
       <c r="O13" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P13" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Q13" t="s">
         <v>206</v>
@@ -3792,31 +3826,34 @@
       <c r="S13" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="14" spans="1:19">
+      <c r="T13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G14" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="H14" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="I14" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="J14" t="s">
         <v>201</v>
@@ -3825,19 +3862,19 @@
         <v>202</v>
       </c>
       <c r="L14" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M14" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N14" t="s">
         <v>204</v>
       </c>
       <c r="O14" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P14" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Q14" t="s">
         <v>206</v>
@@ -3848,31 +3885,34 @@
       <c r="S14" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="T14" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G15" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="H15" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I15" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="J15" t="s">
         <v>201</v>
@@ -3881,19 +3921,19 @@
         <v>202</v>
       </c>
       <c r="L15" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M15" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N15" t="s">
         <v>204</v>
       </c>
       <c r="O15" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P15" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Q15" t="s">
         <v>206</v>
@@ -3904,31 +3944,34 @@
       <c r="S15" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="16" spans="1:19">
+      <c r="T15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G16" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="H16" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I16" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="J16" t="s">
         <v>201</v>
@@ -3937,19 +3980,19 @@
         <v>202</v>
       </c>
       <c r="L16" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M16" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N16" t="s">
         <v>204</v>
       </c>
       <c r="O16" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P16" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Q16" t="s">
         <v>206</v>
@@ -3959,6 +4002,9 @@
       </c>
       <c r="S16" t="s">
         <v>208</v>
+      </c>
+      <c r="T16" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -3987,16 +4033,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4010,7 +4056,7 @@
         <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E2" t="s">
         <v>108</v>
@@ -4035,16 +4081,16 @@
         <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4058,10 +4104,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4069,16 +4115,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4092,10 +4138,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4109,10 +4155,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4126,10 +4172,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4137,16 +4183,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4160,10 +4206,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4177,10 +4223,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -4213,34 +4259,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -4251,10 +4297,10 @@
         <v>106</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G2" t="s">
         <v>108</v>
@@ -4266,7 +4312,7 @@
         <v>108</v>
       </c>
       <c r="J2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K2" t="s">
         <v>108</v>
@@ -4288,10 +4334,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -4302,40 +4348,40 @@
         <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F4" t="s">
         <v>280</v>
       </c>
-      <c r="F4" t="s">
-        <v>279</v>
-      </c>
       <c r="G4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -4358,13 +4404,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -4378,22 +4424,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4407,22 +4453,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4436,22 +4482,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4465,22 +4511,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4494,22 +4540,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4523,22 +4569,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4552,22 +4598,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
+        <v>291</v>
+      </c>
+      <c r="L12" t="s">
+        <v>291</v>
+      </c>
+      <c r="M12" t="s">
         <v>290</v>
-      </c>
-      <c r="L12" t="s">
-        <v>290</v>
-      </c>
-      <c r="M12" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4575,10 +4621,10 @@
         <v>2001</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>7</v>
@@ -4587,7 +4633,7 @@
         <v>8</v>
       </c>
       <c r="N13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -4595,10 +4641,10 @@
         <v>2002</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -4607,7 +4653,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4615,10 +4661,10 @@
         <v>2003</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>16</v>
@@ -4627,7 +4673,7 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4635,19 +4681,19 @@
         <v>2004</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -4655,10 +4701,10 @@
         <v>2005</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>59</v>
@@ -4667,7 +4713,7 @@
         <v>60</v>
       </c>
       <c r="N17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -4675,10 +4721,10 @@
         <v>2006</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>66</v>
@@ -4687,7 +4733,7 @@
         <v>67</v>
       </c>
       <c r="N18" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -4695,10 +4741,10 @@
         <v>2007</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>16</v>
@@ -4707,7 +4753,7 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -4715,19 +4761,19 @@
         <v>2008</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F20" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -4735,10 +4781,10 @@
         <v>3001</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>25</v>
@@ -4752,10 +4798,10 @@
         <v>3002</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>25</v>
@@ -4769,10 +4815,10 @@
         <v>3003</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>34</v>
@@ -4786,10 +4832,10 @@
         <v>3004</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>34</v>
@@ -4803,10 +4849,10 @@
         <v>3005</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>43</v>
@@ -4820,10 +4866,10 @@
         <v>3006</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>43</v>
@@ -4837,10 +4883,10 @@
         <v>3007</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>43</v>
@@ -4849,10 +4895,10 @@
         <v>44</v>
       </c>
       <c r="M27" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N27" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="2:14">
@@ -4860,10 +4906,10 @@
         <v>3008</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>52</v>
@@ -4877,10 +4923,10 @@
         <v>3009</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>52</v>
@@ -4894,10 +4940,10 @@
         <v>3010</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>52</v>
@@ -4906,10 +4952,10 @@
         <v>53</v>
       </c>
       <c r="M30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -4945,31 +4991,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -4995,10 +5041,10 @@
         <v>155</v>
       </c>
       <c r="H2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J2" t="s">
         <v>106</v>
@@ -5012,34 +5058,34 @@
         <v>109</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -5050,31 +5096,31 @@
         <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -5082,7 +5128,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5106,7 +5152,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -5114,7 +5160,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -5138,7 +5184,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -5146,7 +5192,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -5170,7 +5216,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -5178,7 +5224,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -5202,7 +5248,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="375">
   <si>
     <t>Dog</t>
   </si>
@@ -872,6 +872,9 @@
     <t>有些表情需要临时更换头饰，例如被打晕的时候头上转的星星。但目前版本没有</t>
   </si>
   <si>
+    <t>左指画面左侧，而非狗自己的左</t>
+  </si>
+  <si>
     <t>枚举</t>
   </si>
   <si>
@@ -911,6 +914,21 @@
     <t>手心，摆手</t>
   </si>
   <si>
+    <t>Hello</t>
+  </si>
+  <si>
+    <t>哈喽</t>
+  </si>
+  <si>
+    <t>手心，摆手两次</t>
+  </si>
+  <si>
+    <t>哈气</t>
+  </si>
+  <si>
+    <t>舌头上下略微移动</t>
+  </si>
+  <si>
     <t>WaitingForBet</t>
   </si>
   <si>
@@ -986,6 +1004,12 @@
     <t>根据牌型优劣作出相应表情</t>
   </si>
   <si>
+    <t>InteractionHint</t>
+  </si>
+  <si>
+    <t>提示玩家可以询问</t>
+  </si>
+  <si>
     <t>SawNothing</t>
   </si>
   <si>
@@ -1026,12 +1050,6 @@
   </si>
   <si>
     <t>看到葫芦</t>
-  </si>
-  <si>
-    <t>哈气</t>
-  </si>
-  <si>
-    <t>舌头上下略微移动</t>
   </si>
   <si>
     <t>SawFourOfAKind</t>
@@ -1760,7 +1778,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1771,6 +1789,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2313,374 +2334,374 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="5">
         <v>1</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="5">
         <v>2</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>4</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="5">
         <v>8</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="5">
         <v>16</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="P6" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="5">
         <v>32</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="P7" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="5">
         <v>64</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="5">
         <v>128</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="P9" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="5">
         <v>256</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="5">
         <v>512</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="5" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="5">
         <v>1024</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="5">
         <v>2048</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2783,7 +2804,7 @@
       <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>115</v>
       </c>
       <c r="E5" t="s">
@@ -2803,7 +2824,7 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>119</v>
       </c>
       <c r="E6" t="s">
@@ -2823,7 +2844,7 @@
       <c r="C7">
         <v>150</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>123</v>
       </c>
       <c r="E7" t="s">
@@ -2843,7 +2864,7 @@
       <c r="C8">
         <v>200</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>127</v>
       </c>
       <c r="E8" t="s">
@@ -2863,7 +2884,7 @@
       <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>130</v>
       </c>
       <c r="E9" t="s">
@@ -2883,7 +2904,7 @@
       <c r="C10">
         <v>450</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>133</v>
       </c>
       <c r="E10" t="s">
@@ -2903,7 +2924,7 @@
       <c r="C11">
         <v>1000</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>137</v>
       </c>
       <c r="E11" t="s">
@@ -2923,7 +2944,7 @@
       <c r="C12">
         <v>2500</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>141</v>
       </c>
       <c r="E12" t="s">
@@ -2943,7 +2964,7 @@
       <c r="C13">
         <v>12500</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>145</v>
       </c>
       <c r="E13" t="s">
@@ -2974,30 +2995,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="5"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3014,7 +3035,7 @@
       <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>156</v>
       </c>
     </row>
@@ -3038,7 +3059,7 @@
     <row r="5" spans="1:5">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:5">
@@ -3050,7 +3071,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="4"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
@@ -3062,14 +3083,14 @@
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="4"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="4"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
@@ -4097,10 +4118,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E5" t="s">
@@ -4114,10 +4135,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
@@ -4131,10 +4152,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E7" t="s">
@@ -4148,10 +4169,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
@@ -4165,10 +4186,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E9" t="s">
@@ -4199,10 +4220,10 @@
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E11" t="s">
@@ -4216,10 +4237,10 @@
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E12" t="s">
@@ -4238,7 +4259,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="19" customWidth="1"/>
@@ -4339,6 +4360,9 @@
       <c r="I3" s="1" t="s">
         <v>278</v>
       </c>
+      <c r="K3" s="4" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
@@ -4348,50 +4372,50 @@
         <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F4" t="s">
         <v>281</v>
       </c>
-      <c r="F4" t="s">
-        <v>280</v>
-      </c>
       <c r="G4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M4" t="s">
         <v>186</v>
       </c>
       <c r="N4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G5" t="s">
@@ -4404,23 +4428,23 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
@@ -4433,23 +4457,23 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
@@ -4462,23 +4486,23 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G8" t="s">
@@ -4491,23 +4515,23 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>44</v>
       </c>
       <c r="G9" t="s">
@@ -4520,23 +4544,23 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G10" t="s">
@@ -4549,23 +4573,23 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>60</v>
       </c>
       <c r="G11" t="s">
@@ -4578,23 +4602,23 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>67</v>
       </c>
       <c r="G12" t="s">
@@ -4607,355 +4631,404 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
+        <v>292</v>
+      </c>
+      <c r="L12" t="s">
+        <v>292</v>
+      </c>
+      <c r="M12" t="s">
         <v>291</v>
-      </c>
-      <c r="L12" t="s">
-        <v>291</v>
-      </c>
-      <c r="M12" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="B13">
-        <v>2001</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="D13" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>8</v>
+      <c r="D13" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="G13" t="s">
+        <v>169</v>
+      </c>
+      <c r="H13" t="s">
+        <v>172</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>290</v>
+      </c>
+      <c r="L13" t="s">
+        <v>295</v>
+      </c>
+      <c r="M13" t="s">
+        <v>296</v>
       </c>
       <c r="N13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="B14">
-        <v>2002</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E14" s="4" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="B15">
-        <v>2003</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>16</v>
+        <v>2002</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="B16">
-        <v>2004</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>302</v>
+        <v>2003</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>303</v>
+        <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="2:14">
       <c r="B17">
-        <v>2005</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="D17" s="4" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>60</v>
+      <c r="D17" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F17" t="s">
+        <v>309</v>
       </c>
       <c r="N17" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" spans="2:14">
       <c r="B18">
-        <v>2006</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>67</v>
+        <v>2005</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="2:14">
       <c r="B19">
-        <v>2007</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" t="s">
-        <v>17</v>
+        <v>2006</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" spans="2:14">
       <c r="B20">
-        <v>2008</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="E20" t="s">
-        <v>302</v>
+        <v>2007</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>303</v>
+        <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" spans="2:14">
       <c r="B21">
-        <v>3001</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>25</v>
+        <v>2008</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="E21" t="s">
+        <v>308</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>309</v>
+      </c>
+      <c r="N21" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="2:14">
       <c r="B22">
-        <v>3002</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" t="s">
-        <v>26</v>
+        <v>2009</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="23" spans="2:14">
       <c r="B23">
-        <v>3003</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>34</v>
+        <v>3001</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="2:14">
       <c r="B24">
-        <v>3004</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>34</v>
+        <v>3002</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="2:14">
       <c r="B25">
-        <v>3005</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>43</v>
+        <v>3003</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="2:14">
       <c r="B26">
-        <v>3006</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>43</v>
+        <v>3004</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="F26" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="2:14">
       <c r="B27">
-        <v>3007</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="E27" s="4" t="s">
+        <v>3005</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F27" t="s">
         <v>44</v>
       </c>
-      <c r="M27" t="s">
-        <v>331</v>
-      </c>
-      <c r="N27" t="s">
-        <v>332</v>
-      </c>
     </row>
     <row r="28" spans="2:14">
       <c r="B28">
-        <v>3008</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>52</v>
+        <v>3006</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="2:14">
       <c r="B29">
-        <v>3009</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>52</v>
+        <v>3007</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="M29" t="s">
+        <v>296</v>
+      </c>
+      <c r="N29" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="30" spans="2:14">
       <c r="B30">
-        <v>3010</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="E30" s="4" t="s">
+        <v>3008</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F30" t="s">
         <v>53</v>
       </c>
-      <c r="M30" t="s">
-        <v>331</v>
-      </c>
-      <c r="N30" t="s">
-        <v>332</v>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31">
+        <v>3009</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32">
+        <v>3010</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" t="s">
+        <v>53</v>
+      </c>
+      <c r="M32" t="s">
+        <v>296</v>
+      </c>
+      <c r="N32" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -4991,28 +5064,28 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="D1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="G1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="H1" t="s">
         <v>265</v>
       </c>
       <c r="I1" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="J1" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="K1" t="s">
         <v>274</v>
@@ -5058,34 +5131,34 @@
         <v>109</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -5096,31 +5169,31 @@
         <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D4" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E4" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F4" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="G4" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="H4" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="I4" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="J4" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="K4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -5128,7 +5201,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5152,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -5160,7 +5233,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -5184,7 +5257,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -5192,7 +5265,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -5216,7 +5289,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -5224,7 +5297,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -5248,7 +5321,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -965,7 +965,7 @@
     <t>约定</t>
   </si>
   <si>
-    <t>如果玩家进行了询问，再作出相应的预测表情。</t>
+    <t>如果玩家进行了询问，再作出相应的预测表情。（未真实现具体内容只做表内意图表达）</t>
   </si>
   <si>
     <t>HintExhausted</t>
@@ -1001,7 +1001,7 @@
     <t>看到结算结果</t>
   </si>
   <si>
-    <t>根据牌型优劣作出相应表情</t>
+    <t>根据牌型优劣作出相应表情（未真实现具体内容只做表内意图表达）</t>
   </si>
   <si>
     <t>InteractionHint</t>
@@ -1778,7 +1778,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1789,9 +1789,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2334,374 +2331,374 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>4</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>8</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>16</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="P6" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>32</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="P7" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <v>64</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="P8" s="4" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>128</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="P9" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>256</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>512</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>1024</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="4">
         <v>2048</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2804,7 +2801,7 @@
       <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>115</v>
       </c>
       <c r="E5" t="s">
@@ -2824,7 +2821,7 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>119</v>
       </c>
       <c r="E6" t="s">
@@ -2844,7 +2841,7 @@
       <c r="C7">
         <v>150</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>123</v>
       </c>
       <c r="E7" t="s">
@@ -2864,7 +2861,7 @@
       <c r="C8">
         <v>200</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>127</v>
       </c>
       <c r="E8" t="s">
@@ -2884,7 +2881,7 @@
       <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>130</v>
       </c>
       <c r="E9" t="s">
@@ -2904,7 +2901,7 @@
       <c r="C10">
         <v>450</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>133</v>
       </c>
       <c r="E10" t="s">
@@ -2924,7 +2921,7 @@
       <c r="C11">
         <v>1000</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>137</v>
       </c>
       <c r="E11" t="s">
@@ -2944,7 +2941,7 @@
       <c r="C12">
         <v>2500</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>141</v>
       </c>
       <c r="E12" t="s">
@@ -2964,7 +2961,7 @@
       <c r="C13">
         <v>12500</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>145</v>
       </c>
       <c r="E13" t="s">
@@ -2995,30 +2992,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="6"/>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3035,7 +3032,7 @@
       <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>156</v>
       </c>
     </row>
@@ -3059,7 +3056,7 @@
     <row r="5" spans="1:5">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="5"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:5">
@@ -3071,7 +3068,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="5"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
@@ -3083,14 +3080,14 @@
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="5"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="5"/>
+      <c r="C10" s="4"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
@@ -4118,10 +4115,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E5" t="s">
@@ -4135,10 +4132,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
@@ -4152,10 +4149,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E7" t="s">
@@ -4169,10 +4166,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
@@ -4186,10 +4183,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E9" t="s">
@@ -4220,10 +4217,10 @@
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E11" t="s">
@@ -4237,10 +4234,10 @@
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>48</v>
       </c>
       <c r="E12" t="s">
@@ -4360,7 +4357,7 @@
       <c r="I3" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>279</v>
       </c>
     </row>
@@ -4412,10 +4409,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="G5" t="s">
@@ -4441,10 +4438,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
@@ -4470,10 +4467,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
@@ -4499,10 +4496,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>35</v>
       </c>
       <c r="G8" t="s">
@@ -4528,10 +4525,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G9" t="s">
@@ -4557,10 +4554,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="G10" t="s">
@@ -4586,10 +4583,10 @@
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>60</v>
       </c>
       <c r="G11" t="s">
@@ -4615,10 +4612,10 @@
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>67</v>
       </c>
       <c r="G12" t="s">
@@ -4644,10 +4641,10 @@
       <c r="B13">
         <v>1009</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>294</v>
       </c>
       <c r="G13" t="s">
@@ -4676,13 +4673,13 @@
       <c r="B14">
         <v>2001</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
@@ -4696,13 +4693,13 @@
       <c r="B15">
         <v>2002</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F15" t="s">
@@ -4716,13 +4713,13 @@
       <c r="B16">
         <v>2003</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F16" t="s">
@@ -4736,13 +4733,13 @@
       <c r="B17">
         <v>2004</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>308</v>
       </c>
       <c r="F17" t="s">
@@ -4756,16 +4753,16 @@
       <c r="B18">
         <v>2005</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>60</v>
       </c>
       <c r="N18" t="s">
@@ -4776,16 +4773,16 @@
       <c r="B19">
         <v>2006</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>67</v>
       </c>
       <c r="N19" t="s">
@@ -4796,13 +4793,13 @@
       <c r="B20">
         <v>2007</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F20" t="s">
@@ -4816,10 +4813,10 @@
       <c r="B21">
         <v>2008</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>321</v>
       </c>
       <c r="E21" t="s">
@@ -4836,16 +4833,16 @@
       <c r="B22">
         <v>2009</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="4" t="s">
         <v>294</v>
       </c>
     </row>
@@ -4853,13 +4850,13 @@
       <c r="B23">
         <v>3001</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="4" t="s">
         <v>25</v>
       </c>
       <c r="F23" t="s">
@@ -4870,13 +4867,13 @@
       <c r="B24">
         <v>3002</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="4" t="s">
         <v>25</v>
       </c>
       <c r="F24" t="s">
@@ -4887,13 +4884,13 @@
       <c r="B25">
         <v>3003</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F25" t="s">
@@ -4904,13 +4901,13 @@
       <c r="B26">
         <v>3004</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="4" t="s">
         <v>34</v>
       </c>
       <c r="F26" t="s">
@@ -4921,13 +4918,13 @@
       <c r="B27">
         <v>3005</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F27" t="s">
@@ -4938,13 +4935,13 @@
       <c r="B28">
         <v>3006</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F28" t="s">
@@ -4955,13 +4952,13 @@
       <c r="B29">
         <v>3007</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F29" t="s">
@@ -4978,13 +4975,13 @@
       <c r="B30">
         <v>3008</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F30" t="s">
@@ -4995,13 +4992,13 @@
       <c r="B31">
         <v>3009</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F31" t="s">
@@ -5012,13 +5009,13 @@
       <c r="B32">
         <v>3010</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F32" t="s">

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="5"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -14,6 +14,7 @@
     <sheet name="RarityUI" sheetId="7" r:id="rId5"/>
     <sheet name="DogReaction" sheetId="9" r:id="rId6"/>
     <sheet name="DesktopActivityState" sheetId="11" r:id="rId7"/>
+    <sheet name="BGMList" sheetId="12" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="391">
   <si>
     <t>Dog</t>
   </si>
@@ -1158,6 +1159,54 @@
   </si>
   <si>
     <t>HighEnergy</t>
+  </si>
+  <si>
+    <t>VolumeDb</t>
+  </si>
+  <si>
+    <t>Enabled</t>
+  </si>
+  <si>
+    <t>AudioPath</t>
+  </si>
+  <si>
+    <t>单曲音量补偿，默认 0；过响可填 -3、-6</t>
+  </si>
+  <si>
+    <t>用于新版本预留</t>
+  </si>
+  <si>
+    <t>用于显示的名称</t>
+  </si>
+  <si>
+    <t>音量微调</t>
+  </si>
+  <si>
+    <t>是否可被随机播放到</t>
+  </si>
+  <si>
+    <t>Puppy's Nap Time</t>
+  </si>
+  <si>
+    <t>Audio/BGM/Puppy's Nap Time</t>
+  </si>
+  <si>
+    <t>Sunny Day Adventure</t>
+  </si>
+  <si>
+    <t>Audio/BGM/Sunny Day Adventure</t>
+  </si>
+  <si>
+    <t>The Quiet Path</t>
+  </si>
+  <si>
+    <t>Audio/BGM/The Quiet Path</t>
+  </si>
+  <si>
+    <t>Whimsy in the Woods</t>
+  </si>
+  <si>
+    <t>Audio/BGM/Whimsy in the Woods</t>
   </si>
 </sst>
 </file>
@@ -1778,7 +1827,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1793,6 +1842,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2992,7 +3044,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>149</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -3007,7 +3059,7 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="5"/>
+      <c r="A2" s="6"/>
       <c r="B2" s="4" t="s">
         <v>150</v>
       </c>
@@ -4089,7 +4141,7 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="1"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -4351,13 +4403,13 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="5" t="s">
         <v>279</v>
       </c>
     </row>
@@ -5124,37 +5176,37 @@
       </c>
     </row>
     <row r="3" ht="87" spans="1:11">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="5" t="s">
         <v>289</v>
       </c>
     </row>
@@ -5320,6 +5372,167 @@
       <c r="K8" t="s">
         <v>372</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.25" customWidth="1"/>
+    <col min="3" max="3" width="19.5833333333333" customWidth="1"/>
+    <col min="4" max="4" width="12.75" customWidth="1"/>
+    <col min="5" max="5" width="16.9166666666667" customWidth="1"/>
+    <col min="6" max="6" width="30.8333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1" t="s">
+        <v>376</v>
+      </c>
+      <c r="F1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="52.2" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" t="s">
+        <v>380</v>
+      </c>
+      <c r="D4" t="s">
+        <v>381</v>
+      </c>
+      <c r="E4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>383</v>
+      </c>
+      <c r="D5">
+        <v>-6</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>385</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>389</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -1185,28 +1185,28 @@
     <t>是否可被随机播放到</t>
   </si>
   <si>
-    <t>Puppy's Nap Time</t>
-  </si>
-  <si>
-    <t>Audio/BGM/Puppy's Nap Time</t>
-  </si>
-  <si>
-    <t>Sunny Day Adventure</t>
-  </si>
-  <si>
-    <t>Audio/BGM/Sunny Day Adventure</t>
-  </si>
-  <si>
-    <t>The Quiet Path</t>
-  </si>
-  <si>
-    <t>Audio/BGM/The Quiet Path</t>
-  </si>
-  <si>
-    <t>Whimsy in the Woods</t>
-  </si>
-  <si>
-    <t>Audio/BGM/Whimsy in the Woods</t>
+    <t>Rise and Shine</t>
+  </si>
+  <si>
+    <t>Audio/BGM/01.Rise and Shine.mp3</t>
+  </si>
+  <si>
+    <t>On a Roll</t>
+  </si>
+  <si>
+    <t>Audio/BGM/02.On a Roll.mp3</t>
+  </si>
+  <si>
+    <t>Little Wins</t>
+  </si>
+  <si>
+    <t>Audio/BGM/03.Little Wins.mp3</t>
+  </si>
+  <si>
+    <t>Call It a Day</t>
+  </si>
+  <si>
+    <t>Audio/BGM/04.Call It a Day.mp3</t>
   </si>
 </sst>
 </file>
@@ -1827,7 +1827,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1842,9 +1842,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3044,7 +3041,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>149</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -3059,7 +3056,7 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="6"/>
+      <c r="A2" s="5"/>
       <c r="B2" s="4" t="s">
         <v>150</v>
       </c>
@@ -4141,7 +4138,7 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="5"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -4403,13 +4400,13 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="1" t="s">
         <v>279</v>
       </c>
     </row>
@@ -5176,37 +5173,37 @@
       </c>
     </row>
     <row r="3" ht="87" spans="1:11">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="1" t="s">
         <v>289</v>
       </c>
     </row>
@@ -5471,7 +5468,7 @@
         <v>383</v>
       </c>
       <c r="D5">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="7"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="393">
   <si>
     <t>Dog</t>
   </si>
@@ -342,6 +342,9 @@
     <t>HandRank</t>
   </si>
   <si>
+    <t>LuckyWeight</t>
+  </si>
+  <si>
     <t>OriginalName</t>
   </si>
   <si>
@@ -370,6 +373,9 @@
   </si>
   <si>
     <t>赔率</t>
+  </si>
+  <si>
+    <t>幸运发牌权重</t>
   </si>
   <si>
     <t>原始名称</t>
@@ -2760,17 +2766,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="14.8333333333333" customWidth="1"/>
     <col min="4" max="4" width="12.5833333333333" customWidth="1"/>
-    <col min="5" max="5" width="13.75" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12.9166666666667" customWidth="1"/>
+    <col min="5" max="5" width="15.0833333333333" customWidth="1"/>
+    <col min="6" max="6" width="13.75" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
@@ -2783,67 +2790,76 @@
       <c r="D1" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>102</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>103</v>
       </c>
       <c r="G1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" t="s">
         <v>107</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F2" t="s">
-        <v>108</v>
+      <c r="F2" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="G2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>109</v>
+      </c>
+      <c r="H2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>115</v>
+      </c>
+      <c r="H4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="B5">
         <v>1001</v>
       </c>
@@ -2851,19 +2867,22 @@
         <v>50</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" t="s">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>119</v>
+      </c>
+      <c r="H5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -2871,19 +2890,22 @@
         <v>100</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="E6" s="4">
+        <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>123</v>
+      </c>
+      <c r="H6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -2891,19 +2913,22 @@
         <v>150</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" t="s">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="E7" s="4">
+        <v>65</v>
       </c>
       <c r="F7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>127</v>
+      </c>
+      <c r="H7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -2911,19 +2936,22 @@
         <v>200</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" t="s">
-        <v>127</v>
+        <v>129</v>
+      </c>
+      <c r="E8" s="4">
+        <v>65</v>
       </c>
       <c r="F8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>130</v>
+      </c>
+      <c r="H8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -2931,19 +2959,22 @@
         <v>300</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" t="s">
-        <v>130</v>
+        <v>132</v>
+      </c>
+      <c r="E9" s="4">
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>133</v>
+      </c>
+      <c r="H9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -2951,19 +2982,22 @@
         <v>450</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E10" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="E10" s="4">
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>137</v>
+      </c>
+      <c r="H10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="B11">
         <v>1007</v>
       </c>
@@ -2971,19 +3005,22 @@
         <v>1000</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11" t="s">
-        <v>138</v>
+        <v>139</v>
+      </c>
+      <c r="E11" s="4">
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>141</v>
+      </c>
+      <c r="H11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="B12">
         <v>1008</v>
       </c>
@@ -2991,19 +3028,22 @@
         <v>2500</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E12" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="E12" s="4">
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G12" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>145</v>
+      </c>
+      <c r="H12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="B13">
         <v>1009</v>
       </c>
@@ -3011,16 +3051,19 @@
         <v>12500</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" t="s">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="E13" s="4">
+        <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G13" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="H13" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3042,64 +3085,64 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5"/>
       <c r="B2" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" t="s">
         <v>157</v>
-      </c>
-      <c r="B4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" t="s">
-        <v>155</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3179,129 +3222,129 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="R1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="S1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="T1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" ht="34.8" spans="1:20">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -3309,61 +3352,61 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="N4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="R4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="S4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="T4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -3371,58 +3414,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H5" t="s">
+        <v>201</v>
+      </c>
+      <c r="I5" t="s">
+        <v>202</v>
+      </c>
+      <c r="J5" t="s">
+        <v>203</v>
+      </c>
+      <c r="K5" t="s">
+        <v>204</v>
+      </c>
+      <c r="L5" t="s">
+        <v>205</v>
+      </c>
+      <c r="M5" t="s">
         <v>199</v>
       </c>
-      <c r="I5" t="s">
+      <c r="N5" t="s">
+        <v>206</v>
+      </c>
+      <c r="O5" t="s">
+        <v>207</v>
+      </c>
+      <c r="P5" t="s">
         <v>200</v>
       </c>
-      <c r="J5" t="s">
-        <v>201</v>
-      </c>
-      <c r="K5" t="s">
-        <v>202</v>
-      </c>
-      <c r="L5" t="s">
-        <v>203</v>
-      </c>
-      <c r="M5" t="s">
-        <v>197</v>
-      </c>
-      <c r="N5" t="s">
-        <v>204</v>
-      </c>
-      <c r="O5" t="s">
-        <v>205</v>
-      </c>
-      <c r="P5" t="s">
-        <v>198</v>
-      </c>
       <c r="Q5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="R5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -3430,58 +3473,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" t="s">
+        <v>208</v>
+      </c>
+      <c r="G6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" t="s">
+        <v>214</v>
+      </c>
+      <c r="I6" t="s">
+        <v>202</v>
+      </c>
+      <c r="J6" t="s">
+        <v>203</v>
+      </c>
+      <c r="K6" t="s">
+        <v>204</v>
+      </c>
+      <c r="L6" t="s">
+        <v>205</v>
+      </c>
+      <c r="M6" t="s">
+        <v>199</v>
+      </c>
+      <c r="N6" t="s">
+        <v>206</v>
+      </c>
+      <c r="O6" t="s">
+        <v>207</v>
+      </c>
+      <c r="P6" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>208</v>
+      </c>
+      <c r="R6" t="s">
+        <v>209</v>
+      </c>
+      <c r="S6" t="s">
         <v>210</v>
       </c>
-      <c r="D6" t="s">
+      <c r="T6" t="s">
         <v>211</v>
-      </c>
-      <c r="E6" t="s">
-        <v>197</v>
-      </c>
-      <c r="F6" t="s">
-        <v>206</v>
-      </c>
-      <c r="G6" t="s">
-        <v>168</v>
-      </c>
-      <c r="H6" t="s">
-        <v>212</v>
-      </c>
-      <c r="I6" t="s">
-        <v>200</v>
-      </c>
-      <c r="J6" t="s">
-        <v>201</v>
-      </c>
-      <c r="K6" t="s">
-        <v>202</v>
-      </c>
-      <c r="L6" t="s">
-        <v>203</v>
-      </c>
-      <c r="M6" t="s">
-        <v>197</v>
-      </c>
-      <c r="N6" t="s">
-        <v>204</v>
-      </c>
-      <c r="O6" t="s">
-        <v>205</v>
-      </c>
-      <c r="P6" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>206</v>
-      </c>
-      <c r="R6" t="s">
-        <v>207</v>
-      </c>
-      <c r="S6" t="s">
-        <v>208</v>
-      </c>
-      <c r="T6" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -3489,58 +3532,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F7" t="s">
+        <v>209</v>
+      </c>
+      <c r="G7" t="s">
+        <v>170</v>
+      </c>
+      <c r="H7" t="s">
+        <v>217</v>
+      </c>
+      <c r="I7" t="s">
+        <v>202</v>
+      </c>
+      <c r="J7" t="s">
+        <v>203</v>
+      </c>
+      <c r="K7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L7" t="s">
+        <v>205</v>
+      </c>
+      <c r="M7" t="s">
+        <v>199</v>
+      </c>
+      <c r="N7" t="s">
+        <v>206</v>
+      </c>
+      <c r="O7" t="s">
         <v>207</v>
       </c>
-      <c r="G7" t="s">
-        <v>168</v>
-      </c>
-      <c r="H7" t="s">
-        <v>215</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="P7" t="s">
         <v>200</v>
       </c>
-      <c r="J7" t="s">
-        <v>201</v>
-      </c>
-      <c r="K7" t="s">
-        <v>202</v>
-      </c>
-      <c r="L7" t="s">
-        <v>203</v>
-      </c>
-      <c r="M7" t="s">
-        <v>197</v>
-      </c>
-      <c r="N7" t="s">
-        <v>204</v>
-      </c>
-      <c r="O7" t="s">
-        <v>205</v>
-      </c>
-      <c r="P7" t="s">
-        <v>198</v>
-      </c>
       <c r="Q7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="R7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -3548,58 +3591,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E8" t="s">
+        <v>206</v>
+      </c>
+      <c r="F8" t="s">
+        <v>207</v>
+      </c>
+      <c r="G8" t="s">
+        <v>170</v>
+      </c>
+      <c r="H8" t="s">
+        <v>220</v>
+      </c>
+      <c r="I8" t="s">
+        <v>202</v>
+      </c>
+      <c r="J8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K8" t="s">
         <v>204</v>
       </c>
-      <c r="F8" t="s">
+      <c r="L8" t="s">
         <v>205</v>
       </c>
-      <c r="G8" t="s">
-        <v>168</v>
-      </c>
-      <c r="H8" t="s">
-        <v>218</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="M8" t="s">
+        <v>199</v>
+      </c>
+      <c r="N8" t="s">
+        <v>206</v>
+      </c>
+      <c r="O8" t="s">
+        <v>207</v>
+      </c>
+      <c r="P8" t="s">
         <v>200</v>
       </c>
-      <c r="J8" t="s">
-        <v>201</v>
-      </c>
-      <c r="K8" t="s">
-        <v>202</v>
-      </c>
-      <c r="L8" t="s">
-        <v>203</v>
-      </c>
-      <c r="M8" t="s">
-        <v>197</v>
-      </c>
-      <c r="N8" t="s">
-        <v>204</v>
-      </c>
-      <c r="O8" t="s">
-        <v>205</v>
-      </c>
-      <c r="P8" t="s">
-        <v>198</v>
-      </c>
       <c r="Q8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="R8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -3607,58 +3650,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F9" t="s">
+        <v>209</v>
+      </c>
+      <c r="G9" t="s">
+        <v>170</v>
+      </c>
+      <c r="H9" t="s">
+        <v>201</v>
+      </c>
+      <c r="I9" t="s">
+        <v>223</v>
+      </c>
+      <c r="J9" t="s">
+        <v>203</v>
+      </c>
+      <c r="K9" t="s">
+        <v>204</v>
+      </c>
+      <c r="L9" t="s">
+        <v>205</v>
+      </c>
+      <c r="M9" t="s">
+        <v>199</v>
+      </c>
+      <c r="N9" t="s">
+        <v>206</v>
+      </c>
+      <c r="O9" t="s">
         <v>207</v>
       </c>
-      <c r="G9" t="s">
-        <v>168</v>
-      </c>
-      <c r="H9" t="s">
-        <v>199</v>
-      </c>
-      <c r="I9" t="s">
-        <v>221</v>
-      </c>
-      <c r="J9" t="s">
-        <v>201</v>
-      </c>
-      <c r="K9" t="s">
-        <v>202</v>
-      </c>
-      <c r="L9" t="s">
-        <v>203</v>
-      </c>
-      <c r="M9" t="s">
-        <v>197</v>
-      </c>
-      <c r="N9" t="s">
-        <v>204</v>
-      </c>
-      <c r="O9" t="s">
-        <v>205</v>
-      </c>
       <c r="P9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="R9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -3666,58 +3709,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F10" t="s">
+        <v>200</v>
+      </c>
+      <c r="G10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" t="s">
+        <v>201</v>
+      </c>
+      <c r="I10" t="s">
+        <v>226</v>
+      </c>
+      <c r="J10" t="s">
+        <v>203</v>
+      </c>
+      <c r="K10" t="s">
         <v>204</v>
       </c>
-      <c r="F10" t="s">
-        <v>198</v>
-      </c>
-      <c r="G10" t="s">
-        <v>168</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="L10" t="s">
+        <v>205</v>
+      </c>
+      <c r="M10" t="s">
         <v>199</v>
       </c>
-      <c r="I10" t="s">
-        <v>224</v>
-      </c>
-      <c r="J10" t="s">
-        <v>201</v>
-      </c>
-      <c r="K10" t="s">
-        <v>202</v>
-      </c>
-      <c r="L10" t="s">
-        <v>203</v>
-      </c>
-      <c r="M10" t="s">
-        <v>197</v>
-      </c>
       <c r="N10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="R10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -3725,58 +3768,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F11" t="s">
+        <v>211</v>
+      </c>
+      <c r="G11" t="s">
+        <v>170</v>
+      </c>
+      <c r="H11" t="s">
+        <v>214</v>
+      </c>
+      <c r="I11" t="s">
+        <v>223</v>
+      </c>
+      <c r="J11" t="s">
+        <v>203</v>
+      </c>
+      <c r="K11" t="s">
+        <v>204</v>
+      </c>
+      <c r="L11" t="s">
+        <v>205</v>
+      </c>
+      <c r="M11" t="s">
+        <v>199</v>
+      </c>
+      <c r="N11" t="s">
+        <v>206</v>
+      </c>
+      <c r="O11" t="s">
+        <v>207</v>
+      </c>
+      <c r="P11" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>208</v>
+      </c>
+      <c r="R11" t="s">
         <v>209</v>
       </c>
-      <c r="G11" t="s">
-        <v>168</v>
-      </c>
-      <c r="H11" t="s">
-        <v>212</v>
-      </c>
-      <c r="I11" t="s">
-        <v>221</v>
-      </c>
-      <c r="J11" t="s">
-        <v>201</v>
-      </c>
-      <c r="K11" t="s">
-        <v>202</v>
-      </c>
-      <c r="L11" t="s">
-        <v>203</v>
-      </c>
-      <c r="M11" t="s">
-        <v>197</v>
-      </c>
-      <c r="N11" t="s">
-        <v>204</v>
-      </c>
-      <c r="O11" t="s">
-        <v>205</v>
-      </c>
-      <c r="P11" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>206</v>
-      </c>
-      <c r="R11" t="s">
-        <v>207</v>
-      </c>
       <c r="S11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -3784,58 +3827,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="R12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -3843,58 +3886,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D13" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F13" t="s">
+        <v>211</v>
+      </c>
+      <c r="G13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I13" t="s">
+        <v>223</v>
+      </c>
+      <c r="J13" t="s">
+        <v>203</v>
+      </c>
+      <c r="K13" t="s">
+        <v>204</v>
+      </c>
+      <c r="L13" t="s">
+        <v>205</v>
+      </c>
+      <c r="M13" t="s">
+        <v>199</v>
+      </c>
+      <c r="N13" t="s">
+        <v>206</v>
+      </c>
+      <c r="O13" t="s">
+        <v>207</v>
+      </c>
+      <c r="P13" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>208</v>
+      </c>
+      <c r="R13" t="s">
         <v>209</v>
       </c>
-      <c r="G13" t="s">
-        <v>168</v>
-      </c>
-      <c r="H13" t="s">
-        <v>215</v>
-      </c>
-      <c r="I13" t="s">
-        <v>221</v>
-      </c>
-      <c r="J13" t="s">
-        <v>201</v>
-      </c>
-      <c r="K13" t="s">
-        <v>202</v>
-      </c>
-      <c r="L13" t="s">
-        <v>203</v>
-      </c>
-      <c r="M13" t="s">
-        <v>197</v>
-      </c>
-      <c r="N13" t="s">
-        <v>204</v>
-      </c>
-      <c r="O13" t="s">
-        <v>205</v>
-      </c>
-      <c r="P13" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>206</v>
-      </c>
-      <c r="R13" t="s">
-        <v>207</v>
-      </c>
       <c r="S13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T13" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -3902,58 +3945,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J14" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L14" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O14" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="R14" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -3961,58 +4004,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E15" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H15" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I15" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J15" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M15" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O15" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="R15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S15" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T15" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -4020,58 +4063,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D16" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E16" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F16" t="s">
+        <v>210</v>
+      </c>
+      <c r="G16" t="s">
+        <v>170</v>
+      </c>
+      <c r="H16" t="s">
+        <v>220</v>
+      </c>
+      <c r="I16" t="s">
+        <v>226</v>
+      </c>
+      <c r="J16" t="s">
+        <v>203</v>
+      </c>
+      <c r="K16" t="s">
+        <v>204</v>
+      </c>
+      <c r="L16" t="s">
+        <v>205</v>
+      </c>
+      <c r="M16" t="s">
+        <v>199</v>
+      </c>
+      <c r="N16" t="s">
+        <v>206</v>
+      </c>
+      <c r="O16" t="s">
+        <v>207</v>
+      </c>
+      <c r="P16" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q16" t="s">
         <v>208</v>
       </c>
-      <c r="G16" t="s">
-        <v>168</v>
-      </c>
-      <c r="H16" t="s">
-        <v>218</v>
-      </c>
-      <c r="I16" t="s">
-        <v>224</v>
-      </c>
-      <c r="J16" t="s">
-        <v>201</v>
-      </c>
-      <c r="K16" t="s">
-        <v>202</v>
-      </c>
-      <c r="L16" t="s">
-        <v>203</v>
-      </c>
-      <c r="M16" t="s">
-        <v>197</v>
-      </c>
-      <c r="N16" t="s">
-        <v>204</v>
-      </c>
-      <c r="O16" t="s">
-        <v>205</v>
-      </c>
-      <c r="P16" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>206</v>
-      </c>
       <c r="R16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="T16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -4100,41 +4143,41 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4142,22 +4185,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4171,10 +4214,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4182,16 +4225,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4205,10 +4248,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4222,10 +4265,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4239,10 +4282,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4250,16 +4293,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4273,10 +4316,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4290,10 +4333,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4326,132 +4369,132 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" ht="104.4" spans="1:14">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -4474,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -4494,22 +4537,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4523,22 +4566,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4552,22 +4595,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4581,22 +4624,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4610,22 +4653,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4639,22 +4682,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4668,22 +4711,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4691,31 +4734,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L13" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -4723,10 +4766,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -4735,7 +4778,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4743,10 +4786,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>7</v>
@@ -4755,7 +4798,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4763,10 +4806,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>16</v>
@@ -4775,7 +4818,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -4783,19 +4826,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F17" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N17" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -4803,10 +4846,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>59</v>
@@ -4815,7 +4858,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -4823,10 +4866,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>66</v>
@@ -4835,7 +4878,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -4843,10 +4886,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>16</v>
@@ -4855,7 +4898,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -4863,19 +4906,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E21" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F21" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N21" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -4883,16 +4926,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -4900,10 +4943,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>25</v>
@@ -4917,10 +4960,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>25</v>
@@ -4934,10 +4977,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>34</v>
@@ -4951,10 +4994,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>34</v>
@@ -4968,10 +5011,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>43</v>
@@ -4985,10 +5028,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>43</v>
@@ -5002,10 +5045,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>43</v>
@@ -5014,10 +5057,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N29" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -5025,10 +5068,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>52</v>
@@ -5042,10 +5085,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>52</v>
@@ -5059,10 +5102,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>52</v>
@@ -5071,10 +5114,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N32" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -5110,136 +5153,136 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" ht="87" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -5247,7 +5290,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5271,7 +5314,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -5279,7 +5322,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -5303,7 +5346,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -5311,7 +5354,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -5335,7 +5378,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -5343,7 +5386,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -5367,7 +5410,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -5398,66 +5441,66 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="52.2" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5465,7 +5508,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5474,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5482,7 +5525,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -5491,7 +5534,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -5499,7 +5542,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -5508,7 +5551,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -5516,7 +5559,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -5525,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:6">

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="394">
   <si>
     <t>Dog</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>##</t>
+  </si>
+  <si>
+    <t>奖励筹码具体数值</t>
   </si>
   <si>
     <t>id</t>
@@ -2766,18 +2769,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
-    <col min="3" max="3" width="14.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="12.5833333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="13.75" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="12.9166666666667" customWidth="1"/>
+    <col min="3" max="4" width="14.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="12.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="15.0833333333333" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
@@ -2787,23 +2790,23 @@
       <c r="C1" t="s">
         <v>100</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>101</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>102</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>104</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
@@ -2813,40 +2816,41 @@
       <c r="C2" t="s">
         <v>107</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>108</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>107</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="C3"/>
+      <c r="D3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" t="s">
         <v>113</v>
       </c>
       <c r="F4" t="s">
@@ -2858,22 +2862,25 @@
       <c r="H4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
         <v>50</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="E5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="4">
         <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>118</v>
       </c>
       <c r="G5" t="s">
         <v>119</v>
@@ -2881,22 +2888,25 @@
       <c r="H5" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
         <v>100</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="E6" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" s="4">
         <v>80</v>
-      </c>
-      <c r="F6" t="s">
-        <v>122</v>
       </c>
       <c r="G6" t="s">
         <v>123</v>
@@ -2904,22 +2914,25 @@
       <c r="H6" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
         <v>150</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="E7" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="4">
         <v>65</v>
-      </c>
-      <c r="F7" t="s">
-        <v>126</v>
       </c>
       <c r="G7" t="s">
         <v>127</v>
@@ -2927,22 +2940,25 @@
       <c r="H7" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
         <v>200</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="E8" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="4">
         <v>65</v>
-      </c>
-      <c r="F8" t="s">
-        <v>129</v>
       </c>
       <c r="G8" t="s">
         <v>130</v>
@@ -2950,22 +2966,25 @@
       <c r="H8" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
         <v>300</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="E9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="4">
         <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>132</v>
       </c>
       <c r="G9" t="s">
         <v>133</v>
@@ -2973,22 +2992,25 @@
       <c r="H9" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10">
         <v>450</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="E10" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="4">
         <v>28</v>
-      </c>
-      <c r="F10" t="s">
-        <v>136</v>
       </c>
       <c r="G10" t="s">
         <v>137</v>
@@ -2996,22 +3018,25 @@
       <c r="H10" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
         <v>1000</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="E11" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="4">
         <v>14</v>
-      </c>
-      <c r="F11" t="s">
-        <v>140</v>
       </c>
       <c r="G11" t="s">
         <v>141</v>
@@ -3019,22 +3044,25 @@
       <c r="H11" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12">
+        <v>50</v>
+      </c>
+      <c r="D12">
         <v>2500</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="E12" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="4">
         <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>144</v>
       </c>
       <c r="G12" t="s">
         <v>145</v>
@@ -3042,28 +3070,34 @@
       <c r="H12" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13">
+        <v>250</v>
+      </c>
+      <c r="D13">
         <v>12500</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="E13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="4">
         <v>3</v>
-      </c>
-      <c r="F13" t="s">
-        <v>148</v>
       </c>
       <c r="G13" t="s">
         <v>149</v>
       </c>
       <c r="H13" t="s">
         <v>150</v>
+      </c>
+      <c r="I13" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3085,7 +3119,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>110</v>
@@ -3101,48 +3135,48 @@
     <row r="2" spans="1:5">
       <c r="A2" s="5"/>
       <c r="B2" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3222,55 +3256,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="R1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="T1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -3341,10 +3375,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -3358,55 +3392,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="S4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="T4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -3414,58 +3448,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F5" t="s">
+        <v>201</v>
+      </c>
+      <c r="G5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H5" t="s">
+        <v>202</v>
+      </c>
+      <c r="I5" t="s">
+        <v>203</v>
+      </c>
+      <c r="J5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K5" t="s">
+        <v>205</v>
+      </c>
+      <c r="L5" t="s">
+        <v>206</v>
+      </c>
+      <c r="M5" t="s">
         <v>200</v>
       </c>
-      <c r="G5" t="s">
-        <v>170</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="N5" t="s">
+        <v>207</v>
+      </c>
+      <c r="O5" t="s">
+        <v>208</v>
+      </c>
+      <c r="P5" t="s">
         <v>201</v>
       </c>
-      <c r="I5" t="s">
-        <v>202</v>
-      </c>
-      <c r="J5" t="s">
-        <v>203</v>
-      </c>
-      <c r="K5" t="s">
-        <v>204</v>
-      </c>
-      <c r="L5" t="s">
-        <v>205</v>
-      </c>
-      <c r="M5" t="s">
-        <v>199</v>
-      </c>
-      <c r="N5" t="s">
-        <v>206</v>
-      </c>
-      <c r="O5" t="s">
-        <v>207</v>
-      </c>
-      <c r="P5" t="s">
-        <v>200</v>
-      </c>
       <c r="Q5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="R5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="T5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -3473,58 +3507,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I6" t="s">
+        <v>203</v>
+      </c>
+      <c r="J6" t="s">
+        <v>204</v>
+      </c>
+      <c r="K6" t="s">
+        <v>205</v>
+      </c>
+      <c r="L6" t="s">
+        <v>206</v>
+      </c>
+      <c r="M6" t="s">
+        <v>200</v>
+      </c>
+      <c r="N6" t="s">
+        <v>207</v>
+      </c>
+      <c r="O6" t="s">
+        <v>208</v>
+      </c>
+      <c r="P6" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>209</v>
+      </c>
+      <c r="R6" t="s">
+        <v>210</v>
+      </c>
+      <c r="S6" t="s">
+        <v>211</v>
+      </c>
+      <c r="T6" t="s">
         <v>212</v>
-      </c>
-      <c r="D6" t="s">
-        <v>213</v>
-      </c>
-      <c r="E6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G6" t="s">
-        <v>170</v>
-      </c>
-      <c r="H6" t="s">
-        <v>214</v>
-      </c>
-      <c r="I6" t="s">
-        <v>202</v>
-      </c>
-      <c r="J6" t="s">
-        <v>203</v>
-      </c>
-      <c r="K6" t="s">
-        <v>204</v>
-      </c>
-      <c r="L6" t="s">
-        <v>205</v>
-      </c>
-      <c r="M6" t="s">
-        <v>199</v>
-      </c>
-      <c r="N6" t="s">
-        <v>206</v>
-      </c>
-      <c r="O6" t="s">
-        <v>207</v>
-      </c>
-      <c r="P6" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>208</v>
-      </c>
-      <c r="R6" t="s">
-        <v>209</v>
-      </c>
-      <c r="S6" t="s">
-        <v>210</v>
-      </c>
-      <c r="T6" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -3532,58 +3566,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F7" t="s">
+        <v>210</v>
+      </c>
+      <c r="G7" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" t="s">
+        <v>218</v>
+      </c>
+      <c r="I7" t="s">
+        <v>203</v>
+      </c>
+      <c r="J7" t="s">
+        <v>204</v>
+      </c>
+      <c r="K7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L7" t="s">
+        <v>206</v>
+      </c>
+      <c r="M7" t="s">
+        <v>200</v>
+      </c>
+      <c r="N7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O7" t="s">
+        <v>208</v>
+      </c>
+      <c r="P7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q7" t="s">
         <v>209</v>
       </c>
-      <c r="G7" t="s">
-        <v>170</v>
-      </c>
-      <c r="H7" t="s">
-        <v>217</v>
-      </c>
-      <c r="I7" t="s">
-        <v>202</v>
-      </c>
-      <c r="J7" t="s">
-        <v>203</v>
-      </c>
-      <c r="K7" t="s">
-        <v>204</v>
-      </c>
-      <c r="L7" t="s">
-        <v>205</v>
-      </c>
-      <c r="M7" t="s">
-        <v>199</v>
-      </c>
-      <c r="N7" t="s">
-        <v>206</v>
-      </c>
-      <c r="O7" t="s">
-        <v>207</v>
-      </c>
-      <c r="P7" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>208</v>
-      </c>
       <c r="R7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="T7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -3591,58 +3625,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G8" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" t="s">
+        <v>221</v>
+      </c>
+      <c r="I8" t="s">
+        <v>203</v>
+      </c>
+      <c r="J8" t="s">
+        <v>204</v>
+      </c>
+      <c r="K8" t="s">
+        <v>205</v>
+      </c>
+      <c r="L8" t="s">
         <v>206</v>
       </c>
-      <c r="F8" t="s">
+      <c r="M8" t="s">
+        <v>200</v>
+      </c>
+      <c r="N8" t="s">
         <v>207</v>
       </c>
-      <c r="G8" t="s">
-        <v>170</v>
-      </c>
-      <c r="H8" t="s">
-        <v>220</v>
-      </c>
-      <c r="I8" t="s">
-        <v>202</v>
-      </c>
-      <c r="J8" t="s">
-        <v>203</v>
-      </c>
-      <c r="K8" t="s">
-        <v>204</v>
-      </c>
-      <c r="L8" t="s">
-        <v>205</v>
-      </c>
-      <c r="M8" t="s">
-        <v>199</v>
-      </c>
-      <c r="N8" t="s">
-        <v>206</v>
-      </c>
       <c r="O8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="R8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="T8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -3650,58 +3684,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F9" t="s">
+        <v>210</v>
+      </c>
+      <c r="G9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H9" t="s">
+        <v>202</v>
+      </c>
+      <c r="I9" t="s">
+        <v>224</v>
+      </c>
+      <c r="J9" t="s">
+        <v>204</v>
+      </c>
+      <c r="K9" t="s">
+        <v>205</v>
+      </c>
+      <c r="L9" t="s">
+        <v>206</v>
+      </c>
+      <c r="M9" t="s">
+        <v>200</v>
+      </c>
+      <c r="N9" t="s">
+        <v>207</v>
+      </c>
+      <c r="O9" t="s">
+        <v>208</v>
+      </c>
+      <c r="P9" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q9" t="s">
         <v>209</v>
       </c>
-      <c r="G9" t="s">
-        <v>170</v>
-      </c>
-      <c r="H9" t="s">
-        <v>201</v>
-      </c>
-      <c r="I9" t="s">
-        <v>223</v>
-      </c>
-      <c r="J9" t="s">
-        <v>203</v>
-      </c>
-      <c r="K9" t="s">
-        <v>204</v>
-      </c>
-      <c r="L9" t="s">
-        <v>205</v>
-      </c>
-      <c r="M9" t="s">
-        <v>199</v>
-      </c>
-      <c r="N9" t="s">
-        <v>206</v>
-      </c>
-      <c r="O9" t="s">
-        <v>207</v>
-      </c>
-      <c r="P9" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>208</v>
-      </c>
       <c r="R9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="T9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -3709,58 +3743,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F10" t="s">
+        <v>201</v>
+      </c>
+      <c r="G10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10" t="s">
+        <v>202</v>
+      </c>
+      <c r="I10" t="s">
+        <v>227</v>
+      </c>
+      <c r="J10" t="s">
+        <v>204</v>
+      </c>
+      <c r="K10" t="s">
+        <v>205</v>
+      </c>
+      <c r="L10" t="s">
         <v>206</v>
       </c>
-      <c r="F10" t="s">
+      <c r="M10" t="s">
         <v>200</v>
       </c>
-      <c r="G10" t="s">
-        <v>170</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="N10" t="s">
+        <v>207</v>
+      </c>
+      <c r="O10" t="s">
+        <v>208</v>
+      </c>
+      <c r="P10" t="s">
         <v>201</v>
       </c>
-      <c r="I10" t="s">
-        <v>226</v>
-      </c>
-      <c r="J10" t="s">
-        <v>203</v>
-      </c>
-      <c r="K10" t="s">
-        <v>204</v>
-      </c>
-      <c r="L10" t="s">
-        <v>205</v>
-      </c>
-      <c r="M10" t="s">
-        <v>199</v>
-      </c>
-      <c r="N10" t="s">
-        <v>206</v>
-      </c>
-      <c r="O10" t="s">
-        <v>207</v>
-      </c>
-      <c r="P10" t="s">
-        <v>200</v>
-      </c>
       <c r="Q10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="R10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="T10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -3768,58 +3802,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F11" t="s">
+        <v>212</v>
+      </c>
+      <c r="G11" t="s">
+        <v>171</v>
+      </c>
+      <c r="H11" t="s">
+        <v>215</v>
+      </c>
+      <c r="I11" t="s">
+        <v>224</v>
+      </c>
+      <c r="J11" t="s">
+        <v>204</v>
+      </c>
+      <c r="K11" t="s">
+        <v>205</v>
+      </c>
+      <c r="L11" t="s">
+        <v>206</v>
+      </c>
+      <c r="M11" t="s">
+        <v>200</v>
+      </c>
+      <c r="N11" t="s">
+        <v>207</v>
+      </c>
+      <c r="O11" t="s">
+        <v>208</v>
+      </c>
+      <c r="P11" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>209</v>
+      </c>
+      <c r="R11" t="s">
+        <v>210</v>
+      </c>
+      <c r="S11" t="s">
         <v>211</v>
       </c>
-      <c r="G11" t="s">
-        <v>170</v>
-      </c>
-      <c r="H11" t="s">
-        <v>214</v>
-      </c>
-      <c r="I11" t="s">
-        <v>223</v>
-      </c>
-      <c r="J11" t="s">
-        <v>203</v>
-      </c>
-      <c r="K11" t="s">
-        <v>204</v>
-      </c>
-      <c r="L11" t="s">
-        <v>205</v>
-      </c>
-      <c r="M11" t="s">
-        <v>199</v>
-      </c>
-      <c r="N11" t="s">
-        <v>206</v>
-      </c>
-      <c r="O11" t="s">
-        <v>207</v>
-      </c>
-      <c r="P11" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>208</v>
-      </c>
-      <c r="R11" t="s">
-        <v>209</v>
-      </c>
-      <c r="S11" t="s">
-        <v>210</v>
-      </c>
       <c r="T11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -3827,58 +3861,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F12" t="s">
+        <v>201</v>
+      </c>
+      <c r="G12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12" t="s">
+        <v>215</v>
+      </c>
+      <c r="I12" t="s">
+        <v>227</v>
+      </c>
+      <c r="J12" t="s">
+        <v>204</v>
+      </c>
+      <c r="K12" t="s">
+        <v>205</v>
+      </c>
+      <c r="L12" t="s">
+        <v>206</v>
+      </c>
+      <c r="M12" t="s">
         <v>200</v>
       </c>
-      <c r="G12" t="s">
-        <v>170</v>
-      </c>
-      <c r="H12" t="s">
-        <v>214</v>
-      </c>
-      <c r="I12" t="s">
-        <v>226</v>
-      </c>
-      <c r="J12" t="s">
-        <v>203</v>
-      </c>
-      <c r="K12" t="s">
-        <v>204</v>
-      </c>
-      <c r="L12" t="s">
-        <v>205</v>
-      </c>
-      <c r="M12" t="s">
-        <v>199</v>
-      </c>
       <c r="N12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="R12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="T12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -3886,58 +3920,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F13" t="s">
+        <v>212</v>
+      </c>
+      <c r="G13" t="s">
+        <v>171</v>
+      </c>
+      <c r="H13" t="s">
+        <v>218</v>
+      </c>
+      <c r="I13" t="s">
+        <v>224</v>
+      </c>
+      <c r="J13" t="s">
+        <v>204</v>
+      </c>
+      <c r="K13" t="s">
+        <v>205</v>
+      </c>
+      <c r="L13" t="s">
+        <v>206</v>
+      </c>
+      <c r="M13" t="s">
+        <v>200</v>
+      </c>
+      <c r="N13" t="s">
+        <v>207</v>
+      </c>
+      <c r="O13" t="s">
+        <v>208</v>
+      </c>
+      <c r="P13" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>209</v>
+      </c>
+      <c r="R13" t="s">
+        <v>210</v>
+      </c>
+      <c r="S13" t="s">
         <v>211</v>
       </c>
-      <c r="G13" t="s">
-        <v>170</v>
-      </c>
-      <c r="H13" t="s">
-        <v>217</v>
-      </c>
-      <c r="I13" t="s">
-        <v>223</v>
-      </c>
-      <c r="J13" t="s">
-        <v>203</v>
-      </c>
-      <c r="K13" t="s">
-        <v>204</v>
-      </c>
-      <c r="L13" t="s">
-        <v>205</v>
-      </c>
-      <c r="M13" t="s">
-        <v>199</v>
-      </c>
-      <c r="N13" t="s">
-        <v>206</v>
-      </c>
-      <c r="O13" t="s">
-        <v>207</v>
-      </c>
-      <c r="P13" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>208</v>
-      </c>
-      <c r="R13" t="s">
-        <v>209</v>
-      </c>
-      <c r="S13" t="s">
-        <v>210</v>
-      </c>
       <c r="T13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -3945,58 +3979,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F14" t="s">
+        <v>201</v>
+      </c>
+      <c r="G14" t="s">
+        <v>171</v>
+      </c>
+      <c r="H14" t="s">
+        <v>218</v>
+      </c>
+      <c r="I14" t="s">
+        <v>227</v>
+      </c>
+      <c r="J14" t="s">
+        <v>204</v>
+      </c>
+      <c r="K14" t="s">
+        <v>205</v>
+      </c>
+      <c r="L14" t="s">
+        <v>206</v>
+      </c>
+      <c r="M14" t="s">
         <v>200</v>
       </c>
-      <c r="G14" t="s">
-        <v>170</v>
-      </c>
-      <c r="H14" t="s">
-        <v>217</v>
-      </c>
-      <c r="I14" t="s">
-        <v>226</v>
-      </c>
-      <c r="J14" t="s">
-        <v>203</v>
-      </c>
-      <c r="K14" t="s">
-        <v>204</v>
-      </c>
-      <c r="L14" t="s">
-        <v>205</v>
-      </c>
-      <c r="M14" t="s">
-        <v>199</v>
-      </c>
       <c r="N14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="R14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="T14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -4004,58 +4038,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F15" t="s">
+        <v>201</v>
+      </c>
+      <c r="G15" t="s">
+        <v>171</v>
+      </c>
+      <c r="H15" t="s">
+        <v>221</v>
+      </c>
+      <c r="I15" t="s">
+        <v>224</v>
+      </c>
+      <c r="J15" t="s">
+        <v>204</v>
+      </c>
+      <c r="K15" t="s">
+        <v>205</v>
+      </c>
+      <c r="L15" t="s">
+        <v>206</v>
+      </c>
+      <c r="M15" t="s">
         <v>200</v>
       </c>
-      <c r="G15" t="s">
-        <v>170</v>
-      </c>
-      <c r="H15" t="s">
-        <v>220</v>
-      </c>
-      <c r="I15" t="s">
-        <v>223</v>
-      </c>
-      <c r="J15" t="s">
-        <v>203</v>
-      </c>
-      <c r="K15" t="s">
-        <v>204</v>
-      </c>
-      <c r="L15" t="s">
-        <v>205</v>
-      </c>
-      <c r="M15" t="s">
-        <v>199</v>
-      </c>
       <c r="N15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="R15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="T15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -4063,58 +4097,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F16" t="s">
+        <v>211</v>
+      </c>
+      <c r="G16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" t="s">
+        <v>221</v>
+      </c>
+      <c r="I16" t="s">
+        <v>227</v>
+      </c>
+      <c r="J16" t="s">
+        <v>204</v>
+      </c>
+      <c r="K16" t="s">
+        <v>205</v>
+      </c>
+      <c r="L16" t="s">
+        <v>206</v>
+      </c>
+      <c r="M16" t="s">
+        <v>200</v>
+      </c>
+      <c r="N16" t="s">
+        <v>207</v>
+      </c>
+      <c r="O16" t="s">
+        <v>208</v>
+      </c>
+      <c r="P16" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>209</v>
+      </c>
+      <c r="R16" t="s">
         <v>210</v>
       </c>
-      <c r="G16" t="s">
-        <v>170</v>
-      </c>
-      <c r="H16" t="s">
-        <v>220</v>
-      </c>
-      <c r="I16" t="s">
-        <v>226</v>
-      </c>
-      <c r="J16" t="s">
-        <v>203</v>
-      </c>
-      <c r="K16" t="s">
-        <v>204</v>
-      </c>
-      <c r="L16" t="s">
-        <v>205</v>
-      </c>
-      <c r="M16" t="s">
-        <v>199</v>
-      </c>
-      <c r="N16" t="s">
-        <v>206</v>
-      </c>
-      <c r="O16" t="s">
-        <v>207</v>
-      </c>
-      <c r="P16" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>208</v>
-      </c>
-      <c r="R16" t="s">
-        <v>209</v>
-      </c>
       <c r="S16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="T16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -4143,16 +4177,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4166,7 +4200,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -4188,19 +4222,19 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4214,10 +4248,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4225,16 +4259,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4248,10 +4282,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4265,10 +4299,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4282,10 +4316,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4293,16 +4327,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4316,10 +4350,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4333,10 +4367,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -4369,34 +4403,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -4407,10 +4441,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -4422,7 +4456,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -4444,13 +4478,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -4458,43 +4492,43 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E4" t="s">
+        <v>285</v>
+      </c>
+      <c r="F4" t="s">
         <v>284</v>
       </c>
-      <c r="F4" t="s">
-        <v>283</v>
-      </c>
       <c r="G4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -4517,13 +4551,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -4537,22 +4571,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4566,22 +4600,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4595,22 +4629,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4624,22 +4658,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4653,22 +4687,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4682,22 +4716,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4711,22 +4745,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
+        <v>295</v>
+      </c>
+      <c r="L12" t="s">
+        <v>295</v>
+      </c>
+      <c r="M12" t="s">
         <v>294</v>
-      </c>
-      <c r="L12" t="s">
-        <v>294</v>
-      </c>
-      <c r="M12" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4734,31 +4768,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -4766,10 +4800,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -4778,7 +4812,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4786,10 +4820,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>7</v>
@@ -4798,7 +4832,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4806,10 +4840,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>16</v>
@@ -4818,7 +4852,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -4826,19 +4860,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -4846,10 +4880,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>59</v>
@@ -4858,7 +4892,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -4866,10 +4900,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>66</v>
@@ -4878,7 +4912,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -4886,10 +4920,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>16</v>
@@ -4898,7 +4932,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -4906,19 +4940,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E21" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F21" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N21" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -4926,16 +4960,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -4943,10 +4977,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>25</v>
@@ -4960,10 +4994,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>25</v>
@@ -4977,10 +5011,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>34</v>
@@ -4994,10 +5028,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>34</v>
@@ -5011,10 +5045,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>43</v>
@@ -5028,10 +5062,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>43</v>
@@ -5045,10 +5079,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>43</v>
@@ -5057,10 +5091,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N29" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -5068,10 +5102,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>52</v>
@@ -5085,10 +5119,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>52</v>
@@ -5102,10 +5136,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>52</v>
@@ -5114,10 +5148,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N32" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -5153,31 +5187,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -5197,16 +5231,16 @@
         <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -5220,34 +5254,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -5255,34 +5289,34 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -5290,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5314,7 +5348,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -5322,7 +5356,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -5346,7 +5380,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -5354,7 +5388,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -5378,7 +5412,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -5386,7 +5420,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -5410,7 +5444,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -5441,16 +5475,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5464,10 +5498,10 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -5480,10 +5514,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5491,16 +5525,16 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5508,7 +5542,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5517,7 +5551,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5525,7 +5559,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -5534,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -5542,7 +5576,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -5551,7 +5585,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -5559,7 +5593,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -5568,7 +5602,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:6">

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="7"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -15,6 +15,7 @@
     <sheet name="DogReaction" sheetId="9" r:id="rId6"/>
     <sheet name="DesktopActivityState" sheetId="11" r:id="rId7"/>
     <sheet name="BGMList" sheetId="12" r:id="rId8"/>
+    <sheet name="Achievement" sheetId="13" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="398">
   <si>
     <t>Dog</t>
   </si>
@@ -1216,6 +1217,18 @@
   </si>
   <si>
     <t>Audio/BGM/04.Call It a Day.mp3</t>
+  </si>
+  <si>
+    <t>AchievementId</t>
+  </si>
+  <si>
+    <t>ApiName</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_HEADWEAR</t>
   </si>
 </sst>
 </file>
@@ -1840,13 +1853,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2781,10 +2794,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C1" t="s">
@@ -2796,7 +2809,7 @@
       <c r="F1" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H1" t="s">
@@ -2807,10 +2820,10 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C2" t="s">
@@ -2822,7 +2835,7 @@
       <c r="F2" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
@@ -2833,15 +2846,14 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3"/>
+      <c r="B3" s="2"/>
       <c r="D3" t="s">
         <v>111</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
@@ -3146,7 +3158,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>156</v>
       </c>
       <c r="B3" t="s">
@@ -3155,7 +3167,7 @@
       <c r="C3" t="s">
         <v>158</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
@@ -3163,7 +3175,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>160</v>
       </c>
       <c r="B4" t="s">
@@ -3172,7 +3184,7 @@
       <c r="C4" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>1</v>
       </c>
       <c r="E4" t="s">
@@ -3180,42 +3192,42 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="2"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3248,29 +3260,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>168</v>
       </c>
       <c r="J1" t="s">
@@ -3308,84 +3320,84 @@
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="3" ht="34.8" spans="1:20">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:20">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B4" t="s">
@@ -4170,13 +4182,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D1" t="s">
@@ -4190,13 +4202,13 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>109</v>
       </c>
       <c r="D2" t="s">
@@ -4210,12 +4222,12 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -4396,13 +4408,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>268</v>
       </c>
       <c r="E1" t="s">
@@ -4434,13 +4446,13 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>278</v>
       </c>
       <c r="E2" t="s">
@@ -4472,18 +4484,18 @@
       </c>
     </row>
     <row r="3" ht="104.4" spans="1:14">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="E3" s="1" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="E3" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>282</v>
       </c>
     </row>
@@ -5250,37 +5262,37 @@
       </c>
     </row>
     <row r="3" ht="87" spans="1:11">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>292</v>
       </c>
     </row>
@@ -5468,13 +5480,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D1" t="s">
@@ -5488,13 +5500,13 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>109</v>
       </c>
       <c r="D2" t="s">
@@ -5507,16 +5519,16 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="52.2" spans="1:6">
-      <c r="A3" s="3" t="s">
+    <row r="3" s="3" customFormat="1" ht="52.2" spans="1:6">
+      <c r="A3" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="1" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>382</v>
       </c>
     </row>
@@ -5607,6 +5619,69 @@
     </row>
     <row r="9" spans="1:6">
       <c r="F9" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelRow="4" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="13.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="21.0833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>397</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -16,6 +16,7 @@
     <sheet name="DesktopActivityState" sheetId="11" r:id="rId7"/>
     <sheet name="BGMList" sheetId="12" r:id="rId8"/>
     <sheet name="Achievement" sheetId="13" r:id="rId9"/>
+    <sheet name="PlayerStatistic" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="685">
   <si>
     <t>Dog</t>
   </si>
@@ -1225,10 +1226,871 @@
     <t>ApiName</t>
   </si>
   <si>
-    <t>名字</t>
+    <t>RuleType</t>
+  </si>
+  <si>
+    <t>TargetKey</t>
+  </si>
+  <si>
+    <t>TargetValue</t>
+  </si>
+  <si>
+    <t>IsHidden</t>
+  </si>
+  <si>
+    <t>EAchievementRuleType</t>
+  </si>
+  <si>
+    <t>成就唯一 ID；发布后不可复用</t>
+  </si>
+  <si>
+    <t>平台和存档使用的稳定机器名；发布后不要改名</t>
+  </si>
+  <si>
+    <t>FirstExternalItemType=首次非初始获得部位；FirstExternalItemRarity=首次非初始获得指定品质；FirstEvent=首次发生事件；StatisticAtLeast=统计达到数值</t>
+  </si>
+  <si>
+    <t>由 RuleType 决定含义：部位/品质/事件/PlayerStatistic 的 StatisticKey</t>
+  </si>
+  <si>
+    <t>StatisticAtLeast 的数值门槛；首次类规则填 1</t>
+  </si>
+  <si>
+    <t>是否在平台/游戏内解锁前隐藏</t>
+  </si>
+  <si>
+    <t>填写策划说明或设计约束</t>
+  </si>
+  <si>
+    <t>成就 id</t>
+  </si>
+  <si>
+    <t>API 名</t>
+  </si>
+  <si>
+    <t>解锁规则</t>
+  </si>
+  <si>
+    <t>目标</t>
+  </si>
+  <si>
+    <t>目标数值</t>
+  </si>
+  <si>
+    <t>隐藏成就</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_DOG</t>
+  </si>
+  <si>
+    <t>FirstExternalItemType</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得一只狗；默认红柴不计入</t>
   </si>
   <si>
     <t>ACH_FIRST_HEADWEAR</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得头部装饰</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_EYEWEAR</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得眼部装饰</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_ARM</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得玩家手臂</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_CLOTHES</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得衣服</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_TABLE</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得桌布</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_BACKGROUND</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得背景</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_ACCESSORY</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得手部装饰</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_REFRESHMENT</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得饮品/消耗品</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_CARD_BACK</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得卡背</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_CARD_FACE</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得卡面</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_THREE_OF_A_KIND</t>
+  </si>
+  <si>
+    <t>StatisticAtLeast</t>
+  </si>
+  <si>
+    <t>PokerHandRankThreeOfAKindCount</t>
+  </si>
+  <si>
+    <t>首次达成三条</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_STRAIGHT</t>
+  </si>
+  <si>
+    <t>PokerHandRankStraightCount</t>
+  </si>
+  <si>
+    <t>首次达成顺子</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_FLUSH</t>
+  </si>
+  <si>
+    <t>PokerHandRankFlushCount</t>
+  </si>
+  <si>
+    <t>首次达成同花</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_FULL_HOUSE</t>
+  </si>
+  <si>
+    <t>PokerHandRankFullHouseCount</t>
+  </si>
+  <si>
+    <t>首次达成葫芦</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_FOUR_OF_A_KIND</t>
+  </si>
+  <si>
+    <t>PokerHandRankFourOfAKindCount</t>
+  </si>
+  <si>
+    <t>首次达成四条</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_STRAIGHT_FLUSH</t>
+  </si>
+  <si>
+    <t>PokerHandRankStraightFlushCount</t>
+  </si>
+  <si>
+    <t>首次达成同花顺</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_ROYAL_FLUSH</t>
+  </si>
+  <si>
+    <t>PokerHandRankRoyalFlushCount</t>
+  </si>
+  <si>
+    <t>首次达成皇家同花顺</t>
+  </si>
+  <si>
+    <t>ACH_DOG_FIRST_HINT</t>
+  </si>
+  <si>
+    <t>FirstEvent</t>
+  </si>
+  <si>
+    <t>DogHintAsked</t>
+  </si>
+  <si>
+    <t>首次询问狗狗牌运</t>
+  </si>
+  <si>
+    <t>ACH_DOG_FIRST_REFUSAL</t>
+  </si>
+  <si>
+    <t>DogHintRefused</t>
+  </si>
+  <si>
+    <t>首次被狗狗拒绝回答</t>
+  </si>
+  <si>
+    <t>ACH_DOG_FIRST_STARSTRUCK</t>
+  </si>
+  <si>
+    <t>DesktopStarstruckEntered</t>
+  </si>
+  <si>
+    <t>首次打字使狗狗进入崇拜状态；仅状态切换时计一次</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_RARE_ITEM</t>
+  </si>
+  <si>
+    <t>FirstExternalItemRarity</t>
+  </si>
+  <si>
+    <t>首次获得稀有物品</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_EPIC_ITEM</t>
+  </si>
+  <si>
+    <t>首次获得史诗物品</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_LEGENDARY_ITEM</t>
+  </si>
+  <si>
+    <t>首次获得传说物品</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_MYTHIC_ITEM</t>
+  </si>
+  <si>
+    <t>首次获得神话物品</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_BODY_DECORATION</t>
+  </si>
+  <si>
+    <t>BodyDecoration</t>
+  </si>
+  <si>
+    <t>首次获得玩家体表装饰（体毛、纹身、美甲等）</t>
+  </si>
+  <si>
+    <t>StatisticId</t>
+  </si>
+  <si>
+    <t>StatisticKey</t>
+  </si>
+  <si>
+    <t>DisplayName</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>StatisticType</t>
+  </si>
+  <si>
+    <t>PlatformApiName</t>
+  </si>
+  <si>
+    <t>SyncToPlatform</t>
+  </si>
+  <si>
+    <t>EPlayerStatisticUnit</t>
+  </si>
+  <si>
+    <t>EPlayerStatisticType</t>
+  </si>
+  <si>
+    <t>表内稳定数字 ID；发布后不可复用</t>
+  </si>
+  <si>
+    <t>游戏内部、Achievement.TargetKey 和数据导出共用的稳定机器名</t>
+  </si>
+  <si>
+    <t>CSV 数据字典用的中文名称</t>
+  </si>
+  <si>
+    <t>数值单位</t>
+  </si>
+  <si>
+    <t>Counter=只增累计；Maximum=仅保留最高值</t>
+  </si>
+  <si>
+    <t>未来 Steam/其他平台使用的机器名；发布后不要改名</t>
+  </si>
+  <si>
+    <t>未来是否同步到平台统计</t>
+  </si>
+  <si>
+    <t>最重要的统计口径；Debug 行为不应改变任何正式统计</t>
+  </si>
+  <si>
+    <t>统计 id</t>
+  </si>
+  <si>
+    <t>统计键</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>统计类型</t>
+  </si>
+  <si>
+    <t>平台 API 名</t>
+  </si>
+  <si>
+    <t>同步平台</t>
+  </si>
+  <si>
+    <t>GameRuntimeSeconds</t>
+  </si>
+  <si>
+    <t>累计游戏运行时间</t>
+  </si>
+  <si>
+    <t>Seconds</t>
+  </si>
+  <si>
+    <t>Counter</t>
+  </si>
+  <si>
+    <t>STAT_GAME_RUNTIME_SECONDS</t>
+  </si>
+  <si>
+    <t>游戏启动至退出的累计运行秒数；对应现有 TotalPlaySeconds</t>
+  </si>
+  <si>
+    <t>AppLaunchCount</t>
+  </si>
+  <si>
+    <t>游戏启动次数</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>STAT_APP_LAUNCH_COUNT</t>
+  </si>
+  <si>
+    <t>累计正常初始化游戏数据的次数</t>
+  </si>
+  <si>
+    <t>DesktopModeSeconds</t>
+  </si>
+  <si>
+    <t>桌宠模式时长</t>
+  </si>
+  <si>
+    <t>STAT_DESKTOP_MODE_SECONDS</t>
+  </si>
+  <si>
+    <t>桌宠模式实际处于可见状态的累计秒数</t>
+  </si>
+  <si>
+    <t>PokerModeSeconds</t>
+  </si>
+  <si>
+    <t>扑克模式时长</t>
+  </si>
+  <si>
+    <t>STAT_POKER_MODE_SECONDS</t>
+  </si>
+  <si>
+    <t>扑克游玩模式处于激活状态的累计秒数</t>
+  </si>
+  <si>
+    <t>TypingInputCount</t>
+  </si>
+  <si>
+    <t>累计打字输入次数</t>
+  </si>
+  <si>
+    <t>STAT_TYPING_INPUT_COUNT</t>
+  </si>
+  <si>
+    <t>真实全局打字输入次数；不受未来筹码产出倍率影响，目前是打字和筹码1比1，但有频率上限锁</t>
+  </si>
+  <si>
+    <t>TypingChipsEarned</t>
+  </si>
+  <si>
+    <t>累计打字获得筹码</t>
+  </si>
+  <si>
+    <t>Chips</t>
+  </si>
+  <si>
+    <t>STAT_TYPING_CHIPS_EARNED</t>
+  </si>
+  <si>
+    <t>仅累计 GlobalInputTracker 的真实打字奖励筹码</t>
+  </si>
+  <si>
+    <t>PokerHandsPlayed</t>
+  </si>
+  <si>
+    <t>累计扑克局数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_HANDS_PLAYED</t>
+  </si>
+  <si>
+    <t>成功下注并开始发牌的扑克局数</t>
+  </si>
+  <si>
+    <t>PokerHandsWon</t>
+  </si>
+  <si>
+    <t>累计扑克获胜局数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_HANDS_WON</t>
+  </si>
+  <si>
+    <t>最终结算有正向扑克奖励的局数</t>
+  </si>
+  <si>
+    <t>PokerHandsLost</t>
+  </si>
+  <si>
+    <t>累计扑克未获奖局数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_HANDS_LOST</t>
+  </si>
+  <si>
+    <t>最终结算没有扑克奖励的局数</t>
+  </si>
+  <si>
+    <t>PokerChipsWon</t>
+  </si>
+  <si>
+    <t>累计扑克赢取筹码</t>
+  </si>
+  <si>
+    <t>STAT_POKER_CHIPS_WON</t>
+  </si>
+  <si>
+    <t>仅累计玩家实际收取的扑克奖励；不含打字、盲盒和 Debug 发放</t>
+  </si>
+  <si>
+    <t>PokerChipsWagered</t>
+  </si>
+  <si>
+    <t>累计扑克下注筹码</t>
+  </si>
+  <si>
+    <t>STAT_POKER_CHIPS_WAGERED</t>
+  </si>
+  <si>
+    <t>累计实际下注的扑克筹码</t>
+  </si>
+  <si>
+    <t>PokerHandRankNothingCount</t>
+  </si>
+  <si>
+    <t>坏牌次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_NOTHING_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为坏牌的次数</t>
+  </si>
+  <si>
+    <t>PokerHandRankJacksOrBetterCount</t>
+  </si>
+  <si>
+    <t>高对次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_JACKS_OR_BETTER_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为高对的次数</t>
+  </si>
+  <si>
+    <t>PokerHandRankTwoPairCount</t>
+  </si>
+  <si>
+    <t>两对次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_TWO_PAIR_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为两对的次数</t>
+  </si>
+  <si>
+    <t>三条次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_THREE_OF_A_KIND_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为三条的次数</t>
+  </si>
+  <si>
+    <t>顺子次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_STRAIGHT_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为顺子的次数</t>
+  </si>
+  <si>
+    <t>同花次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_FLUSH_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为同花的次数</t>
+  </si>
+  <si>
+    <t>葫芦次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_FULL_HOUSE_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为葫芦的次数</t>
+  </si>
+  <si>
+    <t>四条次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_FOUR_OF_A_KIND_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为四条的次数</t>
+  </si>
+  <si>
+    <t>同花顺次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_STRAIGHT_FLUSH_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为同花顺的次数</t>
+  </si>
+  <si>
+    <t>皇家同花顺次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_ROYAL_FLUSH_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为皇家同花顺的次数</t>
+  </si>
+  <si>
+    <t>BlindBoxOpenedCount</t>
+  </si>
+  <si>
+    <t>打开盲盒次数</t>
+  </si>
+  <si>
+    <t>STAT_BLIND_BOX_OPENED_COUNT</t>
+  </si>
+  <si>
+    <t>成功打开盲盒的次数</t>
+  </si>
+  <si>
+    <t>BlindBoxChipsSpent</t>
+  </si>
+  <si>
+    <t>开启盲盒花费筹码</t>
+  </si>
+  <si>
+    <t>STAT_BLIND_BOX_CHIPS_SPENT</t>
+  </si>
+  <si>
+    <t>累计实际成功开启盲盒时扣除的筹码；不记录因筹码不足而失败的尝试</t>
+  </si>
+  <si>
+    <t>BlindBoxRewardClaimedCount</t>
+  </si>
+  <si>
+    <t>领取盲盒奖励次数</t>
+  </si>
+  <si>
+    <t>STAT_BLIND_BOX_REWARD_CLAIMED_COUNT</t>
+  </si>
+  <si>
+    <t>成功领取盲盒奖励的次数</t>
+  </si>
+  <si>
+    <t>ExternalItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>非初始道具获得数量</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得的道具数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>BlindBoxItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>盲盒获得道具数量</t>
+  </si>
+  <si>
+    <t>STAT_BLIND_BOX_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从盲盒领取到的道具数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>DogHintAskedCount</t>
+  </si>
+  <si>
+    <t>询问狗狗牌运次数</t>
+  </si>
+  <si>
+    <t>STAT_DOG_HINT_ASKED_COUNT</t>
+  </si>
+  <si>
+    <t>玩家询问狗狗牌运的次数</t>
+  </si>
+  <si>
+    <t>DogHintAskedWinningHandCount</t>
+  </si>
+  <si>
+    <t>询问狗狗后获奖局数</t>
+  </si>
+  <si>
+    <t>STAT_DOG_HINT_ASKED_WIN_COUNT</t>
+  </si>
+  <si>
+    <t>该局曾询问狗狗牌运，且最终结算有奖励的次数；不要求玩家完全按建议保留牌</t>
+  </si>
+  <si>
+    <t>ExternalCommonItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得普通物品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_COMMON_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得普通品质物品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalUncommonItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得优秀物品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_UNCOMMON_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得优秀品质物品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalRareItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得稀有物品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_RARE_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得稀有品质物品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalEpicItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得史诗物品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_EPIC_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得史诗品质物品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalLegendaryItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得传说物品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_LEGENDARY_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得传说品质物品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalMythicItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得神话物品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_MYTHIC_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得神话品质物品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalDogAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得狗狗数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_DOG_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得狗狗的数量；重复狗狗按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalHeadwearAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得帽子数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_HEADWEAR_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得头部装饰的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalEyewearAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得眼镜数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_EYEWEAR_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得眼部装饰的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalArmAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得手臂数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_ARM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得 Arm 部位道具的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalClothesAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得衣服数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_CLOTHES_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得衣服的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalTableAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得桌布数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_TABLE_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得桌布的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalBackgroundAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得背景数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_BACKGROUND_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得背景的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalAccessoryAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得手部装饰数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_ACCESSORY_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得手部装饰的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalRefreshmentAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得饮品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_REFRESHMENT_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得饮品/消耗品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalCardBackAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得卡背数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_CARD_BACK_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得卡背的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalCardFaceAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得卡面数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_CARD_FACE_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得卡面的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalBodyDecorationAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得体表装饰数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_BODY_DECORATION_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得体表装饰的数量，例如体毛、纹身、美甲；重复道具按实际数量累计</t>
   </si>
 </sst>
 </file>
@@ -1853,13 +2715,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2779,6 +3641,1476 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.5833333333333" customWidth="1"/>
+    <col min="3" max="3" width="30.9166666666667" customWidth="1"/>
+    <col min="4" max="4" width="22.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="7.91666666666667" customWidth="1"/>
+    <col min="6" max="6" width="13.6666666666667" customWidth="1"/>
+    <col min="7" max="7" width="43.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="20.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="53.0833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H1" t="s">
+        <v>487</v>
+      </c>
+      <c r="I1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F2" t="s">
+        <v>489</v>
+      </c>
+      <c r="G2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="89" customHeight="1" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>498</v>
+      </c>
+      <c r="C4" t="s">
+        <v>499</v>
+      </c>
+      <c r="D4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E4" t="s">
+        <v>500</v>
+      </c>
+      <c r="F4" t="s">
+        <v>501</v>
+      </c>
+      <c r="G4" t="s">
+        <v>502</v>
+      </c>
+      <c r="H4" t="s">
+        <v>503</v>
+      </c>
+      <c r="I4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D5" t="s">
+        <v>505</v>
+      </c>
+      <c r="E5" t="s">
+        <v>506</v>
+      </c>
+      <c r="F5" t="s">
+        <v>507</v>
+      </c>
+      <c r="G5" t="s">
+        <v>508</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>510</v>
+      </c>
+      <c r="D6" t="s">
+        <v>511</v>
+      </c>
+      <c r="E6" t="s">
+        <v>512</v>
+      </c>
+      <c r="F6" t="s">
+        <v>507</v>
+      </c>
+      <c r="G6" t="s">
+        <v>513</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>515</v>
+      </c>
+      <c r="D7" t="s">
+        <v>516</v>
+      </c>
+      <c r="E7" t="s">
+        <v>506</v>
+      </c>
+      <c r="F7" t="s">
+        <v>507</v>
+      </c>
+      <c r="G7" t="s">
+        <v>517</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>375</v>
+      </c>
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>519</v>
+      </c>
+      <c r="D8" t="s">
+        <v>520</v>
+      </c>
+      <c r="E8" t="s">
+        <v>506</v>
+      </c>
+      <c r="F8" t="s">
+        <v>507</v>
+      </c>
+      <c r="G8" t="s">
+        <v>521</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>375</v>
+      </c>
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>523</v>
+      </c>
+      <c r="D9" t="s">
+        <v>524</v>
+      </c>
+      <c r="E9" t="s">
+        <v>512</v>
+      </c>
+      <c r="F9" t="s">
+        <v>507</v>
+      </c>
+      <c r="G9" t="s">
+        <v>525</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>527</v>
+      </c>
+      <c r="D10" t="s">
+        <v>528</v>
+      </c>
+      <c r="E10" t="s">
+        <v>529</v>
+      </c>
+      <c r="F10" t="s">
+        <v>507</v>
+      </c>
+      <c r="G10" t="s">
+        <v>530</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>375</v>
+      </c>
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>532</v>
+      </c>
+      <c r="D11" t="s">
+        <v>533</v>
+      </c>
+      <c r="E11" t="s">
+        <v>512</v>
+      </c>
+      <c r="F11" t="s">
+        <v>507</v>
+      </c>
+      <c r="G11" t="s">
+        <v>534</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>536</v>
+      </c>
+      <c r="D12" t="s">
+        <v>537</v>
+      </c>
+      <c r="E12" t="s">
+        <v>512</v>
+      </c>
+      <c r="F12" t="s">
+        <v>507</v>
+      </c>
+      <c r="G12" t="s">
+        <v>538</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>375</v>
+      </c>
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>540</v>
+      </c>
+      <c r="D13" t="s">
+        <v>541</v>
+      </c>
+      <c r="E13" t="s">
+        <v>512</v>
+      </c>
+      <c r="F13" t="s">
+        <v>507</v>
+      </c>
+      <c r="G13" t="s">
+        <v>542</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>375</v>
+      </c>
+      <c r="B14">
+        <v>1010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>544</v>
+      </c>
+      <c r="D14" t="s">
+        <v>545</v>
+      </c>
+      <c r="E14" t="s">
+        <v>529</v>
+      </c>
+      <c r="F14" t="s">
+        <v>507</v>
+      </c>
+      <c r="G14" t="s">
+        <v>546</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>375</v>
+      </c>
+      <c r="B15">
+        <v>1011</v>
+      </c>
+      <c r="C15" t="s">
+        <v>548</v>
+      </c>
+      <c r="D15" t="s">
+        <v>549</v>
+      </c>
+      <c r="E15" t="s">
+        <v>529</v>
+      </c>
+      <c r="F15" t="s">
+        <v>507</v>
+      </c>
+      <c r="G15" t="s">
+        <v>550</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>375</v>
+      </c>
+      <c r="B16">
+        <v>1012</v>
+      </c>
+      <c r="C16" t="s">
+        <v>552</v>
+      </c>
+      <c r="D16" t="s">
+        <v>553</v>
+      </c>
+      <c r="E16" t="s">
+        <v>512</v>
+      </c>
+      <c r="F16" t="s">
+        <v>507</v>
+      </c>
+      <c r="G16" t="s">
+        <v>554</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>375</v>
+      </c>
+      <c r="B17">
+        <v>1013</v>
+      </c>
+      <c r="C17" t="s">
+        <v>556</v>
+      </c>
+      <c r="D17" t="s">
+        <v>557</v>
+      </c>
+      <c r="E17" t="s">
+        <v>512</v>
+      </c>
+      <c r="F17" t="s">
+        <v>507</v>
+      </c>
+      <c r="G17" t="s">
+        <v>558</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>375</v>
+      </c>
+      <c r="B18">
+        <v>1014</v>
+      </c>
+      <c r="C18" t="s">
+        <v>560</v>
+      </c>
+      <c r="D18" t="s">
+        <v>561</v>
+      </c>
+      <c r="E18" t="s">
+        <v>512</v>
+      </c>
+      <c r="F18" t="s">
+        <v>507</v>
+      </c>
+      <c r="G18" t="s">
+        <v>562</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B19">
+        <v>1015</v>
+      </c>
+      <c r="C19" t="s">
+        <v>439</v>
+      </c>
+      <c r="D19" t="s">
+        <v>564</v>
+      </c>
+      <c r="E19" t="s">
+        <v>512</v>
+      </c>
+      <c r="F19" t="s">
+        <v>507</v>
+      </c>
+      <c r="G19" t="s">
+        <v>565</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>375</v>
+      </c>
+      <c r="B20">
+        <v>1016</v>
+      </c>
+      <c r="C20" t="s">
+        <v>442</v>
+      </c>
+      <c r="D20" t="s">
+        <v>567</v>
+      </c>
+      <c r="E20" t="s">
+        <v>512</v>
+      </c>
+      <c r="F20" t="s">
+        <v>507</v>
+      </c>
+      <c r="G20" t="s">
+        <v>568</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>375</v>
+      </c>
+      <c r="B21">
+        <v>1017</v>
+      </c>
+      <c r="C21" t="s">
+        <v>445</v>
+      </c>
+      <c r="D21" t="s">
+        <v>570</v>
+      </c>
+      <c r="E21" t="s">
+        <v>512</v>
+      </c>
+      <c r="F21" t="s">
+        <v>507</v>
+      </c>
+      <c r="G21" t="s">
+        <v>571</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>375</v>
+      </c>
+      <c r="B22">
+        <v>1018</v>
+      </c>
+      <c r="C22" t="s">
+        <v>448</v>
+      </c>
+      <c r="D22" t="s">
+        <v>573</v>
+      </c>
+      <c r="E22" t="s">
+        <v>512</v>
+      </c>
+      <c r="F22" t="s">
+        <v>507</v>
+      </c>
+      <c r="G22" t="s">
+        <v>574</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>375</v>
+      </c>
+      <c r="B23">
+        <v>1019</v>
+      </c>
+      <c r="C23" t="s">
+        <v>451</v>
+      </c>
+      <c r="D23" t="s">
+        <v>576</v>
+      </c>
+      <c r="E23" t="s">
+        <v>512</v>
+      </c>
+      <c r="F23" t="s">
+        <v>507</v>
+      </c>
+      <c r="G23" t="s">
+        <v>577</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>375</v>
+      </c>
+      <c r="B24">
+        <v>1020</v>
+      </c>
+      <c r="C24" t="s">
+        <v>454</v>
+      </c>
+      <c r="D24" t="s">
+        <v>579</v>
+      </c>
+      <c r="E24" t="s">
+        <v>512</v>
+      </c>
+      <c r="F24" t="s">
+        <v>507</v>
+      </c>
+      <c r="G24" t="s">
+        <v>580</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>375</v>
+      </c>
+      <c r="B25">
+        <v>1021</v>
+      </c>
+      <c r="C25" t="s">
+        <v>457</v>
+      </c>
+      <c r="D25" t="s">
+        <v>582</v>
+      </c>
+      <c r="E25" t="s">
+        <v>512</v>
+      </c>
+      <c r="F25" t="s">
+        <v>507</v>
+      </c>
+      <c r="G25" t="s">
+        <v>583</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>375</v>
+      </c>
+      <c r="B26">
+        <v>1022</v>
+      </c>
+      <c r="C26" t="s">
+        <v>585</v>
+      </c>
+      <c r="D26" t="s">
+        <v>586</v>
+      </c>
+      <c r="E26" t="s">
+        <v>512</v>
+      </c>
+      <c r="F26" t="s">
+        <v>507</v>
+      </c>
+      <c r="G26" t="s">
+        <v>587</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>375</v>
+      </c>
+      <c r="B27">
+        <v>1030</v>
+      </c>
+      <c r="C27" t="s">
+        <v>589</v>
+      </c>
+      <c r="D27" t="s">
+        <v>590</v>
+      </c>
+      <c r="E27" t="s">
+        <v>529</v>
+      </c>
+      <c r="F27" t="s">
+        <v>507</v>
+      </c>
+      <c r="G27" t="s">
+        <v>591</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>375</v>
+      </c>
+      <c r="B28">
+        <v>1023</v>
+      </c>
+      <c r="C28" t="s">
+        <v>593</v>
+      </c>
+      <c r="D28" t="s">
+        <v>594</v>
+      </c>
+      <c r="E28" t="s">
+        <v>512</v>
+      </c>
+      <c r="F28" t="s">
+        <v>507</v>
+      </c>
+      <c r="G28" t="s">
+        <v>595</v>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>375</v>
+      </c>
+      <c r="B29">
+        <v>1024</v>
+      </c>
+      <c r="C29" t="s">
+        <v>597</v>
+      </c>
+      <c r="D29" t="s">
+        <v>598</v>
+      </c>
+      <c r="E29" t="s">
+        <v>512</v>
+      </c>
+      <c r="F29" t="s">
+        <v>507</v>
+      </c>
+      <c r="G29" t="s">
+        <v>599</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>375</v>
+      </c>
+      <c r="B30">
+        <v>1025</v>
+      </c>
+      <c r="C30" t="s">
+        <v>601</v>
+      </c>
+      <c r="D30" t="s">
+        <v>602</v>
+      </c>
+      <c r="E30" t="s">
+        <v>512</v>
+      </c>
+      <c r="F30" t="s">
+        <v>507</v>
+      </c>
+      <c r="G30" t="s">
+        <v>603</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>375</v>
+      </c>
+      <c r="B31">
+        <v>1026</v>
+      </c>
+      <c r="C31" t="s">
+        <v>605</v>
+      </c>
+      <c r="D31" t="s">
+        <v>606</v>
+      </c>
+      <c r="E31" t="s">
+        <v>512</v>
+      </c>
+      <c r="F31" t="s">
+        <v>507</v>
+      </c>
+      <c r="G31" t="s">
+        <v>607</v>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>375</v>
+      </c>
+      <c r="B32">
+        <v>1031</v>
+      </c>
+      <c r="C32" t="s">
+        <v>609</v>
+      </c>
+      <c r="D32" t="s">
+        <v>610</v>
+      </c>
+      <c r="E32" t="s">
+        <v>512</v>
+      </c>
+      <c r="F32" t="s">
+        <v>507</v>
+      </c>
+      <c r="G32" t="s">
+        <v>611</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>375</v>
+      </c>
+      <c r="B33">
+        <v>1032</v>
+      </c>
+      <c r="C33" t="s">
+        <v>613</v>
+      </c>
+      <c r="D33" t="s">
+        <v>614</v>
+      </c>
+      <c r="E33" t="s">
+        <v>512</v>
+      </c>
+      <c r="F33" t="s">
+        <v>507</v>
+      </c>
+      <c r="G33" t="s">
+        <v>615</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>375</v>
+      </c>
+      <c r="B34">
+        <v>1033</v>
+      </c>
+      <c r="C34" t="s">
+        <v>617</v>
+      </c>
+      <c r="D34" t="s">
+        <v>618</v>
+      </c>
+      <c r="E34" t="s">
+        <v>512</v>
+      </c>
+      <c r="F34" t="s">
+        <v>507</v>
+      </c>
+      <c r="G34" t="s">
+        <v>619</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>375</v>
+      </c>
+      <c r="B35">
+        <v>1034</v>
+      </c>
+      <c r="C35" t="s">
+        <v>621</v>
+      </c>
+      <c r="D35" t="s">
+        <v>622</v>
+      </c>
+      <c r="E35" t="s">
+        <v>512</v>
+      </c>
+      <c r="F35" t="s">
+        <v>507</v>
+      </c>
+      <c r="G35" t="s">
+        <v>623</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>375</v>
+      </c>
+      <c r="B36">
+        <v>1035</v>
+      </c>
+      <c r="C36" t="s">
+        <v>625</v>
+      </c>
+      <c r="D36" t="s">
+        <v>626</v>
+      </c>
+      <c r="E36" t="s">
+        <v>512</v>
+      </c>
+      <c r="F36" t="s">
+        <v>507</v>
+      </c>
+      <c r="G36" t="s">
+        <v>627</v>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>375</v>
+      </c>
+      <c r="B37">
+        <v>1036</v>
+      </c>
+      <c r="C37" t="s">
+        <v>629</v>
+      </c>
+      <c r="D37" t="s">
+        <v>630</v>
+      </c>
+      <c r="E37" t="s">
+        <v>512</v>
+      </c>
+      <c r="F37" t="s">
+        <v>507</v>
+      </c>
+      <c r="G37" t="s">
+        <v>631</v>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>375</v>
+      </c>
+      <c r="B38">
+        <v>1037</v>
+      </c>
+      <c r="C38" t="s">
+        <v>633</v>
+      </c>
+      <c r="D38" t="s">
+        <v>634</v>
+      </c>
+      <c r="E38" t="s">
+        <v>512</v>
+      </c>
+      <c r="F38" t="s">
+        <v>507</v>
+      </c>
+      <c r="G38" t="s">
+        <v>635</v>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>375</v>
+      </c>
+      <c r="B39">
+        <v>1038</v>
+      </c>
+      <c r="C39" t="s">
+        <v>637</v>
+      </c>
+      <c r="D39" t="s">
+        <v>638</v>
+      </c>
+      <c r="E39" t="s">
+        <v>512</v>
+      </c>
+      <c r="F39" t="s">
+        <v>507</v>
+      </c>
+      <c r="G39" t="s">
+        <v>639</v>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>375</v>
+      </c>
+      <c r="B40">
+        <v>1039</v>
+      </c>
+      <c r="C40" t="s">
+        <v>641</v>
+      </c>
+      <c r="D40" t="s">
+        <v>642</v>
+      </c>
+      <c r="E40" t="s">
+        <v>512</v>
+      </c>
+      <c r="F40" t="s">
+        <v>507</v>
+      </c>
+      <c r="G40" t="s">
+        <v>643</v>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>375</v>
+      </c>
+      <c r="B41">
+        <v>1040</v>
+      </c>
+      <c r="C41" t="s">
+        <v>645</v>
+      </c>
+      <c r="D41" t="s">
+        <v>646</v>
+      </c>
+      <c r="E41" t="s">
+        <v>512</v>
+      </c>
+      <c r="F41" t="s">
+        <v>507</v>
+      </c>
+      <c r="G41" t="s">
+        <v>647</v>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>375</v>
+      </c>
+      <c r="B42">
+        <v>1041</v>
+      </c>
+      <c r="C42" t="s">
+        <v>649</v>
+      </c>
+      <c r="D42" t="s">
+        <v>650</v>
+      </c>
+      <c r="E42" t="s">
+        <v>512</v>
+      </c>
+      <c r="F42" t="s">
+        <v>507</v>
+      </c>
+      <c r="G42" t="s">
+        <v>651</v>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>375</v>
+      </c>
+      <c r="B43">
+        <v>1042</v>
+      </c>
+      <c r="C43" t="s">
+        <v>653</v>
+      </c>
+      <c r="D43" t="s">
+        <v>654</v>
+      </c>
+      <c r="E43" t="s">
+        <v>512</v>
+      </c>
+      <c r="F43" t="s">
+        <v>507</v>
+      </c>
+      <c r="G43" t="s">
+        <v>655</v>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>375</v>
+      </c>
+      <c r="B44">
+        <v>1043</v>
+      </c>
+      <c r="C44" t="s">
+        <v>657</v>
+      </c>
+      <c r="D44" t="s">
+        <v>658</v>
+      </c>
+      <c r="E44" t="s">
+        <v>512</v>
+      </c>
+      <c r="F44" t="s">
+        <v>507</v>
+      </c>
+      <c r="G44" t="s">
+        <v>659</v>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>375</v>
+      </c>
+      <c r="B45">
+        <v>1044</v>
+      </c>
+      <c r="C45" t="s">
+        <v>661</v>
+      </c>
+      <c r="D45" t="s">
+        <v>662</v>
+      </c>
+      <c r="E45" t="s">
+        <v>512</v>
+      </c>
+      <c r="F45" t="s">
+        <v>507</v>
+      </c>
+      <c r="G45" t="s">
+        <v>663</v>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>375</v>
+      </c>
+      <c r="B46">
+        <v>1045</v>
+      </c>
+      <c r="C46" t="s">
+        <v>665</v>
+      </c>
+      <c r="D46" t="s">
+        <v>666</v>
+      </c>
+      <c r="E46" t="s">
+        <v>512</v>
+      </c>
+      <c r="F46" t="s">
+        <v>507</v>
+      </c>
+      <c r="G46" t="s">
+        <v>667</v>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>375</v>
+      </c>
+      <c r="B47">
+        <v>1046</v>
+      </c>
+      <c r="C47" t="s">
+        <v>669</v>
+      </c>
+      <c r="D47" t="s">
+        <v>670</v>
+      </c>
+      <c r="E47" t="s">
+        <v>512</v>
+      </c>
+      <c r="F47" t="s">
+        <v>507</v>
+      </c>
+      <c r="G47" t="s">
+        <v>671</v>
+      </c>
+      <c r="H47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>375</v>
+      </c>
+      <c r="B48">
+        <v>1047</v>
+      </c>
+      <c r="C48" t="s">
+        <v>673</v>
+      </c>
+      <c r="D48" t="s">
+        <v>674</v>
+      </c>
+      <c r="E48" t="s">
+        <v>512</v>
+      </c>
+      <c r="F48" t="s">
+        <v>507</v>
+      </c>
+      <c r="G48" t="s">
+        <v>675</v>
+      </c>
+      <c r="H48" t="b">
+        <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>375</v>
+      </c>
+      <c r="B49">
+        <v>1048</v>
+      </c>
+      <c r="C49" t="s">
+        <v>677</v>
+      </c>
+      <c r="D49" t="s">
+        <v>678</v>
+      </c>
+      <c r="E49" t="s">
+        <v>512</v>
+      </c>
+      <c r="F49" t="s">
+        <v>507</v>
+      </c>
+      <c r="G49" t="s">
+        <v>679</v>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="B50">
+        <v>1049</v>
+      </c>
+      <c r="C50" t="s">
+        <v>681</v>
+      </c>
+      <c r="D50" t="s">
+        <v>682</v>
+      </c>
+      <c r="E50" t="s">
+        <v>512</v>
+      </c>
+      <c r="F50" t="s">
+        <v>507</v>
+      </c>
+      <c r="G50" t="s">
+        <v>683</v>
+      </c>
+      <c r="H50" t="b">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>684</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -2794,10 +5126,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C1" t="s">
@@ -2809,7 +5141,7 @@
       <c r="F1" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H1" t="s">
@@ -2820,10 +5152,10 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C2" t="s">
@@ -2835,7 +5167,7 @@
       <c r="F2" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
@@ -2846,14 +5178,14 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="3"/>
       <c r="D3" t="s">
         <v>111</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
@@ -3158,7 +5490,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>156</v>
       </c>
       <c r="B3" t="s">
@@ -3167,7 +5499,7 @@
       <c r="C3" t="s">
         <v>158</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
@@ -3175,7 +5507,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>160</v>
       </c>
       <c r="B4" t="s">
@@ -3184,7 +5516,7 @@
       <c r="C4" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" t="s">
@@ -3192,42 +5524,42 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="A8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3260,29 +5592,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>168</v>
       </c>
       <c r="J1" t="s">
@@ -3320,84 +5652,84 @@
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="3" ht="34.8" spans="1:20">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:20">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B4" t="s">
@@ -4182,13 +6514,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>240</v>
       </c>
       <c r="D1" t="s">
@@ -4202,13 +6534,13 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D2" t="s">
@@ -4222,12 +6554,12 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -4408,13 +6740,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>268</v>
       </c>
       <c r="E1" t="s">
@@ -4446,13 +6778,13 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>278</v>
       </c>
       <c r="E2" t="s">
@@ -4484,18 +6816,18 @@
       </c>
     </row>
     <row r="3" ht="104.4" spans="1:14">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="E3" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="E3" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>282</v>
       </c>
     </row>
@@ -5262,37 +7594,37 @@
       </c>
     </row>
     <row r="3" ht="87" spans="1:11">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>292</v>
       </c>
     </row>
@@ -5480,13 +7812,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>240</v>
       </c>
       <c r="D1" t="s">
@@ -5500,13 +7832,13 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D2" t="s">
@@ -5519,16 +7851,16 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" ht="52.2" spans="1:6">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="52.2" spans="1:6">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>382</v>
       </c>
     </row>
@@ -5629,15 +7961,21 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
   <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="13.4166666666667" customWidth="1"/>
-    <col min="3" max="3" width="21.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="28.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="19.0833333333333" customWidth="1"/>
+    <col min="5" max="5" width="29.4166666666667" customWidth="1"/>
+    <col min="6" max="6" width="22.25" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="42.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B1" t="s">
@@ -5646,41 +7984,771 @@
       <c r="C1" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="D1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F1" t="s">
+        <v>398</v>
+      </c>
+      <c r="G1" t="s">
+        <v>399</v>
+      </c>
+      <c r="H1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="D2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" ht="81" customHeight="1" spans="1:8">
+      <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="B3" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>408</v>
       </c>
       <c r="C4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>409</v>
+      </c>
+      <c r="D4" t="s">
+        <v>410</v>
+      </c>
+      <c r="E4" t="s">
+        <v>411</v>
+      </c>
+      <c r="F4" t="s">
+        <v>412</v>
+      </c>
+      <c r="G4" t="s">
+        <v>413</v>
+      </c>
+      <c r="H4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>375</v>
+      </c>
       <c r="B5">
+        <v>1000</v>
+      </c>
+      <c r="C5" t="s">
+        <v>414</v>
+      </c>
+      <c r="D5" t="s">
+        <v>415</v>
+      </c>
+      <c r="E5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B6">
         <v>1001</v>
       </c>
-      <c r="C5" t="s">
-        <v>397</v>
+      <c r="C6" t="s">
+        <v>417</v>
+      </c>
+      <c r="D6" t="s">
+        <v>415</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B7">
+        <v>1002</v>
+      </c>
+      <c r="C7" t="s">
+        <v>419</v>
+      </c>
+      <c r="D7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>375</v>
+      </c>
+      <c r="B8">
+        <v>1003</v>
+      </c>
+      <c r="C8" t="s">
+        <v>421</v>
+      </c>
+      <c r="D8" t="s">
+        <v>415</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>375</v>
+      </c>
+      <c r="B9">
+        <v>1004</v>
+      </c>
+      <c r="C9" t="s">
+        <v>423</v>
+      </c>
+      <c r="D9" t="s">
+        <v>415</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B10">
+        <v>1005</v>
+      </c>
+      <c r="C10" t="s">
+        <v>425</v>
+      </c>
+      <c r="D10" t="s">
+        <v>415</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>375</v>
+      </c>
+      <c r="B11">
+        <v>1006</v>
+      </c>
+      <c r="C11" t="s">
+        <v>427</v>
+      </c>
+      <c r="D11" t="s">
+        <v>415</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B12">
+        <v>1007</v>
+      </c>
+      <c r="C12" t="s">
+        <v>429</v>
+      </c>
+      <c r="D12" t="s">
+        <v>415</v>
+      </c>
+      <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>375</v>
+      </c>
+      <c r="B13">
+        <v>1008</v>
+      </c>
+      <c r="C13" t="s">
+        <v>431</v>
+      </c>
+      <c r="D13" t="s">
+        <v>415</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>375</v>
+      </c>
+      <c r="B14">
+        <v>1009</v>
+      </c>
+      <c r="C14" t="s">
+        <v>433</v>
+      </c>
+      <c r="D14" t="s">
+        <v>415</v>
+      </c>
+      <c r="E14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>375</v>
+      </c>
+      <c r="B15">
+        <v>1010</v>
+      </c>
+      <c r="C15" t="s">
+        <v>435</v>
+      </c>
+      <c r="D15" t="s">
+        <v>415</v>
+      </c>
+      <c r="E15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>375</v>
+      </c>
+      <c r="B16">
+        <v>1101</v>
+      </c>
+      <c r="C16" t="s">
+        <v>437</v>
+      </c>
+      <c r="D16" t="s">
+        <v>438</v>
+      </c>
+      <c r="E16" t="s">
+        <v>439</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>375</v>
+      </c>
+      <c r="B17">
+        <v>1102</v>
+      </c>
+      <c r="C17" t="s">
+        <v>441</v>
+      </c>
+      <c r="D17" t="s">
+        <v>438</v>
+      </c>
+      <c r="E17" t="s">
+        <v>442</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>375</v>
+      </c>
+      <c r="B18">
+        <v>1103</v>
+      </c>
+      <c r="C18" t="s">
+        <v>444</v>
+      </c>
+      <c r="D18" t="s">
+        <v>438</v>
+      </c>
+      <c r="E18" t="s">
+        <v>445</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B19">
+        <v>1104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>447</v>
+      </c>
+      <c r="D19" t="s">
+        <v>438</v>
+      </c>
+      <c r="E19" t="s">
+        <v>448</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>375</v>
+      </c>
+      <c r="B20">
+        <v>1105</v>
+      </c>
+      <c r="C20" t="s">
+        <v>450</v>
+      </c>
+      <c r="D20" t="s">
+        <v>438</v>
+      </c>
+      <c r="E20" t="s">
+        <v>451</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>375</v>
+      </c>
+      <c r="B21">
+        <v>1106</v>
+      </c>
+      <c r="C21" t="s">
+        <v>453</v>
+      </c>
+      <c r="D21" t="s">
+        <v>438</v>
+      </c>
+      <c r="E21" t="s">
+        <v>454</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>375</v>
+      </c>
+      <c r="B22">
+        <v>1107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>456</v>
+      </c>
+      <c r="D22" t="s">
+        <v>438</v>
+      </c>
+      <c r="E22" t="s">
+        <v>457</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>375</v>
+      </c>
+      <c r="B23">
+        <v>1201</v>
+      </c>
+      <c r="C23" t="s">
+        <v>459</v>
+      </c>
+      <c r="D23" t="s">
+        <v>460</v>
+      </c>
+      <c r="E23" t="s">
+        <v>461</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>375</v>
+      </c>
+      <c r="B24">
+        <v>1202</v>
+      </c>
+      <c r="C24" t="s">
+        <v>463</v>
+      </c>
+      <c r="D24" t="s">
+        <v>460</v>
+      </c>
+      <c r="E24" t="s">
+        <v>464</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>375</v>
+      </c>
+      <c r="B25">
+        <v>1203</v>
+      </c>
+      <c r="C25" t="s">
+        <v>466</v>
+      </c>
+      <c r="D25" t="s">
+        <v>460</v>
+      </c>
+      <c r="E25" t="s">
+        <v>467</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>375</v>
+      </c>
+      <c r="B26">
+        <v>1301</v>
+      </c>
+      <c r="C26" t="s">
+        <v>469</v>
+      </c>
+      <c r="D26" t="s">
+        <v>470</v>
+      </c>
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>375</v>
+      </c>
+      <c r="B27">
+        <v>1302</v>
+      </c>
+      <c r="C27" t="s">
+        <v>472</v>
+      </c>
+      <c r="D27" t="s">
+        <v>470</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>375</v>
+      </c>
+      <c r="B28">
+        <v>1303</v>
+      </c>
+      <c r="C28" t="s">
+        <v>474</v>
+      </c>
+      <c r="D28" t="s">
+        <v>470</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>375</v>
+      </c>
+      <c r="B29">
+        <v>1304</v>
+      </c>
+      <c r="C29" t="s">
+        <v>476</v>
+      </c>
+      <c r="D29" t="s">
+        <v>470</v>
+      </c>
+      <c r="E29" t="s">
+        <v>260</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="B30">
+        <v>1011</v>
+      </c>
+      <c r="C30" t="s">
+        <v>478</v>
+      </c>
+      <c r="D30" t="s">
+        <v>415</v>
+      </c>
+      <c r="E30" t="s">
+        <v>479</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="686">
   <si>
     <t>Dog</t>
   </si>
@@ -1239,6 +1239,9 @@
   </si>
   <si>
     <t>EAchievementRuleType</t>
+  </si>
+  <si>
+    <t>long</t>
   </si>
   <si>
     <t>成就唯一 ID；发布后不可复用</t>
@@ -3663,25 +3666,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I1" t="s">
         <v>277</v>
@@ -3701,10 +3704,10 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -3721,28 +3724,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3750,25 +3753,25 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D4" t="s">
         <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I4" t="s">
         <v>292</v>
@@ -3782,25 +3785,25 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3811,25 +3814,25 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3840,25 +3843,25 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D7" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3869,25 +3872,25 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E8" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3898,25 +3901,25 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D9" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3927,25 +3930,25 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E10" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F10" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3956,25 +3959,25 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3985,25 +3988,25 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E12" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G12" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -4014,25 +4017,25 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D13" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F13" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G13" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -4043,25 +4046,25 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D14" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F14" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G14" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -4072,25 +4075,25 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D15" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F15" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G15" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -4101,25 +4104,25 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D16" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E16" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F16" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G16" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -4130,25 +4133,25 @@
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D17" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F17" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G17" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -4159,25 +4162,25 @@
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D18" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E18" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F18" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G18" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -4188,25 +4191,25 @@
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D19" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F19" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G19" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -4217,25 +4220,25 @@
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D20" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E20" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F20" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G20" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -4246,25 +4249,25 @@
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D21" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E21" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F21" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G21" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -4275,25 +4278,25 @@
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D22" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E22" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F22" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G22" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -4304,25 +4307,25 @@
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D23" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E23" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F23" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G23" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -4333,25 +4336,25 @@
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D24" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E24" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F24" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G24" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -4362,25 +4365,25 @@
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D25" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E25" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F25" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G25" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -4391,25 +4394,25 @@
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D26" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E26" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F26" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G26" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -4420,25 +4423,25 @@
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D27" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E27" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F27" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G27" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -4449,25 +4452,25 @@
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D28" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E28" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F28" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G28" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -4478,25 +4481,25 @@
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D29" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F29" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G29" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -4507,25 +4510,25 @@
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D30" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E30" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F30" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G30" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -4536,25 +4539,25 @@
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D31" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E31" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F31" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G31" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -4565,25 +4568,25 @@
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D32" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E32" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F32" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G32" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -4594,25 +4597,25 @@
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D33" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E33" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F33" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G33" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -4623,25 +4626,25 @@
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D34" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E34" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F34" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G34" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -4652,25 +4655,25 @@
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D35" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E35" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F35" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G35" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -4681,25 +4684,25 @@
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D36" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E36" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F36" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G36" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -4710,25 +4713,25 @@
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D37" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E37" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F37" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G37" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -4739,25 +4742,25 @@
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D38" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E38" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F38" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G38" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -4768,25 +4771,25 @@
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D39" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E39" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F39" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G39" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -4797,25 +4800,25 @@
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D40" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E40" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F40" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G40" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -4826,25 +4829,25 @@
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D41" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E41" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F41" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G41" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -4855,25 +4858,25 @@
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D42" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E42" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F42" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G42" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -4884,25 +4887,25 @@
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D43" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E43" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F43" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G43" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -4913,25 +4916,25 @@
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D44" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E44" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F44" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G44" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -4942,25 +4945,25 @@
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D45" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E45" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F45" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G45" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -4971,25 +4974,25 @@
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D46" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E46" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F46" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G46" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -5000,25 +5003,25 @@
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D47" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E47" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F47" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G47" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -5029,25 +5032,25 @@
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D48" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E48" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F48" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G48" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -5058,25 +5061,25 @@
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D49" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E49" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F49" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G49" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5084,25 +5087,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D50" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E50" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F50" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G50" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
   </sheetData>
@@ -8017,7 +8020,7 @@
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>107</v>
+        <v>401</v>
       </c>
       <c r="G2" t="s">
         <v>279</v>
@@ -8031,25 +8034,25 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -8057,22 +8060,22 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H4" t="s">
         <v>292</v>
@@ -8086,10 +8089,10 @@
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8101,7 +8104,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -8112,10 +8115,10 @@
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8127,7 +8130,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -8138,10 +8141,10 @@
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8153,7 +8156,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -8164,10 +8167,10 @@
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D8" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -8179,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -8190,10 +8193,10 @@
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -8205,7 +8208,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -8216,10 +8219,10 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8231,7 +8234,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -8242,10 +8245,10 @@
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -8257,7 +8260,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -8268,10 +8271,10 @@
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D12" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -8283,7 +8286,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -8294,10 +8297,10 @@
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D13" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -8309,7 +8312,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -8320,10 +8323,10 @@
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -8335,7 +8338,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -8346,10 +8349,10 @@
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -8361,7 +8364,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -8372,13 +8375,13 @@
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D16" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E16" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -8387,7 +8390,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -8398,13 +8401,13 @@
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -8413,7 +8416,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -8424,13 +8427,13 @@
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D18" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E18" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -8439,7 +8442,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -8450,13 +8453,13 @@
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E19" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -8465,7 +8468,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -8476,13 +8479,13 @@
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D20" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E20" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -8491,7 +8494,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -8502,13 +8505,13 @@
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D21" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E21" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -8517,7 +8520,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -8528,13 +8531,13 @@
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D22" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E22" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -8543,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -8554,13 +8557,13 @@
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -8569,7 +8572,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -8580,13 +8583,13 @@
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D24" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E24" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -8595,7 +8598,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -8606,13 +8609,13 @@
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D25" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E25" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -8621,7 +8624,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -8632,10 +8635,10 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D26" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E26" t="s">
         <v>20</v>
@@ -8647,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -8658,10 +8661,10 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D27" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E27" t="s">
         <v>11</v>
@@ -8673,7 +8676,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -8684,10 +8687,10 @@
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D28" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E28" t="s">
         <v>2</v>
@@ -8699,7 +8702,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -8710,10 +8713,10 @@
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D29" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E29" t="s">
         <v>260</v>
@@ -8725,7 +8728,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -8733,13 +8736,13 @@
         <v>1011</v>
       </c>
       <c r="C30" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D30" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E30" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -8748,7 +8751,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="694">
   <si>
     <t>Dog</t>
   </si>
@@ -527,6 +527,15 @@
     <t>盲盒消耗筹码倍率</t>
   </si>
   <si>
+    <t>PlayerStatisticScale</t>
+  </si>
+  <si>
+    <t>统计倍率</t>
+  </si>
+  <si>
+    <t>统计时，玩家实际行为乘以倍率作为统计值记录，例如玩家获得1个筹码，倍率是10的话，记为10个筹码</t>
+  </si>
+  <si>
     <t>IconName</t>
   </si>
   <si>
@@ -1619,7 +1628,7 @@
     <t>STAT_TYPING_INPUT_COUNT</t>
   </si>
   <si>
-    <t>真实全局打字输入次数；不受未来筹码产出倍率影响，目前是打字和筹码1比1，但有频率上限锁</t>
+    <t>真实全局打字输入次数；不受未来筹码产出倍率影响，目前是打字和筹码1比1，但有频率上限锁（打字包括鼠标点击）</t>
   </si>
   <si>
     <t>TypingChipsEarned</t>
@@ -1634,7 +1643,7 @@
     <t>STAT_TYPING_CHIPS_EARNED</t>
   </si>
   <si>
-    <t>仅累计 GlobalInputTracker 的真实打字奖励筹码</t>
+    <t>仅累计 GlobalInputTracker 的真实打字奖励筹码（包括鼠标点击）</t>
   </si>
   <si>
     <t>PokerHandsPlayed</t>
@@ -2094,6 +2103,21 @@
   </si>
   <si>
     <t>从非初始来源获得体表装饰的数量，例如体毛、纹身、美甲；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>PeakHalfHourInputChipsEarned</t>
+  </si>
+  <si>
+    <t>半小时周期打字筹码峰值</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>STAT_PEAK_HALF_HOUR_INPUT_CHIPS_EARNED</t>
+  </si>
+  <si>
+    <t>每自然半小时内，通过打字获得的最高筹码数（本游戏包括鼠标）</t>
   </si>
 </sst>
 </file>
@@ -3647,16 +3671,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="11.5833333333333" customWidth="1"/>
     <col min="3" max="3" width="30.9166666666667" customWidth="1"/>
     <col min="4" max="4" width="22.8333333333333" customWidth="1"/>
-    <col min="5" max="5" width="7.91666666666667" customWidth="1"/>
+    <col min="5" max="5" width="14.9166666666667" customWidth="1"/>
     <col min="6" max="6" width="13.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="43.8333333333333" customWidth="1"/>
+    <col min="7" max="7" width="51" customWidth="1"/>
     <col min="8" max="8" width="20.5833333333333" customWidth="1"/>
     <col min="9" max="9" width="53.0833333333333" customWidth="1"/>
   </cols>
@@ -3666,28 +3690,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="G1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="H1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="I1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3704,16 +3728,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -3724,28 +3748,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3753,1333 +3777,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C4" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E4" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F4" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="G4" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="H4" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="I4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D5" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F5" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G5" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>514</v>
+      </c>
+      <c r="D6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E6" t="s">
+        <v>516</v>
+      </c>
+      <c r="F6" t="s">
         <v>511</v>
       </c>
-      <c r="D6" t="s">
-        <v>512</v>
-      </c>
-      <c r="E6" t="s">
-        <v>513</v>
-      </c>
-      <c r="F6" t="s">
-        <v>508</v>
-      </c>
       <c r="G6" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D7" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E7" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F7" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G7" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D8" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E8" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F8" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G8" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D9" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E9" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F9" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G9" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D10" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E10" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F10" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G10" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D11" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E11" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F11" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G11" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D12" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E12" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F12" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G12" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D13" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E13" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F13" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G13" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D14" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E14" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F14" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G14" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D15" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E15" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F15" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G15" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D16" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E16" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F16" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G16" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D17" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E17" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F17" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G17" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D18" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E18" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F18" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G18" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D19" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E19" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F19" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G19" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D20" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E20" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F20" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G20" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D21" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E21" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F21" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G21" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D22" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E22" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F22" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G22" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D23" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E23" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F23" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G23" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D24" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E24" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F24" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G24" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D25" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E25" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F25" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G25" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D26" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E26" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F26" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G26" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D27" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E27" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F27" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G27" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D28" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E28" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F28" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G28" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D29" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E29" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F29" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G29" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D30" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E30" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F30" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G30" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D31" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E31" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F31" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G31" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D32" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="E32" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F32" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G32" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D33" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E33" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F33" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G33" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D34" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E34" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F34" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G34" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D35" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="E35" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F35" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G35" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D36" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E36" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F36" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G36" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D37" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E37" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F37" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G37" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D38" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="E38" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F38" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G38" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D39" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E39" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F39" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G39" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D40" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E40" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F40" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G40" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="D41" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="E41" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F41" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G41" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D42" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E42" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F42" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G42" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D43" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E43" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F43" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G43" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D44" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E44" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F44" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G44" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D45" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E45" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F45" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G45" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D46" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E46" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F46" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G46" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="D47" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="E47" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F47" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G47" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D48" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E48" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F48" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G48" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="D49" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E49" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F49" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G49" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5087,25 +5111,51 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D50" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="E50" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F50" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G50" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>685</v>
+        <v>688</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="B51">
+        <v>1050</v>
+      </c>
+      <c r="C51" t="s">
+        <v>689</v>
+      </c>
+      <c r="D51" t="s">
+        <v>690</v>
+      </c>
+      <c r="E51" t="s">
+        <v>533</v>
+      </c>
+      <c r="F51" t="s">
+        <v>691</v>
+      </c>
+      <c r="G51" t="s">
+        <v>692</v>
+      </c>
+      <c r="H51" t="b">
+        <v>1</v>
+      </c>
+      <c r="I51" t="s">
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -5460,8 +5510,8 @@
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="21.9166666666667" customWidth="1"/>
-    <col min="2" max="2" width="15.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="70.1666666666667" customWidth="1"/>
+    <col min="2" max="2" width="19.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="84.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5503,7 +5553,7 @@
         <v>158</v>
       </c>
       <c r="D3" s="2">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>159</v>
@@ -5520,17 +5570,28 @@
         <v>158</v>
       </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2"/>
@@ -5603,55 +5664,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="P1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="S1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="T1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -5722,10 +5783,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -5739,55 +5800,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="I4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="P4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="R4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="S4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -5795,58 +5856,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I5" t="s">
+        <v>206</v>
+      </c>
+      <c r="J5" t="s">
+        <v>207</v>
+      </c>
+      <c r="K5" t="s">
+        <v>208</v>
+      </c>
+      <c r="L5" t="s">
+        <v>209</v>
+      </c>
+      <c r="M5" t="s">
         <v>203</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
+        <v>210</v>
+      </c>
+      <c r="O5" t="s">
+        <v>211</v>
+      </c>
+      <c r="P5" t="s">
         <v>204</v>
       </c>
-      <c r="K5" t="s">
-        <v>205</v>
-      </c>
-      <c r="L5" t="s">
-        <v>206</v>
-      </c>
-      <c r="M5" t="s">
-        <v>200</v>
-      </c>
-      <c r="N5" t="s">
-        <v>207</v>
-      </c>
-      <c r="O5" t="s">
-        <v>208</v>
-      </c>
-      <c r="P5" t="s">
-        <v>201</v>
-      </c>
       <c r="Q5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="R5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="S5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="T5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -5854,58 +5915,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6" t="s">
+        <v>212</v>
+      </c>
+      <c r="G6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H6" t="s">
+        <v>218</v>
+      </c>
+      <c r="I6" t="s">
+        <v>206</v>
+      </c>
+      <c r="J6" t="s">
+        <v>207</v>
+      </c>
+      <c r="K6" t="s">
+        <v>208</v>
+      </c>
+      <c r="L6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M6" t="s">
+        <v>203</v>
+      </c>
+      <c r="N6" t="s">
+        <v>210</v>
+      </c>
+      <c r="O6" t="s">
+        <v>211</v>
+      </c>
+      <c r="P6" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>212</v>
+      </c>
+      <c r="R6" t="s">
         <v>213</v>
       </c>
-      <c r="D6" t="s">
+      <c r="S6" t="s">
         <v>214</v>
       </c>
-      <c r="E6" t="s">
-        <v>200</v>
-      </c>
-      <c r="F6" t="s">
-        <v>209</v>
-      </c>
-      <c r="G6" t="s">
-        <v>171</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="T6" t="s">
         <v>215</v>
-      </c>
-      <c r="I6" t="s">
-        <v>203</v>
-      </c>
-      <c r="J6" t="s">
-        <v>204</v>
-      </c>
-      <c r="K6" t="s">
-        <v>205</v>
-      </c>
-      <c r="L6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M6" t="s">
-        <v>200</v>
-      </c>
-      <c r="N6" t="s">
-        <v>207</v>
-      </c>
-      <c r="O6" t="s">
-        <v>208</v>
-      </c>
-      <c r="P6" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>209</v>
-      </c>
-      <c r="R6" t="s">
-        <v>210</v>
-      </c>
-      <c r="S6" t="s">
-        <v>211</v>
-      </c>
-      <c r="T6" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -5913,58 +5974,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" t="s">
+        <v>174</v>
+      </c>
+      <c r="H7" t="s">
+        <v>221</v>
+      </c>
+      <c r="I7" t="s">
+        <v>206</v>
+      </c>
+      <c r="J7" t="s">
+        <v>207</v>
+      </c>
+      <c r="K7" t="s">
+        <v>208</v>
+      </c>
+      <c r="L7" t="s">
+        <v>209</v>
+      </c>
+      <c r="M7" t="s">
+        <v>203</v>
+      </c>
+      <c r="N7" t="s">
         <v>210</v>
       </c>
-      <c r="G7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" t="s">
-        <v>218</v>
-      </c>
-      <c r="I7" t="s">
-        <v>203</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="O7" t="s">
+        <v>211</v>
+      </c>
+      <c r="P7" t="s">
         <v>204</v>
       </c>
-      <c r="K7" t="s">
-        <v>205</v>
-      </c>
-      <c r="L7" t="s">
-        <v>206</v>
-      </c>
-      <c r="M7" t="s">
-        <v>200</v>
-      </c>
-      <c r="N7" t="s">
-        <v>207</v>
-      </c>
-      <c r="O7" t="s">
-        <v>208</v>
-      </c>
-      <c r="P7" t="s">
-        <v>201</v>
-      </c>
       <c r="Q7" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="R7" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="S7" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="T7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -5972,58 +6033,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F8" t="s">
+        <v>211</v>
+      </c>
+      <c r="G8" t="s">
+        <v>174</v>
+      </c>
+      <c r="H8" t="s">
+        <v>224</v>
+      </c>
+      <c r="I8" t="s">
+        <v>206</v>
+      </c>
+      <c r="J8" t="s">
         <v>207</v>
       </c>
-      <c r="F8" t="s">
+      <c r="K8" t="s">
         <v>208</v>
       </c>
-      <c r="G8" t="s">
-        <v>171</v>
-      </c>
-      <c r="H8" t="s">
-        <v>221</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
+        <v>209</v>
+      </c>
+      <c r="M8" t="s">
         <v>203</v>
       </c>
-      <c r="J8" t="s">
+      <c r="N8" t="s">
+        <v>210</v>
+      </c>
+      <c r="O8" t="s">
+        <v>211</v>
+      </c>
+      <c r="P8" t="s">
         <v>204</v>
       </c>
-      <c r="K8" t="s">
-        <v>205</v>
-      </c>
-      <c r="L8" t="s">
-        <v>206</v>
-      </c>
-      <c r="M8" t="s">
-        <v>200</v>
-      </c>
-      <c r="N8" t="s">
-        <v>207</v>
-      </c>
-      <c r="O8" t="s">
-        <v>208</v>
-      </c>
-      <c r="P8" t="s">
-        <v>201</v>
-      </c>
       <c r="Q8" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="R8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="S8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="T8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6031,58 +6092,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F9" t="s">
+        <v>213</v>
+      </c>
+      <c r="G9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H9" t="s">
+        <v>205</v>
+      </c>
+      <c r="I9" t="s">
+        <v>227</v>
+      </c>
+      <c r="J9" t="s">
+        <v>207</v>
+      </c>
+      <c r="K9" t="s">
+        <v>208</v>
+      </c>
+      <c r="L9" t="s">
+        <v>209</v>
+      </c>
+      <c r="M9" t="s">
+        <v>203</v>
+      </c>
+      <c r="N9" t="s">
         <v>210</v>
       </c>
-      <c r="G9" t="s">
-        <v>171</v>
-      </c>
-      <c r="H9" t="s">
-        <v>202</v>
-      </c>
-      <c r="I9" t="s">
-        <v>224</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="O9" t="s">
+        <v>211</v>
+      </c>
+      <c r="P9" t="s">
         <v>204</v>
       </c>
-      <c r="K9" t="s">
-        <v>205</v>
-      </c>
-      <c r="L9" t="s">
-        <v>206</v>
-      </c>
-      <c r="M9" t="s">
-        <v>200</v>
-      </c>
-      <c r="N9" t="s">
-        <v>207</v>
-      </c>
-      <c r="O9" t="s">
-        <v>208</v>
-      </c>
-      <c r="P9" t="s">
-        <v>201</v>
-      </c>
       <c r="Q9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="R9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="S9" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="T9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -6090,58 +6151,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F10" t="s">
+        <v>204</v>
+      </c>
+      <c r="G10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H10" t="s">
+        <v>205</v>
+      </c>
+      <c r="I10" t="s">
+        <v>230</v>
+      </c>
+      <c r="J10" t="s">
         <v>207</v>
       </c>
-      <c r="F10" t="s">
-        <v>201</v>
-      </c>
-      <c r="G10" t="s">
-        <v>171</v>
-      </c>
-      <c r="H10" t="s">
-        <v>202</v>
-      </c>
-      <c r="I10" t="s">
-        <v>227</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
+        <v>208</v>
+      </c>
+      <c r="L10" t="s">
+        <v>209</v>
+      </c>
+      <c r="M10" t="s">
+        <v>203</v>
+      </c>
+      <c r="N10" t="s">
+        <v>210</v>
+      </c>
+      <c r="O10" t="s">
+        <v>211</v>
+      </c>
+      <c r="P10" t="s">
         <v>204</v>
       </c>
-      <c r="K10" t="s">
-        <v>205</v>
-      </c>
-      <c r="L10" t="s">
-        <v>206</v>
-      </c>
-      <c r="M10" t="s">
-        <v>200</v>
-      </c>
-      <c r="N10" t="s">
-        <v>207</v>
-      </c>
-      <c r="O10" t="s">
-        <v>208</v>
-      </c>
-      <c r="P10" t="s">
-        <v>201</v>
-      </c>
       <c r="Q10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="R10" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="S10" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="T10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -6149,58 +6210,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F11" t="s">
+        <v>215</v>
+      </c>
+      <c r="G11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I11" t="s">
+        <v>227</v>
+      </c>
+      <c r="J11" t="s">
+        <v>207</v>
+      </c>
+      <c r="K11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L11" t="s">
+        <v>209</v>
+      </c>
+      <c r="M11" t="s">
+        <v>203</v>
+      </c>
+      <c r="N11" t="s">
+        <v>210</v>
+      </c>
+      <c r="O11" t="s">
+        <v>211</v>
+      </c>
+      <c r="P11" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q11" t="s">
         <v>212</v>
       </c>
-      <c r="G11" t="s">
-        <v>171</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="R11" t="s">
+        <v>213</v>
+      </c>
+      <c r="S11" t="s">
+        <v>214</v>
+      </c>
+      <c r="T11" t="s">
         <v>215</v>
-      </c>
-      <c r="I11" t="s">
-        <v>224</v>
-      </c>
-      <c r="J11" t="s">
-        <v>204</v>
-      </c>
-      <c r="K11" t="s">
-        <v>205</v>
-      </c>
-      <c r="L11" t="s">
-        <v>206</v>
-      </c>
-      <c r="M11" t="s">
-        <v>200</v>
-      </c>
-      <c r="N11" t="s">
-        <v>207</v>
-      </c>
-      <c r="O11" t="s">
-        <v>208</v>
-      </c>
-      <c r="P11" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>209</v>
-      </c>
-      <c r="R11" t="s">
-        <v>210</v>
-      </c>
-      <c r="S11" t="s">
-        <v>211</v>
-      </c>
-      <c r="T11" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -6208,58 +6269,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" t="s">
+        <v>234</v>
+      </c>
+      <c r="E12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" t="s">
+        <v>204</v>
+      </c>
+      <c r="G12" t="s">
+        <v>174</v>
+      </c>
+      <c r="H12" t="s">
+        <v>218</v>
+      </c>
+      <c r="I12" t="s">
         <v>230</v>
       </c>
-      <c r="D12" t="s">
-        <v>231</v>
-      </c>
-      <c r="E12" t="s">
-        <v>200</v>
-      </c>
-      <c r="F12" t="s">
-        <v>201</v>
-      </c>
-      <c r="G12" t="s">
-        <v>171</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
+        <v>207</v>
+      </c>
+      <c r="K12" t="s">
+        <v>208</v>
+      </c>
+      <c r="L12" t="s">
+        <v>209</v>
+      </c>
+      <c r="M12" t="s">
+        <v>203</v>
+      </c>
+      <c r="N12" t="s">
+        <v>210</v>
+      </c>
+      <c r="O12" t="s">
+        <v>211</v>
+      </c>
+      <c r="P12" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>212</v>
+      </c>
+      <c r="R12" t="s">
+        <v>213</v>
+      </c>
+      <c r="S12" t="s">
+        <v>214</v>
+      </c>
+      <c r="T12" t="s">
         <v>215</v>
-      </c>
-      <c r="I12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J12" t="s">
-        <v>204</v>
-      </c>
-      <c r="K12" t="s">
-        <v>205</v>
-      </c>
-      <c r="L12" t="s">
-        <v>206</v>
-      </c>
-      <c r="M12" t="s">
-        <v>200</v>
-      </c>
-      <c r="N12" t="s">
-        <v>207</v>
-      </c>
-      <c r="O12" t="s">
-        <v>208</v>
-      </c>
-      <c r="P12" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>209</v>
-      </c>
-      <c r="R12" t="s">
-        <v>210</v>
-      </c>
-      <c r="S12" t="s">
-        <v>211</v>
-      </c>
-      <c r="T12" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -6267,58 +6328,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D13" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F13" t="s">
+        <v>215</v>
+      </c>
+      <c r="G13" t="s">
+        <v>174</v>
+      </c>
+      <c r="H13" t="s">
+        <v>221</v>
+      </c>
+      <c r="I13" t="s">
+        <v>227</v>
+      </c>
+      <c r="J13" t="s">
+        <v>207</v>
+      </c>
+      <c r="K13" t="s">
+        <v>208</v>
+      </c>
+      <c r="L13" t="s">
+        <v>209</v>
+      </c>
+      <c r="M13" t="s">
+        <v>203</v>
+      </c>
+      <c r="N13" t="s">
+        <v>210</v>
+      </c>
+      <c r="O13" t="s">
+        <v>211</v>
+      </c>
+      <c r="P13" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q13" t="s">
         <v>212</v>
       </c>
-      <c r="G13" t="s">
-        <v>171</v>
-      </c>
-      <c r="H13" t="s">
-        <v>218</v>
-      </c>
-      <c r="I13" t="s">
-        <v>224</v>
-      </c>
-      <c r="J13" t="s">
-        <v>204</v>
-      </c>
-      <c r="K13" t="s">
-        <v>205</v>
-      </c>
-      <c r="L13" t="s">
-        <v>206</v>
-      </c>
-      <c r="M13" t="s">
-        <v>200</v>
-      </c>
-      <c r="N13" t="s">
-        <v>207</v>
-      </c>
-      <c r="O13" t="s">
-        <v>208</v>
-      </c>
-      <c r="P13" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>209</v>
-      </c>
       <c r="R13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="S13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="T13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -6326,58 +6387,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D14" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E14" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G14" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H14" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I14" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J14" t="s">
+        <v>207</v>
+      </c>
+      <c r="K14" t="s">
+        <v>208</v>
+      </c>
+      <c r="L14" t="s">
+        <v>209</v>
+      </c>
+      <c r="M14" t="s">
+        <v>203</v>
+      </c>
+      <c r="N14" t="s">
+        <v>210</v>
+      </c>
+      <c r="O14" t="s">
+        <v>211</v>
+      </c>
+      <c r="P14" t="s">
         <v>204</v>
       </c>
-      <c r="K14" t="s">
-        <v>205</v>
-      </c>
-      <c r="L14" t="s">
-        <v>206</v>
-      </c>
-      <c r="M14" t="s">
-        <v>200</v>
-      </c>
-      <c r="N14" t="s">
-        <v>207</v>
-      </c>
-      <c r="O14" t="s">
-        <v>208</v>
-      </c>
-      <c r="P14" t="s">
-        <v>201</v>
-      </c>
       <c r="Q14" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="R14" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="S14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="T14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -6385,58 +6446,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D15" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E15" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G15" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H15" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I15" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J15" t="s">
+        <v>207</v>
+      </c>
+      <c r="K15" t="s">
+        <v>208</v>
+      </c>
+      <c r="L15" t="s">
+        <v>209</v>
+      </c>
+      <c r="M15" t="s">
+        <v>203</v>
+      </c>
+      <c r="N15" t="s">
+        <v>210</v>
+      </c>
+      <c r="O15" t="s">
+        <v>211</v>
+      </c>
+      <c r="P15" t="s">
         <v>204</v>
       </c>
-      <c r="K15" t="s">
-        <v>205</v>
-      </c>
-      <c r="L15" t="s">
-        <v>206</v>
-      </c>
-      <c r="M15" t="s">
-        <v>200</v>
-      </c>
-      <c r="N15" t="s">
-        <v>207</v>
-      </c>
-      <c r="O15" t="s">
-        <v>208</v>
-      </c>
-      <c r="P15" t="s">
-        <v>201</v>
-      </c>
       <c r="Q15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="R15" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="S15" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="T15" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -6444,58 +6505,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D16" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E16" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F16" t="s">
+        <v>214</v>
+      </c>
+      <c r="G16" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" t="s">
+        <v>224</v>
+      </c>
+      <c r="I16" t="s">
+        <v>230</v>
+      </c>
+      <c r="J16" t="s">
+        <v>207</v>
+      </c>
+      <c r="K16" t="s">
+        <v>208</v>
+      </c>
+      <c r="L16" t="s">
+        <v>209</v>
+      </c>
+      <c r="M16" t="s">
+        <v>203</v>
+      </c>
+      <c r="N16" t="s">
+        <v>210</v>
+      </c>
+      <c r="O16" t="s">
         <v>211</v>
       </c>
-      <c r="G16" t="s">
-        <v>171</v>
-      </c>
-      <c r="H16" t="s">
-        <v>221</v>
-      </c>
-      <c r="I16" t="s">
-        <v>227</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="P16" t="s">
         <v>204</v>
       </c>
-      <c r="K16" t="s">
-        <v>205</v>
-      </c>
-      <c r="L16" t="s">
-        <v>206</v>
-      </c>
-      <c r="M16" t="s">
-        <v>200</v>
-      </c>
-      <c r="N16" t="s">
-        <v>207</v>
-      </c>
-      <c r="O16" t="s">
-        <v>208</v>
-      </c>
-      <c r="P16" t="s">
-        <v>201</v>
-      </c>
       <c r="Q16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="R16" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="S16" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="T16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -6524,16 +6585,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6547,7 +6608,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -6572,16 +6633,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6595,10 +6656,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6606,16 +6667,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6629,10 +6690,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6646,10 +6707,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F8" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6663,10 +6724,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F9" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6674,16 +6735,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D10" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E10" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F10" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6697,10 +6758,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F11" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6714,10 +6775,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F12" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -6750,34 +6811,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="J1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="M1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -6788,10 +6849,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -6803,7 +6864,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -6825,13 +6886,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -6842,40 +6903,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K4" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -6898,13 +6959,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M5" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -6918,22 +6979,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -6947,22 +7008,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L7" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -6976,22 +7037,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L8" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7005,22 +7066,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L9" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M9" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7034,22 +7095,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L10" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M10" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7063,22 +7124,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L11" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M11" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7092,22 +7153,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="L12" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M12" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7115,31 +7176,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L13" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N13" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -7147,10 +7208,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -7159,7 +7220,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -7167,10 +7228,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>7</v>
@@ -7179,7 +7240,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7187,10 +7248,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>16</v>
@@ -7199,7 +7260,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7207,19 +7268,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F17" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="N17" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7227,10 +7288,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>59</v>
@@ -7239,7 +7300,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7247,10 +7308,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>66</v>
@@ -7259,7 +7320,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7267,10 +7328,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>16</v>
@@ -7279,7 +7340,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7287,19 +7348,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E21" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F21" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="N21" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -7307,16 +7368,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -7324,10 +7385,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>25</v>
@@ -7341,10 +7402,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>25</v>
@@ -7358,10 +7419,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>34</v>
@@ -7375,10 +7436,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>34</v>
@@ -7392,10 +7453,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>43</v>
@@ -7409,10 +7470,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>43</v>
@@ -7426,10 +7487,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>43</v>
@@ -7438,10 +7499,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N29" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -7449,10 +7510,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>52</v>
@@ -7466,10 +7527,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>52</v>
@@ -7483,10 +7544,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>52</v>
@@ -7495,10 +7556,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N32" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -7534,31 +7595,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="K1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7584,10 +7645,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="I2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -7601,34 +7662,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -7639,31 +7700,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D4" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E4" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F4" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="H4" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="I4" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J4" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -7671,7 +7732,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -7695,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -7703,7 +7764,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7727,7 +7788,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -7735,7 +7796,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -7759,7 +7820,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -7767,7 +7828,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -7791,7 +7852,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -7822,16 +7883,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7848,7 +7909,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -7861,10 +7922,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -7875,13 +7936,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D4" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E4" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7889,7 +7950,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -7898,7 +7959,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7906,7 +7967,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -7915,7 +7976,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7923,7 +7984,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -7932,7 +7993,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7940,7 +8001,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7949,7 +8010,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7982,25 +8043,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="H1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8014,16 +8075,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="G2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -8034,25 +8095,25 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -8060,39 +8121,39 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C4" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D4" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F4" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G4" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="H4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D5" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8104,21 +8165,21 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D6" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8130,21 +8191,21 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8156,21 +8217,21 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D8" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -8182,21 +8243,21 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D9" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -8208,21 +8269,21 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D10" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8234,21 +8295,21 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D11" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -8260,21 +8321,21 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D12" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -8286,21 +8347,21 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D13" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -8312,21 +8373,21 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D14" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -8338,21 +8399,21 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D15" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -8364,24 +8425,24 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D16" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E16" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -8390,24 +8451,24 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
+        <v>445</v>
+      </c>
+      <c r="D17" t="s">
         <v>442</v>
       </c>
-      <c r="D17" t="s">
-        <v>439</v>
-      </c>
       <c r="E17" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -8416,24 +8477,24 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D18" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E18" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -8442,24 +8503,24 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D19" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E19" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -8468,24 +8529,24 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D20" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E20" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -8494,24 +8555,24 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D21" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E21" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -8520,24 +8581,24 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D22" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E22" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -8546,24 +8607,24 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D23" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E23" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -8572,24 +8633,24 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
+        <v>467</v>
+      </c>
+      <c r="D24" t="s">
         <v>464</v>
       </c>
-      <c r="D24" t="s">
-        <v>461</v>
-      </c>
       <c r="E24" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -8598,24 +8659,24 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D25" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E25" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -8624,21 +8685,21 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B26">
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D26" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E26" t="s">
         <v>20</v>
@@ -8650,21 +8711,21 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B27">
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D27" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E27" t="s">
         <v>11</v>
@@ -8676,21 +8737,21 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D28" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E28" t="s">
         <v>2</v>
@@ -8702,24 +8763,24 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D29" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E29" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -8728,7 +8789,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -8736,13 +8797,13 @@
         <v>1011</v>
       </c>
       <c r="C30" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D30" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E30" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -8751,7 +8812,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -1619,28 +1619,28 @@
     <t>扑克游玩模式处于激活状态的累计秒数</t>
   </si>
   <si>
-    <t>TypingInputCount</t>
-  </si>
-  <si>
-    <t>累计打字输入次数</t>
-  </si>
-  <si>
-    <t>STAT_TYPING_INPUT_COUNT</t>
-  </si>
-  <si>
-    <t>真实全局打字输入次数；不受未来筹码产出倍率影响，目前是打字和筹码1比1，但有频率上限锁（打字包括鼠标点击）</t>
-  </si>
-  <si>
-    <t>TypingChipsEarned</t>
-  </si>
-  <si>
-    <t>累计打字获得筹码</t>
+    <t>GlobalInputCount</t>
+  </si>
+  <si>
+    <t>累计全局输入次数（键鼠）</t>
+  </si>
+  <si>
+    <t>STAT_GLOBAL_INPUT_COUNT</t>
+  </si>
+  <si>
+    <t>真实全局输入次数；不受未来筹码产出倍率影响，目前是打字和筹码1比1，但有频率上限锁（打字包括鼠标点击）</t>
+  </si>
+  <si>
+    <t>GlobalInputChipsEarned</t>
+  </si>
+  <si>
+    <t>累计全局输入获得筹码</t>
   </si>
   <si>
     <t>Chips</t>
   </si>
   <si>
-    <t>STAT_TYPING_CHIPS_EARNED</t>
+    <t>STAT_GLOBAL_INPUT_CHIPS_EARNED</t>
   </si>
   <si>
     <t>仅累计 GlobalInputTracker 的真实打字奖励筹码（包括鼠标点击）</t>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -2117,7 +2117,7 @@
     <t>STAT_PEAK_HALF_HOUR_INPUT_CHIPS_EARNED</t>
   </si>
   <si>
-    <t>每自然半小时内，通过打字获得的最高筹码数（本游戏包括鼠标）</t>
+    <t>游戏运行期间，按系统本地时间的自然半小时分段累计键鼠获得的筹码；首尾分段可能不足 30 分钟。</t>
   </si>
 </sst>
 </file>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="9"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="700">
   <si>
     <t>Dog</t>
   </si>
@@ -500,7 +500,7 @@
     <t>名称</t>
   </si>
   <si>
-    <t>value</t>
+    <t>value备注</t>
   </si>
   <si>
     <t>描述</t>
@@ -534,6 +534,24 @@
   </si>
   <si>
     <t>统计时，玩家实际行为乘以倍率作为统计值记录，例如玩家获得1个筹码，倍率是10的话，记为10个筹码</t>
+  </si>
+  <si>
+    <t>BlindBoxBacklogClaimDelaySeconds</t>
+  </si>
+  <si>
+    <t>积压盲盒展示时短间隔时间</t>
+  </si>
+  <si>
+    <t>秒，实际使用时需要受到BlindBoxTimeScale影响，为了不让玩家对于盲盒间隔的心里预期剧烈变化因此设计了该值</t>
+  </si>
+  <si>
+    <t>BlindBoxPostNewbieDelaySeconds</t>
+  </si>
+  <si>
+    <t>新手与正式盲盒的间隔时间</t>
+  </si>
+  <si>
+    <t>秒，新手阶段结束后与第一个正式盲盒的间隔时间</t>
   </si>
   <si>
     <t>IconName</t>
@@ -3690,28 +3708,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="C1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="F1" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="G1" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="H1" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="I1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3728,16 +3746,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F2" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -3748,28 +3766,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3777,1333 +3795,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C4" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D4" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E4" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F4" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="G4" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="H4" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="I4" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D5" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="E5" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="F5" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G5" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="D6" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="E6" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F6" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G6" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D7" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E7" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="F7" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G7" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D8" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="E8" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="F8" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G8" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D9" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E9" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F9" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G9" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D10" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="E10" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F10" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G10" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="D11" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E11" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F11" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G11" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="D12" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="E12" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F12" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G12" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D13" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="E13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F13" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G13" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="D14" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="E14" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F14" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G14" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D15" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="E15" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F15" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G15" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="D16" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="E16" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F16" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G16" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="D17" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E17" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F17" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G17" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="D18" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E18" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F18" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G18" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="D19" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="E19" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F19" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G19" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D20" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E20" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F20" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G20" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D21" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="E21" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F21" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G21" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="D22" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="E22" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F22" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G22" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="D23" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="E23" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F23" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G23" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D24" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E24" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F24" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G24" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D25" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="E25" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F25" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G25" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="D26" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="E26" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F26" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G26" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="D27" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="E27" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F27" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G27" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="D28" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="E28" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F28" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G28" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="D29" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="E29" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F29" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G29" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="D30" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="E30" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F30" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G30" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="D31" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="E31" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F31" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G31" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="D32" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="E32" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F32" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G32" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="D33" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E33" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F33" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G33" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="D34" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E34" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F34" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G34" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="D35" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="E35" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F35" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G35" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D36" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="E36" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F36" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G36" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="D37" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="E37" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F37" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G37" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="D38" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="E38" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F38" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G38" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D39" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="E39" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F39" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G39" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="D40" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="E40" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F40" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G40" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="D41" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="E41" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F41" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G41" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="D42" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="E42" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F42" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G42" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="D43" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="E43" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F43" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G43" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="D44" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="E44" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F44" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G44" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D45" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="E45" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F45" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G45" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="D46" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="E46" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F46" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G46" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="D47" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="E47" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F47" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G47" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="D48" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="E48" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F48" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G48" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="D49" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="E49" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F49" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G49" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5111,25 +5129,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="D50" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E50" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F50" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="G50" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5137,25 +5155,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="D51" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="E51" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F51" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="G51" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -5509,8 +5527,8 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="21.9166666666667" customWidth="1"/>
-    <col min="2" max="2" width="19.8333333333333" customWidth="1"/>
+    <col min="1" max="1" width="36.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="22.4166666666667" customWidth="1"/>
     <col min="5" max="5" width="84.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5594,17 +5612,38 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="2">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="2">
+        <v>60</v>
+      </c>
+      <c r="E7" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2"/>
@@ -5664,55 +5703,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="J1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="K1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="L1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="M1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="N1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="O1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="P1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="Q1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="R1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="S1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="T1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -5783,10 +5822,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -5800,55 +5839,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F4" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="H4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I4" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="J4" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="K4" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="L4" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="M4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="N4" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="O4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="P4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Q4" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="R4" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="S4" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="T4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -5856,58 +5895,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E5" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F5" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G5" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H5" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="I5" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="J5" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="K5" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L5" t="s">
+        <v>215</v>
+      </c>
+      <c r="M5" t="s">
         <v>209</v>
       </c>
-      <c r="M5" t="s">
-        <v>203</v>
-      </c>
       <c r="N5" t="s">
+        <v>216</v>
+      </c>
+      <c r="O5" t="s">
+        <v>217</v>
+      </c>
+      <c r="P5" t="s">
         <v>210</v>
       </c>
-      <c r="O5" t="s">
-        <v>211</v>
-      </c>
-      <c r="P5" t="s">
-        <v>204</v>
-      </c>
       <c r="Q5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="R5" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="S5" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="T5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -5915,58 +5954,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F6" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I6" t="s">
+        <v>212</v>
+      </c>
+      <c r="J6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K6" t="s">
+        <v>214</v>
+      </c>
+      <c r="L6" t="s">
+        <v>215</v>
+      </c>
+      <c r="M6" t="s">
+        <v>209</v>
+      </c>
+      <c r="N6" t="s">
         <v>216</v>
       </c>
-      <c r="D6" t="s">
+      <c r="O6" t="s">
         <v>217</v>
       </c>
-      <c r="E6" t="s">
-        <v>203</v>
-      </c>
-      <c r="F6" t="s">
-        <v>212</v>
-      </c>
-      <c r="G6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="P6" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q6" t="s">
         <v>218</v>
       </c>
-      <c r="I6" t="s">
-        <v>206</v>
-      </c>
-      <c r="J6" t="s">
-        <v>207</v>
-      </c>
-      <c r="K6" t="s">
-        <v>208</v>
-      </c>
-      <c r="L6" t="s">
-        <v>209</v>
-      </c>
-      <c r="M6" t="s">
-        <v>203</v>
-      </c>
-      <c r="N6" t="s">
-        <v>210</v>
-      </c>
-      <c r="O6" t="s">
-        <v>211</v>
-      </c>
-      <c r="P6" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>212</v>
-      </c>
       <c r="R6" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="S6" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="T6" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -5974,58 +6013,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F7" t="s">
         <v>219</v>
       </c>
-      <c r="D7" t="s">
+      <c r="G7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H7" t="s">
+        <v>227</v>
+      </c>
+      <c r="I7" t="s">
+        <v>212</v>
+      </c>
+      <c r="J7" t="s">
+        <v>213</v>
+      </c>
+      <c r="K7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L7" t="s">
+        <v>215</v>
+      </c>
+      <c r="M7" t="s">
+        <v>209</v>
+      </c>
+      <c r="N7" t="s">
+        <v>216</v>
+      </c>
+      <c r="O7" t="s">
+        <v>217</v>
+      </c>
+      <c r="P7" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>218</v>
+      </c>
+      <c r="R7" t="s">
+        <v>219</v>
+      </c>
+      <c r="S7" t="s">
         <v>220</v>
       </c>
-      <c r="E7" t="s">
-        <v>203</v>
-      </c>
-      <c r="F7" t="s">
-        <v>213</v>
-      </c>
-      <c r="G7" t="s">
-        <v>174</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="T7" t="s">
         <v>221</v>
-      </c>
-      <c r="I7" t="s">
-        <v>206</v>
-      </c>
-      <c r="J7" t="s">
-        <v>207</v>
-      </c>
-      <c r="K7" t="s">
-        <v>208</v>
-      </c>
-      <c r="L7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M7" t="s">
-        <v>203</v>
-      </c>
-      <c r="N7" t="s">
-        <v>210</v>
-      </c>
-      <c r="O7" t="s">
-        <v>211</v>
-      </c>
-      <c r="P7" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>212</v>
-      </c>
-      <c r="R7" t="s">
-        <v>213</v>
-      </c>
-      <c r="S7" t="s">
-        <v>214</v>
-      </c>
-      <c r="T7" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -6033,58 +6072,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D8" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H8" t="s">
+        <v>230</v>
+      </c>
+      <c r="I8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J8" t="s">
+        <v>213</v>
+      </c>
+      <c r="K8" t="s">
+        <v>214</v>
+      </c>
+      <c r="L8" t="s">
+        <v>215</v>
+      </c>
+      <c r="M8" t="s">
+        <v>209</v>
+      </c>
+      <c r="N8" t="s">
+        <v>216</v>
+      </c>
+      <c r="O8" t="s">
+        <v>217</v>
+      </c>
+      <c r="P8" t="s">
         <v>210</v>
       </c>
-      <c r="F8" t="s">
-        <v>211</v>
-      </c>
-      <c r="G8" t="s">
-        <v>174</v>
-      </c>
-      <c r="H8" t="s">
-        <v>224</v>
-      </c>
-      <c r="I8" t="s">
-        <v>206</v>
-      </c>
-      <c r="J8" t="s">
-        <v>207</v>
-      </c>
-      <c r="K8" t="s">
-        <v>208</v>
-      </c>
-      <c r="L8" t="s">
-        <v>209</v>
-      </c>
-      <c r="M8" t="s">
-        <v>203</v>
-      </c>
-      <c r="N8" t="s">
-        <v>210</v>
-      </c>
-      <c r="O8" t="s">
-        <v>211</v>
-      </c>
-      <c r="P8" t="s">
-        <v>204</v>
-      </c>
       <c r="Q8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="R8" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="S8" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="T8" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6092,58 +6131,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D9" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J9" t="s">
         <v>213</v>
       </c>
-      <c r="G9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H9" t="s">
-        <v>205</v>
-      </c>
-      <c r="I9" t="s">
-        <v>227</v>
-      </c>
-      <c r="J9" t="s">
-        <v>207</v>
-      </c>
       <c r="K9" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L9" t="s">
+        <v>215</v>
+      </c>
+      <c r="M9" t="s">
         <v>209</v>
       </c>
-      <c r="M9" t="s">
-        <v>203</v>
-      </c>
       <c r="N9" t="s">
+        <v>216</v>
+      </c>
+      <c r="O9" t="s">
+        <v>217</v>
+      </c>
+      <c r="P9" t="s">
         <v>210</v>
       </c>
-      <c r="O9" t="s">
-        <v>211</v>
-      </c>
-      <c r="P9" t="s">
-        <v>204</v>
-      </c>
       <c r="Q9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="R9" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="S9" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="T9" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -6151,58 +6190,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D10" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F10" t="s">
         <v>210</v>
       </c>
-      <c r="F10" t="s">
-        <v>204</v>
-      </c>
       <c r="G10" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H10" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="I10" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J10" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="K10" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L10" t="s">
+        <v>215</v>
+      </c>
+      <c r="M10" t="s">
         <v>209</v>
       </c>
-      <c r="M10" t="s">
-        <v>203</v>
-      </c>
       <c r="N10" t="s">
+        <v>216</v>
+      </c>
+      <c r="O10" t="s">
+        <v>217</v>
+      </c>
+      <c r="P10" t="s">
         <v>210</v>
       </c>
-      <c r="O10" t="s">
-        <v>211</v>
-      </c>
-      <c r="P10" t="s">
-        <v>204</v>
-      </c>
       <c r="Q10" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="R10" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="S10" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="T10" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -6210,58 +6249,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D11" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E11" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G11" t="s">
+        <v>180</v>
+      </c>
+      <c r="H11" t="s">
+        <v>224</v>
+      </c>
+      <c r="I11" t="s">
+        <v>233</v>
+      </c>
+      <c r="J11" t="s">
+        <v>213</v>
+      </c>
+      <c r="K11" t="s">
+        <v>214</v>
+      </c>
+      <c r="L11" t="s">
         <v>215</v>
       </c>
-      <c r="G11" t="s">
-        <v>174</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="M11" t="s">
+        <v>209</v>
+      </c>
+      <c r="N11" t="s">
+        <v>216</v>
+      </c>
+      <c r="O11" t="s">
+        <v>217</v>
+      </c>
+      <c r="P11" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q11" t="s">
         <v>218</v>
       </c>
-      <c r="I11" t="s">
-        <v>227</v>
-      </c>
-      <c r="J11" t="s">
-        <v>207</v>
-      </c>
-      <c r="K11" t="s">
-        <v>208</v>
-      </c>
-      <c r="L11" t="s">
-        <v>209</v>
-      </c>
-      <c r="M11" t="s">
-        <v>203</v>
-      </c>
-      <c r="N11" t="s">
-        <v>210</v>
-      </c>
-      <c r="O11" t="s">
-        <v>211</v>
-      </c>
-      <c r="P11" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>212</v>
-      </c>
       <c r="R11" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="S11" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="T11" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -6269,58 +6308,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="D12" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E12" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F12" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G12" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I12" t="s">
+        <v>236</v>
+      </c>
+      <c r="J12" t="s">
+        <v>213</v>
+      </c>
+      <c r="K12" t="s">
+        <v>214</v>
+      </c>
+      <c r="L12" t="s">
+        <v>215</v>
+      </c>
+      <c r="M12" t="s">
+        <v>209</v>
+      </c>
+      <c r="N12" t="s">
+        <v>216</v>
+      </c>
+      <c r="O12" t="s">
+        <v>217</v>
+      </c>
+      <c r="P12" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q12" t="s">
         <v>218</v>
       </c>
-      <c r="I12" t="s">
-        <v>230</v>
-      </c>
-      <c r="J12" t="s">
-        <v>207</v>
-      </c>
-      <c r="K12" t="s">
-        <v>208</v>
-      </c>
-      <c r="L12" t="s">
-        <v>209</v>
-      </c>
-      <c r="M12" t="s">
-        <v>203</v>
-      </c>
-      <c r="N12" t="s">
-        <v>210</v>
-      </c>
-      <c r="O12" t="s">
-        <v>211</v>
-      </c>
-      <c r="P12" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>212</v>
-      </c>
       <c r="R12" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="S12" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="T12" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -6328,58 +6367,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D13" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E13" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G13" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" t="s">
+        <v>227</v>
+      </c>
+      <c r="I13" t="s">
+        <v>233</v>
+      </c>
+      <c r="J13" t="s">
+        <v>213</v>
+      </c>
+      <c r="K13" t="s">
+        <v>214</v>
+      </c>
+      <c r="L13" t="s">
         <v>215</v>
       </c>
-      <c r="G13" t="s">
-        <v>174</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="M13" t="s">
+        <v>209</v>
+      </c>
+      <c r="N13" t="s">
+        <v>216</v>
+      </c>
+      <c r="O13" t="s">
+        <v>217</v>
+      </c>
+      <c r="P13" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>218</v>
+      </c>
+      <c r="R13" t="s">
+        <v>219</v>
+      </c>
+      <c r="S13" t="s">
+        <v>220</v>
+      </c>
+      <c r="T13" t="s">
         <v>221</v>
-      </c>
-      <c r="I13" t="s">
-        <v>227</v>
-      </c>
-      <c r="J13" t="s">
-        <v>207</v>
-      </c>
-      <c r="K13" t="s">
-        <v>208</v>
-      </c>
-      <c r="L13" t="s">
-        <v>209</v>
-      </c>
-      <c r="M13" t="s">
-        <v>203</v>
-      </c>
-      <c r="N13" t="s">
-        <v>210</v>
-      </c>
-      <c r="O13" t="s">
-        <v>211</v>
-      </c>
-      <c r="P13" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>212</v>
-      </c>
-      <c r="R13" t="s">
-        <v>213</v>
-      </c>
-      <c r="S13" t="s">
-        <v>214</v>
-      </c>
-      <c r="T13" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -6387,58 +6426,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D14" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E14" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F14" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H14" t="s">
+        <v>227</v>
+      </c>
+      <c r="I14" t="s">
+        <v>236</v>
+      </c>
+      <c r="J14" t="s">
+        <v>213</v>
+      </c>
+      <c r="K14" t="s">
+        <v>214</v>
+      </c>
+      <c r="L14" t="s">
+        <v>215</v>
+      </c>
+      <c r="M14" t="s">
+        <v>209</v>
+      </c>
+      <c r="N14" t="s">
+        <v>216</v>
+      </c>
+      <c r="O14" t="s">
+        <v>217</v>
+      </c>
+      <c r="P14" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>218</v>
+      </c>
+      <c r="R14" t="s">
+        <v>219</v>
+      </c>
+      <c r="S14" t="s">
+        <v>220</v>
+      </c>
+      <c r="T14" t="s">
         <v>221</v>
-      </c>
-      <c r="I14" t="s">
-        <v>230</v>
-      </c>
-      <c r="J14" t="s">
-        <v>207</v>
-      </c>
-      <c r="K14" t="s">
-        <v>208</v>
-      </c>
-      <c r="L14" t="s">
-        <v>209</v>
-      </c>
-      <c r="M14" t="s">
-        <v>203</v>
-      </c>
-      <c r="N14" t="s">
-        <v>210</v>
-      </c>
-      <c r="O14" t="s">
-        <v>211</v>
-      </c>
-      <c r="P14" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>212</v>
-      </c>
-      <c r="R14" t="s">
-        <v>213</v>
-      </c>
-      <c r="S14" t="s">
-        <v>214</v>
-      </c>
-      <c r="T14" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -6446,58 +6485,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D15" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E15" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F15" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H15" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="I15" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="J15" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="K15" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L15" t="s">
+        <v>215</v>
+      </c>
+      <c r="M15" t="s">
         <v>209</v>
       </c>
-      <c r="M15" t="s">
-        <v>203</v>
-      </c>
       <c r="N15" t="s">
+        <v>216</v>
+      </c>
+      <c r="O15" t="s">
+        <v>217</v>
+      </c>
+      <c r="P15" t="s">
         <v>210</v>
       </c>
-      <c r="O15" t="s">
-        <v>211</v>
-      </c>
-      <c r="P15" t="s">
-        <v>204</v>
-      </c>
       <c r="Q15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="R15" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="S15" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="T15" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -6505,58 +6544,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D16" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E16" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F16" t="s">
+        <v>220</v>
+      </c>
+      <c r="G16" t="s">
+        <v>180</v>
+      </c>
+      <c r="H16" t="s">
+        <v>230</v>
+      </c>
+      <c r="I16" t="s">
+        <v>236</v>
+      </c>
+      <c r="J16" t="s">
+        <v>213</v>
+      </c>
+      <c r="K16" t="s">
         <v>214</v>
       </c>
-      <c r="G16" t="s">
-        <v>174</v>
-      </c>
-      <c r="H16" t="s">
-        <v>224</v>
-      </c>
-      <c r="I16" t="s">
-        <v>230</v>
-      </c>
-      <c r="J16" t="s">
-        <v>207</v>
-      </c>
-      <c r="K16" t="s">
-        <v>208</v>
-      </c>
       <c r="L16" t="s">
+        <v>215</v>
+      </c>
+      <c r="M16" t="s">
         <v>209</v>
       </c>
-      <c r="M16" t="s">
-        <v>203</v>
-      </c>
       <c r="N16" t="s">
+        <v>216</v>
+      </c>
+      <c r="O16" t="s">
+        <v>217</v>
+      </c>
+      <c r="P16" t="s">
         <v>210</v>
       </c>
-      <c r="O16" t="s">
-        <v>211</v>
-      </c>
-      <c r="P16" t="s">
-        <v>204</v>
-      </c>
       <c r="Q16" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="R16" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="S16" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="T16" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -6585,16 +6624,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6608,7 +6647,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -6633,16 +6672,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D4" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E4" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F4" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6656,10 +6695,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F5" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6667,16 +6706,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="F6" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6690,10 +6729,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="F7" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6707,10 +6746,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="F8" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6724,10 +6763,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F9" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6735,16 +6774,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D10" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E10" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F10" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6758,10 +6797,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F11" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6775,10 +6814,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F12" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -6811,34 +6850,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="G1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="H1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="I1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="J1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="K1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="L1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="M1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="N1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -6849,10 +6888,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -6864,7 +6903,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -6886,13 +6925,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -6903,40 +6942,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D4" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E4" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F4" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G4" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="H4" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="I4" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="J4" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="K4" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="L4" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="M4" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="N4" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -6959,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L5" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M5" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -6979,22 +7018,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H6" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L6" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M6" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7008,22 +7047,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H7" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L7" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M7" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7037,22 +7076,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H8" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L8" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M8" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7066,22 +7105,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H9" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L9" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M9" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7095,22 +7134,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H10" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L10" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M10" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7124,22 +7163,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H11" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L11" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M11" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7153,22 +7192,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H12" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="L12" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="M12" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7176,31 +7215,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="G13" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H13" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L13" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="M13" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="N13" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -7208,10 +7247,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -7220,7 +7259,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -7228,10 +7267,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>7</v>
@@ -7240,7 +7279,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7248,10 +7287,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>16</v>
@@ -7260,7 +7299,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7268,19 +7307,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="F17" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N17" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7288,10 +7327,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>59</v>
@@ -7300,7 +7339,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7308,10 +7347,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>66</v>
@@ -7320,7 +7359,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7328,10 +7367,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>16</v>
@@ -7340,7 +7379,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7348,19 +7387,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E21" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="F21" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N21" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -7368,16 +7407,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -7385,10 +7424,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>25</v>
@@ -7402,10 +7441,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>25</v>
@@ -7419,10 +7458,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>34</v>
@@ -7436,10 +7475,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>34</v>
@@ -7453,10 +7492,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>43</v>
@@ -7470,10 +7509,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>43</v>
@@ -7487,10 +7526,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>43</v>
@@ -7499,10 +7538,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="N29" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -7510,10 +7549,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>52</v>
@@ -7527,10 +7566,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>52</v>
@@ -7544,10 +7583,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>52</v>
@@ -7556,10 +7595,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="N32" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -7595,31 +7634,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D1" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="G1" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="H1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I1" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="J1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="K1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7645,10 +7684,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="I2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -7662,34 +7701,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -7700,31 +7739,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D4" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E4" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F4" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="G4" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H4" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="I4" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J4" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="K4" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -7732,7 +7771,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -7756,7 +7795,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -7764,7 +7803,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -7788,7 +7827,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -7796,7 +7835,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -7820,7 +7859,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -7828,7 +7867,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -7852,7 +7891,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -7883,16 +7922,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="F1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7909,7 +7948,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -7922,10 +7961,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -7936,13 +7975,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D4" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="E4" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7950,7 +7989,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -7959,7 +7998,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7967,7 +8006,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -7976,7 +8015,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7984,7 +8023,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -7993,7 +8032,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8001,7 +8040,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8010,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8043,25 +8082,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="E1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F1" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="G1" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="H1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8075,16 +8114,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="G2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -8095,25 +8134,25 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -8121,39 +8160,39 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C4" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D4" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E4" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="F4" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="G4" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="H4" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D5" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8165,21 +8204,21 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D6" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8191,21 +8230,21 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="D7" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8217,21 +8256,21 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
+        <v>431</v>
+      </c>
+      <c r="D8" t="s">
         <v>425</v>
-      </c>
-      <c r="D8" t="s">
-        <v>419</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -8243,21 +8282,21 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="D9" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -8269,21 +8308,21 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="D10" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8295,21 +8334,21 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D11" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -8321,21 +8360,21 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="D12" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -8347,21 +8386,21 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D13" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -8373,21 +8412,21 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="D14" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -8399,21 +8438,21 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D15" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -8425,24 +8464,24 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D16" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E16" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -8451,24 +8490,24 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D17" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E17" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -8477,24 +8516,24 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
+        <v>454</v>
+      </c>
+      <c r="D18" t="s">
         <v>448</v>
       </c>
-      <c r="D18" t="s">
-        <v>442</v>
-      </c>
       <c r="E18" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -8503,24 +8542,24 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D19" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E19" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -8529,24 +8568,24 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D20" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E20" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -8555,24 +8594,24 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="D21" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E21" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -8581,24 +8620,24 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D22" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E22" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -8607,24 +8646,24 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D23" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="E23" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -8633,24 +8672,24 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D24" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="E24" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -8659,24 +8698,24 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
+        <v>476</v>
+      </c>
+      <c r="D25" t="s">
         <v>470</v>
       </c>
-      <c r="D25" t="s">
-        <v>464</v>
-      </c>
       <c r="E25" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -8685,21 +8724,21 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B26">
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D26" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E26" t="s">
         <v>20</v>
@@ -8711,21 +8750,21 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B27">
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D27" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E27" t="s">
         <v>11</v>
@@ -8737,21 +8776,21 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D28" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E28" t="s">
         <v>2</v>
@@ -8763,24 +8802,24 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
+        <v>486</v>
+      </c>
+      <c r="D29" t="s">
         <v>480</v>
       </c>
-      <c r="D29" t="s">
-        <v>474</v>
-      </c>
       <c r="E29" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -8789,7 +8828,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -8797,13 +8836,13 @@
         <v>1011</v>
       </c>
       <c r="C30" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D30" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E30" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -8812,7 +8851,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -5571,7 +5571,7 @@
         <v>158</v>
       </c>
       <c r="D3" s="2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>159</v>
@@ -5588,7 +5588,7 @@
         <v>158</v>
       </c>
       <c r="D4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>162</v>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -5571,7 +5571,7 @@
         <v>158</v>
       </c>
       <c r="D3" s="2">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>159</v>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="9"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -7783,7 +7783,7 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -7812,7 +7812,7 @@
         <v>80</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -7841,7 +7841,7 @@
         <v>81</v>
       </c>
       <c r="E7">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7870,7 +7870,7 @@
         <v>386</v>
       </c>
       <c r="D8">
-        <v>181</v>
+        <v>281</v>
       </c>
       <c r="E8">
         <v>0</v>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -7841,7 +7841,7 @@
         <v>81</v>
       </c>
       <c r="E7">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7870,13 +7870,13 @@
         <v>386</v>
       </c>
       <c r="D8">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>3</v>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="6"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -392,10 +392,10 @@
     <t>安全中文</t>
   </si>
   <si>
-    <t>JacksOrBetter</t>
-  </si>
-  <si>
-    <t>Jacks or Better</t>
+    <t>OnePair</t>
+  </si>
+  <si>
+    <t>One Pair</t>
   </si>
   <si>
     <t>Top Dogs</t>
@@ -1055,10 +1055,10 @@
     <t>看到坏牌</t>
   </si>
   <si>
-    <t>SawJacksOrBetter</t>
-  </si>
-  <si>
-    <t>看到高对</t>
+    <t>SawOnePair</t>
+  </si>
+  <si>
+    <t>看到一对</t>
   </si>
   <si>
     <t>SawTwoPair</t>
@@ -1736,16 +1736,16 @@
     <t>最终结算为坏牌的次数</t>
   </si>
   <si>
-    <t>PokerHandRankJacksOrBetterCount</t>
-  </si>
-  <si>
-    <t>高对次数</t>
-  </si>
-  <si>
-    <t>STAT_POKER_JACKS_OR_BETTER_COUNT</t>
-  </si>
-  <si>
-    <t>最终结算为高对的次数</t>
+    <t>PokerHandRankOnePairCount</t>
+  </si>
+  <si>
+    <t>一对次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_ONE_PAIR_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为一对的次数</t>
   </si>
   <si>
     <t>PokerHandRankTwoPairCount</t>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="9"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -506,7 +506,7 @@
     <t>描述</t>
   </si>
   <si>
-    <t>BlindBoxTimeScale</t>
+    <t>BlindBoxWaitDurationMultiplier</t>
   </si>
   <si>
     <t>等待盲盒时间倍率</t>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="862">
   <si>
     <t>Dog</t>
   </si>
@@ -552,6 +552,15 @@
   </si>
   <si>
     <t>秒，新手阶段结束后与第一个正式盲盒的间隔时间</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkTreeVisibleBannerCount </t>
+  </si>
+  <si>
+    <t>LinkTree最佳显示条目数量</t>
+  </si>
+  <si>
+    <t>未领取奖励的条目和固定条目数量之和不足该值只，以已领取奖励的条目填充占位</t>
   </si>
   <si>
     <t>IconName</t>
@@ -4188,28 +4197,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="F1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="G1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="H1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4226,16 +4235,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="F2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -4246,28 +4255,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4275,1333 +4284,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C4" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E4" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="F4" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="G4" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="H4" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="I4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="E5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>682</v>
+      </c>
+      <c r="D6" t="s">
+        <v>683</v>
+      </c>
+      <c r="E6" t="s">
+        <v>684</v>
+      </c>
+      <c r="F6" t="s">
         <v>679</v>
       </c>
-      <c r="D6" t="s">
-        <v>680</v>
-      </c>
-      <c r="E6" t="s">
-        <v>681</v>
-      </c>
-      <c r="F6" t="s">
-        <v>676</v>
-      </c>
       <c r="G6" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D7" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E7" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F7" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G7" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D8" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E8" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F8" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G8" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="D9" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="E9" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F9" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G9" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D10" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="E10" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F10" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G10" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="D11" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E11" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F11" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G11" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D12" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="E12" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F12" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G12" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D13" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="E13" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F13" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G13" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D14" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E14" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F14" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G14" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D15" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="E15" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F15" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G15" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D16" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="E16" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F16" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G16" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D17" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E17" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F17" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G17" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D18" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="E18" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F18" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G18" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D19" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E19" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F19" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G19" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D20" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E20" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F20" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G20" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D21" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E21" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F21" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G21" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D22" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="E22" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F22" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G22" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D23" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="E23" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F23" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G23" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D24" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="E24" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F24" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G24" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D25" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E25" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F25" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G25" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D26" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="E26" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F26" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G26" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="D27" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="E27" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F27" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G27" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D28" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="E28" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F28" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G28" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D29" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="E29" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F29" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G29" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D30" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E30" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F30" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G30" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D31" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="E31" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F31" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G31" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D32" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E32" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F32" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G32" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D33" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="E33" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F33" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G33" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="D34" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="E34" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F34" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G34" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D35" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="E35" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F35" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G35" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D36" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E36" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F36" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G36" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="D37" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="E37" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F37" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G37" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D38" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="E38" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F38" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G38" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D39" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="E39" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F39" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G39" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="D40" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E40" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F40" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G40" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D41" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E41" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F41" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G41" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="D42" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="E42" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F42" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G42" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D43" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E43" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F43" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G43" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D44" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="E44" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F44" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G44" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D45" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="E45" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F45" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G45" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D46" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E46" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F46" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G46" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D47" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E47" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F47" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G47" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="D48" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="E48" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F48" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G48" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D49" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="E49" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F49" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G49" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5609,25 +5618,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="D50" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="E50" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F50" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G50" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5635,25 +5644,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="D51" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="E51" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F51" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="G51" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -6126,9 +6135,21 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="2">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
@@ -6183,55 +6204,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="L1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="M1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="O1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="P1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="R1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="S1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="T1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6302,10 +6323,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6319,55 +6340,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="O4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="P4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="R4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="S4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="T4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6375,58 +6396,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I5" t="s">
+        <v>215</v>
+      </c>
+      <c r="J5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K5" t="s">
+        <v>217</v>
+      </c>
+      <c r="L5" t="s">
+        <v>218</v>
+      </c>
+      <c r="M5" t="s">
         <v>212</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
+        <v>219</v>
+      </c>
+      <c r="O5" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" t="s">
         <v>213</v>
       </c>
-      <c r="K5" t="s">
-        <v>214</v>
-      </c>
-      <c r="L5" t="s">
-        <v>215</v>
-      </c>
-      <c r="M5" t="s">
-        <v>209</v>
-      </c>
-      <c r="N5" t="s">
-        <v>216</v>
-      </c>
-      <c r="O5" t="s">
-        <v>217</v>
-      </c>
-      <c r="P5" t="s">
-        <v>210</v>
-      </c>
       <c r="Q5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -6434,58 +6455,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I6" t="s">
+        <v>215</v>
+      </c>
+      <c r="J6" t="s">
+        <v>216</v>
+      </c>
+      <c r="K6" t="s">
+        <v>217</v>
+      </c>
+      <c r="L6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M6" t="s">
+        <v>212</v>
+      </c>
+      <c r="N6" t="s">
+        <v>219</v>
+      </c>
+      <c r="O6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P6" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>221</v>
+      </c>
+      <c r="R6" t="s">
         <v>222</v>
       </c>
-      <c r="D6" t="s">
+      <c r="S6" t="s">
         <v>223</v>
       </c>
-      <c r="E6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F6" t="s">
-        <v>218</v>
-      </c>
-      <c r="G6" t="s">
-        <v>180</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="T6" t="s">
         <v>224</v>
-      </c>
-      <c r="I6" t="s">
-        <v>212</v>
-      </c>
-      <c r="J6" t="s">
-        <v>213</v>
-      </c>
-      <c r="K6" t="s">
-        <v>214</v>
-      </c>
-      <c r="L6" t="s">
-        <v>215</v>
-      </c>
-      <c r="M6" t="s">
-        <v>209</v>
-      </c>
-      <c r="N6" t="s">
-        <v>216</v>
-      </c>
-      <c r="O6" t="s">
-        <v>217</v>
-      </c>
-      <c r="P6" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>218</v>
-      </c>
-      <c r="R6" t="s">
-        <v>219</v>
-      </c>
-      <c r="S6" t="s">
-        <v>220</v>
-      </c>
-      <c r="T6" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -6493,58 +6514,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E7" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I7" t="s">
+        <v>215</v>
+      </c>
+      <c r="J7" t="s">
+        <v>216</v>
+      </c>
+      <c r="K7" t="s">
+        <v>217</v>
+      </c>
+      <c r="L7" t="s">
+        <v>218</v>
+      </c>
+      <c r="M7" t="s">
+        <v>212</v>
+      </c>
+      <c r="N7" t="s">
         <v>219</v>
       </c>
-      <c r="G7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H7" t="s">
-        <v>227</v>
-      </c>
-      <c r="I7" t="s">
-        <v>212</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="O7" t="s">
+        <v>220</v>
+      </c>
+      <c r="P7" t="s">
         <v>213</v>
       </c>
-      <c r="K7" t="s">
-        <v>214</v>
-      </c>
-      <c r="L7" t="s">
-        <v>215</v>
-      </c>
-      <c r="M7" t="s">
-        <v>209</v>
-      </c>
-      <c r="N7" t="s">
-        <v>216</v>
-      </c>
-      <c r="O7" t="s">
-        <v>217</v>
-      </c>
-      <c r="P7" t="s">
-        <v>210</v>
-      </c>
       <c r="Q7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -6552,58 +6573,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E8" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" t="s">
+        <v>220</v>
+      </c>
+      <c r="G8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" t="s">
+        <v>233</v>
+      </c>
+      <c r="I8" t="s">
+        <v>215</v>
+      </c>
+      <c r="J8" t="s">
         <v>216</v>
       </c>
-      <c r="F8" t="s">
+      <c r="K8" t="s">
         <v>217</v>
       </c>
-      <c r="G8" t="s">
-        <v>180</v>
-      </c>
-      <c r="H8" t="s">
-        <v>230</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
+        <v>218</v>
+      </c>
+      <c r="M8" t="s">
         <v>212</v>
       </c>
-      <c r="J8" t="s">
+      <c r="N8" t="s">
+        <v>219</v>
+      </c>
+      <c r="O8" t="s">
+        <v>220</v>
+      </c>
+      <c r="P8" t="s">
         <v>213</v>
       </c>
-      <c r="K8" t="s">
-        <v>214</v>
-      </c>
-      <c r="L8" t="s">
-        <v>215</v>
-      </c>
-      <c r="M8" t="s">
-        <v>209</v>
-      </c>
-      <c r="N8" t="s">
-        <v>216</v>
-      </c>
-      <c r="O8" t="s">
-        <v>217</v>
-      </c>
-      <c r="P8" t="s">
-        <v>210</v>
-      </c>
       <c r="Q8" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R8" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6611,58 +6632,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H9" t="s">
+        <v>214</v>
+      </c>
+      <c r="I9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J9" t="s">
+        <v>216</v>
+      </c>
+      <c r="K9" t="s">
+        <v>217</v>
+      </c>
+      <c r="L9" t="s">
+        <v>218</v>
+      </c>
+      <c r="M9" t="s">
+        <v>212</v>
+      </c>
+      <c r="N9" t="s">
         <v>219</v>
       </c>
-      <c r="G9" t="s">
-        <v>180</v>
-      </c>
-      <c r="H9" t="s">
-        <v>211</v>
-      </c>
-      <c r="I9" t="s">
-        <v>233</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="O9" t="s">
+        <v>220</v>
+      </c>
+      <c r="P9" t="s">
         <v>213</v>
       </c>
-      <c r="K9" t="s">
-        <v>214</v>
-      </c>
-      <c r="L9" t="s">
-        <v>215</v>
-      </c>
-      <c r="M9" t="s">
-        <v>209</v>
-      </c>
-      <c r="N9" t="s">
-        <v>216</v>
-      </c>
-      <c r="O9" t="s">
-        <v>217</v>
-      </c>
-      <c r="P9" t="s">
-        <v>210</v>
-      </c>
       <c r="Q9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R9" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S9" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -6670,58 +6691,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D10" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F10" t="s">
+        <v>213</v>
+      </c>
+      <c r="G10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" t="s">
+        <v>214</v>
+      </c>
+      <c r="I10" t="s">
+        <v>239</v>
+      </c>
+      <c r="J10" t="s">
         <v>216</v>
       </c>
-      <c r="F10" t="s">
-        <v>210</v>
-      </c>
-      <c r="G10" t="s">
-        <v>180</v>
-      </c>
-      <c r="H10" t="s">
-        <v>211</v>
-      </c>
-      <c r="I10" t="s">
-        <v>236</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
+        <v>217</v>
+      </c>
+      <c r="L10" t="s">
+        <v>218</v>
+      </c>
+      <c r="M10" t="s">
+        <v>212</v>
+      </c>
+      <c r="N10" t="s">
+        <v>219</v>
+      </c>
+      <c r="O10" t="s">
+        <v>220</v>
+      </c>
+      <c r="P10" t="s">
         <v>213</v>
       </c>
-      <c r="K10" t="s">
-        <v>214</v>
-      </c>
-      <c r="L10" t="s">
-        <v>215</v>
-      </c>
-      <c r="M10" t="s">
-        <v>209</v>
-      </c>
-      <c r="N10" t="s">
-        <v>216</v>
-      </c>
-      <c r="O10" t="s">
-        <v>217</v>
-      </c>
-      <c r="P10" t="s">
-        <v>210</v>
-      </c>
       <c r="Q10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S10" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -6729,58 +6750,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D11" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F11" t="s">
+        <v>224</v>
+      </c>
+      <c r="G11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H11" t="s">
+        <v>227</v>
+      </c>
+      <c r="I11" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" t="s">
+        <v>216</v>
+      </c>
+      <c r="K11" t="s">
+        <v>217</v>
+      </c>
+      <c r="L11" t="s">
+        <v>218</v>
+      </c>
+      <c r="M11" t="s">
+        <v>212</v>
+      </c>
+      <c r="N11" t="s">
+        <v>219</v>
+      </c>
+      <c r="O11" t="s">
+        <v>220</v>
+      </c>
+      <c r="P11" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q11" t="s">
         <v>221</v>
       </c>
-      <c r="G11" t="s">
-        <v>180</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="R11" t="s">
+        <v>222</v>
+      </c>
+      <c r="S11" t="s">
+        <v>223</v>
+      </c>
+      <c r="T11" t="s">
         <v>224</v>
-      </c>
-      <c r="I11" t="s">
-        <v>233</v>
-      </c>
-      <c r="J11" t="s">
-        <v>213</v>
-      </c>
-      <c r="K11" t="s">
-        <v>214</v>
-      </c>
-      <c r="L11" t="s">
-        <v>215</v>
-      </c>
-      <c r="M11" t="s">
-        <v>209</v>
-      </c>
-      <c r="N11" t="s">
-        <v>216</v>
-      </c>
-      <c r="O11" t="s">
-        <v>217</v>
-      </c>
-      <c r="P11" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>218</v>
-      </c>
-      <c r="R11" t="s">
-        <v>219</v>
-      </c>
-      <c r="S11" t="s">
-        <v>220</v>
-      </c>
-      <c r="T11" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -6788,58 +6809,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" t="s">
+        <v>243</v>
+      </c>
+      <c r="E12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" t="s">
+        <v>183</v>
+      </c>
+      <c r="H12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I12" t="s">
         <v>239</v>
       </c>
-      <c r="D12" t="s">
-        <v>240</v>
-      </c>
-      <c r="E12" t="s">
-        <v>209</v>
-      </c>
-      <c r="F12" t="s">
-        <v>210</v>
-      </c>
-      <c r="G12" t="s">
-        <v>180</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
+        <v>216</v>
+      </c>
+      <c r="K12" t="s">
+        <v>217</v>
+      </c>
+      <c r="L12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M12" t="s">
+        <v>212</v>
+      </c>
+      <c r="N12" t="s">
+        <v>219</v>
+      </c>
+      <c r="O12" t="s">
+        <v>220</v>
+      </c>
+      <c r="P12" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>221</v>
+      </c>
+      <c r="R12" t="s">
+        <v>222</v>
+      </c>
+      <c r="S12" t="s">
+        <v>223</v>
+      </c>
+      <c r="T12" t="s">
         <v>224</v>
-      </c>
-      <c r="I12" t="s">
-        <v>236</v>
-      </c>
-      <c r="J12" t="s">
-        <v>213</v>
-      </c>
-      <c r="K12" t="s">
-        <v>214</v>
-      </c>
-      <c r="L12" t="s">
-        <v>215</v>
-      </c>
-      <c r="M12" t="s">
-        <v>209</v>
-      </c>
-      <c r="N12" t="s">
-        <v>216</v>
-      </c>
-      <c r="O12" t="s">
-        <v>217</v>
-      </c>
-      <c r="P12" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>218</v>
-      </c>
-      <c r="R12" t="s">
-        <v>219</v>
-      </c>
-      <c r="S12" t="s">
-        <v>220</v>
-      </c>
-      <c r="T12" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -6847,58 +6868,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F13" t="s">
+        <v>224</v>
+      </c>
+      <c r="G13" t="s">
+        <v>183</v>
+      </c>
+      <c r="H13" t="s">
+        <v>230</v>
+      </c>
+      <c r="I13" t="s">
+        <v>236</v>
+      </c>
+      <c r="J13" t="s">
+        <v>216</v>
+      </c>
+      <c r="K13" t="s">
+        <v>217</v>
+      </c>
+      <c r="L13" t="s">
+        <v>218</v>
+      </c>
+      <c r="M13" t="s">
+        <v>212</v>
+      </c>
+      <c r="N13" t="s">
+        <v>219</v>
+      </c>
+      <c r="O13" t="s">
+        <v>220</v>
+      </c>
+      <c r="P13" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q13" t="s">
         <v>221</v>
       </c>
-      <c r="G13" t="s">
-        <v>180</v>
-      </c>
-      <c r="H13" t="s">
-        <v>227</v>
-      </c>
-      <c r="I13" t="s">
-        <v>233</v>
-      </c>
-      <c r="J13" t="s">
-        <v>213</v>
-      </c>
-      <c r="K13" t="s">
-        <v>214</v>
-      </c>
-      <c r="L13" t="s">
-        <v>215</v>
-      </c>
-      <c r="M13" t="s">
-        <v>209</v>
-      </c>
-      <c r="N13" t="s">
-        <v>216</v>
-      </c>
-      <c r="O13" t="s">
-        <v>217</v>
-      </c>
-      <c r="P13" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>218</v>
-      </c>
       <c r="R13" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S13" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -6906,58 +6927,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D14" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E14" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F14" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G14" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H14" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J14" t="s">
+        <v>216</v>
+      </c>
+      <c r="K14" t="s">
+        <v>217</v>
+      </c>
+      <c r="L14" t="s">
+        <v>218</v>
+      </c>
+      <c r="M14" t="s">
+        <v>212</v>
+      </c>
+      <c r="N14" t="s">
+        <v>219</v>
+      </c>
+      <c r="O14" t="s">
+        <v>220</v>
+      </c>
+      <c r="P14" t="s">
         <v>213</v>
       </c>
-      <c r="K14" t="s">
-        <v>214</v>
-      </c>
-      <c r="L14" t="s">
-        <v>215</v>
-      </c>
-      <c r="M14" t="s">
-        <v>209</v>
-      </c>
-      <c r="N14" t="s">
-        <v>216</v>
-      </c>
-      <c r="O14" t="s">
-        <v>217</v>
-      </c>
-      <c r="P14" t="s">
-        <v>210</v>
-      </c>
       <c r="Q14" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R14" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S14" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -6965,58 +6986,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D15" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F15" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G15" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="J15" t="s">
+        <v>216</v>
+      </c>
+      <c r="K15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L15" t="s">
+        <v>218</v>
+      </c>
+      <c r="M15" t="s">
+        <v>212</v>
+      </c>
+      <c r="N15" t="s">
+        <v>219</v>
+      </c>
+      <c r="O15" t="s">
+        <v>220</v>
+      </c>
+      <c r="P15" t="s">
         <v>213</v>
       </c>
-      <c r="K15" t="s">
-        <v>214</v>
-      </c>
-      <c r="L15" t="s">
-        <v>215</v>
-      </c>
-      <c r="M15" t="s">
-        <v>209</v>
-      </c>
-      <c r="N15" t="s">
-        <v>216</v>
-      </c>
-      <c r="O15" t="s">
-        <v>217</v>
-      </c>
-      <c r="P15" t="s">
-        <v>210</v>
-      </c>
       <c r="Q15" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R15" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S15" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T15" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -7024,58 +7045,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D16" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F16" t="s">
+        <v>223</v>
+      </c>
+      <c r="G16" t="s">
+        <v>183</v>
+      </c>
+      <c r="H16" t="s">
+        <v>233</v>
+      </c>
+      <c r="I16" t="s">
+        <v>239</v>
+      </c>
+      <c r="J16" t="s">
+        <v>216</v>
+      </c>
+      <c r="K16" t="s">
+        <v>217</v>
+      </c>
+      <c r="L16" t="s">
+        <v>218</v>
+      </c>
+      <c r="M16" t="s">
+        <v>212</v>
+      </c>
+      <c r="N16" t="s">
+        <v>219</v>
+      </c>
+      <c r="O16" t="s">
         <v>220</v>
       </c>
-      <c r="G16" t="s">
-        <v>180</v>
-      </c>
-      <c r="H16" t="s">
-        <v>230</v>
-      </c>
-      <c r="I16" t="s">
-        <v>236</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="P16" t="s">
         <v>213</v>
       </c>
-      <c r="K16" t="s">
-        <v>214</v>
-      </c>
-      <c r="L16" t="s">
-        <v>215</v>
-      </c>
-      <c r="M16" t="s">
-        <v>209</v>
-      </c>
-      <c r="N16" t="s">
-        <v>216</v>
-      </c>
-      <c r="O16" t="s">
-        <v>217</v>
-      </c>
-      <c r="P16" t="s">
-        <v>210</v>
-      </c>
       <c r="Q16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R16" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S16" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -7104,16 +7125,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7127,7 +7148,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7152,16 +7173,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7175,10 +7196,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7186,16 +7207,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7209,10 +7230,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7226,10 +7247,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F8" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7243,10 +7264,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7254,16 +7275,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E10" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7277,10 +7298,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7294,10 +7315,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F12" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -7330,34 +7351,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="J1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7368,10 +7389,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7383,7 +7404,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7405,13 +7426,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7422,40 +7443,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D4" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E4" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F4" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="H4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="K4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="M4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7478,13 +7499,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7498,22 +7519,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7527,22 +7548,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M7" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7556,22 +7577,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7585,22 +7606,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7614,22 +7635,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M10" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7643,22 +7664,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H11" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M11" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7672,22 +7693,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="L12" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M12" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7695,31 +7716,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H13" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L13" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N13" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -7727,10 +7748,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -7739,7 +7760,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -7747,10 +7768,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -7759,7 +7780,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7767,10 +7788,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -7779,7 +7800,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7787,19 +7808,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F17" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N17" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7807,10 +7828,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -7819,7 +7840,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7827,10 +7848,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -7839,7 +7860,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7847,10 +7868,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -7859,7 +7880,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7867,19 +7888,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E21" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F21" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N21" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -7887,16 +7908,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -7904,10 +7925,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -7921,10 +7942,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -7938,10 +7959,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -7955,10 +7976,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -7972,10 +7993,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -7989,10 +8010,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -8006,10 +8027,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -8018,10 +8039,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N29" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -8029,10 +8050,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -8046,10 +8067,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -8063,10 +8084,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -8075,10 +8096,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N32" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -8114,31 +8135,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="J1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8164,10 +8185,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -8181,34 +8202,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8219,31 +8240,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D4" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="G4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="H4" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="I4" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J4" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8251,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8275,7 +8296,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8283,7 +8304,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8307,7 +8328,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8315,7 +8336,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8339,7 +8360,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8347,7 +8368,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -8371,7 +8392,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -8402,16 +8423,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8428,7 +8449,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -8441,10 +8462,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8455,13 +8476,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E4" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8469,7 +8490,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8478,7 +8499,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8486,7 +8507,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -8495,7 +8516,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8503,7 +8524,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -8512,7 +8533,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8520,7 +8541,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8529,7 +8550,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8567,40 +8588,40 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="H1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="I1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="J1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="K1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -8614,16 +8635,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -8649,40 +8670,40 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="I3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="J3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8690,54 +8711,54 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="G4" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="H4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I4" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="K4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D5" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8749,36 +8770,36 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="I5" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="J5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K5" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L5" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M5" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D6" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8790,36 +8811,36 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I6" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="J6" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="K6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L6" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M6" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8831,36 +8852,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I7" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="J7" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="K7" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L7" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M7" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D8" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -8872,36 +8893,36 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="I8" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="J8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K8" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L8" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D9" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -8913,36 +8934,36 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="I9" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="J9" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K9" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="L9" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="M9" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D10" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8954,36 +8975,36 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="I10" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="J10" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K10" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="L10" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M10" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D11" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -8995,36 +9016,36 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="I11" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J11" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K11" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L11" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M11" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D12" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -9036,36 +9057,36 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="I12" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="J12" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K12" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L12" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="M12" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D13" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -9077,36 +9098,36 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="I13" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="J13" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K13" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="L13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M13" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D14" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -9118,36 +9139,36 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="I14" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="J14" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="K14" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="L14" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M14" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D15" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -9159,39 +9180,39 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="I15" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="J15" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="K15" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L15" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="M15" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D16" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E16" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -9200,39 +9221,39 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="I16" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="J16" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K16" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="L16" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="M16" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D17" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E17" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -9241,39 +9262,39 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="I17" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="J17" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="K17" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L17" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M17" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D18" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E18" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -9282,39 +9303,39 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="I18" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="J18" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="K18" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L18" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="M18" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D19" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E19" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -9323,39 +9344,39 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I19" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="J19" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K19" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="L19" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="M19" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D20" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E20" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -9364,39 +9385,39 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="I20" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="J20" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="K20" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="L20" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="M20" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D21" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E21" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -9405,39 +9426,39 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="I21" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="J21" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="K21" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="L21" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="M21" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D22" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E22" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -9446,39 +9467,39 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="I22" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="J22" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="K22" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="L22" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="M22" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D23" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E23" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -9487,39 +9508,39 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="I23" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="J23" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="K23" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="L23" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M23" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D24" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E24" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -9528,39 +9549,39 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="I24" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="J24" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="K24" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="L24" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="M24" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D25" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E25" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -9569,22 +9590,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="I25" t="s">
         <v>52</v>
       </c>
       <c r="J25" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="K25" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="L25" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="M25" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -9592,10 +9613,10 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D26" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -9607,22 +9628,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="I26" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="J26" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="K26" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L26" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="M26" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -9630,13 +9651,13 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D27" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E27" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -9645,36 +9666,36 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="I27" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="J27" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="K27" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L27" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="M27" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D28" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -9686,36 +9707,36 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="I28" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="J28" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="K28" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="L28" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="M28" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D29" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -9727,36 +9748,36 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="I29" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="J29" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="K29" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="L29" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="M29" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D30" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E30" t="s">
         <v>2</v>
@@ -9768,39 +9789,39 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="I30" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="J30" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="K30" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="L30" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M30" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D31" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E31" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -9809,22 +9830,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="I31" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="J31" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K31" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="L31" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="M31" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -9832,13 +9853,13 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D32" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E32" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -9847,22 +9868,22 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="I32" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="J32" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="K32" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="L32" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="M32" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -554,7 +554,7 @@
     <t>秒，新手阶段结束后与第一个正式盲盒的间隔时间</t>
   </si>
   <si>
-    <t xml:space="preserve">LinkTreeVisibleBannerCount </t>
+    <t>LinkTreeVisibleBannerCount</t>
   </si>
   <si>
     <t>LinkTree最佳显示条目数量</t>
@@ -6145,7 +6145,7 @@
         <v>107</v>
       </c>
       <c r="D8" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>174</v>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="865">
   <si>
     <t>Dog</t>
   </si>
@@ -561,6 +561,15 @@
   </si>
   <si>
     <t>未领取奖励的条目和固定条目数量之和不足该值只，以已领取奖励的条目填充占位</t>
+  </si>
+  <si>
+    <t>SteamPlaytimeDropLeadSecondsSteam</t>
+  </si>
+  <si>
+    <t>Steam提前准备盲盒的秒数</t>
+  </si>
+  <si>
+    <t>掉落提前秒数Steam游玩时间掉落相对本地盲盒展示时间提前请求的秒数，用于避开服务器计时边界。正式配置时改为60</t>
   </si>
   <si>
     <t>IconName</t>
@@ -4197,28 +4206,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="F1" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="G1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="H1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="I1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4235,16 +4244,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="F2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -4255,28 +4264,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4284,1333 +4293,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C4" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E4" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="F4" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="G4" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="H4" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="I4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="D5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="E5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="F5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G5" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>685</v>
+      </c>
+      <c r="D6" t="s">
+        <v>686</v>
+      </c>
+      <c r="E6" t="s">
+        <v>687</v>
+      </c>
+      <c r="F6" t="s">
         <v>682</v>
       </c>
-      <c r="D6" t="s">
-        <v>683</v>
-      </c>
-      <c r="E6" t="s">
-        <v>684</v>
-      </c>
-      <c r="F6" t="s">
-        <v>679</v>
-      </c>
       <c r="G6" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D7" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="E7" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="F7" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G7" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D8" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="E8" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="F8" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G8" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="D9" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E9" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F9" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G9" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D10" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="E10" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F10" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G10" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D11" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E11" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F11" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G11" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D12" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="E12" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F12" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G12" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D13" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="E13" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F13" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G13" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D14" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E14" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F14" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G14" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D15" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="E15" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F15" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G15" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="D16" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="E16" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F16" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G16" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="D17" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="E17" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F17" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G17" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D18" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E18" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F18" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G18" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D19" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E19" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F19" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G19" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D20" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E20" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F20" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G20" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D21" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="E21" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F21" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G21" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D22" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="E22" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F22" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G22" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D23" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="E23" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F23" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G23" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D24" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E24" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F24" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G24" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D25" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="E25" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F25" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G25" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D26" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="E26" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F26" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G26" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D27" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="E27" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F27" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G27" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D28" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="E28" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F28" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G28" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D29" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="E29" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F29" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G29" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D30" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="E30" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F30" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G30" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="D31" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E31" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F31" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G31" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D32" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="E32" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F32" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G32" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="D33" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="E33" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F33" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G33" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="D34" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E34" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F34" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G34" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D35" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="E35" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F35" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G35" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D36" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E36" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F36" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G36" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D37" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="E37" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F37" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G37" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D38" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="E38" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F38" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G38" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D39" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="E39" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F39" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G39" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D40" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="E40" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F40" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G40" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D41" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="E41" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F41" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G41" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="D42" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="E42" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F42" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G42" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D43" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E43" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F43" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G43" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D44" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="E44" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F44" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G44" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D45" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="E45" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F45" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G45" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D46" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="E46" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F46" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G46" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="D47" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E47" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F47" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G47" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D48" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="E48" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F48" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G48" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D49" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E49" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F49" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G49" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5618,25 +5627,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="D50" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E50" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F50" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G50" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5644,25 +5653,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="D51" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="E51" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F51" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="G51" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -6060,7 +6069,7 @@
         <v>158</v>
       </c>
       <c r="D3" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>159</v>
@@ -6152,11 +6161,21 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="2">
+        <v>60</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2"/>
@@ -6204,55 +6223,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="L1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="O1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="R1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="S1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="T1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6323,10 +6342,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6340,55 +6359,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="L4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="M4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="N4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="O4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="P4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="S4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="T4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6396,58 +6415,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I5" t="s">
+        <v>218</v>
+      </c>
+      <c r="J5" t="s">
+        <v>219</v>
+      </c>
+      <c r="K5" t="s">
+        <v>220</v>
+      </c>
+      <c r="L5" t="s">
+        <v>221</v>
+      </c>
+      <c r="M5" t="s">
         <v>215</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
+        <v>222</v>
+      </c>
+      <c r="O5" t="s">
+        <v>223</v>
+      </c>
+      <c r="P5" t="s">
         <v>216</v>
       </c>
-      <c r="K5" t="s">
-        <v>217</v>
-      </c>
-      <c r="L5" t="s">
-        <v>218</v>
-      </c>
-      <c r="M5" t="s">
-        <v>212</v>
-      </c>
-      <c r="N5" t="s">
-        <v>219</v>
-      </c>
-      <c r="O5" t="s">
-        <v>220</v>
-      </c>
-      <c r="P5" t="s">
-        <v>213</v>
-      </c>
       <c r="Q5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -6455,58 +6474,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F6" t="s">
+        <v>224</v>
+      </c>
+      <c r="G6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I6" t="s">
+        <v>218</v>
+      </c>
+      <c r="J6" t="s">
+        <v>219</v>
+      </c>
+      <c r="K6" t="s">
+        <v>220</v>
+      </c>
+      <c r="L6" t="s">
+        <v>221</v>
+      </c>
+      <c r="M6" t="s">
+        <v>215</v>
+      </c>
+      <c r="N6" t="s">
+        <v>222</v>
+      </c>
+      <c r="O6" t="s">
+        <v>223</v>
+      </c>
+      <c r="P6" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>224</v>
+      </c>
+      <c r="R6" t="s">
         <v>225</v>
       </c>
-      <c r="D6" t="s">
+      <c r="S6" t="s">
         <v>226</v>
       </c>
-      <c r="E6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F6" t="s">
-        <v>221</v>
-      </c>
-      <c r="G6" t="s">
-        <v>183</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="T6" t="s">
         <v>227</v>
-      </c>
-      <c r="I6" t="s">
-        <v>215</v>
-      </c>
-      <c r="J6" t="s">
-        <v>216</v>
-      </c>
-      <c r="K6" t="s">
-        <v>217</v>
-      </c>
-      <c r="L6" t="s">
-        <v>218</v>
-      </c>
-      <c r="M6" t="s">
-        <v>212</v>
-      </c>
-      <c r="N6" t="s">
-        <v>219</v>
-      </c>
-      <c r="O6" t="s">
-        <v>220</v>
-      </c>
-      <c r="P6" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>221</v>
-      </c>
-      <c r="R6" t="s">
-        <v>222</v>
-      </c>
-      <c r="S6" t="s">
-        <v>223</v>
-      </c>
-      <c r="T6" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -6514,58 +6533,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F7" t="s">
+        <v>225</v>
+      </c>
+      <c r="G7" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" t="s">
+        <v>233</v>
+      </c>
+      <c r="I7" t="s">
+        <v>218</v>
+      </c>
+      <c r="J7" t="s">
+        <v>219</v>
+      </c>
+      <c r="K7" t="s">
+        <v>220</v>
+      </c>
+      <c r="L7" t="s">
+        <v>221</v>
+      </c>
+      <c r="M7" t="s">
+        <v>215</v>
+      </c>
+      <c r="N7" t="s">
         <v>222</v>
       </c>
-      <c r="G7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" t="s">
-        <v>230</v>
-      </c>
-      <c r="I7" t="s">
-        <v>215</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="O7" t="s">
+        <v>223</v>
+      </c>
+      <c r="P7" t="s">
         <v>216</v>
       </c>
-      <c r="K7" t="s">
-        <v>217</v>
-      </c>
-      <c r="L7" t="s">
-        <v>218</v>
-      </c>
-      <c r="M7" t="s">
-        <v>212</v>
-      </c>
-      <c r="N7" t="s">
-        <v>219</v>
-      </c>
-      <c r="O7" t="s">
-        <v>220</v>
-      </c>
-      <c r="P7" t="s">
-        <v>213</v>
-      </c>
       <c r="Q7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S7" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -6573,58 +6592,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D8" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F8" t="s">
+        <v>223</v>
+      </c>
+      <c r="G8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H8" t="s">
+        <v>236</v>
+      </c>
+      <c r="I8" t="s">
+        <v>218</v>
+      </c>
+      <c r="J8" t="s">
         <v>219</v>
       </c>
-      <c r="F8" t="s">
+      <c r="K8" t="s">
         <v>220</v>
       </c>
-      <c r="G8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" t="s">
-        <v>233</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
+        <v>221</v>
+      </c>
+      <c r="M8" t="s">
         <v>215</v>
       </c>
-      <c r="J8" t="s">
+      <c r="N8" t="s">
+        <v>222</v>
+      </c>
+      <c r="O8" t="s">
+        <v>223</v>
+      </c>
+      <c r="P8" t="s">
         <v>216</v>
       </c>
-      <c r="K8" t="s">
-        <v>217</v>
-      </c>
-      <c r="L8" t="s">
-        <v>218</v>
-      </c>
-      <c r="M8" t="s">
-        <v>212</v>
-      </c>
-      <c r="N8" t="s">
-        <v>219</v>
-      </c>
-      <c r="O8" t="s">
-        <v>220</v>
-      </c>
-      <c r="P8" t="s">
-        <v>213</v>
-      </c>
       <c r="Q8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S8" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6632,58 +6651,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F9" t="s">
+        <v>225</v>
+      </c>
+      <c r="G9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I9" t="s">
+        <v>239</v>
+      </c>
+      <c r="J9" t="s">
+        <v>219</v>
+      </c>
+      <c r="K9" t="s">
+        <v>220</v>
+      </c>
+      <c r="L9" t="s">
+        <v>221</v>
+      </c>
+      <c r="M9" t="s">
+        <v>215</v>
+      </c>
+      <c r="N9" t="s">
         <v>222</v>
       </c>
-      <c r="G9" t="s">
-        <v>183</v>
-      </c>
-      <c r="H9" t="s">
-        <v>214</v>
-      </c>
-      <c r="I9" t="s">
-        <v>236</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="O9" t="s">
+        <v>223</v>
+      </c>
+      <c r="P9" t="s">
         <v>216</v>
       </c>
-      <c r="K9" t="s">
-        <v>217</v>
-      </c>
-      <c r="L9" t="s">
-        <v>218</v>
-      </c>
-      <c r="M9" t="s">
-        <v>212</v>
-      </c>
-      <c r="N9" t="s">
-        <v>219</v>
-      </c>
-      <c r="O9" t="s">
-        <v>220</v>
-      </c>
-      <c r="P9" t="s">
-        <v>213</v>
-      </c>
       <c r="Q9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T9" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -6691,58 +6710,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D10" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F10" t="s">
+        <v>216</v>
+      </c>
+      <c r="G10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H10" t="s">
+        <v>217</v>
+      </c>
+      <c r="I10" t="s">
+        <v>242</v>
+      </c>
+      <c r="J10" t="s">
         <v>219</v>
       </c>
-      <c r="F10" t="s">
-        <v>213</v>
-      </c>
-      <c r="G10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" t="s">
-        <v>214</v>
-      </c>
-      <c r="I10" t="s">
-        <v>239</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
+        <v>220</v>
+      </c>
+      <c r="L10" t="s">
+        <v>221</v>
+      </c>
+      <c r="M10" t="s">
+        <v>215</v>
+      </c>
+      <c r="N10" t="s">
+        <v>222</v>
+      </c>
+      <c r="O10" t="s">
+        <v>223</v>
+      </c>
+      <c r="P10" t="s">
         <v>216</v>
       </c>
-      <c r="K10" t="s">
-        <v>217</v>
-      </c>
-      <c r="L10" t="s">
-        <v>218</v>
-      </c>
-      <c r="M10" t="s">
-        <v>212</v>
-      </c>
-      <c r="N10" t="s">
-        <v>219</v>
-      </c>
-      <c r="O10" t="s">
-        <v>220</v>
-      </c>
-      <c r="P10" t="s">
-        <v>213</v>
-      </c>
       <c r="Q10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T10" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -6750,58 +6769,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F11" t="s">
+        <v>227</v>
+      </c>
+      <c r="G11" t="s">
+        <v>186</v>
+      </c>
+      <c r="H11" t="s">
+        <v>230</v>
+      </c>
+      <c r="I11" t="s">
+        <v>239</v>
+      </c>
+      <c r="J11" t="s">
+        <v>219</v>
+      </c>
+      <c r="K11" t="s">
+        <v>220</v>
+      </c>
+      <c r="L11" t="s">
+        <v>221</v>
+      </c>
+      <c r="M11" t="s">
+        <v>215</v>
+      </c>
+      <c r="N11" t="s">
+        <v>222</v>
+      </c>
+      <c r="O11" t="s">
+        <v>223</v>
+      </c>
+      <c r="P11" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q11" t="s">
         <v>224</v>
       </c>
-      <c r="G11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="R11" t="s">
+        <v>225</v>
+      </c>
+      <c r="S11" t="s">
+        <v>226</v>
+      </c>
+      <c r="T11" t="s">
         <v>227</v>
-      </c>
-      <c r="I11" t="s">
-        <v>236</v>
-      </c>
-      <c r="J11" t="s">
-        <v>216</v>
-      </c>
-      <c r="K11" t="s">
-        <v>217</v>
-      </c>
-      <c r="L11" t="s">
-        <v>218</v>
-      </c>
-      <c r="M11" t="s">
-        <v>212</v>
-      </c>
-      <c r="N11" t="s">
-        <v>219</v>
-      </c>
-      <c r="O11" t="s">
-        <v>220</v>
-      </c>
-      <c r="P11" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>221</v>
-      </c>
-      <c r="R11" t="s">
-        <v>222</v>
-      </c>
-      <c r="S11" t="s">
-        <v>223</v>
-      </c>
-      <c r="T11" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -6809,58 +6828,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" t="s">
+        <v>246</v>
+      </c>
+      <c r="E12" t="s">
+        <v>215</v>
+      </c>
+      <c r="F12" t="s">
+        <v>216</v>
+      </c>
+      <c r="G12" t="s">
+        <v>186</v>
+      </c>
+      <c r="H12" t="s">
+        <v>230</v>
+      </c>
+      <c r="I12" t="s">
         <v>242</v>
       </c>
-      <c r="D12" t="s">
-        <v>243</v>
-      </c>
-      <c r="E12" t="s">
-        <v>212</v>
-      </c>
-      <c r="F12" t="s">
-        <v>213</v>
-      </c>
-      <c r="G12" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
+        <v>219</v>
+      </c>
+      <c r="K12" t="s">
+        <v>220</v>
+      </c>
+      <c r="L12" t="s">
+        <v>221</v>
+      </c>
+      <c r="M12" t="s">
+        <v>215</v>
+      </c>
+      <c r="N12" t="s">
+        <v>222</v>
+      </c>
+      <c r="O12" t="s">
+        <v>223</v>
+      </c>
+      <c r="P12" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>224</v>
+      </c>
+      <c r="R12" t="s">
+        <v>225</v>
+      </c>
+      <c r="S12" t="s">
+        <v>226</v>
+      </c>
+      <c r="T12" t="s">
         <v>227</v>
-      </c>
-      <c r="I12" t="s">
-        <v>239</v>
-      </c>
-      <c r="J12" t="s">
-        <v>216</v>
-      </c>
-      <c r="K12" t="s">
-        <v>217</v>
-      </c>
-      <c r="L12" t="s">
-        <v>218</v>
-      </c>
-      <c r="M12" t="s">
-        <v>212</v>
-      </c>
-      <c r="N12" t="s">
-        <v>219</v>
-      </c>
-      <c r="O12" t="s">
-        <v>220</v>
-      </c>
-      <c r="P12" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>221</v>
-      </c>
-      <c r="R12" t="s">
-        <v>222</v>
-      </c>
-      <c r="S12" t="s">
-        <v>223</v>
-      </c>
-      <c r="T12" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -6868,58 +6887,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F13" t="s">
+        <v>227</v>
+      </c>
+      <c r="G13" t="s">
+        <v>186</v>
+      </c>
+      <c r="H13" t="s">
+        <v>233</v>
+      </c>
+      <c r="I13" t="s">
+        <v>239</v>
+      </c>
+      <c r="J13" t="s">
+        <v>219</v>
+      </c>
+      <c r="K13" t="s">
+        <v>220</v>
+      </c>
+      <c r="L13" t="s">
+        <v>221</v>
+      </c>
+      <c r="M13" t="s">
+        <v>215</v>
+      </c>
+      <c r="N13" t="s">
+        <v>222</v>
+      </c>
+      <c r="O13" t="s">
+        <v>223</v>
+      </c>
+      <c r="P13" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q13" t="s">
         <v>224</v>
       </c>
-      <c r="G13" t="s">
-        <v>183</v>
-      </c>
-      <c r="H13" t="s">
-        <v>230</v>
-      </c>
-      <c r="I13" t="s">
-        <v>236</v>
-      </c>
-      <c r="J13" t="s">
-        <v>216</v>
-      </c>
-      <c r="K13" t="s">
-        <v>217</v>
-      </c>
-      <c r="L13" t="s">
-        <v>218</v>
-      </c>
-      <c r="M13" t="s">
-        <v>212</v>
-      </c>
-      <c r="N13" t="s">
-        <v>219</v>
-      </c>
-      <c r="O13" t="s">
-        <v>220</v>
-      </c>
-      <c r="P13" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>221</v>
-      </c>
       <c r="R13" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T13" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -6927,58 +6946,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G14" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H14" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I14" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J14" t="s">
+        <v>219</v>
+      </c>
+      <c r="K14" t="s">
+        <v>220</v>
+      </c>
+      <c r="L14" t="s">
+        <v>221</v>
+      </c>
+      <c r="M14" t="s">
+        <v>215</v>
+      </c>
+      <c r="N14" t="s">
+        <v>222</v>
+      </c>
+      <c r="O14" t="s">
+        <v>223</v>
+      </c>
+      <c r="P14" t="s">
         <v>216</v>
       </c>
-      <c r="K14" t="s">
-        <v>217</v>
-      </c>
-      <c r="L14" t="s">
-        <v>218</v>
-      </c>
-      <c r="M14" t="s">
-        <v>212</v>
-      </c>
-      <c r="N14" t="s">
-        <v>219</v>
-      </c>
-      <c r="O14" t="s">
-        <v>220</v>
-      </c>
-      <c r="P14" t="s">
-        <v>213</v>
-      </c>
       <c r="Q14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R14" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T14" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -6986,58 +7005,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D15" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E15" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F15" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I15" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J15" t="s">
+        <v>219</v>
+      </c>
+      <c r="K15" t="s">
+        <v>220</v>
+      </c>
+      <c r="L15" t="s">
+        <v>221</v>
+      </c>
+      <c r="M15" t="s">
+        <v>215</v>
+      </c>
+      <c r="N15" t="s">
+        <v>222</v>
+      </c>
+      <c r="O15" t="s">
+        <v>223</v>
+      </c>
+      <c r="P15" t="s">
         <v>216</v>
       </c>
-      <c r="K15" t="s">
-        <v>217</v>
-      </c>
-      <c r="L15" t="s">
-        <v>218</v>
-      </c>
-      <c r="M15" t="s">
-        <v>212</v>
-      </c>
-      <c r="N15" t="s">
-        <v>219</v>
-      </c>
-      <c r="O15" t="s">
-        <v>220</v>
-      </c>
-      <c r="P15" t="s">
-        <v>213</v>
-      </c>
       <c r="Q15" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R15" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S15" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T15" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -7045,58 +7064,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D16" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F16" t="s">
+        <v>226</v>
+      </c>
+      <c r="G16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H16" t="s">
+        <v>236</v>
+      </c>
+      <c r="I16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J16" t="s">
+        <v>219</v>
+      </c>
+      <c r="K16" t="s">
+        <v>220</v>
+      </c>
+      <c r="L16" t="s">
+        <v>221</v>
+      </c>
+      <c r="M16" t="s">
+        <v>215</v>
+      </c>
+      <c r="N16" t="s">
+        <v>222</v>
+      </c>
+      <c r="O16" t="s">
         <v>223</v>
       </c>
-      <c r="G16" t="s">
-        <v>183</v>
-      </c>
-      <c r="H16" t="s">
-        <v>233</v>
-      </c>
-      <c r="I16" t="s">
-        <v>239</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="P16" t="s">
         <v>216</v>
       </c>
-      <c r="K16" t="s">
-        <v>217</v>
-      </c>
-      <c r="L16" t="s">
-        <v>218</v>
-      </c>
-      <c r="M16" t="s">
-        <v>212</v>
-      </c>
-      <c r="N16" t="s">
-        <v>219</v>
-      </c>
-      <c r="O16" t="s">
-        <v>220</v>
-      </c>
-      <c r="P16" t="s">
-        <v>213</v>
-      </c>
       <c r="Q16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R16" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S16" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T16" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -7125,16 +7144,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7148,7 +7167,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7173,16 +7192,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7196,10 +7215,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7207,16 +7226,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7230,10 +7249,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F7" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7247,10 +7266,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7264,10 +7283,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7275,16 +7294,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E10" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F10" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7298,10 +7317,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7315,10 +7334,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -7351,34 +7370,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="N1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7389,10 +7408,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7404,7 +7423,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7426,13 +7445,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7443,40 +7462,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="I4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="N4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7499,13 +7518,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7519,22 +7538,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7548,22 +7567,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H7" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M7" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7577,22 +7596,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M8" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7606,22 +7625,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L9" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7635,22 +7654,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L10" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7664,22 +7683,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M11" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7693,22 +7712,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H12" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L12" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M12" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7716,31 +7735,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G13" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L13" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M13" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N13" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -7748,10 +7767,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -7760,7 +7779,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -7768,10 +7787,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -7780,7 +7799,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7788,10 +7807,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -7800,7 +7819,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7808,19 +7827,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F17" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N17" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7828,10 +7847,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -7840,7 +7859,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7848,10 +7867,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -7860,7 +7879,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7868,10 +7887,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -7880,7 +7899,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7888,19 +7907,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E21" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F21" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N21" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -7908,16 +7927,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -7925,10 +7944,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -7942,10 +7961,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -7959,10 +7978,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -7976,10 +7995,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -7993,10 +8012,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -8010,10 +8029,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -8027,10 +8046,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -8039,10 +8058,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N29" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -8050,10 +8069,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -8067,10 +8086,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -8084,10 +8103,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -8096,10 +8115,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N32" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -8135,31 +8154,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="K1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8185,10 +8204,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -8202,34 +8221,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8240,31 +8259,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E4" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F4" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G4" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H4" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="I4" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J4" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="K4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8272,7 +8291,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8296,7 +8315,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8304,7 +8323,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8328,7 +8347,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8336,7 +8355,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8360,7 +8379,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8368,7 +8387,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -8392,7 +8411,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -8423,16 +8442,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8449,7 +8468,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -8462,10 +8481,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8476,13 +8495,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D4" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8490,7 +8509,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8499,7 +8518,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8507,7 +8526,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -8516,7 +8535,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8524,7 +8543,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -8533,7 +8552,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8541,7 +8560,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8550,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8588,40 +8607,40 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="G1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="H1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="J1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="K1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -8635,16 +8654,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -8670,40 +8689,40 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M3" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8711,54 +8730,54 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D4" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E4" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="H4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K4" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M4" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8770,36 +8789,36 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I5" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="J5" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="K5" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L5" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M5" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D6" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8811,36 +8830,36 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="I6" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J6" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="K6" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L6" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M6" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D7" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8852,36 +8871,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="I7" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="J7" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K7" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L7" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M7" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D8" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -8893,36 +8912,36 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="I8" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="J8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K8" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L8" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M8" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D9" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -8934,36 +8953,36 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="I9" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="J9" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K9" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L9" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M9" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D10" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8975,36 +8994,36 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="I10" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J10" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K10" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L10" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M10" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D11" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -9016,36 +9035,36 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="I11" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="J11" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K11" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L11" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M11" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D12" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -9057,36 +9076,36 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="I12" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="J12" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K12" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L12" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M12" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D13" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -9098,36 +9117,36 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="I13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="J13" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K13" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M13" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D14" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -9139,36 +9158,36 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="I14" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="J14" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="K14" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="L14" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="M14" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D15" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -9180,39 +9199,39 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="I15" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="J15" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K15" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="L15" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M15" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D16" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E16" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -9221,39 +9240,39 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="I16" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J16" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="K16" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L16" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="M16" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D17" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E17" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -9262,39 +9281,39 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="I17" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="J17" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K17" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="L17" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="M17" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D18" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E18" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -9303,39 +9322,39 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="I18" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J18" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K18" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="L18" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="M18" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D19" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E19" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -9344,39 +9363,39 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="I19" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="J19" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="K19" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L19" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="M19" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D20" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E20" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -9385,39 +9404,39 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="I20" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="J20" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K20" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L20" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="M20" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D21" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E21" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -9426,39 +9445,39 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="I21" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="J21" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K21" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L21" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="M21" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D22" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E22" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -9467,39 +9486,39 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="I22" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="J22" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K22" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="L22" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="M22" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D23" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E23" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -9508,39 +9527,39 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="I23" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="J23" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="K23" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="L23" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="M23" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D24" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E24" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -9549,39 +9568,39 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="I24" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="J24" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K24" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="L24" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M24" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D25" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E25" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -9590,22 +9609,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="I25" t="s">
         <v>52</v>
       </c>
       <c r="J25" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="K25" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L25" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="M25" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -9613,10 +9632,10 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D26" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -9628,22 +9647,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="I26" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="J26" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="K26" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="L26" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M26" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -9651,13 +9670,13 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D27" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E27" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -9666,36 +9685,36 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="I27" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="J27" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="K27" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="L27" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="M27" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D28" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -9707,36 +9726,36 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="I28" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="J28" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="K28" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="L28" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="M28" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D29" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -9748,36 +9767,36 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="I29" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="J29" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="K29" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L29" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="M29" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D30" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E30" t="s">
         <v>2</v>
@@ -9789,39 +9808,39 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="I30" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="J30" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="K30" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L30" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="M30" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D31" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E31" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -9830,22 +9849,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="I31" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="J31" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="K31" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="L31" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="M31" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -9853,13 +9872,13 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D32" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E32" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -9868,22 +9887,22 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="I32" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="J32" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="K32" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L32" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="M32" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -563,7 +563,7 @@
     <t>未领取奖励的条目和固定条目数量之和不足该值只，以已领取奖励的条目填充占位</t>
   </si>
   <si>
-    <t>SteamPlaytimeDropLeadSecondsSteam</t>
+    <t>SteamPlaytimeDropLeadSeconds</t>
   </si>
   <si>
     <t>Steam提前准备盲盒的秒数</t>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="862">
   <si>
     <t>Dog</t>
   </si>
@@ -536,22 +536,13 @@
     <t>统计时，玩家实际行为乘以倍率作为统计值记录，例如玩家获得1个筹码，倍率是10的话，记为10个筹码</t>
   </si>
   <si>
-    <t>BlindBoxBacklogClaimDelaySeconds</t>
-  </si>
-  <si>
-    <t>积压盲盒展示时短间隔时间</t>
-  </si>
-  <si>
-    <t>秒，实际使用时需要受到BlindBoxTimeScale影响，为了不让玩家对于盲盒间隔的心里预期剧烈变化因此设计了该值</t>
-  </si>
-  <si>
-    <t>BlindBoxPostNewbieDelaySeconds</t>
-  </si>
-  <si>
-    <t>新手与正式盲盒的间隔时间</t>
-  </si>
-  <si>
-    <t>秒，新手阶段结束后与第一个正式盲盒的间隔时间</t>
+    <t>BlindBoxLoopIntervalSeconds</t>
+  </si>
+  <si>
+    <t>正常阶段盲盒展示间隔</t>
+  </si>
+  <si>
+    <t>秒；第 12 个新手奖励入账后，按此基础间隔产生展示点并触发循环 Steam 掉落检查；实际时长受 BlindBoxWaitDurationMultiplier 影响</t>
   </si>
   <si>
     <t>LinkTreeVisibleBannerCount</t>
@@ -560,7 +551,7 @@
     <t>LinkTree最佳显示条目数量</t>
   </si>
   <si>
-    <t>未领取奖励的条目和固定条目数量之和不足该值只，以已领取奖励的条目填充占位</t>
+    <t>未领取奖励的条目和固定条目数量之和不足该值时，以已领取奖励的条目填充占位</t>
   </si>
   <si>
     <t>SteamPlaytimeDropLeadSeconds</t>
@@ -569,7 +560,7 @@
     <t>Steam提前准备盲盒的秒数</t>
   </si>
   <si>
-    <t>掉落提前秒数Steam游玩时间掉落相对本地盲盒展示时间提前请求的秒数，用于避开服务器计时边界。正式配置时改为60</t>
+    <t>仅用于前 12 个一次性游玩投放；相对本地盲盒展示时间提前请求，用于避开 Steam 分钟计时边界</t>
   </si>
   <si>
     <t>IconName</t>
@@ -4206,28 +4197,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C1" t="s">
+        <v>654</v>
+      </c>
+      <c r="D1" t="s">
+        <v>655</v>
+      </c>
+      <c r="E1" t="s">
         <v>656</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>657</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>658</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>659</v>
       </c>
-      <c r="F1" t="s">
-        <v>660</v>
-      </c>
-      <c r="G1" t="s">
-        <v>661</v>
-      </c>
-      <c r="H1" t="s">
-        <v>662</v>
-      </c>
       <c r="I1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4244,16 +4235,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -4264,28 +4255,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>669</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4293,1333 +4284,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>670</v>
+      </c>
+      <c r="C4" t="s">
+        <v>671</v>
+      </c>
+      <c r="D4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E4" t="s">
+        <v>672</v>
+      </c>
+      <c r="F4" t="s">
         <v>673</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>674</v>
       </c>
-      <c r="D4" t="s">
-        <v>260</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>675</v>
       </c>
-      <c r="F4" t="s">
-        <v>676</v>
-      </c>
-      <c r="G4" t="s">
-        <v>677</v>
-      </c>
-      <c r="H4" t="s">
-        <v>678</v>
-      </c>
       <c r="I4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
+        <v>676</v>
+      </c>
+      <c r="D5" t="s">
+        <v>677</v>
+      </c>
+      <c r="E5" t="s">
+        <v>678</v>
+      </c>
+      <c r="F5" t="s">
         <v>679</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
         <v>680</v>
-      </c>
-      <c r="E5" t="s">
-        <v>681</v>
-      </c>
-      <c r="F5" t="s">
-        <v>682</v>
-      </c>
-      <c r="G5" t="s">
-        <v>683</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>682</v>
+      </c>
+      <c r="D6" t="s">
+        <v>683</v>
+      </c>
+      <c r="E6" t="s">
+        <v>684</v>
+      </c>
+      <c r="F6" t="s">
+        <v>679</v>
+      </c>
+      <c r="G6" t="s">
         <v>685</v>
-      </c>
-      <c r="D6" t="s">
-        <v>686</v>
-      </c>
-      <c r="E6" t="s">
-        <v>687</v>
-      </c>
-      <c r="F6" t="s">
-        <v>682</v>
-      </c>
-      <c r="G6" t="s">
-        <v>688</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D7" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E7" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="F7" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G7" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D8" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E8" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="F8" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G8" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D9" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="E9" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F9" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G9" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
+        <v>699</v>
+      </c>
+      <c r="D10" t="s">
+        <v>700</v>
+      </c>
+      <c r="E10" t="s">
+        <v>701</v>
+      </c>
+      <c r="F10" t="s">
+        <v>679</v>
+      </c>
+      <c r="G10" t="s">
         <v>702</v>
-      </c>
-      <c r="D10" t="s">
-        <v>703</v>
-      </c>
-      <c r="E10" t="s">
-        <v>704</v>
-      </c>
-      <c r="F10" t="s">
-        <v>682</v>
-      </c>
-      <c r="G10" t="s">
-        <v>705</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D11" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E11" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F11" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G11" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D12" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E12" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F12" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G12" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D13" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E13" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F13" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G13" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E14" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F14" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G14" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D15" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E15" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F15" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G15" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D16" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E16" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F16" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G16" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D17" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="E17" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F17" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G17" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D18" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="E18" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F18" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G18" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D19" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E19" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F19" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G19" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D20" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="E20" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F20" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G20" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D21" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="E21" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F21" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G21" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D22" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E22" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F22" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G22" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D23" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E23" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F23" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G23" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D24" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="E24" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F24" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G24" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D25" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E25" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F25" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G25" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D26" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="E26" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F26" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G26" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D27" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="E27" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F27" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G27" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D28" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E28" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F28" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G28" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D29" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E29" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F29" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G29" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D30" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E30" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F30" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G30" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D31" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E31" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F31" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G31" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D32" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="E32" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F32" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G32" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D33" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="E33" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F33" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G33" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D34" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="E34" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F34" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G34" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D35" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="E35" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F35" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G35" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D36" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="E36" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F36" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G36" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="D37" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="E37" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F37" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G37" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D38" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="E38" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F38" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G38" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D39" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="E39" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F39" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G39" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="D40" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="E40" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F40" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G40" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D41" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="E41" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F41" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G41" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D42" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E42" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F42" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G42" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="D43" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E43" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F43" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G43" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="D44" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="E44" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F44" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G44" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="D45" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="E45" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F45" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G45" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D46" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="E46" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F46" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G46" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="D47" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="E47" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F47" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G47" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D48" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="E48" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F48" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G48" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="D49" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="E49" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F49" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G49" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5627,25 +5618,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="D50" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="E50" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F50" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="G50" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5653,25 +5644,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
+        <v>857</v>
+      </c>
+      <c r="D51" t="s">
+        <v>858</v>
+      </c>
+      <c r="E51" t="s">
+        <v>701</v>
+      </c>
+      <c r="F51" t="s">
+        <v>859</v>
+      </c>
+      <c r="G51" t="s">
         <v>860</v>
-      </c>
-      <c r="D51" t="s">
-        <v>861</v>
-      </c>
-      <c r="E51" t="s">
-        <v>704</v>
-      </c>
-      <c r="F51" t="s">
-        <v>862</v>
-      </c>
-      <c r="G51" t="s">
-        <v>863</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -6120,7 +6111,7 @@
         <v>158</v>
       </c>
       <c r="D6" s="2">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>168</v>
@@ -6134,10 +6125,10 @@
         <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="D7" s="2">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
         <v>171</v>
@@ -6154,28 +6145,18 @@
         <v>107</v>
       </c>
       <c r="D8" s="2">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" s="2">
-        <v>60</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2"/>
@@ -6223,55 +6204,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" t="s">
         <v>181</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="K1" t="s">
         <v>182</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="L1" t="s">
         <v>183</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>184</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>185</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>186</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>187</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>188</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>189</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>190</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>191</v>
-      </c>
-      <c r="R1" t="s">
-        <v>192</v>
-      </c>
-      <c r="S1" t="s">
-        <v>193</v>
-      </c>
-      <c r="T1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6342,10 +6323,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6359,55 +6340,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" t="s">
         <v>196</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>197</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>198</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>199</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>200</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>201</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>202</v>
       </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
         <v>203</v>
       </c>
-      <c r="L4" t="s">
+      <c r="O4" t="s">
         <v>204</v>
       </c>
-      <c r="M4" t="s">
+      <c r="P4" t="s">
         <v>205</v>
       </c>
-      <c r="N4" t="s">
+      <c r="Q4" t="s">
         <v>206</v>
       </c>
-      <c r="O4" t="s">
+      <c r="R4" t="s">
         <v>207</v>
       </c>
-      <c r="P4" t="s">
+      <c r="S4" t="s">
         <v>208</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="T4" t="s">
         <v>209</v>
-      </c>
-      <c r="R4" t="s">
-        <v>210</v>
-      </c>
-      <c r="S4" t="s">
-        <v>211</v>
-      </c>
-      <c r="T4" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6415,58 +6396,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" t="s">
         <v>213</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H5" t="s">
         <v>214</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
         <v>215</v>
       </c>
-      <c r="F5" t="s">
+      <c r="J5" t="s">
         <v>216</v>
       </c>
-      <c r="G5" t="s">
-        <v>186</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>217</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>218</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
+        <v>212</v>
+      </c>
+      <c r="N5" t="s">
         <v>219</v>
       </c>
-      <c r="K5" t="s">
+      <c r="O5" t="s">
         <v>220</v>
       </c>
-      <c r="L5" t="s">
+      <c r="P5" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q5" t="s">
         <v>221</v>
       </c>
-      <c r="M5" t="s">
-        <v>215</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="R5" t="s">
         <v>222</v>
       </c>
-      <c r="O5" t="s">
+      <c r="S5" t="s">
         <v>223</v>
       </c>
-      <c r="P5" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q5" t="s">
+      <c r="T5" t="s">
         <v>224</v>
-      </c>
-      <c r="R5" t="s">
-        <v>225</v>
-      </c>
-      <c r="S5" t="s">
-        <v>226</v>
-      </c>
-      <c r="T5" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -6474,58 +6455,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I6" t="s">
         <v>215</v>
       </c>
-      <c r="F6" t="s">
+      <c r="J6" t="s">
+        <v>216</v>
+      </c>
+      <c r="K6" t="s">
+        <v>217</v>
+      </c>
+      <c r="L6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M6" t="s">
+        <v>212</v>
+      </c>
+      <c r="N6" t="s">
+        <v>219</v>
+      </c>
+      <c r="O6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P6" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>221</v>
+      </c>
+      <c r="R6" t="s">
+        <v>222</v>
+      </c>
+      <c r="S6" t="s">
+        <v>223</v>
+      </c>
+      <c r="T6" t="s">
         <v>224</v>
-      </c>
-      <c r="G6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H6" t="s">
-        <v>230</v>
-      </c>
-      <c r="I6" t="s">
-        <v>218</v>
-      </c>
-      <c r="J6" t="s">
-        <v>219</v>
-      </c>
-      <c r="K6" t="s">
-        <v>220</v>
-      </c>
-      <c r="L6" t="s">
-        <v>221</v>
-      </c>
-      <c r="M6" t="s">
-        <v>215</v>
-      </c>
-      <c r="N6" t="s">
-        <v>222</v>
-      </c>
-      <c r="O6" t="s">
-        <v>223</v>
-      </c>
-      <c r="P6" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>224</v>
-      </c>
-      <c r="R6" t="s">
-        <v>225</v>
-      </c>
-      <c r="S6" t="s">
-        <v>226</v>
-      </c>
-      <c r="T6" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -6533,58 +6514,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I7" t="s">
         <v>215</v>
       </c>
-      <c r="F7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G7" t="s">
-        <v>186</v>
-      </c>
-      <c r="H7" t="s">
-        <v>233</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
+        <v>216</v>
+      </c>
+      <c r="K7" t="s">
+        <v>217</v>
+      </c>
+      <c r="L7" t="s">
         <v>218</v>
       </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
+        <v>212</v>
+      </c>
+      <c r="N7" t="s">
         <v>219</v>
       </c>
-      <c r="K7" t="s">
+      <c r="O7" t="s">
         <v>220</v>
       </c>
-      <c r="L7" t="s">
+      <c r="P7" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q7" t="s">
         <v>221</v>
       </c>
-      <c r="M7" t="s">
-        <v>215</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="R7" t="s">
         <v>222</v>
       </c>
-      <c r="O7" t="s">
+      <c r="S7" t="s">
         <v>223</v>
       </c>
-      <c r="P7" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q7" t="s">
+      <c r="T7" t="s">
         <v>224</v>
-      </c>
-      <c r="R7" t="s">
-        <v>225</v>
-      </c>
-      <c r="S7" t="s">
-        <v>226</v>
-      </c>
-      <c r="T7" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -6592,58 +6573,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E8" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" t="s">
+        <v>220</v>
+      </c>
+      <c r="G8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" t="s">
+        <v>233</v>
+      </c>
+      <c r="I8" t="s">
+        <v>215</v>
+      </c>
+      <c r="J8" t="s">
+        <v>216</v>
+      </c>
+      <c r="K8" t="s">
+        <v>217</v>
+      </c>
+      <c r="L8" t="s">
+        <v>218</v>
+      </c>
+      <c r="M8" t="s">
+        <v>212</v>
+      </c>
+      <c r="N8" t="s">
+        <v>219</v>
+      </c>
+      <c r="O8" t="s">
+        <v>220</v>
+      </c>
+      <c r="P8" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>221</v>
+      </c>
+      <c r="R8" t="s">
         <v>222</v>
       </c>
-      <c r="F8" t="s">
+      <c r="S8" t="s">
         <v>223</v>
       </c>
-      <c r="G8" t="s">
-        <v>186</v>
-      </c>
-      <c r="H8" t="s">
-        <v>236</v>
-      </c>
-      <c r="I8" t="s">
-        <v>218</v>
-      </c>
-      <c r="J8" t="s">
-        <v>219</v>
-      </c>
-      <c r="K8" t="s">
-        <v>220</v>
-      </c>
-      <c r="L8" t="s">
-        <v>221</v>
-      </c>
-      <c r="M8" t="s">
-        <v>215</v>
-      </c>
-      <c r="N8" t="s">
-        <v>222</v>
-      </c>
-      <c r="O8" t="s">
-        <v>223</v>
-      </c>
-      <c r="P8" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q8" t="s">
+      <c r="T8" t="s">
         <v>224</v>
-      </c>
-      <c r="R8" t="s">
-        <v>225</v>
-      </c>
-      <c r="S8" t="s">
-        <v>226</v>
-      </c>
-      <c r="T8" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6651,58 +6632,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H9" t="s">
+        <v>214</v>
+      </c>
+      <c r="I9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J9" t="s">
+        <v>216</v>
+      </c>
+      <c r="K9" t="s">
         <v>217</v>
       </c>
-      <c r="I9" t="s">
-        <v>239</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
+        <v>218</v>
+      </c>
+      <c r="M9" t="s">
+        <v>212</v>
+      </c>
+      <c r="N9" t="s">
         <v>219</v>
       </c>
-      <c r="K9" t="s">
+      <c r="O9" t="s">
         <v>220</v>
       </c>
-      <c r="L9" t="s">
+      <c r="P9" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q9" t="s">
         <v>221</v>
       </c>
-      <c r="M9" t="s">
-        <v>215</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="R9" t="s">
         <v>222</v>
       </c>
-      <c r="O9" t="s">
+      <c r="S9" t="s">
         <v>223</v>
       </c>
-      <c r="P9" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q9" t="s">
+      <c r="T9" t="s">
         <v>224</v>
-      </c>
-      <c r="R9" t="s">
-        <v>225</v>
-      </c>
-      <c r="S9" t="s">
-        <v>226</v>
-      </c>
-      <c r="T9" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -6710,58 +6691,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F10" t="s">
+        <v>213</v>
+      </c>
+      <c r="G10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" t="s">
+        <v>214</v>
+      </c>
+      <c r="I10" t="s">
+        <v>239</v>
+      </c>
+      <c r="J10" t="s">
+        <v>216</v>
+      </c>
+      <c r="K10" t="s">
+        <v>217</v>
+      </c>
+      <c r="L10" t="s">
+        <v>218</v>
+      </c>
+      <c r="M10" t="s">
+        <v>212</v>
+      </c>
+      <c r="N10" t="s">
+        <v>219</v>
+      </c>
+      <c r="O10" t="s">
+        <v>220</v>
+      </c>
+      <c r="P10" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>221</v>
+      </c>
+      <c r="R10" t="s">
         <v>222</v>
       </c>
-      <c r="F10" t="s">
-        <v>216</v>
-      </c>
-      <c r="G10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H10" t="s">
-        <v>217</v>
-      </c>
-      <c r="I10" t="s">
-        <v>242</v>
-      </c>
-      <c r="J10" t="s">
-        <v>219</v>
-      </c>
-      <c r="K10" t="s">
-        <v>220</v>
-      </c>
-      <c r="L10" t="s">
-        <v>221</v>
-      </c>
-      <c r="M10" t="s">
-        <v>215</v>
-      </c>
-      <c r="N10" t="s">
-        <v>222</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="S10" t="s">
         <v>223</v>
       </c>
-      <c r="P10" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q10" t="s">
+      <c r="T10" t="s">
         <v>224</v>
-      </c>
-      <c r="R10" t="s">
-        <v>225</v>
-      </c>
-      <c r="S10" t="s">
-        <v>226</v>
-      </c>
-      <c r="T10" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -6769,58 +6750,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D11" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F11" t="s">
+        <v>224</v>
+      </c>
+      <c r="G11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H11" t="s">
         <v>227</v>
       </c>
-      <c r="G11" t="s">
-        <v>186</v>
-      </c>
-      <c r="H11" t="s">
-        <v>230</v>
-      </c>
       <c r="I11" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J11" t="s">
+        <v>216</v>
+      </c>
+      <c r="K11" t="s">
+        <v>217</v>
+      </c>
+      <c r="L11" t="s">
+        <v>218</v>
+      </c>
+      <c r="M11" t="s">
+        <v>212</v>
+      </c>
+      <c r="N11" t="s">
         <v>219</v>
       </c>
-      <c r="K11" t="s">
+      <c r="O11" t="s">
         <v>220</v>
       </c>
-      <c r="L11" t="s">
+      <c r="P11" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q11" t="s">
         <v>221</v>
       </c>
-      <c r="M11" t="s">
-        <v>215</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="R11" t="s">
         <v>222</v>
       </c>
-      <c r="O11" t="s">
+      <c r="S11" t="s">
         <v>223</v>
       </c>
-      <c r="P11" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q11" t="s">
+      <c r="T11" t="s">
         <v>224</v>
-      </c>
-      <c r="R11" t="s">
-        <v>225</v>
-      </c>
-      <c r="S11" t="s">
-        <v>226</v>
-      </c>
-      <c r="T11" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -6828,58 +6809,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F12" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" t="s">
+        <v>183</v>
+      </c>
+      <c r="H12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I12" t="s">
+        <v>239</v>
+      </c>
+      <c r="J12" t="s">
         <v>216</v>
       </c>
-      <c r="G12" t="s">
-        <v>186</v>
-      </c>
-      <c r="H12" t="s">
-        <v>230</v>
-      </c>
-      <c r="I12" t="s">
-        <v>242</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
+        <v>217</v>
+      </c>
+      <c r="L12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M12" t="s">
+        <v>212</v>
+      </c>
+      <c r="N12" t="s">
         <v>219</v>
       </c>
-      <c r="K12" t="s">
+      <c r="O12" t="s">
         <v>220</v>
       </c>
-      <c r="L12" t="s">
+      <c r="P12" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q12" t="s">
         <v>221</v>
       </c>
-      <c r="M12" t="s">
-        <v>215</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="R12" t="s">
         <v>222</v>
       </c>
-      <c r="O12" t="s">
+      <c r="S12" t="s">
         <v>223</v>
       </c>
-      <c r="P12" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q12" t="s">
+      <c r="T12" t="s">
         <v>224</v>
-      </c>
-      <c r="R12" t="s">
-        <v>225</v>
-      </c>
-      <c r="S12" t="s">
-        <v>226</v>
-      </c>
-      <c r="T12" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -6887,58 +6868,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E13" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F13" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G13" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H13" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I13" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J13" t="s">
+        <v>216</v>
+      </c>
+      <c r="K13" t="s">
+        <v>217</v>
+      </c>
+      <c r="L13" t="s">
+        <v>218</v>
+      </c>
+      <c r="M13" t="s">
+        <v>212</v>
+      </c>
+      <c r="N13" t="s">
         <v>219</v>
       </c>
-      <c r="K13" t="s">
+      <c r="O13" t="s">
         <v>220</v>
       </c>
-      <c r="L13" t="s">
+      <c r="P13" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q13" t="s">
         <v>221</v>
       </c>
-      <c r="M13" t="s">
-        <v>215</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="R13" t="s">
         <v>222</v>
       </c>
-      <c r="O13" t="s">
+      <c r="S13" t="s">
         <v>223</v>
       </c>
-      <c r="P13" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q13" t="s">
+      <c r="T13" t="s">
         <v>224</v>
-      </c>
-      <c r="R13" t="s">
-        <v>225</v>
-      </c>
-      <c r="S13" t="s">
-        <v>226</v>
-      </c>
-      <c r="T13" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -6946,58 +6927,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D14" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E14" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F14" t="s">
+        <v>213</v>
+      </c>
+      <c r="G14" t="s">
+        <v>183</v>
+      </c>
+      <c r="H14" t="s">
+        <v>230</v>
+      </c>
+      <c r="I14" t="s">
+        <v>239</v>
+      </c>
+      <c r="J14" t="s">
         <v>216</v>
       </c>
-      <c r="G14" t="s">
-        <v>186</v>
-      </c>
-      <c r="H14" t="s">
-        <v>233</v>
-      </c>
-      <c r="I14" t="s">
-        <v>242</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
+        <v>217</v>
+      </c>
+      <c r="L14" t="s">
+        <v>218</v>
+      </c>
+      <c r="M14" t="s">
+        <v>212</v>
+      </c>
+      <c r="N14" t="s">
         <v>219</v>
       </c>
-      <c r="K14" t="s">
+      <c r="O14" t="s">
         <v>220</v>
       </c>
-      <c r="L14" t="s">
+      <c r="P14" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q14" t="s">
         <v>221</v>
       </c>
-      <c r="M14" t="s">
-        <v>215</v>
-      </c>
-      <c r="N14" t="s">
+      <c r="R14" t="s">
         <v>222</v>
       </c>
-      <c r="O14" t="s">
+      <c r="S14" t="s">
         <v>223</v>
       </c>
-      <c r="P14" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q14" t="s">
+      <c r="T14" t="s">
         <v>224</v>
-      </c>
-      <c r="R14" t="s">
-        <v>225</v>
-      </c>
-      <c r="S14" t="s">
-        <v>226</v>
-      </c>
-      <c r="T14" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -7005,58 +6986,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D15" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E15" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F15" t="s">
+        <v>213</v>
+      </c>
+      <c r="G15" t="s">
+        <v>183</v>
+      </c>
+      <c r="H15" t="s">
+        <v>233</v>
+      </c>
+      <c r="I15" t="s">
+        <v>236</v>
+      </c>
+      <c r="J15" t="s">
         <v>216</v>
       </c>
-      <c r="G15" t="s">
-        <v>186</v>
-      </c>
-      <c r="H15" t="s">
-        <v>236</v>
-      </c>
-      <c r="I15" t="s">
-        <v>239</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L15" t="s">
+        <v>218</v>
+      </c>
+      <c r="M15" t="s">
+        <v>212</v>
+      </c>
+      <c r="N15" t="s">
         <v>219</v>
       </c>
-      <c r="K15" t="s">
+      <c r="O15" t="s">
         <v>220</v>
       </c>
-      <c r="L15" t="s">
+      <c r="P15" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q15" t="s">
         <v>221</v>
       </c>
-      <c r="M15" t="s">
-        <v>215</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="R15" t="s">
         <v>222</v>
       </c>
-      <c r="O15" t="s">
+      <c r="S15" t="s">
         <v>223</v>
       </c>
-      <c r="P15" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q15" t="s">
+      <c r="T15" t="s">
         <v>224</v>
-      </c>
-      <c r="R15" t="s">
-        <v>225</v>
-      </c>
-      <c r="S15" t="s">
-        <v>226</v>
-      </c>
-      <c r="T15" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -7064,58 +7045,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D16" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F16" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G16" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H16" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J16" t="s">
+        <v>216</v>
+      </c>
+      <c r="K16" t="s">
+        <v>217</v>
+      </c>
+      <c r="L16" t="s">
+        <v>218</v>
+      </c>
+      <c r="M16" t="s">
+        <v>212</v>
+      </c>
+      <c r="N16" t="s">
         <v>219</v>
       </c>
-      <c r="K16" t="s">
+      <c r="O16" t="s">
         <v>220</v>
       </c>
-      <c r="L16" t="s">
+      <c r="P16" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q16" t="s">
         <v>221</v>
       </c>
-      <c r="M16" t="s">
-        <v>215</v>
-      </c>
-      <c r="N16" t="s">
+      <c r="R16" t="s">
         <v>222</v>
       </c>
-      <c r="O16" t="s">
+      <c r="S16" t="s">
         <v>223</v>
       </c>
-      <c r="P16" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q16" t="s">
+      <c r="T16" t="s">
         <v>224</v>
-      </c>
-      <c r="R16" t="s">
-        <v>225</v>
-      </c>
-      <c r="S16" t="s">
-        <v>226</v>
-      </c>
-      <c r="T16" t="s">
-        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -7144,16 +7125,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F1" t="s">
         <v>255</v>
-      </c>
-      <c r="D1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7167,7 +7148,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7192,16 +7173,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F4" t="s">
         <v>260</v>
-      </c>
-      <c r="D4" t="s">
-        <v>261</v>
-      </c>
-      <c r="E4" t="s">
-        <v>262</v>
-      </c>
-      <c r="F4" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7215,10 +7196,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7226,16 +7207,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7249,10 +7230,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7266,10 +7247,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7283,10 +7264,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7294,16 +7275,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
+        <v>272</v>
+      </c>
+      <c r="D10" t="s">
+        <v>273</v>
+      </c>
+      <c r="E10" t="s">
+        <v>274</v>
+      </c>
+      <c r="F10" t="s">
         <v>275</v>
-      </c>
-      <c r="D10" t="s">
-        <v>276</v>
-      </c>
-      <c r="E10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F10" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7317,10 +7298,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F11" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7334,10 +7315,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F12" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -7370,34 +7351,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H1" t="s">
         <v>283</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>284</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>285</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>286</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>287</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>288</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>289</v>
-      </c>
-      <c r="L1" t="s">
-        <v>290</v>
-      </c>
-      <c r="M1" t="s">
-        <v>291</v>
-      </c>
-      <c r="N1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7408,10 +7389,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7423,7 +7404,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7445,13 +7426,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7462,40 +7443,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F4" t="s">
+        <v>296</v>
+      </c>
+      <c r="G4" t="s">
         <v>298</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>299</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>300</v>
       </c>
-      <c r="F4" t="s">
-        <v>299</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>301</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>302</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>303</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
+        <v>201</v>
+      </c>
+      <c r="N4" t="s">
         <v>304</v>
-      </c>
-      <c r="K4" t="s">
-        <v>305</v>
-      </c>
-      <c r="L4" t="s">
-        <v>306</v>
-      </c>
-      <c r="M4" t="s">
-        <v>204</v>
-      </c>
-      <c r="N4" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7518,13 +7499,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7538,22 +7519,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H6" t="s">
         <v>187</v>
-      </c>
-      <c r="H6" t="s">
-        <v>190</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7567,22 +7548,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7596,22 +7577,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H8" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7625,22 +7606,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7654,22 +7635,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7683,22 +7664,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L11" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7712,22 +7693,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H12" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="L12" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M12" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7735,31 +7716,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G13" t="s">
+        <v>184</v>
+      </c>
+      <c r="H13" t="s">
         <v>187</v>
-      </c>
-      <c r="H13" t="s">
-        <v>190</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M13" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N13" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -7767,10 +7748,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -7779,7 +7760,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -7787,10 +7768,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -7799,7 +7780,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7807,10 +7788,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -7819,7 +7800,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7827,19 +7808,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="F17" t="s">
         <v>324</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="N17" t="s">
         <v>325</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="F17" t="s">
-        <v>327</v>
-      </c>
-      <c r="N17" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7847,10 +7828,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -7859,7 +7840,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7867,10 +7848,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -7879,7 +7860,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7887,10 +7868,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -7899,7 +7880,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7907,19 +7888,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E21" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F21" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="N21" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -7927,16 +7908,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -7944,10 +7925,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -7961,10 +7942,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -7978,10 +7959,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -7995,10 +7976,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -8012,10 +7993,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -8029,10 +8010,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -8046,10 +8027,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -8058,10 +8039,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N29" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -8069,10 +8050,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -8086,10 +8067,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -8103,10 +8084,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -8115,10 +8096,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N32" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -8154,31 +8135,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F1" t="s">
         <v>363</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>364</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1" t="s">
         <v>365</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>366</v>
       </c>
-      <c r="G1" t="s">
-        <v>367</v>
-      </c>
-      <c r="H1" t="s">
-        <v>283</v>
-      </c>
-      <c r="I1" t="s">
-        <v>368</v>
-      </c>
-      <c r="J1" t="s">
-        <v>369</v>
-      </c>
       <c r="K1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8204,10 +8185,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -8221,34 +8202,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8259,31 +8240,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E4" t="s">
+        <v>378</v>
+      </c>
+      <c r="F4" t="s">
         <v>379</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>380</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>381</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>382</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>383</v>
       </c>
-      <c r="H4" t="s">
-        <v>384</v>
-      </c>
-      <c r="I4" t="s">
-        <v>385</v>
-      </c>
-      <c r="J4" t="s">
-        <v>386</v>
-      </c>
       <c r="K4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8291,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8315,7 +8296,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8323,7 +8304,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8347,7 +8328,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8355,7 +8336,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8379,7 +8360,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8387,7 +8368,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -8411,7 +8392,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -8442,16 +8423,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8468,7 +8449,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -8481,10 +8462,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8495,13 +8476,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8509,7 +8490,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8518,7 +8499,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8526,7 +8507,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -8535,7 +8516,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8543,7 +8524,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -8552,7 +8533,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8560,7 +8541,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8569,7 +8550,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8607,40 +8588,40 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E1" t="s">
         <v>409</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>410</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>411</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I1" t="s">
         <v>412</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>413</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>414</v>
       </c>
-      <c r="H1" t="s">
-        <v>292</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>415</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>416</v>
-      </c>
-      <c r="K1" t="s">
-        <v>417</v>
-      </c>
-      <c r="L1" t="s">
-        <v>418</v>
-      </c>
-      <c r="M1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -8654,16 +8635,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="G2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -8689,40 +8670,40 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" t="s">
         <v>426</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" t="s">
         <v>427</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="K3" t="s">
         <v>428</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
         <v>429</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>430</v>
-      </c>
-      <c r="K3" t="s">
-        <v>431</v>
-      </c>
-      <c r="L3" t="s">
-        <v>432</v>
-      </c>
-      <c r="M3" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8730,54 +8711,54 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C4" t="s">
+        <v>432</v>
+      </c>
+      <c r="D4" t="s">
+        <v>433</v>
+      </c>
+      <c r="E4" t="s">
         <v>434</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>435</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>436</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
+        <v>304</v>
+      </c>
+      <c r="I4" t="s">
         <v>437</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>438</v>
       </c>
-      <c r="G4" t="s">
+      <c r="K4" t="s">
         <v>439</v>
       </c>
-      <c r="H4" t="s">
-        <v>307</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>440</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>441</v>
-      </c>
-      <c r="K4" t="s">
-        <v>442</v>
-      </c>
-      <c r="L4" t="s">
-        <v>443</v>
-      </c>
-      <c r="M4" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D5" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8789,36 +8770,36 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
+        <v>444</v>
+      </c>
+      <c r="I5" t="s">
+        <v>445</v>
+      </c>
+      <c r="J5" t="s">
+        <v>446</v>
+      </c>
+      <c r="K5" t="s">
         <v>447</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>448</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>449</v>
-      </c>
-      <c r="K5" t="s">
-        <v>450</v>
-      </c>
-      <c r="L5" t="s">
-        <v>451</v>
-      </c>
-      <c r="M5" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D6" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8830,36 +8811,36 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
+        <v>451</v>
+      </c>
+      <c r="I6" t="s">
+        <v>452</v>
+      </c>
+      <c r="J6" t="s">
+        <v>453</v>
+      </c>
+      <c r="K6" t="s">
         <v>454</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>455</v>
       </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>456</v>
-      </c>
-      <c r="K6" t="s">
-        <v>457</v>
-      </c>
-      <c r="L6" t="s">
-        <v>458</v>
-      </c>
-      <c r="M6" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D7" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8871,36 +8852,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
+        <v>458</v>
+      </c>
+      <c r="I7" t="s">
+        <v>459</v>
+      </c>
+      <c r="J7" t="s">
+        <v>460</v>
+      </c>
+      <c r="K7" t="s">
         <v>461</v>
       </c>
-      <c r="I7" t="s">
+      <c r="L7" t="s">
         <v>462</v>
       </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
         <v>463</v>
-      </c>
-      <c r="K7" t="s">
-        <v>464</v>
-      </c>
-      <c r="L7" t="s">
-        <v>465</v>
-      </c>
-      <c r="M7" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D8" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -8912,36 +8893,36 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="I8" t="s">
+        <v>466</v>
+      </c>
+      <c r="J8" t="s">
+        <v>467</v>
+      </c>
+      <c r="K8" t="s">
         <v>468</v>
       </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
         <v>469</v>
       </c>
-      <c r="J8" t="s">
+      <c r="M8" t="s">
         <v>470</v>
-      </c>
-      <c r="K8" t="s">
-        <v>471</v>
-      </c>
-      <c r="L8" t="s">
-        <v>472</v>
-      </c>
-      <c r="M8" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -8953,36 +8934,36 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
+        <v>472</v>
+      </c>
+      <c r="I9" t="s">
+        <v>473</v>
+      </c>
+      <c r="J9" t="s">
+        <v>474</v>
+      </c>
+      <c r="K9" t="s">
         <v>475</v>
       </c>
-      <c r="I9" t="s">
+      <c r="L9" t="s">
         <v>476</v>
       </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>477</v>
-      </c>
-      <c r="K9" t="s">
-        <v>478</v>
-      </c>
-      <c r="L9" t="s">
-        <v>479</v>
-      </c>
-      <c r="M9" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D10" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8994,36 +8975,36 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
+        <v>479</v>
+      </c>
+      <c r="I10" t="s">
+        <v>480</v>
+      </c>
+      <c r="J10" t="s">
+        <v>481</v>
+      </c>
+      <c r="K10" t="s">
         <v>482</v>
       </c>
-      <c r="I10" t="s">
+      <c r="L10" t="s">
         <v>483</v>
       </c>
-      <c r="J10" t="s">
+      <c r="M10" t="s">
         <v>484</v>
-      </c>
-      <c r="K10" t="s">
-        <v>485</v>
-      </c>
-      <c r="L10" t="s">
-        <v>486</v>
-      </c>
-      <c r="M10" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D11" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -9035,36 +9016,36 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
+        <v>486</v>
+      </c>
+      <c r="I11" t="s">
+        <v>487</v>
+      </c>
+      <c r="J11" t="s">
+        <v>488</v>
+      </c>
+      <c r="K11" t="s">
         <v>489</v>
       </c>
-      <c r="I11" t="s">
+      <c r="L11" t="s">
         <v>490</v>
       </c>
-      <c r="J11" t="s">
+      <c r="M11" t="s">
         <v>491</v>
-      </c>
-      <c r="K11" t="s">
-        <v>492</v>
-      </c>
-      <c r="L11" t="s">
-        <v>493</v>
-      </c>
-      <c r="M11" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D12" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -9076,36 +9057,36 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
+        <v>493</v>
+      </c>
+      <c r="I12" t="s">
+        <v>494</v>
+      </c>
+      <c r="J12" t="s">
+        <v>495</v>
+      </c>
+      <c r="K12" t="s">
         <v>496</v>
       </c>
-      <c r="I12" t="s">
+      <c r="L12" t="s">
         <v>497</v>
       </c>
-      <c r="J12" t="s">
+      <c r="M12" t="s">
         <v>498</v>
-      </c>
-      <c r="K12" t="s">
-        <v>499</v>
-      </c>
-      <c r="L12" t="s">
-        <v>500</v>
-      </c>
-      <c r="M12" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D13" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -9117,36 +9098,36 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
+        <v>500</v>
+      </c>
+      <c r="I13" t="s">
+        <v>501</v>
+      </c>
+      <c r="J13" t="s">
+        <v>502</v>
+      </c>
+      <c r="K13" t="s">
         <v>503</v>
       </c>
-      <c r="I13" t="s">
+      <c r="L13" t="s">
         <v>504</v>
       </c>
-      <c r="J13" t="s">
+      <c r="M13" t="s">
         <v>505</v>
-      </c>
-      <c r="K13" t="s">
-        <v>506</v>
-      </c>
-      <c r="L13" t="s">
-        <v>507</v>
-      </c>
-      <c r="M13" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D14" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -9158,36 +9139,36 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
+        <v>507</v>
+      </c>
+      <c r="I14" t="s">
+        <v>508</v>
+      </c>
+      <c r="J14" t="s">
+        <v>509</v>
+      </c>
+      <c r="K14" t="s">
         <v>510</v>
       </c>
-      <c r="I14" t="s">
+      <c r="L14" t="s">
         <v>511</v>
       </c>
-      <c r="J14" t="s">
+      <c r="M14" t="s">
         <v>512</v>
-      </c>
-      <c r="K14" t="s">
-        <v>513</v>
-      </c>
-      <c r="L14" t="s">
-        <v>514</v>
-      </c>
-      <c r="M14" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D15" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -9199,39 +9180,39 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
+        <v>514</v>
+      </c>
+      <c r="I15" t="s">
+        <v>515</v>
+      </c>
+      <c r="J15" t="s">
+        <v>516</v>
+      </c>
+      <c r="K15" t="s">
         <v>517</v>
       </c>
-      <c r="I15" t="s">
+      <c r="L15" t="s">
         <v>518</v>
       </c>
-      <c r="J15" t="s">
+      <c r="M15" t="s">
         <v>519</v>
-      </c>
-      <c r="K15" t="s">
-        <v>520</v>
-      </c>
-      <c r="L15" t="s">
-        <v>521</v>
-      </c>
-      <c r="M15" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D16" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E16" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -9240,39 +9221,39 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
+        <v>523</v>
+      </c>
+      <c r="I16" t="s">
+        <v>524</v>
+      </c>
+      <c r="J16" t="s">
+        <v>525</v>
+      </c>
+      <c r="K16" t="s">
         <v>526</v>
       </c>
-      <c r="I16" t="s">
+      <c r="L16" t="s">
         <v>527</v>
       </c>
-      <c r="J16" t="s">
+      <c r="M16" t="s">
         <v>528</v>
-      </c>
-      <c r="K16" t="s">
-        <v>529</v>
-      </c>
-      <c r="L16" t="s">
-        <v>530</v>
-      </c>
-      <c r="M16" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D17" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E17" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -9281,39 +9262,39 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
+        <v>531</v>
+      </c>
+      <c r="I17" t="s">
+        <v>532</v>
+      </c>
+      <c r="J17" t="s">
+        <v>533</v>
+      </c>
+      <c r="K17" t="s">
         <v>534</v>
       </c>
-      <c r="I17" t="s">
+      <c r="L17" t="s">
         <v>535</v>
       </c>
-      <c r="J17" t="s">
+      <c r="M17" t="s">
         <v>536</v>
-      </c>
-      <c r="K17" t="s">
-        <v>537</v>
-      </c>
-      <c r="L17" t="s">
-        <v>538</v>
-      </c>
-      <c r="M17" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D18" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E18" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -9322,39 +9303,39 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
+        <v>539</v>
+      </c>
+      <c r="I18" t="s">
+        <v>540</v>
+      </c>
+      <c r="J18" t="s">
+        <v>541</v>
+      </c>
+      <c r="K18" t="s">
         <v>542</v>
       </c>
-      <c r="I18" t="s">
+      <c r="L18" t="s">
         <v>543</v>
       </c>
-      <c r="J18" t="s">
+      <c r="M18" t="s">
         <v>544</v>
-      </c>
-      <c r="K18" t="s">
-        <v>545</v>
-      </c>
-      <c r="L18" t="s">
-        <v>546</v>
-      </c>
-      <c r="M18" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D19" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E19" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -9363,39 +9344,39 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
+        <v>547</v>
+      </c>
+      <c r="I19" t="s">
+        <v>548</v>
+      </c>
+      <c r="J19" t="s">
+        <v>549</v>
+      </c>
+      <c r="K19" t="s">
         <v>550</v>
       </c>
-      <c r="I19" t="s">
+      <c r="L19" t="s">
         <v>551</v>
       </c>
-      <c r="J19" t="s">
+      <c r="M19" t="s">
         <v>552</v>
-      </c>
-      <c r="K19" t="s">
-        <v>553</v>
-      </c>
-      <c r="L19" t="s">
-        <v>554</v>
-      </c>
-      <c r="M19" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D20" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E20" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -9404,39 +9385,39 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
+        <v>555</v>
+      </c>
+      <c r="I20" t="s">
+        <v>556</v>
+      </c>
+      <c r="J20" t="s">
+        <v>557</v>
+      </c>
+      <c r="K20" t="s">
         <v>558</v>
       </c>
-      <c r="I20" t="s">
+      <c r="L20" t="s">
         <v>559</v>
       </c>
-      <c r="J20" t="s">
+      <c r="M20" t="s">
         <v>560</v>
-      </c>
-      <c r="K20" t="s">
-        <v>561</v>
-      </c>
-      <c r="L20" t="s">
-        <v>562</v>
-      </c>
-      <c r="M20" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D21" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E21" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -9445,39 +9426,39 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
+        <v>563</v>
+      </c>
+      <c r="I21" t="s">
+        <v>564</v>
+      </c>
+      <c r="J21" t="s">
+        <v>565</v>
+      </c>
+      <c r="K21" t="s">
         <v>566</v>
       </c>
-      <c r="I21" t="s">
+      <c r="L21" t="s">
         <v>567</v>
       </c>
-      <c r="J21" t="s">
+      <c r="M21" t="s">
         <v>568</v>
-      </c>
-      <c r="K21" t="s">
-        <v>569</v>
-      </c>
-      <c r="L21" t="s">
-        <v>570</v>
-      </c>
-      <c r="M21" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D22" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E22" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -9486,39 +9467,39 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
+        <v>571</v>
+      </c>
+      <c r="I22" t="s">
+        <v>572</v>
+      </c>
+      <c r="J22" t="s">
+        <v>573</v>
+      </c>
+      <c r="K22" t="s">
         <v>574</v>
       </c>
-      <c r="I22" t="s">
+      <c r="L22" t="s">
         <v>575</v>
       </c>
-      <c r="J22" t="s">
+      <c r="M22" t="s">
         <v>576</v>
-      </c>
-      <c r="K22" t="s">
-        <v>577</v>
-      </c>
-      <c r="L22" t="s">
-        <v>578</v>
-      </c>
-      <c r="M22" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D23" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E23" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -9527,39 +9508,39 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
+        <v>580</v>
+      </c>
+      <c r="I23" t="s">
+        <v>581</v>
+      </c>
+      <c r="J23" t="s">
+        <v>582</v>
+      </c>
+      <c r="K23" t="s">
         <v>583</v>
       </c>
-      <c r="I23" t="s">
+      <c r="L23" t="s">
         <v>584</v>
       </c>
-      <c r="J23" t="s">
+      <c r="M23" t="s">
         <v>585</v>
-      </c>
-      <c r="K23" t="s">
-        <v>586</v>
-      </c>
-      <c r="L23" t="s">
-        <v>587</v>
-      </c>
-      <c r="M23" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D24" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E24" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -9568,39 +9549,39 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
+        <v>588</v>
+      </c>
+      <c r="I24" t="s">
+        <v>589</v>
+      </c>
+      <c r="J24" t="s">
+        <v>590</v>
+      </c>
+      <c r="K24" t="s">
         <v>591</v>
       </c>
-      <c r="I24" t="s">
+      <c r="L24" t="s">
         <v>592</v>
       </c>
-      <c r="J24" t="s">
+      <c r="M24" t="s">
         <v>593</v>
-      </c>
-      <c r="K24" t="s">
-        <v>594</v>
-      </c>
-      <c r="L24" t="s">
-        <v>595</v>
-      </c>
-      <c r="M24" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D25" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E25" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -9609,22 +9590,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="I25" t="s">
         <v>52</v>
       </c>
       <c r="J25" t="s">
+        <v>597</v>
+      </c>
+      <c r="K25" t="s">
+        <v>598</v>
+      </c>
+      <c r="L25" t="s">
+        <v>599</v>
+      </c>
+      <c r="M25" t="s">
         <v>600</v>
-      </c>
-      <c r="K25" t="s">
-        <v>601</v>
-      </c>
-      <c r="L25" t="s">
-        <v>602</v>
-      </c>
-      <c r="M25" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -9632,10 +9613,10 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D26" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -9647,22 +9628,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
+        <v>603</v>
+      </c>
+      <c r="I26" t="s">
+        <v>604</v>
+      </c>
+      <c r="J26" t="s">
+        <v>605</v>
+      </c>
+      <c r="K26" t="s">
         <v>606</v>
       </c>
-      <c r="I26" t="s">
+      <c r="L26" t="s">
         <v>607</v>
       </c>
-      <c r="J26" t="s">
+      <c r="M26" t="s">
         <v>608</v>
-      </c>
-      <c r="K26" t="s">
-        <v>609</v>
-      </c>
-      <c r="L26" t="s">
-        <v>610</v>
-      </c>
-      <c r="M26" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -9670,13 +9651,13 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D27" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E27" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -9685,36 +9666,36 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
+        <v>611</v>
+      </c>
+      <c r="I27" t="s">
+        <v>612</v>
+      </c>
+      <c r="J27" t="s">
+        <v>613</v>
+      </c>
+      <c r="K27" t="s">
         <v>614</v>
       </c>
-      <c r="I27" t="s">
+      <c r="L27" t="s">
         <v>615</v>
       </c>
-      <c r="J27" t="s">
+      <c r="M27" t="s">
         <v>616</v>
-      </c>
-      <c r="K27" t="s">
-        <v>617</v>
-      </c>
-      <c r="L27" t="s">
-        <v>618</v>
-      </c>
-      <c r="M27" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="D28" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -9726,36 +9707,36 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
+        <v>618</v>
+      </c>
+      <c r="I28" t="s">
+        <v>619</v>
+      </c>
+      <c r="J28" t="s">
+        <v>620</v>
+      </c>
+      <c r="K28" t="s">
         <v>621</v>
       </c>
-      <c r="I28" t="s">
+      <c r="L28" t="s">
         <v>622</v>
       </c>
-      <c r="J28" t="s">
+      <c r="M28" t="s">
         <v>623</v>
-      </c>
-      <c r="K28" t="s">
-        <v>624</v>
-      </c>
-      <c r="L28" t="s">
-        <v>625</v>
-      </c>
-      <c r="M28" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D29" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -9767,36 +9748,36 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
+        <v>625</v>
+      </c>
+      <c r="I29" t="s">
+        <v>626</v>
+      </c>
+      <c r="J29" t="s">
+        <v>627</v>
+      </c>
+      <c r="K29" t="s">
         <v>628</v>
       </c>
-      <c r="I29" t="s">
+      <c r="L29" t="s">
         <v>629</v>
       </c>
-      <c r="J29" t="s">
+      <c r="M29" t="s">
         <v>630</v>
-      </c>
-      <c r="K29" t="s">
-        <v>631</v>
-      </c>
-      <c r="L29" t="s">
-        <v>632</v>
-      </c>
-      <c r="M29" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D30" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E30" t="s">
         <v>2</v>
@@ -9808,39 +9789,39 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
+        <v>632</v>
+      </c>
+      <c r="I30" t="s">
+        <v>633</v>
+      </c>
+      <c r="J30" t="s">
+        <v>634</v>
+      </c>
+      <c r="K30" t="s">
         <v>635</v>
       </c>
-      <c r="I30" t="s">
+      <c r="L30" t="s">
         <v>636</v>
       </c>
-      <c r="J30" t="s">
+      <c r="M30" t="s">
         <v>637</v>
-      </c>
-      <c r="K30" t="s">
-        <v>638</v>
-      </c>
-      <c r="L30" t="s">
-        <v>639</v>
-      </c>
-      <c r="M30" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D31" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E31" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -9849,22 +9830,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
+        <v>639</v>
+      </c>
+      <c r="I31" t="s">
+        <v>640</v>
+      </c>
+      <c r="J31" t="s">
+        <v>641</v>
+      </c>
+      <c r="K31" t="s">
         <v>642</v>
       </c>
-      <c r="I31" t="s">
+      <c r="L31" t="s">
         <v>643</v>
       </c>
-      <c r="J31" t="s">
+      <c r="M31" t="s">
         <v>644</v>
-      </c>
-      <c r="K31" t="s">
-        <v>645</v>
-      </c>
-      <c r="L31" t="s">
-        <v>646</v>
-      </c>
-      <c r="M31" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -9872,13 +9853,13 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D32" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E32" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -9887,22 +9868,22 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
+        <v>647</v>
+      </c>
+      <c r="I32" t="s">
+        <v>648</v>
+      </c>
+      <c r="J32" t="s">
+        <v>649</v>
+      </c>
+      <c r="K32" t="s">
         <v>650</v>
       </c>
-      <c r="I32" t="s">
+      <c r="L32" t="s">
         <v>651</v>
       </c>
-      <c r="J32" t="s">
+      <c r="M32" t="s">
         <v>652</v>
-      </c>
-      <c r="K32" t="s">
-        <v>653</v>
-      </c>
-      <c r="L32" t="s">
-        <v>654</v>
-      </c>
-      <c r="M32" t="s">
-        <v>655</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="865">
   <si>
     <t>Dog</t>
   </si>
@@ -560,7 +560,16 @@
     <t>Steam提前准备盲盒的秒数</t>
   </si>
   <si>
-    <t>仅用于前 12 个一次性游玩投放；相对本地盲盒展示时间提前请求，用于避开 Steam 分钟计时边界</t>
+    <t>秒；仅供转换器使用，仅用于前 12 个一次性游玩投放；相对本地盲盒展示时间提前请求，用于避开 Steam 分钟计时边界</t>
+  </si>
+  <si>
+    <t>SteamPlaytimeRequestLeadSeconds</t>
+  </si>
+  <si>
+    <t>Steam掉落请求提前秒数</t>
+  </si>
+  <si>
+    <t>仅供客户端使用。在本地展示前多久开始调用 TriggerItemDrop。</t>
   </si>
   <si>
     <t>IconName</t>
@@ -2634,7 +2643,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2644,6 +2653,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF1C1E21"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -3112,16 +3128,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3130,119 +3143,122 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3263,6 +3279,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4197,28 +4222,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="F1" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="G1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="H1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="I1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4235,16 +4260,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="F2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -4255,28 +4280,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4284,1333 +4309,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C4" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E4" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="F4" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="G4" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="H4" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="I4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="D5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="E5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="F5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G5" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>685</v>
+      </c>
+      <c r="D6" t="s">
+        <v>686</v>
+      </c>
+      <c r="E6" t="s">
+        <v>687</v>
+      </c>
+      <c r="F6" t="s">
         <v>682</v>
       </c>
-      <c r="D6" t="s">
-        <v>683</v>
-      </c>
-      <c r="E6" t="s">
-        <v>684</v>
-      </c>
-      <c r="F6" t="s">
-        <v>679</v>
-      </c>
       <c r="G6" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D7" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="E7" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="F7" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G7" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D8" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="E8" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="F8" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G8" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="D9" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E9" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F9" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G9" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D10" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="E10" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F10" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G10" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D11" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E11" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F11" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G11" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D12" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="E12" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F12" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G12" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D13" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="E13" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F13" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G13" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D14" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E14" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F14" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G14" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D15" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="E15" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F15" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G15" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="D16" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="E16" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F16" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G16" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="D17" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="E17" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F17" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G17" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D18" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E18" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F18" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G18" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D19" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E19" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F19" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G19" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D20" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E20" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F20" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G20" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D21" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="E21" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F21" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G21" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D22" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="E22" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F22" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G22" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D23" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="E23" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F23" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G23" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D24" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E24" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F24" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G24" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D25" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="E25" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F25" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G25" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D26" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="E26" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F26" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G26" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D27" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="E27" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F27" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G27" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D28" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="E28" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F28" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G28" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D29" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="E29" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F29" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G29" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D30" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="E30" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F30" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G30" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="D31" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E31" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F31" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G31" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D32" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="E32" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F32" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G32" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="D33" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="E33" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F33" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G33" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="D34" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E34" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F34" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G34" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D35" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="E35" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F35" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G35" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D36" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E36" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F36" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G36" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D37" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="E37" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F37" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G37" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D38" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="E38" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F38" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G38" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D39" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="E39" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F39" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G39" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D40" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="E40" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F40" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G40" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D41" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="E41" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F41" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G41" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="D42" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="E42" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F42" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G42" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D43" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E43" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F43" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G43" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D44" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="E44" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F44" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G44" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D45" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="E45" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F45" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G45" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D46" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="E46" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F46" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G46" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="D47" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E47" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F47" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G47" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D48" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="E48" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F48" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G48" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D49" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E49" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F49" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G49" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5618,25 +5643,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="D50" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E50" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F50" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G50" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5644,25 +5669,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="D51" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="E51" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F51" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="G51" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -6013,8 +6038,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="36.6666666666667" customWidth="1"/>
     <col min="2" max="2" width="22.4166666666667" customWidth="1"/>
@@ -6152,11 +6177,21 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="2">
+        <v>90</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2"/>
@@ -6164,6 +6199,24 @@
       <c r="C10" s="5"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
+    </row>
+    <row r="17" spans="5:8">
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="5:8">
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="5:8">
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6204,55 +6257,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="L1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="O1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="R1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="S1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="T1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6323,10 +6376,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6340,55 +6393,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="L4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="M4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="N4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="O4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="P4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="S4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="T4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6396,58 +6449,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I5" t="s">
+        <v>218</v>
+      </c>
+      <c r="J5" t="s">
+        <v>219</v>
+      </c>
+      <c r="K5" t="s">
+        <v>220</v>
+      </c>
+      <c r="L5" t="s">
+        <v>221</v>
+      </c>
+      <c r="M5" t="s">
         <v>215</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
+        <v>222</v>
+      </c>
+      <c r="O5" t="s">
+        <v>223</v>
+      </c>
+      <c r="P5" t="s">
         <v>216</v>
       </c>
-      <c r="K5" t="s">
-        <v>217</v>
-      </c>
-      <c r="L5" t="s">
-        <v>218</v>
-      </c>
-      <c r="M5" t="s">
-        <v>212</v>
-      </c>
-      <c r="N5" t="s">
-        <v>219</v>
-      </c>
-      <c r="O5" t="s">
-        <v>220</v>
-      </c>
-      <c r="P5" t="s">
-        <v>213</v>
-      </c>
       <c r="Q5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -6455,58 +6508,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F6" t="s">
+        <v>224</v>
+      </c>
+      <c r="G6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I6" t="s">
+        <v>218</v>
+      </c>
+      <c r="J6" t="s">
+        <v>219</v>
+      </c>
+      <c r="K6" t="s">
+        <v>220</v>
+      </c>
+      <c r="L6" t="s">
+        <v>221</v>
+      </c>
+      <c r="M6" t="s">
+        <v>215</v>
+      </c>
+      <c r="N6" t="s">
+        <v>222</v>
+      </c>
+      <c r="O6" t="s">
+        <v>223</v>
+      </c>
+      <c r="P6" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>224</v>
+      </c>
+      <c r="R6" t="s">
         <v>225</v>
       </c>
-      <c r="D6" t="s">
+      <c r="S6" t="s">
         <v>226</v>
       </c>
-      <c r="E6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F6" t="s">
-        <v>221</v>
-      </c>
-      <c r="G6" t="s">
-        <v>183</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="T6" t="s">
         <v>227</v>
-      </c>
-      <c r="I6" t="s">
-        <v>215</v>
-      </c>
-      <c r="J6" t="s">
-        <v>216</v>
-      </c>
-      <c r="K6" t="s">
-        <v>217</v>
-      </c>
-      <c r="L6" t="s">
-        <v>218</v>
-      </c>
-      <c r="M6" t="s">
-        <v>212</v>
-      </c>
-      <c r="N6" t="s">
-        <v>219</v>
-      </c>
-      <c r="O6" t="s">
-        <v>220</v>
-      </c>
-      <c r="P6" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>221</v>
-      </c>
-      <c r="R6" t="s">
-        <v>222</v>
-      </c>
-      <c r="S6" t="s">
-        <v>223</v>
-      </c>
-      <c r="T6" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -6514,58 +6567,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F7" t="s">
+        <v>225</v>
+      </c>
+      <c r="G7" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" t="s">
+        <v>233</v>
+      </c>
+      <c r="I7" t="s">
+        <v>218</v>
+      </c>
+      <c r="J7" t="s">
+        <v>219</v>
+      </c>
+      <c r="K7" t="s">
+        <v>220</v>
+      </c>
+      <c r="L7" t="s">
+        <v>221</v>
+      </c>
+      <c r="M7" t="s">
+        <v>215</v>
+      </c>
+      <c r="N7" t="s">
         <v>222</v>
       </c>
-      <c r="G7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" t="s">
-        <v>230</v>
-      </c>
-      <c r="I7" t="s">
-        <v>215</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="O7" t="s">
+        <v>223</v>
+      </c>
+      <c r="P7" t="s">
         <v>216</v>
       </c>
-      <c r="K7" t="s">
-        <v>217</v>
-      </c>
-      <c r="L7" t="s">
-        <v>218</v>
-      </c>
-      <c r="M7" t="s">
-        <v>212</v>
-      </c>
-      <c r="N7" t="s">
-        <v>219</v>
-      </c>
-      <c r="O7" t="s">
-        <v>220</v>
-      </c>
-      <c r="P7" t="s">
-        <v>213</v>
-      </c>
       <c r="Q7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S7" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -6573,58 +6626,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D8" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F8" t="s">
+        <v>223</v>
+      </c>
+      <c r="G8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H8" t="s">
+        <v>236</v>
+      </c>
+      <c r="I8" t="s">
+        <v>218</v>
+      </c>
+      <c r="J8" t="s">
         <v>219</v>
       </c>
-      <c r="F8" t="s">
+      <c r="K8" t="s">
         <v>220</v>
       </c>
-      <c r="G8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" t="s">
-        <v>233</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
+        <v>221</v>
+      </c>
+      <c r="M8" t="s">
         <v>215</v>
       </c>
-      <c r="J8" t="s">
+      <c r="N8" t="s">
+        <v>222</v>
+      </c>
+      <c r="O8" t="s">
+        <v>223</v>
+      </c>
+      <c r="P8" t="s">
         <v>216</v>
       </c>
-      <c r="K8" t="s">
-        <v>217</v>
-      </c>
-      <c r="L8" t="s">
-        <v>218</v>
-      </c>
-      <c r="M8" t="s">
-        <v>212</v>
-      </c>
-      <c r="N8" t="s">
-        <v>219</v>
-      </c>
-      <c r="O8" t="s">
-        <v>220</v>
-      </c>
-      <c r="P8" t="s">
-        <v>213</v>
-      </c>
       <c r="Q8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S8" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6632,58 +6685,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F9" t="s">
+        <v>225</v>
+      </c>
+      <c r="G9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I9" t="s">
+        <v>239</v>
+      </c>
+      <c r="J9" t="s">
+        <v>219</v>
+      </c>
+      <c r="K9" t="s">
+        <v>220</v>
+      </c>
+      <c r="L9" t="s">
+        <v>221</v>
+      </c>
+      <c r="M9" t="s">
+        <v>215</v>
+      </c>
+      <c r="N9" t="s">
         <v>222</v>
       </c>
-      <c r="G9" t="s">
-        <v>183</v>
-      </c>
-      <c r="H9" t="s">
-        <v>214</v>
-      </c>
-      <c r="I9" t="s">
-        <v>236</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="O9" t="s">
+        <v>223</v>
+      </c>
+      <c r="P9" t="s">
         <v>216</v>
       </c>
-      <c r="K9" t="s">
-        <v>217</v>
-      </c>
-      <c r="L9" t="s">
-        <v>218</v>
-      </c>
-      <c r="M9" t="s">
-        <v>212</v>
-      </c>
-      <c r="N9" t="s">
-        <v>219</v>
-      </c>
-      <c r="O9" t="s">
-        <v>220</v>
-      </c>
-      <c r="P9" t="s">
-        <v>213</v>
-      </c>
       <c r="Q9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T9" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -6691,58 +6744,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D10" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F10" t="s">
+        <v>216</v>
+      </c>
+      <c r="G10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H10" t="s">
+        <v>217</v>
+      </c>
+      <c r="I10" t="s">
+        <v>242</v>
+      </c>
+      <c r="J10" t="s">
         <v>219</v>
       </c>
-      <c r="F10" t="s">
-        <v>213</v>
-      </c>
-      <c r="G10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" t="s">
-        <v>214</v>
-      </c>
-      <c r="I10" t="s">
-        <v>239</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
+        <v>220</v>
+      </c>
+      <c r="L10" t="s">
+        <v>221</v>
+      </c>
+      <c r="M10" t="s">
+        <v>215</v>
+      </c>
+      <c r="N10" t="s">
+        <v>222</v>
+      </c>
+      <c r="O10" t="s">
+        <v>223</v>
+      </c>
+      <c r="P10" t="s">
         <v>216</v>
       </c>
-      <c r="K10" t="s">
-        <v>217</v>
-      </c>
-      <c r="L10" t="s">
-        <v>218</v>
-      </c>
-      <c r="M10" t="s">
-        <v>212</v>
-      </c>
-      <c r="N10" t="s">
-        <v>219</v>
-      </c>
-      <c r="O10" t="s">
-        <v>220</v>
-      </c>
-      <c r="P10" t="s">
-        <v>213</v>
-      </c>
       <c r="Q10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T10" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -6750,58 +6803,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F11" t="s">
+        <v>227</v>
+      </c>
+      <c r="G11" t="s">
+        <v>186</v>
+      </c>
+      <c r="H11" t="s">
+        <v>230</v>
+      </c>
+      <c r="I11" t="s">
+        <v>239</v>
+      </c>
+      <c r="J11" t="s">
+        <v>219</v>
+      </c>
+      <c r="K11" t="s">
+        <v>220</v>
+      </c>
+      <c r="L11" t="s">
+        <v>221</v>
+      </c>
+      <c r="M11" t="s">
+        <v>215</v>
+      </c>
+      <c r="N11" t="s">
+        <v>222</v>
+      </c>
+      <c r="O11" t="s">
+        <v>223</v>
+      </c>
+      <c r="P11" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q11" t="s">
         <v>224</v>
       </c>
-      <c r="G11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="R11" t="s">
+        <v>225</v>
+      </c>
+      <c r="S11" t="s">
+        <v>226</v>
+      </c>
+      <c r="T11" t="s">
         <v>227</v>
-      </c>
-      <c r="I11" t="s">
-        <v>236</v>
-      </c>
-      <c r="J11" t="s">
-        <v>216</v>
-      </c>
-      <c r="K11" t="s">
-        <v>217</v>
-      </c>
-      <c r="L11" t="s">
-        <v>218</v>
-      </c>
-      <c r="M11" t="s">
-        <v>212</v>
-      </c>
-      <c r="N11" t="s">
-        <v>219</v>
-      </c>
-      <c r="O11" t="s">
-        <v>220</v>
-      </c>
-      <c r="P11" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>221</v>
-      </c>
-      <c r="R11" t="s">
-        <v>222</v>
-      </c>
-      <c r="S11" t="s">
-        <v>223</v>
-      </c>
-      <c r="T11" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -6809,58 +6862,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" t="s">
+        <v>246</v>
+      </c>
+      <c r="E12" t="s">
+        <v>215</v>
+      </c>
+      <c r="F12" t="s">
+        <v>216</v>
+      </c>
+      <c r="G12" t="s">
+        <v>186</v>
+      </c>
+      <c r="H12" t="s">
+        <v>230</v>
+      </c>
+      <c r="I12" t="s">
         <v>242</v>
       </c>
-      <c r="D12" t="s">
-        <v>243</v>
-      </c>
-      <c r="E12" t="s">
-        <v>212</v>
-      </c>
-      <c r="F12" t="s">
-        <v>213</v>
-      </c>
-      <c r="G12" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
+        <v>219</v>
+      </c>
+      <c r="K12" t="s">
+        <v>220</v>
+      </c>
+      <c r="L12" t="s">
+        <v>221</v>
+      </c>
+      <c r="M12" t="s">
+        <v>215</v>
+      </c>
+      <c r="N12" t="s">
+        <v>222</v>
+      </c>
+      <c r="O12" t="s">
+        <v>223</v>
+      </c>
+      <c r="P12" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>224</v>
+      </c>
+      <c r="R12" t="s">
+        <v>225</v>
+      </c>
+      <c r="S12" t="s">
+        <v>226</v>
+      </c>
+      <c r="T12" t="s">
         <v>227</v>
-      </c>
-      <c r="I12" t="s">
-        <v>239</v>
-      </c>
-      <c r="J12" t="s">
-        <v>216</v>
-      </c>
-      <c r="K12" t="s">
-        <v>217</v>
-      </c>
-      <c r="L12" t="s">
-        <v>218</v>
-      </c>
-      <c r="M12" t="s">
-        <v>212</v>
-      </c>
-      <c r="N12" t="s">
-        <v>219</v>
-      </c>
-      <c r="O12" t="s">
-        <v>220</v>
-      </c>
-      <c r="P12" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>221</v>
-      </c>
-      <c r="R12" t="s">
-        <v>222</v>
-      </c>
-      <c r="S12" t="s">
-        <v>223</v>
-      </c>
-      <c r="T12" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -6868,58 +6921,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F13" t="s">
+        <v>227</v>
+      </c>
+      <c r="G13" t="s">
+        <v>186</v>
+      </c>
+      <c r="H13" t="s">
+        <v>233</v>
+      </c>
+      <c r="I13" t="s">
+        <v>239</v>
+      </c>
+      <c r="J13" t="s">
+        <v>219</v>
+      </c>
+      <c r="K13" t="s">
+        <v>220</v>
+      </c>
+      <c r="L13" t="s">
+        <v>221</v>
+      </c>
+      <c r="M13" t="s">
+        <v>215</v>
+      </c>
+      <c r="N13" t="s">
+        <v>222</v>
+      </c>
+      <c r="O13" t="s">
+        <v>223</v>
+      </c>
+      <c r="P13" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q13" t="s">
         <v>224</v>
       </c>
-      <c r="G13" t="s">
-        <v>183</v>
-      </c>
-      <c r="H13" t="s">
-        <v>230</v>
-      </c>
-      <c r="I13" t="s">
-        <v>236</v>
-      </c>
-      <c r="J13" t="s">
-        <v>216</v>
-      </c>
-      <c r="K13" t="s">
-        <v>217</v>
-      </c>
-      <c r="L13" t="s">
-        <v>218</v>
-      </c>
-      <c r="M13" t="s">
-        <v>212</v>
-      </c>
-      <c r="N13" t="s">
-        <v>219</v>
-      </c>
-      <c r="O13" t="s">
-        <v>220</v>
-      </c>
-      <c r="P13" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>221</v>
-      </c>
       <c r="R13" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T13" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -6927,58 +6980,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G14" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H14" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I14" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J14" t="s">
+        <v>219</v>
+      </c>
+      <c r="K14" t="s">
+        <v>220</v>
+      </c>
+      <c r="L14" t="s">
+        <v>221</v>
+      </c>
+      <c r="M14" t="s">
+        <v>215</v>
+      </c>
+      <c r="N14" t="s">
+        <v>222</v>
+      </c>
+      <c r="O14" t="s">
+        <v>223</v>
+      </c>
+      <c r="P14" t="s">
         <v>216</v>
       </c>
-      <c r="K14" t="s">
-        <v>217</v>
-      </c>
-      <c r="L14" t="s">
-        <v>218</v>
-      </c>
-      <c r="M14" t="s">
-        <v>212</v>
-      </c>
-      <c r="N14" t="s">
-        <v>219</v>
-      </c>
-      <c r="O14" t="s">
-        <v>220</v>
-      </c>
-      <c r="P14" t="s">
-        <v>213</v>
-      </c>
       <c r="Q14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R14" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T14" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -6986,58 +7039,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D15" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E15" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F15" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I15" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J15" t="s">
+        <v>219</v>
+      </c>
+      <c r="K15" t="s">
+        <v>220</v>
+      </c>
+      <c r="L15" t="s">
+        <v>221</v>
+      </c>
+      <c r="M15" t="s">
+        <v>215</v>
+      </c>
+      <c r="N15" t="s">
+        <v>222</v>
+      </c>
+      <c r="O15" t="s">
+        <v>223</v>
+      </c>
+      <c r="P15" t="s">
         <v>216</v>
       </c>
-      <c r="K15" t="s">
-        <v>217</v>
-      </c>
-      <c r="L15" t="s">
-        <v>218</v>
-      </c>
-      <c r="M15" t="s">
-        <v>212</v>
-      </c>
-      <c r="N15" t="s">
-        <v>219</v>
-      </c>
-      <c r="O15" t="s">
-        <v>220</v>
-      </c>
-      <c r="P15" t="s">
-        <v>213</v>
-      </c>
       <c r="Q15" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R15" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S15" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T15" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -7045,58 +7098,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D16" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F16" t="s">
+        <v>226</v>
+      </c>
+      <c r="G16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H16" t="s">
+        <v>236</v>
+      </c>
+      <c r="I16" t="s">
+        <v>242</v>
+      </c>
+      <c r="J16" t="s">
+        <v>219</v>
+      </c>
+      <c r="K16" t="s">
+        <v>220</v>
+      </c>
+      <c r="L16" t="s">
+        <v>221</v>
+      </c>
+      <c r="M16" t="s">
+        <v>215</v>
+      </c>
+      <c r="N16" t="s">
+        <v>222</v>
+      </c>
+      <c r="O16" t="s">
         <v>223</v>
       </c>
-      <c r="G16" t="s">
-        <v>183</v>
-      </c>
-      <c r="H16" t="s">
-        <v>233</v>
-      </c>
-      <c r="I16" t="s">
-        <v>239</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="P16" t="s">
         <v>216</v>
       </c>
-      <c r="K16" t="s">
-        <v>217</v>
-      </c>
-      <c r="L16" t="s">
-        <v>218</v>
-      </c>
-      <c r="M16" t="s">
-        <v>212</v>
-      </c>
-      <c r="N16" t="s">
-        <v>219</v>
-      </c>
-      <c r="O16" t="s">
-        <v>220</v>
-      </c>
-      <c r="P16" t="s">
-        <v>213</v>
-      </c>
       <c r="Q16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R16" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S16" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="T16" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -7125,16 +7178,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7148,7 +7201,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7173,16 +7226,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7196,10 +7249,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7207,16 +7260,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7230,10 +7283,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F7" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7247,10 +7300,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7264,10 +7317,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7275,16 +7328,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E10" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F10" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7298,10 +7351,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7315,10 +7368,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -7351,34 +7404,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="N1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7389,10 +7442,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7404,7 +7457,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7426,13 +7479,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7443,40 +7496,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="I4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="N4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7499,13 +7552,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7519,22 +7572,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7548,22 +7601,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H7" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M7" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7577,22 +7630,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M8" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7606,22 +7659,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L9" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7635,22 +7688,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L10" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7664,22 +7717,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M11" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7693,22 +7746,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H12" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L12" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M12" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7716,31 +7769,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G13" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L13" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M13" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N13" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -7748,10 +7801,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -7760,7 +7813,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -7768,10 +7821,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -7780,7 +7833,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7788,10 +7841,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -7800,7 +7853,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7808,19 +7861,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F17" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N17" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7828,10 +7881,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -7840,7 +7893,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7848,10 +7901,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -7860,7 +7913,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7868,10 +7921,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -7880,7 +7933,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7888,19 +7941,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E21" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F21" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N21" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -7908,16 +7961,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -7925,10 +7978,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -7942,10 +7995,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -7959,10 +8012,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -7976,10 +8029,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -7993,10 +8046,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -8010,10 +8063,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -8027,10 +8080,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -8039,10 +8092,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N29" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -8050,10 +8103,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -8067,10 +8120,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -8084,10 +8137,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -8096,10 +8149,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N32" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -8135,31 +8188,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="K1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8185,10 +8238,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -8202,34 +8255,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8240,31 +8293,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E4" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F4" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G4" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H4" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="I4" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J4" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="K4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8272,7 +8325,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8296,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8304,7 +8357,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8328,7 +8381,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8336,7 +8389,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8360,7 +8413,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8368,7 +8421,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -8392,7 +8445,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -8423,16 +8476,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8449,7 +8502,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -8462,10 +8515,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8476,13 +8529,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D4" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8490,7 +8543,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8499,7 +8552,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8507,7 +8560,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -8516,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8524,7 +8577,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -8533,7 +8586,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8541,7 +8594,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8550,7 +8603,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8588,40 +8641,40 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="G1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="H1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="J1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="K1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -8635,16 +8688,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -8670,40 +8723,40 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M3" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8711,54 +8764,54 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D4" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E4" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="H4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K4" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M4" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8770,36 +8823,36 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I5" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="J5" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="K5" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L5" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M5" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D6" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8811,36 +8864,36 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="I6" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J6" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="K6" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L6" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M6" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D7" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8852,36 +8905,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="I7" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="J7" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K7" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L7" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M7" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D8" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -8893,36 +8946,36 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="I8" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="J8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K8" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L8" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M8" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D9" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -8934,36 +8987,36 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="I9" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="J9" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K9" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L9" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M9" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D10" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8975,36 +9028,36 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="I10" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J10" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="K10" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L10" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M10" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D11" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -9016,36 +9069,36 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="I11" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="J11" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K11" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L11" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M11" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D12" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -9057,36 +9110,36 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="I12" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="J12" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K12" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L12" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M12" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D13" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -9098,36 +9151,36 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="I13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="J13" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K13" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M13" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D14" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -9139,36 +9192,36 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="I14" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="J14" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="K14" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="L14" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="M14" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D15" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -9180,39 +9233,39 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="I15" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="J15" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K15" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="L15" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M15" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D16" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E16" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -9221,39 +9274,39 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="I16" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J16" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="K16" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L16" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="M16" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D17" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E17" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -9262,39 +9315,39 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="I17" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="J17" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K17" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="L17" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="M17" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D18" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E18" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -9303,39 +9356,39 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="I18" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J18" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K18" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="L18" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="M18" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D19" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E19" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -9344,39 +9397,39 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="I19" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="J19" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="K19" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L19" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="M19" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D20" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E20" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -9385,39 +9438,39 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="I20" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="J20" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K20" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L20" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="M20" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D21" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E21" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -9426,39 +9479,39 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="I21" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="J21" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K21" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L21" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="M21" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D22" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E22" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -9467,39 +9520,39 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="I22" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="J22" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K22" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="L22" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="M22" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D23" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E23" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -9508,39 +9561,39 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="I23" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="J23" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="K23" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="L23" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="M23" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D24" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E24" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -9549,39 +9602,39 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="I24" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="J24" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K24" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="L24" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M24" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D25" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E25" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -9590,22 +9643,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="I25" t="s">
         <v>52</v>
       </c>
       <c r="J25" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="K25" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L25" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="M25" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -9613,10 +9666,10 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D26" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -9628,22 +9681,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="I26" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="J26" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="K26" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="L26" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M26" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -9651,13 +9704,13 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D27" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E27" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -9666,36 +9719,36 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="I27" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="J27" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="K27" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="L27" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="M27" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D28" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -9707,36 +9760,36 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="I28" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="J28" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="K28" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="L28" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="M28" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D29" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -9748,36 +9801,36 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="I29" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="J29" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="K29" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L29" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="M29" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D30" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E30" t="s">
         <v>2</v>
@@ -9789,39 +9842,39 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="I30" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="J30" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="K30" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L30" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="M30" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D31" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E31" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -9830,22 +9883,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="I31" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="J31" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="K31" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="L31" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="M31" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -9853,13 +9906,13 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D32" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E32" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -9868,22 +9921,22 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="I32" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="J32" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="K32" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L32" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="M32" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/xlsx/Main.xlsx
+++ b/luban-excels/xlsx/Main.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="868">
   <si>
     <t>Dog</t>
   </si>
@@ -570,6 +570,15 @@
   </si>
   <si>
     <t>仅供客户端使用。在本地展示前多久开始调用 TriggerItemDrop。</t>
+  </si>
+  <si>
+    <t>BlindBoxLoopSteamVoucherInventoryLimit</t>
+  </si>
+  <si>
+    <t>循环Steam盲盒券库存上限</t>
+  </si>
+  <si>
+    <t>正常循环阶段允许玩家在 Steam 库存中累计的盲盒成本券数量上限。客户端统计对应 ItemDef 的所有实例及堆叠数量；达到上限时暂停调用循环 PlaytimeGenerator，消耗后低于上限时恢复请求。填 0 表示不限制。</t>
   </si>
   <si>
     <t>IconName</t>
@@ -3258,7 +3267,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3282,9 +3291,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4222,28 +4228,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C1" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="D1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="E1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="F1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="G1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="H1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="I1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4260,16 +4266,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="F2" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -4280,28 +4286,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4309,1333 +4315,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C4" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E4" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F4" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G4" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="H4" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="I4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D5" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F5" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G5" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>688</v>
+      </c>
+      <c r="D6" t="s">
+        <v>689</v>
+      </c>
+      <c r="E6" t="s">
+        <v>690</v>
+      </c>
+      <c r="F6" t="s">
         <v>685</v>
       </c>
-      <c r="D6" t="s">
-        <v>686</v>
-      </c>
-      <c r="E6" t="s">
-        <v>687</v>
-      </c>
-      <c r="F6" t="s">
-        <v>682</v>
-      </c>
       <c r="G6" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="D7" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E7" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F7" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G7" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D8" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E8" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F8" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G8" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="D9" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="E9" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F9" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G9" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D10" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="E10" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F10" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G10" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D11" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E11" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F11" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G11" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D12" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="E12" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F12" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G12" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="D13" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E13" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F13" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G13" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="D14" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E14" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F14" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G14" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D15" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="E15" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F15" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G15" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D16" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="E16" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F16" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G16" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="D17" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="E17" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F17" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G17" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D18" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E18" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F18" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G18" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D19" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E19" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F19" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G19" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D20" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="E20" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F20" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G20" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D21" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="E21" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F21" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G21" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D22" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="E22" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F22" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G22" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D23" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E23" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F23" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G23" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D24" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="E24" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F24" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G24" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D25" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="E25" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F25" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G25" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="D26" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="E26" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F26" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G26" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="D27" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="E27" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F27" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G27" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="D28" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="E28" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F28" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G28" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D29" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="E29" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F29" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G29" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="D30" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="E30" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F30" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G30" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="D31" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="E31" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F31" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G31" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D32" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="E32" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F32" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G32" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="D33" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="E33" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F33" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G33" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="D34" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="E34" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F34" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G34" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="D35" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="E35" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F35" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G35" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D36" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="E36" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F36" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G36" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="D37" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="E37" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F37" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G37" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="D38" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="E38" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F38" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G38" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="D39" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="E39" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F39" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G39" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="D40" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="E40" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F40" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G40" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D41" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="E41" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F41" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G41" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D42" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="E42" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F42" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G42" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D43" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="E43" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F43" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G43" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D44" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="E44" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F44" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G44" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="D45" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E45" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F45" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G45" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D46" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="E46" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F46" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G46" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="D47" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E47" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F47" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G47" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="D48" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="E48" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F48" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G48" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="D49" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="E49" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F49" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G49" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5643,25 +5649,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="D50" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="E50" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F50" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G50" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5669,25 +5675,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="D51" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="E51" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F51" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="G51" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
   </sheetData>
@@ -6194,11 +6200,21 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="2">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="17" spans="5:8">
       <c r="E17" s="7"/>
@@ -6207,16 +6223,16 @@
       <c r="H17" s="7"/>
     </row>
     <row r="18" spans="5:8">
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="9"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="8"/>
     </row>
     <row r="19" spans="5:8">
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="9"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6257,55 +6273,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="O1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="P1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="R1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="S1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="T1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6376,10 +6392,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6393,55 +6409,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="L4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="M4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="N4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="P4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="R4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="S4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="T4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6449,58 +6465,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I5" t="s">
+        <v>221</v>
+      </c>
+      <c r="J5" t="s">
+        <v>222</v>
+      </c>
+      <c r="K5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L5" t="s">
+        <v>224</v>
+      </c>
+      <c r="M5" t="s">
         <v>218</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
+        <v>225</v>
+      </c>
+      <c r="O5" t="s">
+        <v>226</v>
+      </c>
+      <c r="P5" t="s">
         <v>219</v>
       </c>
-      <c r="K5" t="s">
-        <v>220</v>
-      </c>
-      <c r="L5" t="s">
-        <v>221</v>
-      </c>
-      <c r="M5" t="s">
-        <v>215</v>
-      </c>
-      <c r="N5" t="s">
-        <v>222</v>
-      </c>
-      <c r="O5" t="s">
-        <v>223</v>
-      </c>
-      <c r="P5" t="s">
-        <v>216</v>
-      </c>
       <c r="Q5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="T5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -6508,58 +6524,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H6" t="s">
+        <v>233</v>
+      </c>
+      <c r="I6" t="s">
+        <v>221</v>
+      </c>
+      <c r="J6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K6" t="s">
+        <v>223</v>
+      </c>
+      <c r="L6" t="s">
+        <v>224</v>
+      </c>
+      <c r="M6" t="s">
+        <v>218</v>
+      </c>
+      <c r="N6" t="s">
+        <v>225</v>
+      </c>
+      <c r="O6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P6" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>227</v>
+      </c>
+      <c r="R6" t="s">
         <v>228</v>
       </c>
-      <c r="D6" t="s">
+      <c r="S6" t="s">
         <v>229</v>
       </c>
-      <c r="E6" t="s">
-        <v>215</v>
-      </c>
-      <c r="F6" t="s">
-        <v>224</v>
-      </c>
-      <c r="G6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="T6" t="s">
         <v>230</v>
-      </c>
-      <c r="I6" t="s">
-        <v>218</v>
-      </c>
-      <c r="J6" t="s">
-        <v>219</v>
-      </c>
-      <c r="K6" t="s">
-        <v>220</v>
-      </c>
-      <c r="L6" t="s">
-        <v>221</v>
-      </c>
-      <c r="M6" t="s">
-        <v>215</v>
-      </c>
-      <c r="N6" t="s">
-        <v>222</v>
-      </c>
-      <c r="O6" t="s">
-        <v>223</v>
-      </c>
-      <c r="P6" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>224</v>
-      </c>
-      <c r="R6" t="s">
-        <v>225</v>
-      </c>
-      <c r="S6" t="s">
-        <v>226</v>
-      </c>
-      <c r="T6" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -6567,58 +6583,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D7" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G7" t="s">
+        <v>189</v>
+      </c>
+      <c r="H7" t="s">
+        <v>236</v>
+      </c>
+      <c r="I7" t="s">
+        <v>221</v>
+      </c>
+      <c r="J7" t="s">
+        <v>222</v>
+      </c>
+      <c r="K7" t="s">
+        <v>223</v>
+      </c>
+      <c r="L7" t="s">
+        <v>224</v>
+      </c>
+      <c r="M7" t="s">
+        <v>218</v>
+      </c>
+      <c r="N7" t="s">
         <v>225</v>
       </c>
-      <c r="G7" t="s">
-        <v>186</v>
-      </c>
-      <c r="H7" t="s">
-        <v>233</v>
-      </c>
-      <c r="I7" t="s">
-        <v>218</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="O7" t="s">
+        <v>226</v>
+      </c>
+      <c r="P7" t="s">
         <v>219</v>
       </c>
-      <c r="K7" t="s">
-        <v>220</v>
-      </c>
-      <c r="L7" t="s">
-        <v>221</v>
-      </c>
-      <c r="M7" t="s">
-        <v>215</v>
-      </c>
-      <c r="N7" t="s">
-        <v>222</v>
-      </c>
-      <c r="O7" t="s">
-        <v>223</v>
-      </c>
-      <c r="P7" t="s">
-        <v>216</v>
-      </c>
       <c r="Q7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="T7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -6626,58 +6642,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D8" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F8" t="s">
+        <v>226</v>
+      </c>
+      <c r="G8" t="s">
+        <v>189</v>
+      </c>
+      <c r="H8" t="s">
+        <v>239</v>
+      </c>
+      <c r="I8" t="s">
+        <v>221</v>
+      </c>
+      <c r="J8" t="s">
         <v>222</v>
       </c>
-      <c r="F8" t="s">
+      <c r="K8" t="s">
         <v>223</v>
       </c>
-      <c r="G8" t="s">
-        <v>186</v>
-      </c>
-      <c r="H8" t="s">
-        <v>236</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
+        <v>224</v>
+      </c>
+      <c r="M8" t="s">
         <v>218</v>
       </c>
-      <c r="J8" t="s">
+      <c r="N8" t="s">
+        <v>225</v>
+      </c>
+      <c r="O8" t="s">
+        <v>226</v>
+      </c>
+      <c r="P8" t="s">
         <v>219</v>
       </c>
-      <c r="K8" t="s">
-        <v>220</v>
-      </c>
-      <c r="L8" t="s">
-        <v>221</v>
-      </c>
-      <c r="M8" t="s">
-        <v>215</v>
-      </c>
-      <c r="N8" t="s">
-        <v>222</v>
-      </c>
-      <c r="O8" t="s">
-        <v>223</v>
-      </c>
-      <c r="P8" t="s">
-        <v>216</v>
-      </c>
       <c r="Q8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R8" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="T8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6685,58 +6701,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F9" t="s">
+        <v>228</v>
+      </c>
+      <c r="G9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H9" t="s">
+        <v>220</v>
+      </c>
+      <c r="I9" t="s">
+        <v>242</v>
+      </c>
+      <c r="J9" t="s">
+        <v>222</v>
+      </c>
+      <c r="K9" t="s">
+        <v>223</v>
+      </c>
+      <c r="L9" t="s">
+        <v>224</v>
+      </c>
+      <c r="M9" t="s">
+        <v>218</v>
+      </c>
+      <c r="N9" t="s">
         <v>225</v>
       </c>
-      <c r="G9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I9" t="s">
-        <v>239</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="O9" t="s">
+        <v>226</v>
+      </c>
+      <c r="P9" t="s">
         <v>219</v>
       </c>
-      <c r="K9" t="s">
-        <v>220</v>
-      </c>
-      <c r="L9" t="s">
-        <v>221</v>
-      </c>
-      <c r="M9" t="s">
-        <v>215</v>
-      </c>
-      <c r="N9" t="s">
-        <v>222</v>
-      </c>
-      <c r="O9" t="s">
-        <v>223</v>
-      </c>
-      <c r="P9" t="s">
-        <v>216</v>
-      </c>
       <c r="Q9" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R9" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S9" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="T9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -6744,58 +6760,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10" t="s">
+        <v>219</v>
+      </c>
+      <c r="G10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H10" t="s">
+        <v>220</v>
+      </c>
+      <c r="I10" t="s">
+        <v>245</v>
+      </c>
+      <c r="J10" t="s">
         <v>222</v>
       </c>
-      <c r="F10" t="s">
-        <v>216</v>
-      </c>
-      <c r="G10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H10" t="s">
-        <v>217</v>
-      </c>
-      <c r="I10" t="s">
-        <v>242</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
+        <v>223</v>
+      </c>
+      <c r="L10" t="s">
+        <v>224</v>
+      </c>
+      <c r="M10" t="s">
+        <v>218</v>
+      </c>
+      <c r="N10" t="s">
+        <v>225</v>
+      </c>
+      <c r="O10" t="s">
+        <v>226</v>
+      </c>
+      <c r="P10" t="s">
         <v>219</v>
       </c>
-      <c r="K10" t="s">
-        <v>220</v>
-      </c>
-      <c r="L10" t="s">
-        <v>221</v>
-      </c>
-      <c r="M10" t="s">
-        <v>215</v>
-      </c>
-      <c r="N10" t="s">
-        <v>222</v>
-      </c>
-      <c r="O10" t="s">
-        <v>223</v>
-      </c>
-      <c r="P10" t="s">
-        <v>216</v>
-      </c>
       <c r="Q10" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R10" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="T10" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -6803,58 +6819,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E11" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G11" t="s">
+        <v>189</v>
+      </c>
+      <c r="H11" t="s">
+        <v>233</v>
+      </c>
+      <c r="I11" t="s">
+        <v>242</v>
+      </c>
+      <c r="J11" t="s">
+        <v>222</v>
+      </c>
+      <c r="K11" t="s">
+        <v>223</v>
+      </c>
+      <c r="L11" t="s">
+        <v>224</v>
+      </c>
+      <c r="M11" t="s">
+        <v>218</v>
+      </c>
+      <c r="N11" t="s">
+        <v>225</v>
+      </c>
+      <c r="O11" t="s">
+        <v>226</v>
+      </c>
+      <c r="P11" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q11" t="s">
         <v>227</v>
       </c>
-      <c r="G11" t="s">
-        <v>186</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="R11" t="s">
+        <v>228</v>
+      </c>
+      <c r="S11" t="s">
+        <v>229</v>
+      </c>
+      <c r="T11" t="s">
         <v>230</v>
-      </c>
-      <c r="I11" t="s">
-        <v>239</v>
-      </c>
-      <c r="J11" t="s">
-        <v>219</v>
-      </c>
-      <c r="K11" t="s">
-        <v>220</v>
-      </c>
-      <c r="L11" t="s">
-        <v>221</v>
-      </c>
-      <c r="M11" t="s">
-        <v>215</v>
-      </c>
-      <c r="N11" t="s">
-        <v>222</v>
-      </c>
-      <c r="O11" t="s">
-        <v>223</v>
-      </c>
-      <c r="P11" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>224</v>
-      </c>
-      <c r="R11" t="s">
-        <v>225</v>
-      </c>
-      <c r="S11" t="s">
-        <v>226</v>
-      </c>
-      <c r="T11" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -6862,58 +6878,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D12" t="s">
+        <v>249</v>
+      </c>
+      <c r="E12" t="s">
+        <v>218</v>
+      </c>
+      <c r="F12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G12" t="s">
+        <v>189</v>
+      </c>
+      <c r="H12" t="s">
+        <v>233</v>
+      </c>
+      <c r="I12" t="s">
         <v>245</v>
       </c>
-      <c r="D12" t="s">
-        <v>246</v>
-      </c>
-      <c r="E12" t="s">
-        <v>215</v>
-      </c>
-      <c r="F12" t="s">
-        <v>216</v>
-      </c>
-      <c r="G12" t="s">
-        <v>186</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
+        <v>222</v>
+      </c>
+      <c r="K12" t="s">
+        <v>223</v>
+      </c>
+      <c r="L12" t="s">
+        <v>224</v>
+      </c>
+      <c r="M12" t="s">
+        <v>218</v>
+      </c>
+      <c r="N12" t="s">
+        <v>225</v>
+      </c>
+      <c r="O12" t="s">
+        <v>226</v>
+      </c>
+      <c r="P12" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>227</v>
+      </c>
+      <c r="R12" t="s">
+        <v>228</v>
+      </c>
+      <c r="S12" t="s">
+        <v>229</v>
+      </c>
+      <c r="T12" t="s">
         <v>230</v>
-      </c>
-      <c r="I12" t="s">
-        <v>242</v>
-      </c>
-      <c r="J12" t="s">
-        <v>219</v>
-      </c>
-      <c r="K12" t="s">
-        <v>220</v>
-      </c>
-      <c r="L12" t="s">
-        <v>221</v>
-      </c>
-      <c r="M12" t="s">
-        <v>215</v>
-      </c>
-      <c r="N12" t="s">
-        <v>222</v>
-      </c>
-      <c r="O12" t="s">
-        <v>223</v>
-      </c>
-      <c r="P12" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>224</v>
-      </c>
-      <c r="R12" t="s">
-        <v>225</v>
-      </c>
-      <c r="S12" t="s">
-        <v>226</v>
-      </c>
-      <c r="T12" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -6921,58 +6937,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E13" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F13" t="s">
+        <v>230</v>
+      </c>
+      <c r="G13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H13" t="s">
+        <v>236</v>
+      </c>
+      <c r="I13" t="s">
+        <v>242</v>
+      </c>
+      <c r="J13" t="s">
+        <v>222</v>
+      </c>
+      <c r="K13" t="s">
+        <v>223</v>
+      </c>
+      <c r="L13" t="s">
+        <v>224</v>
+      </c>
+      <c r="M13" t="s">
+        <v>218</v>
+      </c>
+      <c r="N13" t="s">
+        <v>225</v>
+      </c>
+      <c r="O13" t="s">
+        <v>226</v>
+      </c>
+      <c r="P13" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q13" t="s">
         <v>227</v>
       </c>
-      <c r="G13" t="s">
-        <v>186</v>
-      </c>
-      <c r="H13" t="s">
-        <v>233</v>
-      </c>
-      <c r="I13" t="s">
-        <v>239</v>
-      </c>
-      <c r="J13" t="s">
-        <v>219</v>
-      </c>
-      <c r="K13" t="s">
-        <v>220</v>
-      </c>
-      <c r="L13" t="s">
-        <v>221</v>
-      </c>
-      <c r="M13" t="s">
-        <v>215</v>
-      </c>
-      <c r="N13" t="s">
-        <v>222</v>
-      </c>
-      <c r="O13" t="s">
-        <v>223</v>
-      </c>
-      <c r="P13" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>224</v>
-      </c>
       <c r="R13" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S13" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="T13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -6980,58 +6996,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D14" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F14" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G14" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H14" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J14" t="s">
+        <v>222</v>
+      </c>
+      <c r="K14" t="s">
+        <v>223</v>
+      </c>
+      <c r="L14" t="s">
+        <v>224</v>
+      </c>
+      <c r="M14" t="s">
+        <v>218</v>
+      </c>
+      <c r="N14" t="s">
+        <v>225</v>
+      </c>
+      <c r="O14" t="s">
+        <v>226</v>
+      </c>
+      <c r="P14" t="s">
         <v>219</v>
       </c>
-      <c r="K14" t="s">
-        <v>220</v>
-      </c>
-      <c r="L14" t="s">
-        <v>221</v>
-      </c>
-      <c r="M14" t="s">
-        <v>215</v>
-      </c>
-      <c r="N14" t="s">
-        <v>222</v>
-      </c>
-      <c r="O14" t="s">
-        <v>223</v>
-      </c>
-      <c r="P14" t="s">
-        <v>216</v>
-      </c>
       <c r="Q14" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R14" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S14" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="T14" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -7039,58 +7055,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D15" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F15" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G15" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H15" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I15" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J15" t="s">
+        <v>222</v>
+      </c>
+      <c r="K15" t="s">
+        <v>223</v>
+      </c>
+      <c r="L15" t="s">
+        <v>224</v>
+      </c>
+      <c r="M15" t="s">
+        <v>218</v>
+      </c>
+      <c r="N15" t="s">
+        <v>225</v>
+      </c>
+      <c r="O15" t="s">
+        <v>226</v>
+      </c>
+      <c r="P15" t="s">
         <v>219</v>
       </c>
-      <c r="K15" t="s">
-        <v>220</v>
-      </c>
-      <c r="L15" t="s">
-        <v>221</v>
-      </c>
-      <c r="M15" t="s">
-        <v>215</v>
-      </c>
-      <c r="N15" t="s">
-        <v>222</v>
-      </c>
-      <c r="O15" t="s">
-        <v>223</v>
-      </c>
-      <c r="P15" t="s">
-        <v>216</v>
-      </c>
       <c r="Q15" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R15" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S15" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="T15" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -7098,58 +7114,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D16" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E16" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F16" t="s">
+        <v>229</v>
+      </c>
+      <c r="G16" t="s">
+        <v>189</v>
+      </c>
+      <c r="H16" t="s">
+        <v>239</v>
+      </c>
+      <c r="I16" t="s">
+        <v>245</v>
+      </c>
+      <c r="J16" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" t="s">
+        <v>223</v>
+      </c>
+      <c r="L16" t="s">
+        <v>224</v>
+      </c>
+      <c r="M16" t="s">
+        <v>218</v>
+      </c>
+      <c r="N16" t="s">
+        <v>225</v>
+      </c>
+      <c r="O16" t="s">
         <v>226</v>
       </c>
-      <c r="G16" t="s">
-        <v>186</v>
-      </c>
-      <c r="H16" t="s">
-        <v>236</v>
-      </c>
-      <c r="I16" t="s">
-        <v>242</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="P16" t="s">
         <v>219</v>
       </c>
-      <c r="K16" t="s">
-        <v>220</v>
-      </c>
-      <c r="L16" t="s">
-        <v>221</v>
-      </c>
-      <c r="M16" t="s">
-        <v>215</v>
-      </c>
-      <c r="N16" t="s">
-        <v>222</v>
-      </c>
-      <c r="O16" t="s">
-        <v>223</v>
-      </c>
-      <c r="P16" t="s">
-        <v>216</v>
-      </c>
       <c r="Q16" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R16" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S16" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="T16" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -7178,16 +7194,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7201,7 +7217,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7226,16 +7242,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7249,10 +7265,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7260,16 +7276,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7283,10 +7299,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7300,10 +7316,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7317,10 +7333,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F9" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7328,16 +7344,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D10" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7351,10 +7367,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F11" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7368,10 +7384,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F12" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -7404,34 +7420,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="I1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="J1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="M1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7442,10 +7458,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7457,7 +7473,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7479,13 +7495,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7496,40 +7512,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="I4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="J4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="K4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="M4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7552,13 +7568,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7572,22 +7588,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7601,22 +7617,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M7" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7630,22 +7646,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L8" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M8" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7659,22 +7675,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L9" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M9" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7688,22 +7704,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L10" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M10" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7717,22 +7733,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M11" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7746,22 +7762,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L12" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M12" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7769,31 +7785,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L13" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M13" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="N13" t="s">
-        <v>315</v>
+        <v>318</v>
    